--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -30,497 +30,12 @@
 </workbook>
 </file>
 
-<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="160">
-  <si>
-    <t>#</t>
-  </si>
-  <si>
-    <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-  </si>
-  <si>
-    <t>1.  WITHDRAWAL HEADER / CHANGE CONTEXT</t>
-  </si>
-  <si>
-    <t>2.  WITHDRAWAL DECISION / CONTAINMENT CONTROL</t>
-  </si>
-  <si>
-    <t>2.  WORKING TABLE / DETAIL LINES</t>
-  </si>
-  <si>
-    <t>3.  POINT-OF-USE SWEEP / WITHDRAWAL CHECK</t>
-  </si>
-  <si>
-    <t>4.  OPEN WITHDRAWAL GAPS / CONTAINMENT ACTIONS</t>
-  </si>
-  <si>
-    <t>5.  APPROVAL / SWEEP CLOSE-OUT</t>
-  </si>
-  <si>
-    <t>=IF(COUNTA(AR22:AR31)=0,"",IF(COUNTIF(AR22:AR31,"FAIL")+COUNTIF(AR22:AR31,"HOLD")&gt;0,"HOLD",IF(COUNTIF(AR22:AR31,"PASS")=COUNTA(AR22:AR31),"APPROVED","CONDITIONAL")))</t>
-  </si>
-  <si>
-    <t>=IF(COUNTA(AR22:AR31)=0,"",IF(COUNTIF(AR22:AR31,"FAIL")+COUNTIF(AR22:AR31,"HOLD")&gt;0,"OPEN","CLOSED"))</t>
-  </si>
-  <si>
-    <t>=ROW()-ROW($A$17)+1</t>
-  </si>
-  <si>
-    <t>APPROVED</t>
-  </si>
-  <si>
-    <t>Acceptance / Control Rule</t>
-  </si>
-  <si>
-    <t>Acknowledgement evidence is retained.</t>
-  </si>
-  <si>
-    <t>Action Owner</t>
-  </si>
-  <si>
-    <t>Affected Package / Snapshot</t>
-  </si>
-  <si>
-    <t>Affected part / rev / job / operation scope is complete.</t>
-  </si>
-  <si>
-    <t>Approved</t>
-  </si>
-  <si>
-    <t>Approved by</t>
-  </si>
-  <si>
-    <t>Audit trail can reconstruct who withdrew what, where and when.</t>
-  </si>
-  <si>
-    <t>Authority, timing and closure meet the supersedure rule.</t>
-  </si>
-  <si>
-    <t>BASELINE_INDEX</t>
-  </si>
-  <si>
-    <t>CAP</t>
-  </si>
-  <si>
-    <t>CLOSED</t>
-  </si>
-  <si>
-    <t>CON</t>
-  </si>
-  <si>
-    <t>CONDITIONAL</t>
-  </si>
-  <si>
-    <t>Cat.</t>
-  </si>
-  <si>
-    <t>Closure Rule</t>
-  </si>
-  <si>
-    <t>Confirmation log for machine, CMM, warehouse, shipping and kiosk withdrawal.</t>
-  </si>
-  <si>
-    <t>Controlled Status</t>
-  </si>
-  <si>
-    <t>Controlled list of affected baseline/snapshot packages and supersedure scope.</t>
-  </si>
-  <si>
-    <t>DOC</t>
-  </si>
-  <si>
-    <t>Data Structure</t>
-  </si>
-  <si>
-    <t>Date / Time</t>
-  </si>
-  <si>
-    <t>Digital links, kiosks or read-only release paths for the old package are blocked or marked superseded.</t>
-  </si>
-  <si>
-    <t>Do not delete historical lines once a point-of-use confirmation has been recorded.</t>
-  </si>
-  <si>
-    <t>Do not delete historical lines once issue or withdrawal has been recorded.</t>
-  </si>
-  <si>
-    <t>Document / Record</t>
-  </si>
-  <si>
-    <t>Due Date</t>
-  </si>
-  <si>
-    <t>Eff. Date</t>
-  </si>
-  <si>
-    <t>Effective From / Freeze Time</t>
-  </si>
-  <si>
-    <t>Emergency or temporary controlled-copy use is recorded and time-limited.</t>
-  </si>
-  <si>
-    <t>Emergency use has scope, owner and expiry.</t>
-  </si>
-  <si>
-    <t>Engineering / QA / Planning</t>
-  </si>
-  <si>
-    <t>Engineering Lead</t>
-  </si>
-  <si>
-    <t>Engineering Manager</t>
-  </si>
-  <si>
-    <t>Escalation if Blocked</t>
-  </si>
-  <si>
-    <t>Every recipient / owner is named.</t>
-  </si>
-  <si>
-    <t>Evidence Folder / SSOT Path</t>
-  </si>
-  <si>
-    <t>Evidence Ref</t>
-  </si>
-  <si>
-    <t>FAIL</t>
-  </si>
-  <si>
-    <t>FRM-202</t>
-  </si>
-  <si>
-    <t>FRM-302</t>
-  </si>
-  <si>
-    <t>FRM-306</t>
-  </si>
-  <si>
-    <t>FRM-307 ? PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
-  </si>
-  <si>
-    <t>FRM-511</t>
-  </si>
-  <si>
-    <t>FRM-519</t>
-  </si>
-  <si>
-    <t>Form Code</t>
-  </si>
-  <si>
-    <t>Gap / Open Risk / Missing Confirmation</t>
-  </si>
-  <si>
-    <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
-  </si>
-  <si>
-    <t>HOLD</t>
-  </si>
-  <si>
-    <t>IN PROGRESS</t>
-  </si>
-  <si>
-    <t>JOB-240001</t>
-  </si>
-  <si>
-    <t>JOB-240002</t>
-  </si>
-  <si>
-    <t>JOB-240003</t>
-  </si>
-  <si>
-    <t>Job / WO</t>
-  </si>
-  <si>
-    <t>MONITORING</t>
-  </si>
-  <si>
-    <t>Machine / CMM / warehouse / shipping point-of-use list is complete.</t>
-  </si>
-  <si>
-    <t>NA</t>
-  </si>
-  <si>
-    <t>NOTICE  ?  Controlled withdrawal scope log; keep source files external. Maintain traceability to the parent form, superseding package, point-of-use impact and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
-  </si>
-  <si>
-    <t>NOTICE  ?  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-307_[EVENTID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
-  </si>
-  <si>
-    <t>NOTICE  ?  Point-of-use sweep confirmation log. Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, timestamps and result fields controlled.</t>
-  </si>
-  <si>
-    <t>Name  /  Signature  /  Date</t>
-  </si>
-  <si>
-    <t>New Effective Ref</t>
-  </si>
-  <si>
-    <t>New effective package reference is current.</t>
-  </si>
-  <si>
-    <t>No uncontrolled copy remains in active use.</t>
-  </si>
-  <si>
-    <t>Note</t>
-  </si>
-  <si>
-    <t>OPEN</t>
-  </si>
-  <si>
-    <t>Obsolete sweep closes within the required window.</t>
-  </si>
-  <si>
-    <t>Old Ref / Location</t>
-  </si>
-  <si>
-    <t>Old digital access is no longer the effective release.</t>
-  </si>
-  <si>
-    <t>Open Mandatory Risk / Gap</t>
-  </si>
-  <si>
-    <t>Open jobs, WIP and pending releases are reviewed for impact.</t>
-  </si>
-  <si>
-    <t>Operator, QC, planner and shipping notification is complete.</t>
-  </si>
-  <si>
-    <t>Owner</t>
-  </si>
-  <si>
-    <t>Owner / Confirmer</t>
-  </si>
-  <si>
-    <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
-  </si>
-  <si>
-    <t>PASS</t>
-  </si>
-  <si>
-    <t>PN-1001 / Rev.A</t>
-  </si>
-  <si>
-    <t>PN-1002 / Rev.B</t>
-  </si>
-  <si>
-    <t>PN-1003 / Rev.C</t>
-  </si>
-  <si>
-    <t>POINT-OF-USE SWEEP LOG</t>
-  </si>
-  <si>
-    <t>Package Owner</t>
-  </si>
-  <si>
-    <t>Paper copies, local packets and printed snapshots are pulled or replaced at point of use.</t>
-  </si>
-  <si>
-    <t>Parent Form</t>
-  </si>
-  <si>
-    <t>Part / Rev / Job</t>
-  </si>
-  <si>
-    <t>Part No. / Revision / Job No.</t>
-  </si>
-  <si>
-    <t>Planning Lead</t>
-  </si>
-  <si>
-    <t>Point of Use / Location</t>
-  </si>
-  <si>
-    <t>Prepared by</t>
-  </si>
-  <si>
-    <t>Production Supervisor</t>
-  </si>
-  <si>
-    <t>QA Engineer</t>
-  </si>
-  <si>
-    <t>QUA</t>
-  </si>
-  <si>
-    <t>Quality Management System  ?  Controlled Document</t>
-  </si>
-  <si>
-    <t>Quality Management System  ·  Controlled Document</t>
-  </si>
-  <si>
-    <t>REF LINKS</t>
-  </si>
-  <si>
-    <t>REF_DOCUMENT_CODE_MASTER</t>
-  </si>
-  <si>
-    <t>REF_JOB_WO_MASTER</t>
-  </si>
-  <si>
-    <t>REF_OWNER_PERSON_MASTER</t>
-  </si>
-  <si>
-    <t>REF_PART_REV_MASTER</t>
-  </si>
-  <si>
-    <t>REJECT</t>
-  </si>
-  <si>
-    <t>REL</t>
-  </si>
-  <si>
-    <t>Record Status</t>
-  </si>
-  <si>
-    <t>Ref Type</t>
-  </si>
-  <si>
-    <t>Ref.</t>
-  </si>
-  <si>
-    <t>Reference superseding package, withdrawal evidence and active M365 links only.</t>
-  </si>
-  <si>
-    <t>Required Action</t>
-  </si>
-  <si>
-    <t>Result</t>
-  </si>
-  <si>
-    <t>Retention Rule</t>
-  </si>
-  <si>
-    <t>Revalidation trigger is raised where required.</t>
-  </si>
-  <si>
-    <t>Reviewed By</t>
-  </si>
-  <si>
-    <t>Reviewed by</t>
-  </si>
-  <si>
-    <t>Revision</t>
-  </si>
-  <si>
-    <t>SIGNOFFS</t>
-  </si>
-  <si>
-    <t>SUPERSEDED</t>
-  </si>
-  <si>
-    <t>Setup Technician</t>
-  </si>
-  <si>
-    <t>Source of Truth</t>
-  </si>
-  <si>
-    <t>Status</t>
-  </si>
-  <si>
-    <t>Structured Excel Table with filters and print-title rows.</t>
-  </si>
-  <si>
-    <t>Superseding Package ID</t>
-  </si>
-  <si>
-    <t>Superseding package is approved and uniquely identified.</t>
-  </si>
-  <si>
-    <t>Support Tab</t>
-  </si>
-  <si>
-    <t>Support sheet only — not a replacement for ERP / M365 system-of-record.</t>
-  </si>
-  <si>
-    <t>Sweep Status</t>
-  </si>
-  <si>
-    <t>Sweep confirmation by point of use.</t>
-  </si>
-  <si>
-    <t>System of Record</t>
-  </si>
-  <si>
-    <t>TEC</t>
-  </si>
-  <si>
-    <t>Tab Purpose</t>
-  </si>
-  <si>
-    <t>Unique Ref</t>
-  </si>
-  <si>
-    <t>Update Trigger</t>
-  </si>
-  <si>
-    <t>Update when each affected point of use confirms pull / replace / supersede completion.</t>
-  </si>
-  <si>
-    <t>Update when the superseding package, affected scope or revalidation status changes.</t>
-  </si>
-  <si>
-    <t>Use controlled parent-form references, approved release links and withdrawal evidence only.</t>
-  </si>
-  <si>
-    <t>Use controlled parent-form references, withdrawal evidence and point-of-use confirmation only.</t>
-  </si>
-  <si>
-    <t>V0</t>
-  </si>
-  <si>
-    <t>VAL_DECISION_GATE_CORE</t>
-  </si>
-  <si>
-    <t>VAL_RESULT_CORE</t>
-  </si>
-  <si>
-    <t>VAL_STATUS_CORE</t>
-  </si>
-  <si>
-    <t>VOID</t>
-  </si>
-  <si>
-    <t>Verified by</t>
-  </si>
-  <si>
-    <t>WITHDRAWAL SCOPE / AFFECTED PACKAGE LOG</t>
-  </si>
-  <si>
-    <t>Withdrawal / Sweep Item</t>
-  </si>
-  <si>
-    <t>Withdrawal Decision</t>
-  </si>
-  <si>
-    <t>Withdrawal Event ID</t>
-  </si>
-  <si>
-    <t>Withdrawal Trigger / Reason</t>
-  </si>
-  <si>
-    <t>Withdrawal Type</t>
-  </si>
-  <si>
-    <t>Withdrawal evidence is linked to SSOT and issue history.</t>
-  </si>
-  <si>
-    <t>Withdrawal scope can reconstruct impact.</t>
-  </si>
-  <si>
-    <t>Working Owner</t>
-  </si>
-  <si>
-    <t>YYYY-MM-DD</t>
-  </si>
-</sst>
-</file>
-
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd"/>
   </numFmts>
-  <fonts count="94">
+  <fonts count="95">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -1052,6 +567,9 @@
       <color rgb="007B4F00"/>
       <sz val="7"/>
     </font>
+    <font>
+      <name val="Segoe UI"/>
+    </font>
   </fonts>
   <fills count="62">
     <fill>
@@ -1361,7 +879,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="394">
+  <borders count="395">
     <border>
       <left/>
       <right/>
@@ -5634,11 +5152,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="799">
+  <cellXfs count="819">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7622,6 +7150,40 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="392" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="393" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="314" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="315" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="316" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="315" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="317" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="319" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="320" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="88" fillId="57" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="302" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="323" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="324" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="325" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="90" fillId="0" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="88" fillId="57" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="394" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="324" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="56" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -11495,7 +11057,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AN7"/>
+  <dimension ref="A1:AN16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -11540,376 +11102,1817 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1">
-      <c r="A1" s="406" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="B1" s="406" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="C1" s="406" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D1" s="406" t="n"/>
-      <c r="E1" s="406" t="n"/>
-      <c r="F1" s="406" t="n"/>
-      <c r="G1" s="406" t="n"/>
-      <c r="H1" s="406" t="n"/>
-      <c r="I1" s="406" t="n"/>
-      <c r="J1" s="406" t="n"/>
-      <c r="K1" s="406" t="n"/>
-      <c r="L1" s="406" t="n"/>
-      <c r="M1" s="406" t="n"/>
-      <c r="N1" s="406" t="n"/>
-      <c r="O1" s="406" t="n"/>
-      <c r="P1" s="406" t="n"/>
-      <c r="Q1" s="406" t="n"/>
-      <c r="R1" s="406" t="n"/>
-      <c r="S1" s="406" t="n"/>
-      <c r="T1" s="406" t="n"/>
-      <c r="U1" s="406" t="n"/>
-      <c r="V1" s="406" t="n"/>
-      <c r="W1" s="406" t="n"/>
-      <c r="X1" s="406" t="n"/>
-      <c r="Y1" s="406" t="n"/>
-      <c r="Z1" s="406" t="n"/>
-      <c r="AA1" s="406" t="n"/>
-      <c r="AB1" s="406" t="n"/>
-      <c r="AC1" s="406" t="n"/>
-      <c r="AD1" s="406" t="n"/>
-      <c r="AE1" s="406" t="n"/>
-      <c r="AF1" s="406" t="n"/>
-      <c r="AG1" s="406" t="n"/>
-      <c r="AH1" s="406" t="n"/>
-      <c r="AI1" s="406" t="n"/>
-      <c r="AJ1" s="406" t="n"/>
-      <c r="AK1" s="406" t="n"/>
-      <c r="AL1" s="406" t="n"/>
-      <c r="AM1" s="406" t="n"/>
-      <c r="AN1" s="406" t="n"/>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="799" t="n"/>
+      <c r="B1" s="800" t="n"/>
+      <c r="C1" s="800" t="n"/>
+      <c r="D1" s="800" t="n"/>
+      <c r="E1" s="800" t="n"/>
+      <c r="F1" s="800" t="n"/>
+      <c r="G1" s="800" t="n"/>
+      <c r="H1" s="801" t="n"/>
+      <c r="I1" s="802" t="inlineStr">
+        <is>
+          <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
+        </is>
+      </c>
+      <c r="J1" s="800" t="n"/>
+      <c r="K1" s="800" t="n"/>
+      <c r="L1" s="800" t="n"/>
+      <c r="M1" s="800" t="n"/>
+      <c r="N1" s="800" t="n"/>
+      <c r="O1" s="800" t="n"/>
+      <c r="P1" s="800" t="n"/>
+      <c r="Q1" s="800" t="n"/>
+      <c r="R1" s="800" t="n"/>
+      <c r="S1" s="800" t="n"/>
+      <c r="T1" s="800" t="n"/>
+      <c r="U1" s="800" t="n"/>
+      <c r="V1" s="800" t="n"/>
+      <c r="W1" s="800" t="n"/>
+      <c r="X1" s="800" t="n"/>
+      <c r="Y1" s="800" t="n"/>
+      <c r="Z1" s="800" t="n"/>
+      <c r="AA1" s="800" t="n"/>
+      <c r="AB1" s="800" t="n"/>
+      <c r="AC1" s="800" t="n"/>
+      <c r="AD1" s="801" t="n"/>
+      <c r="AE1" s="507" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="800" t="n"/>
+      <c r="AG1" s="800" t="n"/>
+      <c r="AH1" s="803" t="n"/>
+      <c r="AI1" s="510" t="inlineStr">
+        <is>
+          <t>FRM-306</t>
+        </is>
+      </c>
+      <c r="AJ1" s="800" t="n"/>
+      <c r="AK1" s="800" t="n"/>
+      <c r="AL1" s="800" t="n"/>
+      <c r="AM1" s="800" t="n"/>
+      <c r="AN1" s="801" t="n"/>
     </row>
-    <row r="2">
-      <c r="A2" s="406" t="inlineStr">
-        <is>
-          <t>PASS</t>
-        </is>
-      </c>
-      <c r="B2" s="406" t="inlineStr">
-        <is>
-          <t>APPROVED</t>
-        </is>
-      </c>
-      <c r="C2" s="406" t="inlineStr">
-        <is>
-          <t>OPEN</t>
-        </is>
-      </c>
-      <c r="D2" s="406" t="n"/>
-      <c r="E2" s="406" t="n"/>
-      <c r="F2" s="406" t="n"/>
-      <c r="G2" s="406" t="n"/>
-      <c r="H2" s="406" t="n"/>
-      <c r="I2" s="406" t="n"/>
-      <c r="J2" s="406" t="n"/>
-      <c r="K2" s="406" t="n"/>
-      <c r="L2" s="406" t="n"/>
-      <c r="M2" s="406" t="n"/>
-      <c r="N2" s="406" t="n"/>
-      <c r="O2" s="406" t="n"/>
-      <c r="P2" s="406" t="n"/>
-      <c r="Q2" s="406" t="n"/>
-      <c r="R2" s="406" t="n"/>
-      <c r="S2" s="406" t="n"/>
-      <c r="T2" s="406" t="n"/>
-      <c r="U2" s="406" t="n"/>
-      <c r="V2" s="406" t="n"/>
-      <c r="W2" s="406" t="n"/>
-      <c r="X2" s="406" t="n"/>
-      <c r="Y2" s="406" t="n"/>
-      <c r="Z2" s="406" t="n"/>
-      <c r="AA2" s="406" t="n"/>
-      <c r="AB2" s="406" t="n"/>
-      <c r="AC2" s="406" t="n"/>
-      <c r="AD2" s="406" t="n"/>
-      <c r="AE2" s="406" t="n"/>
-      <c r="AF2" s="406" t="n"/>
-      <c r="AG2" s="406" t="n"/>
-      <c r="AH2" s="406" t="n"/>
-      <c r="AI2" s="406" t="n"/>
-      <c r="AJ2" s="406" t="n"/>
-      <c r="AK2" s="406" t="n"/>
-      <c r="AL2" s="406" t="n"/>
-      <c r="AM2" s="406" t="n"/>
-      <c r="AN2" s="406" t="n"/>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="804" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="805" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="805" t="n"/>
+      <c r="AE2" s="806" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="807" t="n"/>
+      <c r="AI2" s="808" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="805" t="n"/>
     </row>
-    <row r="3">
-      <c r="A3" s="406" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="B3" s="406" t="inlineStr">
-        <is>
-          <t>CONDITIONAL</t>
-        </is>
-      </c>
-      <c r="C3" s="406" t="inlineStr">
-        <is>
-          <t>IN PROGRESS</t>
-        </is>
-      </c>
-      <c r="D3" s="406" t="n"/>
-      <c r="E3" s="406" t="n"/>
-      <c r="F3" s="406" t="n"/>
-      <c r="G3" s="406" t="n"/>
-      <c r="H3" s="406" t="n"/>
-      <c r="I3" s="406" t="n"/>
-      <c r="J3" s="406" t="n"/>
-      <c r="K3" s="406" t="n"/>
-      <c r="L3" s="406" t="n"/>
-      <c r="M3" s="406" t="n"/>
-      <c r="N3" s="406" t="n"/>
-      <c r="O3" s="406" t="n"/>
-      <c r="P3" s="406" t="n"/>
-      <c r="Q3" s="406" t="n"/>
-      <c r="R3" s="406" t="n"/>
-      <c r="S3" s="406" t="n"/>
-      <c r="T3" s="406" t="n"/>
-      <c r="U3" s="406" t="n"/>
-      <c r="V3" s="406" t="n"/>
-      <c r="W3" s="406" t="n"/>
-      <c r="X3" s="406" t="n"/>
-      <c r="Y3" s="406" t="n"/>
-      <c r="Z3" s="406" t="n"/>
-      <c r="AA3" s="406" t="n"/>
-      <c r="AB3" s="406" t="n"/>
-      <c r="AC3" s="406" t="n"/>
-      <c r="AD3" s="406" t="n"/>
-      <c r="AE3" s="406" t="n"/>
-      <c r="AF3" s="406" t="n"/>
-      <c r="AG3" s="406" t="n"/>
-      <c r="AH3" s="406" t="n"/>
-      <c r="AI3" s="406" t="n"/>
-      <c r="AJ3" s="406" t="n"/>
-      <c r="AK3" s="406" t="n"/>
-      <c r="AL3" s="406" t="n"/>
-      <c r="AM3" s="406" t="n"/>
-      <c r="AN3" s="406" t="n"/>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="804" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="805" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="805" t="n"/>
+      <c r="AE3" s="806" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="807" t="n"/>
+      <c r="AI3" s="808" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="805" t="n"/>
     </row>
-    <row r="4">
-      <c r="A4" s="406" t="inlineStr">
-        <is>
-          <t>FAIL</t>
-        </is>
-      </c>
-      <c r="B4" s="406" t="inlineStr">
-        <is>
-          <t>HOLD</t>
-        </is>
-      </c>
-      <c r="C4" s="406" t="inlineStr">
-        <is>
-          <t>CLOSED</t>
-        </is>
-      </c>
-      <c r="D4" s="406" t="n"/>
-      <c r="E4" s="406" t="n"/>
-      <c r="F4" s="406" t="n"/>
-      <c r="G4" s="406" t="n"/>
-      <c r="H4" s="406" t="n"/>
-      <c r="I4" s="406" t="n"/>
-      <c r="J4" s="406" t="n"/>
-      <c r="K4" s="406" t="n"/>
-      <c r="L4" s="406" t="n"/>
-      <c r="M4" s="406" t="n"/>
-      <c r="N4" s="406" t="n"/>
-      <c r="O4" s="406" t="n"/>
-      <c r="P4" s="406" t="n"/>
-      <c r="Q4" s="406" t="n"/>
-      <c r="R4" s="406" t="n"/>
-      <c r="S4" s="406" t="n"/>
-      <c r="T4" s="406" t="n"/>
-      <c r="U4" s="406" t="n"/>
-      <c r="V4" s="406" t="n"/>
-      <c r="W4" s="406" t="n"/>
-      <c r="X4" s="406" t="n"/>
-      <c r="Y4" s="406" t="n"/>
-      <c r="Z4" s="406" t="n"/>
-      <c r="AA4" s="406" t="n"/>
-      <c r="AB4" s="406" t="n"/>
-      <c r="AC4" s="406" t="n"/>
-      <c r="AD4" s="406" t="n"/>
-      <c r="AE4" s="406" t="n"/>
-      <c r="AF4" s="406" t="n"/>
-      <c r="AG4" s="406" t="n"/>
-      <c r="AH4" s="406" t="n"/>
-      <c r="AI4" s="406" t="n"/>
-      <c r="AJ4" s="406" t="n"/>
-      <c r="AK4" s="406" t="n"/>
-      <c r="AL4" s="406" t="n"/>
-      <c r="AM4" s="406" t="n"/>
-      <c r="AN4" s="406" t="n"/>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="804" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="805" t="n"/>
+      <c r="I4" s="809" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="805" t="n"/>
+      <c r="AE4" s="806" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="807" t="n"/>
+      <c r="AI4" s="808" t="inlineStr">
+        <is>
+          <t>Engineering / QA / Planning</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="805" t="n"/>
     </row>
-    <row r="5">
-      <c r="A5" s="406" t="inlineStr">
-        <is>
-          <t>NA</t>
-        </is>
-      </c>
-      <c r="B5" s="406" t="inlineStr">
-        <is>
-          <t>REJECT</t>
-        </is>
-      </c>
-      <c r="C5" s="406" t="inlineStr">
-        <is>
-          <t>MONITORING</t>
-        </is>
-      </c>
-      <c r="D5" s="406" t="n"/>
-      <c r="E5" s="406" t="n"/>
-      <c r="F5" s="406" t="n"/>
-      <c r="G5" s="406" t="n"/>
-      <c r="H5" s="406" t="n"/>
-      <c r="I5" s="406" t="n"/>
-      <c r="J5" s="406" t="n"/>
-      <c r="K5" s="406" t="n"/>
-      <c r="L5" s="406" t="n"/>
-      <c r="M5" s="406" t="n"/>
-      <c r="N5" s="406" t="n"/>
-      <c r="O5" s="406" t="n"/>
-      <c r="P5" s="406" t="n"/>
-      <c r="Q5" s="406" t="n"/>
-      <c r="R5" s="406" t="n"/>
-      <c r="S5" s="406" t="n"/>
-      <c r="T5" s="406" t="n"/>
-      <c r="U5" s="406" t="n"/>
-      <c r="V5" s="406" t="n"/>
-      <c r="W5" s="406" t="n"/>
-      <c r="X5" s="406" t="n"/>
-      <c r="Y5" s="406" t="n"/>
-      <c r="Z5" s="406" t="n"/>
-      <c r="AA5" s="406" t="n"/>
-      <c r="AB5" s="406" t="n"/>
-      <c r="AC5" s="406" t="n"/>
-      <c r="AD5" s="406" t="n"/>
-      <c r="AE5" s="406" t="n"/>
-      <c r="AF5" s="406" t="n"/>
-      <c r="AG5" s="406" t="n"/>
-      <c r="AH5" s="406" t="n"/>
-      <c r="AI5" s="406" t="n"/>
-      <c r="AJ5" s="406" t="n"/>
-      <c r="AK5" s="406" t="n"/>
-      <c r="AL5" s="406" t="n"/>
-      <c r="AM5" s="406" t="n"/>
-      <c r="AN5" s="406" t="n"/>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="810" t="n"/>
+      <c r="B5" s="811" t="n"/>
+      <c r="C5" s="811" t="n"/>
+      <c r="D5" s="811" t="n"/>
+      <c r="E5" s="811" t="n"/>
+      <c r="F5" s="811" t="n"/>
+      <c r="G5" s="811" t="n"/>
+      <c r="H5" s="812" t="n"/>
+      <c r="I5" s="813" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="811" t="n"/>
+      <c r="K5" s="811" t="n"/>
+      <c r="L5" s="811" t="n"/>
+      <c r="M5" s="811" t="n"/>
+      <c r="N5" s="811" t="n"/>
+      <c r="O5" s="811" t="n"/>
+      <c r="P5" s="811" t="n"/>
+      <c r="Q5" s="811" t="n"/>
+      <c r="R5" s="811" t="n"/>
+      <c r="S5" s="811" t="n"/>
+      <c r="T5" s="811" t="n"/>
+      <c r="U5" s="811" t="n"/>
+      <c r="V5" s="811" t="n"/>
+      <c r="W5" s="811" t="n"/>
+      <c r="X5" s="811" t="n"/>
+      <c r="Y5" s="811" t="n"/>
+      <c r="Z5" s="811" t="n"/>
+      <c r="AA5" s="811" t="n"/>
+      <c r="AB5" s="811" t="n"/>
+      <c r="AC5" s="811" t="n"/>
+      <c r="AD5" s="812" t="n"/>
+      <c r="AE5" s="814" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="811" t="n"/>
+      <c r="AG5" s="811" t="n"/>
+      <c r="AH5" s="815" t="n"/>
+      <c r="AI5" s="816" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="811" t="n"/>
+      <c r="AK5" s="811" t="n"/>
+      <c r="AL5" s="811" t="n"/>
+      <c r="AM5" s="811" t="n"/>
+      <c r="AN5" s="812" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="406" t="n"/>
-      <c r="B6" s="406" t="n"/>
-      <c r="C6" s="406" t="inlineStr">
-        <is>
-          <t>SUPERSEDED</t>
-        </is>
-      </c>
-      <c r="D6" s="406" t="n"/>
-      <c r="E6" s="406" t="n"/>
-      <c r="F6" s="406" t="n"/>
-      <c r="G6" s="406" t="n"/>
-      <c r="H6" s="406" t="n"/>
-      <c r="I6" s="406" t="n"/>
-      <c r="J6" s="406" t="n"/>
-      <c r="K6" s="406" t="n"/>
-      <c r="L6" s="406" t="n"/>
-      <c r="M6" s="406" t="n"/>
-      <c r="N6" s="406" t="n"/>
-      <c r="O6" s="406" t="n"/>
-      <c r="P6" s="406" t="n"/>
-      <c r="Q6" s="406" t="n"/>
-      <c r="R6" s="406" t="n"/>
-      <c r="S6" s="406" t="n"/>
-      <c r="T6" s="406" t="n"/>
-      <c r="U6" s="406" t="n"/>
-      <c r="V6" s="406" t="n"/>
-      <c r="W6" s="406" t="n"/>
-      <c r="X6" s="406" t="n"/>
-      <c r="Y6" s="406" t="n"/>
-      <c r="Z6" s="406" t="n"/>
-      <c r="AA6" s="406" t="n"/>
-      <c r="AB6" s="406" t="n"/>
-      <c r="AC6" s="406" t="n"/>
-      <c r="AD6" s="406" t="n"/>
-      <c r="AE6" s="406" t="n"/>
-      <c r="AF6" s="406" t="n"/>
-      <c r="AG6" s="406" t="n"/>
-      <c r="AH6" s="406" t="n"/>
-      <c r="AI6" s="406" t="n"/>
-      <c r="AJ6" s="406" t="n"/>
-      <c r="AK6" s="406" t="n"/>
-      <c r="AL6" s="406" t="n"/>
-      <c r="AM6" s="406" t="n"/>
-      <c r="AN6" s="406" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="817" t="n"/>
+      <c r="B6" s="817" t="n"/>
+      <c r="C6" s="817" t="n"/>
+      <c r="D6" s="817" t="n"/>
+      <c r="E6" s="817" t="n"/>
+      <c r="F6" s="817" t="n"/>
+      <c r="G6" s="817" t="n"/>
+      <c r="H6" s="817" t="n"/>
+      <c r="I6" s="817" t="n"/>
+      <c r="J6" s="817" t="n"/>
+      <c r="K6" s="817" t="n"/>
+      <c r="L6" s="817" t="n"/>
+      <c r="M6" s="817" t="n"/>
+      <c r="N6" s="817" t="n"/>
+      <c r="O6" s="817" t="n"/>
+      <c r="P6" s="817" t="n"/>
+      <c r="Q6" s="817" t="n"/>
+      <c r="R6" s="817" t="n"/>
+      <c r="S6" s="817" t="n"/>
+      <c r="T6" s="817" t="n"/>
+      <c r="U6" s="817" t="n"/>
+      <c r="V6" s="817" t="n"/>
+      <c r="W6" s="817" t="n"/>
+      <c r="X6" s="817" t="n"/>
+      <c r="Y6" s="817" t="n"/>
+      <c r="Z6" s="817" t="n"/>
+      <c r="AA6" s="817" t="n"/>
+      <c r="AB6" s="817" t="n"/>
+      <c r="AC6" s="817" t="n"/>
+      <c r="AD6" s="817" t="n"/>
+      <c r="AE6" s="817" t="n"/>
+      <c r="AF6" s="817" t="n"/>
+      <c r="AG6" s="817" t="n"/>
+      <c r="AH6" s="817" t="n"/>
+      <c r="AI6" s="817" t="n"/>
+      <c r="AJ6" s="817" t="n"/>
+      <c r="AK6" s="817" t="n"/>
+      <c r="AL6" s="817" t="n"/>
+      <c r="AM6" s="817" t="n"/>
+      <c r="AN6" s="817" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="406" t="n"/>
-      <c r="B7" s="406" t="n"/>
+      <c r="A7" s="406" t="inlineStr">
+        <is>
+          <t>VAL_RESULT_CORE</t>
+        </is>
+      </c>
+      <c r="B7" s="406" t="inlineStr">
+        <is>
+          <t>VAL_DECISION_GATE_CORE</t>
+        </is>
+      </c>
       <c r="C7" s="406" t="inlineStr">
         <is>
+          <t>VAL_STATUS_CORE</t>
+        </is>
+      </c>
+      <c r="D7" s="818" t="n"/>
+      <c r="E7" s="818" t="n"/>
+      <c r="F7" s="818" t="n"/>
+      <c r="G7" s="818" t="n"/>
+      <c r="H7" s="818" t="n"/>
+      <c r="I7" s="818" t="n"/>
+      <c r="J7" s="818" t="n"/>
+      <c r="K7" s="818" t="n"/>
+      <c r="L7" s="818" t="n"/>
+      <c r="M7" s="818" t="n"/>
+      <c r="N7" s="818" t="n"/>
+      <c r="O7" s="818" t="n"/>
+      <c r="P7" s="818" t="n"/>
+      <c r="Q7" s="818" t="n"/>
+      <c r="R7" s="818" t="n"/>
+      <c r="S7" s="818" t="n"/>
+      <c r="T7" s="818" t="n"/>
+      <c r="U7" s="818" t="n"/>
+      <c r="V7" s="818" t="n"/>
+      <c r="W7" s="818" t="n"/>
+      <c r="X7" s="818" t="n"/>
+      <c r="Y7" s="818" t="n"/>
+      <c r="Z7" s="818" t="n"/>
+      <c r="AA7" s="818" t="n"/>
+      <c r="AB7" s="818" t="n"/>
+      <c r="AC7" s="818" t="n"/>
+      <c r="AD7" s="818" t="n"/>
+      <c r="AE7" s="818" t="n"/>
+      <c r="AF7" s="818" t="n"/>
+      <c r="AG7" s="818" t="n"/>
+      <c r="AH7" s="818" t="n"/>
+      <c r="AI7" s="818" t="n"/>
+      <c r="AJ7" s="818" t="n"/>
+      <c r="AK7" s="818" t="n"/>
+      <c r="AL7" s="818" t="n"/>
+      <c r="AM7" s="818" t="n"/>
+      <c r="AN7" s="818" t="n"/>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="406" t="inlineStr">
+        <is>
+          <t>PASS</t>
+        </is>
+      </c>
+      <c r="B8" s="406" t="inlineStr">
+        <is>
+          <t>APPROVED</t>
+        </is>
+      </c>
+      <c r="C8" s="406" t="inlineStr">
+        <is>
+          <t>OPEN</t>
+        </is>
+      </c>
+      <c r="D8" s="818" t="n"/>
+      <c r="E8" s="818" t="n"/>
+      <c r="F8" s="818" t="n"/>
+      <c r="G8" s="818" t="n"/>
+      <c r="H8" s="818" t="n"/>
+      <c r="I8" s="818" t="n"/>
+      <c r="J8" s="818" t="n"/>
+      <c r="K8" s="818" t="n"/>
+      <c r="L8" s="818" t="n"/>
+      <c r="M8" s="818" t="n"/>
+      <c r="N8" s="818" t="n"/>
+      <c r="O8" s="818" t="n"/>
+      <c r="P8" s="818" t="n"/>
+      <c r="Q8" s="818" t="n"/>
+      <c r="R8" s="818" t="n"/>
+      <c r="S8" s="818" t="n"/>
+      <c r="T8" s="818" t="n"/>
+      <c r="U8" s="818" t="n"/>
+      <c r="V8" s="818" t="n"/>
+      <c r="W8" s="818" t="n"/>
+      <c r="X8" s="818" t="n"/>
+      <c r="Y8" s="818" t="n"/>
+      <c r="Z8" s="818" t="n"/>
+      <c r="AA8" s="818" t="n"/>
+      <c r="AB8" s="818" t="n"/>
+      <c r="AC8" s="818" t="n"/>
+      <c r="AD8" s="818" t="n"/>
+      <c r="AE8" s="818" t="n"/>
+      <c r="AF8" s="818" t="n"/>
+      <c r="AG8" s="818" t="n"/>
+      <c r="AH8" s="818" t="n"/>
+      <c r="AI8" s="818" t="n"/>
+      <c r="AJ8" s="818" t="n"/>
+      <c r="AK8" s="818" t="n"/>
+      <c r="AL8" s="818" t="n"/>
+      <c r="AM8" s="818" t="n"/>
+      <c r="AN8" s="818" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="406" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="B9" s="406" t="inlineStr">
+        <is>
+          <t>CONDITIONAL</t>
+        </is>
+      </c>
+      <c r="C9" s="406" t="inlineStr">
+        <is>
+          <t>IN PROGRESS</t>
+        </is>
+      </c>
+      <c r="D9" s="818" t="n"/>
+      <c r="E9" s="818" t="n"/>
+      <c r="F9" s="818" t="n"/>
+      <c r="G9" s="818" t="n"/>
+      <c r="H9" s="818" t="n"/>
+      <c r="I9" s="818" t="n"/>
+      <c r="J9" s="818" t="n"/>
+      <c r="K9" s="818" t="n"/>
+      <c r="L9" s="818" t="n"/>
+      <c r="M9" s="818" t="n"/>
+      <c r="N9" s="818" t="n"/>
+      <c r="O9" s="818" t="n"/>
+      <c r="P9" s="818" t="n"/>
+      <c r="Q9" s="818" t="n"/>
+      <c r="R9" s="818" t="n"/>
+      <c r="S9" s="818" t="n"/>
+      <c r="T9" s="818" t="n"/>
+      <c r="U9" s="818" t="n"/>
+      <c r="V9" s="818" t="n"/>
+      <c r="W9" s="818" t="n"/>
+      <c r="X9" s="818" t="n"/>
+      <c r="Y9" s="818" t="n"/>
+      <c r="Z9" s="818" t="n"/>
+      <c r="AA9" s="818" t="n"/>
+      <c r="AB9" s="818" t="n"/>
+      <c r="AC9" s="818" t="n"/>
+      <c r="AD9" s="818" t="n"/>
+      <c r="AE9" s="818" t="n"/>
+      <c r="AF9" s="818" t="n"/>
+      <c r="AG9" s="818" t="n"/>
+      <c r="AH9" s="818" t="n"/>
+      <c r="AI9" s="818" t="n"/>
+      <c r="AJ9" s="818" t="n"/>
+      <c r="AK9" s="818" t="n"/>
+      <c r="AL9" s="818" t="n"/>
+      <c r="AM9" s="818" t="n"/>
+      <c r="AN9" s="818" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="406" t="inlineStr">
+        <is>
+          <t>FAIL</t>
+        </is>
+      </c>
+      <c r="B10" s="406" t="inlineStr">
+        <is>
+          <t>HOLD</t>
+        </is>
+      </c>
+      <c r="C10" s="406" t="inlineStr">
+        <is>
+          <t>CLOSED</t>
+        </is>
+      </c>
+      <c r="D10" s="818" t="n"/>
+      <c r="E10" s="818" t="n"/>
+      <c r="F10" s="818" t="n"/>
+      <c r="G10" s="818" t="n"/>
+      <c r="H10" s="818" t="n"/>
+      <c r="I10" s="818" t="n"/>
+      <c r="J10" s="818" t="n"/>
+      <c r="K10" s="818" t="n"/>
+      <c r="L10" s="818" t="n"/>
+      <c r="M10" s="818" t="n"/>
+      <c r="N10" s="818" t="n"/>
+      <c r="O10" s="818" t="n"/>
+      <c r="P10" s="818" t="n"/>
+      <c r="Q10" s="818" t="n"/>
+      <c r="R10" s="818" t="n"/>
+      <c r="S10" s="818" t="n"/>
+      <c r="T10" s="818" t="n"/>
+      <c r="U10" s="818" t="n"/>
+      <c r="V10" s="818" t="n"/>
+      <c r="W10" s="818" t="n"/>
+      <c r="X10" s="818" t="n"/>
+      <c r="Y10" s="818" t="n"/>
+      <c r="Z10" s="818" t="n"/>
+      <c r="AA10" s="818" t="n"/>
+      <c r="AB10" s="818" t="n"/>
+      <c r="AC10" s="818" t="n"/>
+      <c r="AD10" s="818" t="n"/>
+      <c r="AE10" s="818" t="n"/>
+      <c r="AF10" s="818" t="n"/>
+      <c r="AG10" s="818" t="n"/>
+      <c r="AH10" s="818" t="n"/>
+      <c r="AI10" s="818" t="n"/>
+      <c r="AJ10" s="818" t="n"/>
+      <c r="AK10" s="818" t="n"/>
+      <c r="AL10" s="818" t="n"/>
+      <c r="AM10" s="818" t="n"/>
+      <c r="AN10" s="818" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="406" t="inlineStr">
+        <is>
+          <t>NA</t>
+        </is>
+      </c>
+      <c r="B11" s="406" t="inlineStr">
+        <is>
+          <t>REJECT</t>
+        </is>
+      </c>
+      <c r="C11" s="406" t="inlineStr">
+        <is>
+          <t>MONITORING</t>
+        </is>
+      </c>
+      <c r="D11" s="818" t="n"/>
+      <c r="E11" s="818" t="n"/>
+      <c r="F11" s="818" t="n"/>
+      <c r="G11" s="818" t="n"/>
+      <c r="H11" s="818" t="n"/>
+      <c r="I11" s="818" t="n"/>
+      <c r="J11" s="818" t="n"/>
+      <c r="K11" s="818" t="n"/>
+      <c r="L11" s="818" t="n"/>
+      <c r="M11" s="818" t="n"/>
+      <c r="N11" s="818" t="n"/>
+      <c r="O11" s="818" t="n"/>
+      <c r="P11" s="818" t="n"/>
+      <c r="Q11" s="818" t="n"/>
+      <c r="R11" s="818" t="n"/>
+      <c r="S11" s="818" t="n"/>
+      <c r="T11" s="818" t="n"/>
+      <c r="U11" s="818" t="n"/>
+      <c r="V11" s="818" t="n"/>
+      <c r="W11" s="818" t="n"/>
+      <c r="X11" s="818" t="n"/>
+      <c r="Y11" s="818" t="n"/>
+      <c r="Z11" s="818" t="n"/>
+      <c r="AA11" s="818" t="n"/>
+      <c r="AB11" s="818" t="n"/>
+      <c r="AC11" s="818" t="n"/>
+      <c r="AD11" s="818" t="n"/>
+      <c r="AE11" s="818" t="n"/>
+      <c r="AF11" s="818" t="n"/>
+      <c r="AG11" s="818" t="n"/>
+      <c r="AH11" s="818" t="n"/>
+      <c r="AI11" s="818" t="n"/>
+      <c r="AJ11" s="818" t="n"/>
+      <c r="AK11" s="818" t="n"/>
+      <c r="AL11" s="818" t="n"/>
+      <c r="AM11" s="818" t="n"/>
+      <c r="AN11" s="818" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="818" t="n"/>
+      <c r="B12" s="818" t="n"/>
+      <c r="C12" s="406" t="inlineStr">
+        <is>
+          <t>SUPERSEDED</t>
+        </is>
+      </c>
+      <c r="D12" s="818" t="n"/>
+      <c r="E12" s="818" t="n"/>
+      <c r="F12" s="818" t="n"/>
+      <c r="G12" s="818" t="n"/>
+      <c r="H12" s="818" t="n"/>
+      <c r="I12" s="818" t="n"/>
+      <c r="J12" s="818" t="n"/>
+      <c r="K12" s="818" t="n"/>
+      <c r="L12" s="818" t="n"/>
+      <c r="M12" s="818" t="n"/>
+      <c r="N12" s="818" t="n"/>
+      <c r="O12" s="818" t="n"/>
+      <c r="P12" s="818" t="n"/>
+      <c r="Q12" s="818" t="n"/>
+      <c r="R12" s="818" t="n"/>
+      <c r="S12" s="818" t="n"/>
+      <c r="T12" s="818" t="n"/>
+      <c r="U12" s="818" t="n"/>
+      <c r="V12" s="818" t="n"/>
+      <c r="W12" s="818" t="n"/>
+      <c r="X12" s="818" t="n"/>
+      <c r="Y12" s="818" t="n"/>
+      <c r="Z12" s="818" t="n"/>
+      <c r="AA12" s="818" t="n"/>
+      <c r="AB12" s="818" t="n"/>
+      <c r="AC12" s="818" t="n"/>
+      <c r="AD12" s="818" t="n"/>
+      <c r="AE12" s="818" t="n"/>
+      <c r="AF12" s="818" t="n"/>
+      <c r="AG12" s="818" t="n"/>
+      <c r="AH12" s="818" t="n"/>
+      <c r="AI12" s="818" t="n"/>
+      <c r="AJ12" s="818" t="n"/>
+      <c r="AK12" s="818" t="n"/>
+      <c r="AL12" s="818" t="n"/>
+      <c r="AM12" s="818" t="n"/>
+      <c r="AN12" s="818" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="818" t="n"/>
+      <c r="B13" s="818" t="n"/>
+      <c r="C13" s="406" t="inlineStr">
+        <is>
           <t>VOID</t>
         </is>
       </c>
-      <c r="D7" s="406" t="n"/>
-      <c r="E7" s="406" t="n"/>
-      <c r="F7" s="406" t="n"/>
-      <c r="G7" s="406" t="n"/>
-      <c r="H7" s="406" t="n"/>
-      <c r="I7" s="406" t="n"/>
-      <c r="J7" s="406" t="n"/>
-      <c r="K7" s="406" t="n"/>
-      <c r="L7" s="406" t="n"/>
-      <c r="M7" s="406" t="n"/>
-      <c r="N7" s="406" t="n"/>
-      <c r="O7" s="406" t="n"/>
-      <c r="P7" s="406" t="n"/>
-      <c r="Q7" s="406" t="n"/>
-      <c r="R7" s="406" t="n"/>
-      <c r="S7" s="406" t="n"/>
-      <c r="T7" s="406" t="n"/>
-      <c r="U7" s="406" t="n"/>
-      <c r="V7" s="406" t="n"/>
-      <c r="W7" s="406" t="n"/>
-      <c r="X7" s="406" t="n"/>
-      <c r="Y7" s="406" t="n"/>
-      <c r="Z7" s="406" t="n"/>
-      <c r="AA7" s="406" t="n"/>
-      <c r="AB7" s="406" t="n"/>
-      <c r="AC7" s="406" t="n"/>
-      <c r="AD7" s="406" t="n"/>
-      <c r="AE7" s="406" t="n"/>
-      <c r="AF7" s="406" t="n"/>
-      <c r="AG7" s="406" t="n"/>
-      <c r="AH7" s="406" t="n"/>
-      <c r="AI7" s="406" t="n"/>
-      <c r="AJ7" s="406" t="n"/>
-      <c r="AK7" s="406" t="n"/>
-      <c r="AL7" s="406" t="n"/>
-      <c r="AM7" s="406" t="n"/>
-      <c r="AN7" s="406" t="n"/>
+      <c r="D13" s="818" t="n"/>
+      <c r="E13" s="818" t="n"/>
+      <c r="F13" s="818" t="n"/>
+      <c r="G13" s="818" t="n"/>
+      <c r="H13" s="818" t="n"/>
+      <c r="I13" s="818" t="n"/>
+      <c r="J13" s="818" t="n"/>
+      <c r="K13" s="818" t="n"/>
+      <c r="L13" s="818" t="n"/>
+      <c r="M13" s="818" t="n"/>
+      <c r="N13" s="818" t="n"/>
+      <c r="O13" s="818" t="n"/>
+      <c r="P13" s="818" t="n"/>
+      <c r="Q13" s="818" t="n"/>
+      <c r="R13" s="818" t="n"/>
+      <c r="S13" s="818" t="n"/>
+      <c r="T13" s="818" t="n"/>
+      <c r="U13" s="818" t="n"/>
+      <c r="V13" s="818" t="n"/>
+      <c r="W13" s="818" t="n"/>
+      <c r="X13" s="818" t="n"/>
+      <c r="Y13" s="818" t="n"/>
+      <c r="Z13" s="818" t="n"/>
+      <c r="AA13" s="818" t="n"/>
+      <c r="AB13" s="818" t="n"/>
+      <c r="AC13" s="818" t="n"/>
+      <c r="AD13" s="818" t="n"/>
+      <c r="AE13" s="818" t="n"/>
+      <c r="AF13" s="818" t="n"/>
+      <c r="AG13" s="818" t="n"/>
+      <c r="AH13" s="818" t="n"/>
+      <c r="AI13" s="818" t="n"/>
+      <c r="AJ13" s="818" t="n"/>
+      <c r="AK13" s="818" t="n"/>
+      <c r="AL13" s="818" t="n"/>
+      <c r="AM13" s="818" t="n"/>
+      <c r="AN13" s="818" t="n"/>
     </row>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
+    <row r="14" hidden="1">
+      <c r="A14" s="818" t="n"/>
+      <c r="B14" s="818" t="n"/>
+      <c r="C14" s="818" t="n"/>
+      <c r="D14" s="818" t="n"/>
+      <c r="E14" s="818" t="n"/>
+      <c r="F14" s="818" t="n"/>
+      <c r="G14" s="818" t="n"/>
+      <c r="H14" s="818" t="n"/>
+      <c r="I14" s="818" t="n"/>
+      <c r="J14" s="818" t="n"/>
+      <c r="K14" s="818" t="n"/>
+      <c r="L14" s="818" t="n"/>
+      <c r="M14" s="818" t="n"/>
+      <c r="N14" s="818" t="n"/>
+      <c r="O14" s="818" t="n"/>
+      <c r="P14" s="818" t="n"/>
+      <c r="Q14" s="818" t="n"/>
+      <c r="R14" s="818" t="n"/>
+      <c r="S14" s="818" t="n"/>
+      <c r="T14" s="818" t="n"/>
+      <c r="U14" s="818" t="n"/>
+      <c r="V14" s="818" t="n"/>
+      <c r="W14" s="818" t="n"/>
+      <c r="X14" s="818" t="n"/>
+      <c r="Y14" s="818" t="n"/>
+      <c r="Z14" s="818" t="n"/>
+      <c r="AA14" s="818" t="n"/>
+      <c r="AB14" s="818" t="n"/>
+      <c r="AC14" s="818" t="n"/>
+      <c r="AD14" s="818" t="n"/>
+      <c r="AE14" s="818" t="n"/>
+      <c r="AF14" s="818" t="n"/>
+      <c r="AG14" s="818" t="n"/>
+      <c r="AH14" s="818" t="n"/>
+      <c r="AI14" s="818" t="n"/>
+      <c r="AJ14" s="818" t="n"/>
+      <c r="AK14" s="818" t="n"/>
+      <c r="AL14" s="818" t="n"/>
+      <c r="AM14" s="818" t="n"/>
+      <c r="AN14" s="818" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="818" t="n"/>
+      <c r="B15" s="818" t="n"/>
+      <c r="C15" s="818" t="n"/>
+      <c r="D15" s="818" t="n"/>
+      <c r="E15" s="818" t="n"/>
+      <c r="F15" s="818" t="n"/>
+      <c r="G15" s="818" t="n"/>
+      <c r="H15" s="818" t="n"/>
+      <c r="I15" s="818" t="n"/>
+      <c r="J15" s="818" t="n"/>
+      <c r="K15" s="818" t="n"/>
+      <c r="L15" s="818" t="n"/>
+      <c r="M15" s="818" t="n"/>
+      <c r="N15" s="818" t="n"/>
+      <c r="O15" s="818" t="n"/>
+      <c r="P15" s="818" t="n"/>
+      <c r="Q15" s="818" t="n"/>
+      <c r="R15" s="818" t="n"/>
+      <c r="S15" s="818" t="n"/>
+      <c r="T15" s="818" t="n"/>
+      <c r="U15" s="818" t="n"/>
+      <c r="V15" s="818" t="n"/>
+      <c r="W15" s="818" t="n"/>
+      <c r="X15" s="818" t="n"/>
+      <c r="Y15" s="818" t="n"/>
+      <c r="Z15" s="818" t="n"/>
+      <c r="AA15" s="818" t="n"/>
+      <c r="AB15" s="818" t="n"/>
+      <c r="AC15" s="818" t="n"/>
+      <c r="AD15" s="818" t="n"/>
+      <c r="AE15" s="818" t="n"/>
+      <c r="AF15" s="818" t="n"/>
+      <c r="AG15" s="818" t="n"/>
+      <c r="AH15" s="818" t="n"/>
+      <c r="AI15" s="818" t="n"/>
+      <c r="AJ15" s="818" t="n"/>
+      <c r="AK15" s="818" t="n"/>
+      <c r="AL15" s="818" t="n"/>
+      <c r="AM15" s="818" t="n"/>
+      <c r="AN15" s="818" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="818" t="n"/>
+      <c r="B16" s="818" t="n"/>
+      <c r="C16" s="818" t="n"/>
+      <c r="D16" s="818" t="n"/>
+      <c r="E16" s="818" t="n"/>
+      <c r="F16" s="818" t="n"/>
+      <c r="G16" s="818" t="n"/>
+      <c r="H16" s="818" t="n"/>
+      <c r="I16" s="818" t="n"/>
+      <c r="J16" s="818" t="n"/>
+      <c r="K16" s="818" t="n"/>
+      <c r="L16" s="818" t="n"/>
+      <c r="M16" s="818" t="n"/>
+      <c r="N16" s="818" t="n"/>
+      <c r="O16" s="818" t="n"/>
+      <c r="P16" s="818" t="n"/>
+      <c r="Q16" s="818" t="n"/>
+      <c r="R16" s="818" t="n"/>
+      <c r="S16" s="818" t="n"/>
+      <c r="T16" s="818" t="n"/>
+      <c r="U16" s="818" t="n"/>
+      <c r="V16" s="818" t="n"/>
+      <c r="W16" s="818" t="n"/>
+      <c r="X16" s="818" t="n"/>
+      <c r="Y16" s="818" t="n"/>
+      <c r="Z16" s="818" t="n"/>
+      <c r="AA16" s="818" t="n"/>
+      <c r="AB16" s="818" t="n"/>
+      <c r="AC16" s="818" t="n"/>
+      <c r="AD16" s="818" t="n"/>
+      <c r="AE16" s="818" t="n"/>
+      <c r="AF16" s="818" t="n"/>
+      <c r="AG16" s="818" t="n"/>
+      <c r="AH16" s="818" t="n"/>
+      <c r="AI16" s="818" t="n"/>
+      <c r="AJ16" s="818" t="n"/>
+      <c r="AK16" s="818" t="n"/>
+      <c r="AL16" s="818" t="n"/>
+      <c r="AM16" s="818" t="n"/>
+      <c r="AN16" s="818" t="n"/>
+    </row>
+    <row r="17" hidden="1"/>
+    <row r="18" hidden="1"/>
+    <row r="19" hidden="1"/>
+    <row r="20" hidden="1"/>
+    <row r="21" hidden="1"/>
+    <row r="22" hidden="1"/>
+    <row r="23" hidden="1"/>
+    <row r="24" hidden="1"/>
+    <row r="25" hidden="1"/>
+    <row r="26" hidden="1"/>
+    <row r="27" hidden="1"/>
+    <row r="28" hidden="1"/>
+    <row r="29" hidden="1"/>
+    <row r="30" hidden="1"/>
+    <row r="31" hidden="1"/>
+    <row r="32" hidden="1"/>
+    <row r="33" hidden="1"/>
+    <row r="34" hidden="1"/>
+    <row r="35" hidden="1"/>
+    <row r="36" hidden="1"/>
+    <row r="37" hidden="1"/>
+    <row r="38" hidden="1"/>
+    <row r="39" hidden="1"/>
+    <row r="40" hidden="1"/>
+    <row r="41" hidden="1"/>
+    <row r="42" hidden="1"/>
+    <row r="43" hidden="1"/>
+    <row r="44" hidden="1"/>
+    <row r="45" hidden="1"/>
+    <row r="46" hidden="1"/>
+    <row r="47" hidden="1"/>
+    <row r="48" hidden="1"/>
+    <row r="49" hidden="1"/>
+    <row r="50" hidden="1"/>
+    <row r="51" hidden="1"/>
+    <row r="52" hidden="1"/>
+    <row r="53" hidden="1"/>
+    <row r="54" hidden="1"/>
+    <row r="55" hidden="1"/>
+    <row r="56" hidden="1"/>
+    <row r="57" hidden="1"/>
+    <row r="58" hidden="1"/>
+    <row r="59" hidden="1"/>
+    <row r="60" hidden="1"/>
+    <row r="61" hidden="1"/>
+    <row r="62" hidden="1"/>
+    <row r="63" hidden="1"/>
+    <row r="64" hidden="1"/>
+    <row r="65" hidden="1"/>
+    <row r="66" hidden="1"/>
+    <row r="67" hidden="1"/>
+    <row r="68" hidden="1"/>
+    <row r="69" hidden="1"/>
+    <row r="70" hidden="1"/>
+    <row r="71" hidden="1"/>
+    <row r="72" hidden="1"/>
+    <row r="73" hidden="1"/>
+    <row r="74" hidden="1"/>
+    <row r="75" hidden="1"/>
+    <row r="76" hidden="1"/>
+    <row r="77" hidden="1"/>
+    <row r="78" hidden="1"/>
+    <row r="79" hidden="1"/>
+    <row r="80" hidden="1"/>
+    <row r="81" hidden="1"/>
+    <row r="82" hidden="1"/>
+    <row r="83" hidden="1"/>
+    <row r="84" hidden="1"/>
+    <row r="85" hidden="1"/>
+    <row r="86" hidden="1"/>
+    <row r="87" hidden="1"/>
+    <row r="88" hidden="1"/>
+    <row r="89" hidden="1"/>
+    <row r="90" hidden="1"/>
+    <row r="91" hidden="1"/>
+    <row r="92" hidden="1"/>
+    <row r="93" hidden="1"/>
+    <row r="94" hidden="1"/>
+    <row r="95" hidden="1"/>
+    <row r="96" hidden="1"/>
+    <row r="97" hidden="1"/>
+    <row r="98" hidden="1"/>
+    <row r="99" hidden="1"/>
+    <row r="100" hidden="1"/>
+    <row r="101" hidden="1"/>
+    <row r="102" hidden="1"/>
+    <row r="103" hidden="1"/>
+    <row r="104" hidden="1"/>
+    <row r="105" hidden="1"/>
+    <row r="106" hidden="1"/>
+    <row r="107" hidden="1"/>
+    <row r="108" hidden="1"/>
+    <row r="109" hidden="1"/>
+    <row r="110" hidden="1"/>
+    <row r="111" hidden="1"/>
+    <row r="112" hidden="1"/>
+    <row r="113" hidden="1"/>
+    <row r="114" hidden="1"/>
+    <row r="115" hidden="1"/>
+    <row r="116" hidden="1"/>
+    <row r="117" hidden="1"/>
+    <row r="118" hidden="1"/>
+    <row r="119" hidden="1"/>
+    <row r="120" hidden="1"/>
+    <row r="121" hidden="1"/>
+    <row r="122" hidden="1"/>
+    <row r="123" hidden="1"/>
+    <row r="124" hidden="1"/>
+    <row r="125" hidden="1"/>
+    <row r="126" hidden="1"/>
+    <row r="127" hidden="1"/>
+    <row r="128" hidden="1"/>
+    <row r="129" hidden="1"/>
+    <row r="130" hidden="1"/>
+    <row r="131" hidden="1"/>
+    <row r="132" hidden="1"/>
+    <row r="133" hidden="1"/>
+    <row r="134" hidden="1"/>
+    <row r="135" hidden="1"/>
+    <row r="136" hidden="1"/>
+    <row r="137" hidden="1"/>
+    <row r="138" hidden="1"/>
+    <row r="139" hidden="1"/>
+    <row r="140" hidden="1"/>
+    <row r="141" hidden="1"/>
+    <row r="142" hidden="1"/>
+    <row r="143" hidden="1"/>
+    <row r="144" hidden="1"/>
+    <row r="145" hidden="1"/>
+    <row r="146" hidden="1"/>
+    <row r="147" hidden="1"/>
+    <row r="148" hidden="1"/>
+    <row r="149" hidden="1"/>
+    <row r="150" hidden="1"/>
+    <row r="151" hidden="1"/>
+    <row r="152" hidden="1"/>
+    <row r="153" hidden="1"/>
+    <row r="154" hidden="1"/>
+    <row r="155" hidden="1"/>
+    <row r="156" hidden="1"/>
+    <row r="157" hidden="1"/>
+    <row r="158" hidden="1"/>
+    <row r="159" hidden="1"/>
+    <row r="160" hidden="1"/>
+    <row r="161" hidden="1"/>
+    <row r="162" hidden="1"/>
+    <row r="163" hidden="1"/>
+    <row r="164" hidden="1"/>
+    <row r="165" hidden="1"/>
+    <row r="166" hidden="1"/>
+    <row r="167" hidden="1"/>
+    <row r="168" hidden="1"/>
+    <row r="169" hidden="1"/>
+    <row r="170" hidden="1"/>
+    <row r="171" hidden="1"/>
+    <row r="172" hidden="1"/>
+    <row r="173" hidden="1"/>
+    <row r="174" hidden="1"/>
+    <row r="175" hidden="1"/>
+    <row r="176" hidden="1"/>
+    <row r="177" hidden="1"/>
+    <row r="178" hidden="1"/>
+    <row r="179" hidden="1"/>
+    <row r="180" hidden="1"/>
+    <row r="181" hidden="1"/>
+    <row r="182" hidden="1"/>
+    <row r="183" hidden="1"/>
+    <row r="184" hidden="1"/>
+    <row r="185" hidden="1"/>
+    <row r="186" hidden="1"/>
+    <row r="187" hidden="1"/>
+    <row r="188" hidden="1"/>
+    <row r="189" hidden="1"/>
+    <row r="190" hidden="1"/>
+    <row r="191" hidden="1"/>
+    <row r="192" hidden="1"/>
+    <row r="193" hidden="1"/>
+    <row r="194" hidden="1"/>
+    <row r="195" hidden="1"/>
+    <row r="196" hidden="1"/>
+    <row r="197" hidden="1"/>
+    <row r="198" hidden="1"/>
+    <row r="199" hidden="1"/>
+    <row r="200" hidden="1"/>
+  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
+  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
+  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:AN15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="15" customHeight="1">
+      <c r="A1" s="799" t="n"/>
+      <c r="B1" s="800" t="n"/>
+      <c r="C1" s="800" t="n"/>
+      <c r="D1" s="800" t="n"/>
+      <c r="E1" s="800" t="n"/>
+      <c r="F1" s="800" t="n"/>
+      <c r="G1" s="800" t="n"/>
+      <c r="H1" s="801" t="n"/>
+      <c r="I1" s="802" t="inlineStr">
+        <is>
+          <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
+        </is>
+      </c>
+      <c r="J1" s="800" t="n"/>
+      <c r="K1" s="800" t="n"/>
+      <c r="L1" s="800" t="n"/>
+      <c r="M1" s="800" t="n"/>
+      <c r="N1" s="800" t="n"/>
+      <c r="O1" s="800" t="n"/>
+      <c r="P1" s="800" t="n"/>
+      <c r="Q1" s="800" t="n"/>
+      <c r="R1" s="800" t="n"/>
+      <c r="S1" s="800" t="n"/>
+      <c r="T1" s="800" t="n"/>
+      <c r="U1" s="800" t="n"/>
+      <c r="V1" s="800" t="n"/>
+      <c r="W1" s="800" t="n"/>
+      <c r="X1" s="800" t="n"/>
+      <c r="Y1" s="800" t="n"/>
+      <c r="Z1" s="800" t="n"/>
+      <c r="AA1" s="800" t="n"/>
+      <c r="AB1" s="800" t="n"/>
+      <c r="AC1" s="800" t="n"/>
+      <c r="AD1" s="801" t="n"/>
+      <c r="AE1" s="507" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="800" t="n"/>
+      <c r="AG1" s="800" t="n"/>
+      <c r="AH1" s="803" t="n"/>
+      <c r="AI1" s="510" t="inlineStr">
+        <is>
+          <t>FRM-306</t>
+        </is>
+      </c>
+      <c r="AJ1" s="800" t="n"/>
+      <c r="AK1" s="800" t="n"/>
+      <c r="AL1" s="800" t="n"/>
+      <c r="AM1" s="800" t="n"/>
+      <c r="AN1" s="801" t="n"/>
+    </row>
+    <row r="2" ht="15" customHeight="1">
+      <c r="A2" s="804" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="805" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="805" t="n"/>
+      <c r="AE2" s="806" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="807" t="n"/>
+      <c r="AI2" s="808" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="805" t="n"/>
+    </row>
+    <row r="3" ht="15" customHeight="1">
+      <c r="A3" s="804" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="805" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="805" t="n"/>
+      <c r="AE3" s="806" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="807" t="n"/>
+      <c r="AI3" s="808" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="805" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1">
+      <c r="A4" s="804" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="805" t="n"/>
+      <c r="I4" s="809" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="805" t="n"/>
+      <c r="AE4" s="806" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="807" t="n"/>
+      <c r="AI4" s="808" t="inlineStr">
+        <is>
+          <t>Engineering / QA / Planning</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="805" t="n"/>
+    </row>
+    <row r="5" ht="15" customHeight="1">
+      <c r="A5" s="810" t="n"/>
+      <c r="B5" s="811" t="n"/>
+      <c r="C5" s="811" t="n"/>
+      <c r="D5" s="811" t="n"/>
+      <c r="E5" s="811" t="n"/>
+      <c r="F5" s="811" t="n"/>
+      <c r="G5" s="811" t="n"/>
+      <c r="H5" s="812" t="n"/>
+      <c r="I5" s="813" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="811" t="n"/>
+      <c r="K5" s="811" t="n"/>
+      <c r="L5" s="811" t="n"/>
+      <c r="M5" s="811" t="n"/>
+      <c r="N5" s="811" t="n"/>
+      <c r="O5" s="811" t="n"/>
+      <c r="P5" s="811" t="n"/>
+      <c r="Q5" s="811" t="n"/>
+      <c r="R5" s="811" t="n"/>
+      <c r="S5" s="811" t="n"/>
+      <c r="T5" s="811" t="n"/>
+      <c r="U5" s="811" t="n"/>
+      <c r="V5" s="811" t="n"/>
+      <c r="W5" s="811" t="n"/>
+      <c r="X5" s="811" t="n"/>
+      <c r="Y5" s="811" t="n"/>
+      <c r="Z5" s="811" t="n"/>
+      <c r="AA5" s="811" t="n"/>
+      <c r="AB5" s="811" t="n"/>
+      <c r="AC5" s="811" t="n"/>
+      <c r="AD5" s="812" t="n"/>
+      <c r="AE5" s="814" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="811" t="n"/>
+      <c r="AG5" s="811" t="n"/>
+      <c r="AH5" s="815" t="n"/>
+      <c r="AI5" s="816" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="811" t="n"/>
+      <c r="AK5" s="811" t="n"/>
+      <c r="AL5" s="811" t="n"/>
+      <c r="AM5" s="811" t="n"/>
+      <c r="AN5" s="812" t="n"/>
+    </row>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="817" t="n"/>
+      <c r="B6" s="817" t="n"/>
+      <c r="C6" s="817" t="n"/>
+      <c r="D6" s="817" t="n"/>
+      <c r="E6" s="817" t="n"/>
+      <c r="F6" s="817" t="n"/>
+      <c r="G6" s="817" t="n"/>
+      <c r="H6" s="817" t="n"/>
+      <c r="I6" s="817" t="n"/>
+      <c r="J6" s="817" t="n"/>
+      <c r="K6" s="817" t="n"/>
+      <c r="L6" s="817" t="n"/>
+      <c r="M6" s="817" t="n"/>
+      <c r="N6" s="817" t="n"/>
+      <c r="O6" s="817" t="n"/>
+      <c r="P6" s="817" t="n"/>
+      <c r="Q6" s="817" t="n"/>
+      <c r="R6" s="817" t="n"/>
+      <c r="S6" s="817" t="n"/>
+      <c r="T6" s="817" t="n"/>
+      <c r="U6" s="817" t="n"/>
+      <c r="V6" s="817" t="n"/>
+      <c r="W6" s="817" t="n"/>
+      <c r="X6" s="817" t="n"/>
+      <c r="Y6" s="817" t="n"/>
+      <c r="Z6" s="817" t="n"/>
+      <c r="AA6" s="817" t="n"/>
+      <c r="AB6" s="817" t="n"/>
+      <c r="AC6" s="817" t="n"/>
+      <c r="AD6" s="817" t="n"/>
+      <c r="AE6" s="817" t="n"/>
+      <c r="AF6" s="817" t="n"/>
+      <c r="AG6" s="817" t="n"/>
+      <c r="AH6" s="817" t="n"/>
+      <c r="AI6" s="817" t="n"/>
+      <c r="AJ6" s="817" t="n"/>
+      <c r="AK6" s="817" t="n"/>
+      <c r="AL6" s="817" t="n"/>
+      <c r="AM6" s="817" t="n"/>
+      <c r="AN6" s="817" t="n"/>
+    </row>
+    <row r="7" hidden="1">
+      <c r="A7" s="588" t="inlineStr">
+        <is>
+          <t>REF_PART_REV_MASTER</t>
+        </is>
+      </c>
+      <c r="B7" s="543" t="inlineStr">
+        <is>
+          <t>REF_JOB_WO_MASTER</t>
+        </is>
+      </c>
+      <c r="C7" s="543" t="inlineStr">
+        <is>
+          <t>REF_OWNER_PERSON_MASTER</t>
+        </is>
+      </c>
+      <c r="D7" s="543" t="inlineStr">
+        <is>
+          <t>REF_DOCUMENT_CODE_MASTER</t>
+        </is>
+      </c>
+      <c r="E7" s="818" t="n"/>
+      <c r="F7" s="818" t="n"/>
+      <c r="G7" s="818" t="n"/>
+      <c r="H7" s="818" t="n"/>
+      <c r="I7" s="818" t="n"/>
+      <c r="J7" s="818" t="n"/>
+      <c r="K7" s="818" t="n"/>
+      <c r="L7" s="818" t="n"/>
+      <c r="M7" s="818" t="n"/>
+      <c r="N7" s="818" t="n"/>
+      <c r="O7" s="818" t="n"/>
+      <c r="P7" s="818" t="n"/>
+      <c r="Q7" s="818" t="n"/>
+      <c r="R7" s="818" t="n"/>
+      <c r="S7" s="818" t="n"/>
+      <c r="T7" s="818" t="n"/>
+      <c r="U7" s="818" t="n"/>
+      <c r="V7" s="818" t="n"/>
+      <c r="W7" s="818" t="n"/>
+      <c r="X7" s="818" t="n"/>
+      <c r="Y7" s="818" t="n"/>
+      <c r="Z7" s="818" t="n"/>
+      <c r="AA7" s="818" t="n"/>
+      <c r="AB7" s="818" t="n"/>
+      <c r="AC7" s="818" t="n"/>
+      <c r="AD7" s="818" t="n"/>
+      <c r="AE7" s="818" t="n"/>
+      <c r="AF7" s="818" t="n"/>
+      <c r="AG7" s="818" t="n"/>
+      <c r="AH7" s="818" t="n"/>
+      <c r="AI7" s="818" t="n"/>
+      <c r="AJ7" s="818" t="n"/>
+      <c r="AK7" s="818" t="n"/>
+      <c r="AL7" s="818" t="n"/>
+      <c r="AM7" s="818" t="n"/>
+      <c r="AN7" s="818" t="n"/>
+    </row>
+    <row r="8" hidden="1">
+      <c r="A8" s="584" t="inlineStr">
+        <is>
+          <t>PN-1001 / Rev.A</t>
+        </is>
+      </c>
+      <c r="B8" s="402" t="inlineStr">
+        <is>
+          <t>JOB-240001</t>
+        </is>
+      </c>
+      <c r="C8" s="402" t="inlineStr">
+        <is>
+          <t>Planning Lead</t>
+        </is>
+      </c>
+      <c r="D8" s="402" t="inlineStr">
+        <is>
+          <t>FRM-202</t>
+        </is>
+      </c>
+      <c r="E8" s="818" t="n"/>
+      <c r="F8" s="818" t="n"/>
+      <c r="G8" s="818" t="n"/>
+      <c r="H8" s="818" t="n"/>
+      <c r="I8" s="818" t="n"/>
+      <c r="J8" s="818" t="n"/>
+      <c r="K8" s="818" t="n"/>
+      <c r="L8" s="818" t="n"/>
+      <c r="M8" s="818" t="n"/>
+      <c r="N8" s="818" t="n"/>
+      <c r="O8" s="818" t="n"/>
+      <c r="P8" s="818" t="n"/>
+      <c r="Q8" s="818" t="n"/>
+      <c r="R8" s="818" t="n"/>
+      <c r="S8" s="818" t="n"/>
+      <c r="T8" s="818" t="n"/>
+      <c r="U8" s="818" t="n"/>
+      <c r="V8" s="818" t="n"/>
+      <c r="W8" s="818" t="n"/>
+      <c r="X8" s="818" t="n"/>
+      <c r="Y8" s="818" t="n"/>
+      <c r="Z8" s="818" t="n"/>
+      <c r="AA8" s="818" t="n"/>
+      <c r="AB8" s="818" t="n"/>
+      <c r="AC8" s="818" t="n"/>
+      <c r="AD8" s="818" t="n"/>
+      <c r="AE8" s="818" t="n"/>
+      <c r="AF8" s="818" t="n"/>
+      <c r="AG8" s="818" t="n"/>
+      <c r="AH8" s="818" t="n"/>
+      <c r="AI8" s="818" t="n"/>
+      <c r="AJ8" s="818" t="n"/>
+      <c r="AK8" s="818" t="n"/>
+      <c r="AL8" s="818" t="n"/>
+      <c r="AM8" s="818" t="n"/>
+      <c r="AN8" s="818" t="n"/>
+    </row>
+    <row r="9" hidden="1">
+      <c r="A9" s="584" t="inlineStr">
+        <is>
+          <t>PN-1002 / Rev.B</t>
+        </is>
+      </c>
+      <c r="B9" s="402" t="inlineStr">
+        <is>
+          <t>JOB-240002</t>
+        </is>
+      </c>
+      <c r="C9" s="402" t="inlineStr">
+        <is>
+          <t>Production Supervisor</t>
+        </is>
+      </c>
+      <c r="D9" s="402" t="inlineStr">
+        <is>
+          <t>FRM-302</t>
+        </is>
+      </c>
+      <c r="E9" s="818" t="n"/>
+      <c r="F9" s="818" t="n"/>
+      <c r="G9" s="818" t="n"/>
+      <c r="H9" s="818" t="n"/>
+      <c r="I9" s="818" t="n"/>
+      <c r="J9" s="818" t="n"/>
+      <c r="K9" s="818" t="n"/>
+      <c r="L9" s="818" t="n"/>
+      <c r="M9" s="818" t="n"/>
+      <c r="N9" s="818" t="n"/>
+      <c r="O9" s="818" t="n"/>
+      <c r="P9" s="818" t="n"/>
+      <c r="Q9" s="818" t="n"/>
+      <c r="R9" s="818" t="n"/>
+      <c r="S9" s="818" t="n"/>
+      <c r="T9" s="818" t="n"/>
+      <c r="U9" s="818" t="n"/>
+      <c r="V9" s="818" t="n"/>
+      <c r="W9" s="818" t="n"/>
+      <c r="X9" s="818" t="n"/>
+      <c r="Y9" s="818" t="n"/>
+      <c r="Z9" s="818" t="n"/>
+      <c r="AA9" s="818" t="n"/>
+      <c r="AB9" s="818" t="n"/>
+      <c r="AC9" s="818" t="n"/>
+      <c r="AD9" s="818" t="n"/>
+      <c r="AE9" s="818" t="n"/>
+      <c r="AF9" s="818" t="n"/>
+      <c r="AG9" s="818" t="n"/>
+      <c r="AH9" s="818" t="n"/>
+      <c r="AI9" s="818" t="n"/>
+      <c r="AJ9" s="818" t="n"/>
+      <c r="AK9" s="818" t="n"/>
+      <c r="AL9" s="818" t="n"/>
+      <c r="AM9" s="818" t="n"/>
+      <c r="AN9" s="818" t="n"/>
+    </row>
+    <row r="10" hidden="1">
+      <c r="A10" s="584" t="inlineStr">
+        <is>
+          <t>PN-1003 / Rev.C</t>
+        </is>
+      </c>
+      <c r="B10" s="402" t="inlineStr">
+        <is>
+          <t>JOB-240003</t>
+        </is>
+      </c>
+      <c r="C10" s="402" t="inlineStr">
+        <is>
+          <t>QA Engineer</t>
+        </is>
+      </c>
+      <c r="D10" s="402" t="inlineStr">
+        <is>
+          <t>FRM-306</t>
+        </is>
+      </c>
+      <c r="E10" s="818" t="n"/>
+      <c r="F10" s="818" t="n"/>
+      <c r="G10" s="818" t="n"/>
+      <c r="H10" s="818" t="n"/>
+      <c r="I10" s="818" t="n"/>
+      <c r="J10" s="818" t="n"/>
+      <c r="K10" s="818" t="n"/>
+      <c r="L10" s="818" t="n"/>
+      <c r="M10" s="818" t="n"/>
+      <c r="N10" s="818" t="n"/>
+      <c r="O10" s="818" t="n"/>
+      <c r="P10" s="818" t="n"/>
+      <c r="Q10" s="818" t="n"/>
+      <c r="R10" s="818" t="n"/>
+      <c r="S10" s="818" t="n"/>
+      <c r="T10" s="818" t="n"/>
+      <c r="U10" s="818" t="n"/>
+      <c r="V10" s="818" t="n"/>
+      <c r="W10" s="818" t="n"/>
+      <c r="X10" s="818" t="n"/>
+      <c r="Y10" s="818" t="n"/>
+      <c r="Z10" s="818" t="n"/>
+      <c r="AA10" s="818" t="n"/>
+      <c r="AB10" s="818" t="n"/>
+      <c r="AC10" s="818" t="n"/>
+      <c r="AD10" s="818" t="n"/>
+      <c r="AE10" s="818" t="n"/>
+      <c r="AF10" s="818" t="n"/>
+      <c r="AG10" s="818" t="n"/>
+      <c r="AH10" s="818" t="n"/>
+      <c r="AI10" s="818" t="n"/>
+      <c r="AJ10" s="818" t="n"/>
+      <c r="AK10" s="818" t="n"/>
+      <c r="AL10" s="818" t="n"/>
+      <c r="AM10" s="818" t="n"/>
+      <c r="AN10" s="818" t="n"/>
+    </row>
+    <row r="11" hidden="1">
+      <c r="A11" s="818" t="n"/>
+      <c r="B11" s="818" t="n"/>
+      <c r="C11" s="402" t="inlineStr">
+        <is>
+          <t>Engineering Lead</t>
+        </is>
+      </c>
+      <c r="D11" s="402" t="inlineStr">
+        <is>
+          <t>FRM-511</t>
+        </is>
+      </c>
+      <c r="E11" s="818" t="n"/>
+      <c r="F11" s="818" t="n"/>
+      <c r="G11" s="818" t="n"/>
+      <c r="H11" s="818" t="n"/>
+      <c r="I11" s="818" t="n"/>
+      <c r="J11" s="818" t="n"/>
+      <c r="K11" s="818" t="n"/>
+      <c r="L11" s="818" t="n"/>
+      <c r="M11" s="818" t="n"/>
+      <c r="N11" s="818" t="n"/>
+      <c r="O11" s="818" t="n"/>
+      <c r="P11" s="818" t="n"/>
+      <c r="Q11" s="818" t="n"/>
+      <c r="R11" s="818" t="n"/>
+      <c r="S11" s="818" t="n"/>
+      <c r="T11" s="818" t="n"/>
+      <c r="U11" s="818" t="n"/>
+      <c r="V11" s="818" t="n"/>
+      <c r="W11" s="818" t="n"/>
+      <c r="X11" s="818" t="n"/>
+      <c r="Y11" s="818" t="n"/>
+      <c r="Z11" s="818" t="n"/>
+      <c r="AA11" s="818" t="n"/>
+      <c r="AB11" s="818" t="n"/>
+      <c r="AC11" s="818" t="n"/>
+      <c r="AD11" s="818" t="n"/>
+      <c r="AE11" s="818" t="n"/>
+      <c r="AF11" s="818" t="n"/>
+      <c r="AG11" s="818" t="n"/>
+      <c r="AH11" s="818" t="n"/>
+      <c r="AI11" s="818" t="n"/>
+      <c r="AJ11" s="818" t="n"/>
+      <c r="AK11" s="818" t="n"/>
+      <c r="AL11" s="818" t="n"/>
+      <c r="AM11" s="818" t="n"/>
+      <c r="AN11" s="818" t="n"/>
+    </row>
+    <row r="12" hidden="1">
+      <c r="A12" s="818" t="n"/>
+      <c r="B12" s="818" t="n"/>
+      <c r="C12" s="552" t="inlineStr">
+        <is>
+          <t>Setup Technician</t>
+        </is>
+      </c>
+      <c r="D12" s="552" t="inlineStr">
+        <is>
+          <t>FRM-519</t>
+        </is>
+      </c>
+      <c r="E12" s="818" t="n"/>
+      <c r="F12" s="818" t="n"/>
+      <c r="G12" s="818" t="n"/>
+      <c r="H12" s="818" t="n"/>
+      <c r="I12" s="818" t="n"/>
+      <c r="J12" s="818" t="n"/>
+      <c r="K12" s="818" t="n"/>
+      <c r="L12" s="818" t="n"/>
+      <c r="M12" s="818" t="n"/>
+      <c r="N12" s="818" t="n"/>
+      <c r="O12" s="818" t="n"/>
+      <c r="P12" s="818" t="n"/>
+      <c r="Q12" s="818" t="n"/>
+      <c r="R12" s="818" t="n"/>
+      <c r="S12" s="818" t="n"/>
+      <c r="T12" s="818" t="n"/>
+      <c r="U12" s="818" t="n"/>
+      <c r="V12" s="818" t="n"/>
+      <c r="W12" s="818" t="n"/>
+      <c r="X12" s="818" t="n"/>
+      <c r="Y12" s="818" t="n"/>
+      <c r="Z12" s="818" t="n"/>
+      <c r="AA12" s="818" t="n"/>
+      <c r="AB12" s="818" t="n"/>
+      <c r="AC12" s="818" t="n"/>
+      <c r="AD12" s="818" t="n"/>
+      <c r="AE12" s="818" t="n"/>
+      <c r="AF12" s="818" t="n"/>
+      <c r="AG12" s="818" t="n"/>
+      <c r="AH12" s="818" t="n"/>
+      <c r="AI12" s="818" t="n"/>
+      <c r="AJ12" s="818" t="n"/>
+      <c r="AK12" s="818" t="n"/>
+      <c r="AL12" s="818" t="n"/>
+      <c r="AM12" s="818" t="n"/>
+      <c r="AN12" s="818" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="818" t="n"/>
+      <c r="B13" s="818" t="n"/>
+      <c r="C13" s="818" t="n"/>
+      <c r="D13" s="818" t="n"/>
+      <c r="E13" s="818" t="n"/>
+      <c r="F13" s="818" t="n"/>
+      <c r="G13" s="818" t="n"/>
+      <c r="H13" s="818" t="n"/>
+      <c r="I13" s="818" t="n"/>
+      <c r="J13" s="818" t="n"/>
+      <c r="K13" s="818" t="n"/>
+      <c r="L13" s="818" t="n"/>
+      <c r="M13" s="818" t="n"/>
+      <c r="N13" s="818" t="n"/>
+      <c r="O13" s="818" t="n"/>
+      <c r="P13" s="818" t="n"/>
+      <c r="Q13" s="818" t="n"/>
+      <c r="R13" s="818" t="n"/>
+      <c r="S13" s="818" t="n"/>
+      <c r="T13" s="818" t="n"/>
+      <c r="U13" s="818" t="n"/>
+      <c r="V13" s="818" t="n"/>
+      <c r="W13" s="818" t="n"/>
+      <c r="X13" s="818" t="n"/>
+      <c r="Y13" s="818" t="n"/>
+      <c r="Z13" s="818" t="n"/>
+      <c r="AA13" s="818" t="n"/>
+      <c r="AB13" s="818" t="n"/>
+      <c r="AC13" s="818" t="n"/>
+      <c r="AD13" s="818" t="n"/>
+      <c r="AE13" s="818" t="n"/>
+      <c r="AF13" s="818" t="n"/>
+      <c r="AG13" s="818" t="n"/>
+      <c r="AH13" s="818" t="n"/>
+      <c r="AI13" s="818" t="n"/>
+      <c r="AJ13" s="818" t="n"/>
+      <c r="AK13" s="818" t="n"/>
+      <c r="AL13" s="818" t="n"/>
+      <c r="AM13" s="818" t="n"/>
+      <c r="AN13" s="818" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="818" t="n"/>
+      <c r="B14" s="818" t="n"/>
+      <c r="C14" s="818" t="n"/>
+      <c r="D14" s="818" t="n"/>
+      <c r="E14" s="818" t="n"/>
+      <c r="F14" s="818" t="n"/>
+      <c r="G14" s="818" t="n"/>
+      <c r="H14" s="818" t="n"/>
+      <c r="I14" s="818" t="n"/>
+      <c r="J14" s="818" t="n"/>
+      <c r="K14" s="818" t="n"/>
+      <c r="L14" s="818" t="n"/>
+      <c r="M14" s="818" t="n"/>
+      <c r="N14" s="818" t="n"/>
+      <c r="O14" s="818" t="n"/>
+      <c r="P14" s="818" t="n"/>
+      <c r="Q14" s="818" t="n"/>
+      <c r="R14" s="818" t="n"/>
+      <c r="S14" s="818" t="n"/>
+      <c r="T14" s="818" t="n"/>
+      <c r="U14" s="818" t="n"/>
+      <c r="V14" s="818" t="n"/>
+      <c r="W14" s="818" t="n"/>
+      <c r="X14" s="818" t="n"/>
+      <c r="Y14" s="818" t="n"/>
+      <c r="Z14" s="818" t="n"/>
+      <c r="AA14" s="818" t="n"/>
+      <c r="AB14" s="818" t="n"/>
+      <c r="AC14" s="818" t="n"/>
+      <c r="AD14" s="818" t="n"/>
+      <c r="AE14" s="818" t="n"/>
+      <c r="AF14" s="818" t="n"/>
+      <c r="AG14" s="818" t="n"/>
+      <c r="AH14" s="818" t="n"/>
+      <c r="AI14" s="818" t="n"/>
+      <c r="AJ14" s="818" t="n"/>
+      <c r="AK14" s="818" t="n"/>
+      <c r="AL14" s="818" t="n"/>
+      <c r="AM14" s="818" t="n"/>
+      <c r="AN14" s="818" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="818" t="n"/>
+      <c r="B15" s="818" t="n"/>
+      <c r="C15" s="818" t="n"/>
+      <c r="D15" s="818" t="n"/>
+      <c r="E15" s="818" t="n"/>
+      <c r="F15" s="818" t="n"/>
+      <c r="G15" s="818" t="n"/>
+      <c r="H15" s="818" t="n"/>
+      <c r="I15" s="818" t="n"/>
+      <c r="J15" s="818" t="n"/>
+      <c r="K15" s="818" t="n"/>
+      <c r="L15" s="818" t="n"/>
+      <c r="M15" s="818" t="n"/>
+      <c r="N15" s="818" t="n"/>
+      <c r="O15" s="818" t="n"/>
+      <c r="P15" s="818" t="n"/>
+      <c r="Q15" s="818" t="n"/>
+      <c r="R15" s="818" t="n"/>
+      <c r="S15" s="818" t="n"/>
+      <c r="T15" s="818" t="n"/>
+      <c r="U15" s="818" t="n"/>
+      <c r="V15" s="818" t="n"/>
+      <c r="W15" s="818" t="n"/>
+      <c r="X15" s="818" t="n"/>
+      <c r="Y15" s="818" t="n"/>
+      <c r="Z15" s="818" t="n"/>
+      <c r="AA15" s="818" t="n"/>
+      <c r="AB15" s="818" t="n"/>
+      <c r="AC15" s="818" t="n"/>
+      <c r="AD15" s="818" t="n"/>
+      <c r="AE15" s="818" t="n"/>
+      <c r="AF15" s="818" t="n"/>
+      <c r="AG15" s="818" t="n"/>
+      <c r="AH15" s="818" t="n"/>
+      <c r="AI15" s="818" t="n"/>
+      <c r="AJ15" s="818" t="n"/>
+      <c r="AK15" s="818" t="n"/>
+      <c r="AL15" s="818" t="n"/>
+      <c r="AM15" s="818" t="n"/>
+      <c r="AN15" s="818" t="n"/>
+    </row>
     <row r="16" hidden="1"/>
     <row r="17" hidden="1"/>
     <row r="18" hidden="1"/>
@@ -12096,589 +13099,22 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
-  <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:AN6"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="2.33" customWidth="1" min="1" max="1"/>
-    <col width="2.33" customWidth="1" min="2" max="2"/>
-    <col width="2.33" customWidth="1" min="3" max="3"/>
-    <col width="2.33" customWidth="1" min="4" max="4"/>
-    <col hidden="1" width="2.33" customWidth="1" min="5" max="16384"/>
-    <col width="2.33" customWidth="1" min="6" max="6"/>
-    <col width="2.33" customWidth="1" min="7" max="7"/>
-    <col width="2.33" customWidth="1" min="8" max="8"/>
-    <col width="2.33" customWidth="1" min="9" max="9"/>
-    <col width="2.33" customWidth="1" min="10" max="10"/>
-    <col width="2.33" customWidth="1" min="11" max="11"/>
-    <col width="2.33" customWidth="1" min="12" max="12"/>
-    <col width="2.33" customWidth="1" min="13" max="13"/>
-    <col width="2.33" customWidth="1" min="14" max="14"/>
-    <col width="2.33" customWidth="1" min="15" max="15"/>
-    <col width="2.33" customWidth="1" min="16" max="16"/>
-    <col width="2.33" customWidth="1" min="17" max="17"/>
-    <col width="2.33" customWidth="1" min="18" max="18"/>
-    <col width="2.33" customWidth="1" min="19" max="19"/>
-    <col width="2.33" customWidth="1" min="20" max="20"/>
-    <col width="2.33" customWidth="1" min="21" max="21"/>
-    <col width="2.33" customWidth="1" min="22" max="22"/>
-    <col width="2.33" customWidth="1" min="23" max="23"/>
-    <col width="2.33" customWidth="1" min="24" max="24"/>
-    <col width="2.33" customWidth="1" min="25" max="25"/>
-    <col width="2.33" customWidth="1" min="26" max="26"/>
-    <col width="2.33" customWidth="1" min="27" max="27"/>
-    <col width="2.33" customWidth="1" min="28" max="28"/>
-    <col width="2.33" customWidth="1" min="29" max="29"/>
-    <col width="2.33" customWidth="1" min="30" max="30"/>
-    <col width="2.33" customWidth="1" min="31" max="31"/>
-    <col width="2.33" customWidth="1" min="32" max="32"/>
-    <col width="2.33" customWidth="1" min="33" max="33"/>
-    <col width="2.33" customWidth="1" min="34" max="34"/>
-    <col width="2.33" customWidth="1" min="35" max="35"/>
-    <col width="2.33" customWidth="1" min="36" max="36"/>
-    <col width="2.33" customWidth="1" min="37" max="37"/>
-    <col width="2.33" customWidth="1" min="38" max="38"/>
-    <col width="2.33" customWidth="1" min="39" max="39"/>
-    <col width="2.33" customWidth="1" min="40" max="40"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" s="588" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="B1" s="543" t="inlineStr">
-        <is>
-          <t>REF_JOB_WO_MASTER</t>
-        </is>
-      </c>
-      <c r="C1" s="543" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="D1" s="543" t="inlineStr">
-        <is>
-          <t>REF_DOCUMENT_CODE_MASTER</t>
-        </is>
-      </c>
-      <c r="E1" s="543" t="n"/>
-      <c r="F1" s="543" t="n"/>
-      <c r="G1" s="543" t="n"/>
-      <c r="H1" s="543" t="n"/>
-      <c r="I1" s="543" t="n"/>
-      <c r="J1" s="543" t="n"/>
-      <c r="K1" s="543" t="n"/>
-      <c r="L1" s="543" t="n"/>
-      <c r="M1" s="543" t="n"/>
-      <c r="N1" s="543" t="n"/>
-      <c r="O1" s="543" t="n"/>
-      <c r="P1" s="543" t="n"/>
-      <c r="Q1" s="543" t="n"/>
-      <c r="R1" s="543" t="n"/>
-      <c r="S1" s="543" t="n"/>
-      <c r="T1" s="543" t="n"/>
-      <c r="U1" s="543" t="n"/>
-      <c r="V1" s="543" t="n"/>
-      <c r="W1" s="543" t="n"/>
-      <c r="X1" s="543" t="n"/>
-      <c r="Y1" s="543" t="n"/>
-      <c r="Z1" s="543" t="n"/>
-      <c r="AA1" s="543" t="n"/>
-      <c r="AB1" s="543" t="n"/>
-      <c r="AC1" s="543" t="n"/>
-      <c r="AD1" s="543" t="n"/>
-      <c r="AE1" s="543" t="n"/>
-      <c r="AF1" s="543" t="n"/>
-      <c r="AG1" s="543" t="n"/>
-      <c r="AH1" s="543" t="n"/>
-      <c r="AI1" s="543" t="n"/>
-      <c r="AJ1" s="543" t="n"/>
-      <c r="AK1" s="543" t="n"/>
-      <c r="AL1" s="543" t="n"/>
-      <c r="AM1" s="543" t="n"/>
-      <c r="AN1" s="546" t="n"/>
-    </row>
-    <row r="2">
-      <c r="A2" s="584" t="inlineStr">
-        <is>
-          <t>PN-1001 / Rev.A</t>
-        </is>
-      </c>
-      <c r="B2" s="402" t="inlineStr">
-        <is>
-          <t>JOB-240001</t>
-        </is>
-      </c>
-      <c r="C2" s="402" t="inlineStr">
-        <is>
-          <t>Planning Lead</t>
-        </is>
-      </c>
-      <c r="D2" s="402" t="inlineStr">
-        <is>
-          <t>FRM-202</t>
-        </is>
-      </c>
-      <c r="E2" s="402" t="n"/>
-      <c r="F2" s="402" t="n"/>
-      <c r="G2" s="402" t="n"/>
-      <c r="H2" s="402" t="n"/>
-      <c r="I2" s="402" t="n"/>
-      <c r="J2" s="402" t="n"/>
-      <c r="K2" s="402" t="n"/>
-      <c r="L2" s="402" t="n"/>
-      <c r="M2" s="402" t="n"/>
-      <c r="N2" s="402" t="n"/>
-      <c r="O2" s="402" t="n"/>
-      <c r="P2" s="402" t="n"/>
-      <c r="Q2" s="402" t="n"/>
-      <c r="R2" s="402" t="n"/>
-      <c r="S2" s="402" t="n"/>
-      <c r="T2" s="402" t="n"/>
-      <c r="U2" s="402" t="n"/>
-      <c r="V2" s="402" t="n"/>
-      <c r="W2" s="402" t="n"/>
-      <c r="X2" s="402" t="n"/>
-      <c r="Y2" s="402" t="n"/>
-      <c r="Z2" s="402" t="n"/>
-      <c r="AA2" s="402" t="n"/>
-      <c r="AB2" s="402" t="n"/>
-      <c r="AC2" s="402" t="n"/>
-      <c r="AD2" s="402" t="n"/>
-      <c r="AE2" s="402" t="n"/>
-      <c r="AF2" s="402" t="n"/>
-      <c r="AG2" s="402" t="n"/>
-      <c r="AH2" s="402" t="n"/>
-      <c r="AI2" s="402" t="n"/>
-      <c r="AJ2" s="402" t="n"/>
-      <c r="AK2" s="402" t="n"/>
-      <c r="AL2" s="402" t="n"/>
-      <c r="AM2" s="402" t="n"/>
-      <c r="AN2" s="550" t="n"/>
-    </row>
-    <row r="3">
-      <c r="A3" s="584" t="inlineStr">
-        <is>
-          <t>PN-1002 / Rev.B</t>
-        </is>
-      </c>
-      <c r="B3" s="402" t="inlineStr">
-        <is>
-          <t>JOB-240002</t>
-        </is>
-      </c>
-      <c r="C3" s="402" t="inlineStr">
-        <is>
-          <t>Production Supervisor</t>
-        </is>
-      </c>
-      <c r="D3" s="402" t="inlineStr">
-        <is>
-          <t>FRM-302</t>
-        </is>
-      </c>
-      <c r="E3" s="402" t="n"/>
-      <c r="F3" s="402" t="n"/>
-      <c r="G3" s="402" t="n"/>
-      <c r="H3" s="402" t="n"/>
-      <c r="I3" s="402" t="n"/>
-      <c r="J3" s="402" t="n"/>
-      <c r="K3" s="402" t="n"/>
-      <c r="L3" s="402" t="n"/>
-      <c r="M3" s="402" t="n"/>
-      <c r="N3" s="402" t="n"/>
-      <c r="O3" s="402" t="n"/>
-      <c r="P3" s="402" t="n"/>
-      <c r="Q3" s="402" t="n"/>
-      <c r="R3" s="402" t="n"/>
-      <c r="S3" s="402" t="n"/>
-      <c r="T3" s="402" t="n"/>
-      <c r="U3" s="402" t="n"/>
-      <c r="V3" s="402" t="n"/>
-      <c r="W3" s="402" t="n"/>
-      <c r="X3" s="402" t="n"/>
-      <c r="Y3" s="402" t="n"/>
-      <c r="Z3" s="402" t="n"/>
-      <c r="AA3" s="402" t="n"/>
-      <c r="AB3" s="402" t="n"/>
-      <c r="AC3" s="402" t="n"/>
-      <c r="AD3" s="402" t="n"/>
-      <c r="AE3" s="402" t="n"/>
-      <c r="AF3" s="402" t="n"/>
-      <c r="AG3" s="402" t="n"/>
-      <c r="AH3" s="402" t="n"/>
-      <c r="AI3" s="402" t="n"/>
-      <c r="AJ3" s="402" t="n"/>
-      <c r="AK3" s="402" t="n"/>
-      <c r="AL3" s="402" t="n"/>
-      <c r="AM3" s="402" t="n"/>
-      <c r="AN3" s="550" t="n"/>
-    </row>
-    <row r="4">
-      <c r="A4" s="584" t="inlineStr">
-        <is>
-          <t>PN-1003 / Rev.C</t>
-        </is>
-      </c>
-      <c r="B4" s="402" t="inlineStr">
-        <is>
-          <t>JOB-240003</t>
-        </is>
-      </c>
-      <c r="C4" s="402" t="inlineStr">
-        <is>
-          <t>QA Engineer</t>
-        </is>
-      </c>
-      <c r="D4" s="402" t="inlineStr">
-        <is>
-          <t>FRM-306</t>
-        </is>
-      </c>
-      <c r="E4" s="402" t="n"/>
-      <c r="F4" s="402" t="n"/>
-      <c r="G4" s="402" t="n"/>
-      <c r="H4" s="402" t="n"/>
-      <c r="I4" s="402" t="n"/>
-      <c r="J4" s="402" t="n"/>
-      <c r="K4" s="402" t="n"/>
-      <c r="L4" s="402" t="n"/>
-      <c r="M4" s="402" t="n"/>
-      <c r="N4" s="402" t="n"/>
-      <c r="O4" s="402" t="n"/>
-      <c r="P4" s="402" t="n"/>
-      <c r="Q4" s="402" t="n"/>
-      <c r="R4" s="402" t="n"/>
-      <c r="S4" s="402" t="n"/>
-      <c r="T4" s="402" t="n"/>
-      <c r="U4" s="402" t="n"/>
-      <c r="V4" s="402" t="n"/>
-      <c r="W4" s="402" t="n"/>
-      <c r="X4" s="402" t="n"/>
-      <c r="Y4" s="402" t="n"/>
-      <c r="Z4" s="402" t="n"/>
-      <c r="AA4" s="402" t="n"/>
-      <c r="AB4" s="402" t="n"/>
-      <c r="AC4" s="402" t="n"/>
-      <c r="AD4" s="402" t="n"/>
-      <c r="AE4" s="402" t="n"/>
-      <c r="AF4" s="402" t="n"/>
-      <c r="AG4" s="402" t="n"/>
-      <c r="AH4" s="402" t="n"/>
-      <c r="AI4" s="402" t="n"/>
-      <c r="AJ4" s="402" t="n"/>
-      <c r="AK4" s="402" t="n"/>
-      <c r="AL4" s="402" t="n"/>
-      <c r="AM4" s="402" t="n"/>
-      <c r="AN4" s="550" t="n"/>
-    </row>
-    <row r="5">
-      <c r="A5" s="584" t="n"/>
-      <c r="B5" s="402" t="n"/>
-      <c r="C5" s="402" t="inlineStr">
-        <is>
-          <t>Engineering Lead</t>
-        </is>
-      </c>
-      <c r="D5" s="402" t="inlineStr">
-        <is>
-          <t>FRM-511</t>
-        </is>
-      </c>
-      <c r="E5" s="402" t="n"/>
-      <c r="F5" s="402" t="n"/>
-      <c r="G5" s="402" t="n"/>
-      <c r="H5" s="402" t="n"/>
-      <c r="I5" s="402" t="n"/>
-      <c r="J5" s="402" t="n"/>
-      <c r="K5" s="402" t="n"/>
-      <c r="L5" s="402" t="n"/>
-      <c r="M5" s="402" t="n"/>
-      <c r="N5" s="402" t="n"/>
-      <c r="O5" s="402" t="n"/>
-      <c r="P5" s="402" t="n"/>
-      <c r="Q5" s="402" t="n"/>
-      <c r="R5" s="402" t="n"/>
-      <c r="S5" s="402" t="n"/>
-      <c r="T5" s="402" t="n"/>
-      <c r="U5" s="402" t="n"/>
-      <c r="V5" s="402" t="n"/>
-      <c r="W5" s="402" t="n"/>
-      <c r="X5" s="402" t="n"/>
-      <c r="Y5" s="402" t="n"/>
-      <c r="Z5" s="402" t="n"/>
-      <c r="AA5" s="402" t="n"/>
-      <c r="AB5" s="402" t="n"/>
-      <c r="AC5" s="402" t="n"/>
-      <c r="AD5" s="402" t="n"/>
-      <c r="AE5" s="402" t="n"/>
-      <c r="AF5" s="402" t="n"/>
-      <c r="AG5" s="402" t="n"/>
-      <c r="AH5" s="402" t="n"/>
-      <c r="AI5" s="402" t="n"/>
-      <c r="AJ5" s="402" t="n"/>
-      <c r="AK5" s="402" t="n"/>
-      <c r="AL5" s="402" t="n"/>
-      <c r="AM5" s="402" t="n"/>
-      <c r="AN5" s="550" t="n"/>
-    </row>
-    <row r="6">
-      <c r="A6" s="586" t="n"/>
-      <c r="B6" s="552" t="n"/>
-      <c r="C6" s="552" t="inlineStr">
-        <is>
-          <t>Setup Technician</t>
-        </is>
-      </c>
-      <c r="D6" s="552" t="inlineStr">
-        <is>
-          <t>FRM-519</t>
-        </is>
-      </c>
-      <c r="E6" s="552" t="n"/>
-      <c r="F6" s="552" t="n"/>
-      <c r="G6" s="552" t="n"/>
-      <c r="H6" s="552" t="n"/>
-      <c r="I6" s="552" t="n"/>
-      <c r="J6" s="552" t="n"/>
-      <c r="K6" s="552" t="n"/>
-      <c r="L6" s="552" t="n"/>
-      <c r="M6" s="552" t="n"/>
-      <c r="N6" s="552" t="n"/>
-      <c r="O6" s="552" t="n"/>
-      <c r="P6" s="552" t="n"/>
-      <c r="Q6" s="552" t="n"/>
-      <c r="R6" s="552" t="n"/>
-      <c r="S6" s="552" t="n"/>
-      <c r="T6" s="552" t="n"/>
-      <c r="U6" s="552" t="n"/>
-      <c r="V6" s="552" t="n"/>
-      <c r="W6" s="552" t="n"/>
-      <c r="X6" s="552" t="n"/>
-      <c r="Y6" s="552" t="n"/>
-      <c r="Z6" s="552" t="n"/>
-      <c r="AA6" s="552" t="n"/>
-      <c r="AB6" s="552" t="n"/>
-      <c r="AC6" s="552" t="n"/>
-      <c r="AD6" s="552" t="n"/>
-      <c r="AE6" s="552" t="n"/>
-      <c r="AF6" s="552" t="n"/>
-      <c r="AG6" s="552" t="n"/>
-      <c r="AH6" s="552" t="n"/>
-      <c r="AI6" s="552" t="n"/>
-      <c r="AJ6" s="552" t="n"/>
-      <c r="AK6" s="552" t="n"/>
-      <c r="AL6" s="552" t="n"/>
-      <c r="AM6" s="552" t="n"/>
-      <c r="AN6" s="555" t="n"/>
-    </row>
-    <row r="7" hidden="1"/>
-    <row r="8" hidden="1"/>
-    <row r="9" hidden="1"/>
-    <row r="10" hidden="1"/>
-    <row r="11" hidden="1"/>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
-    <row r="21" hidden="1"/>
-    <row r="22" hidden="1"/>
-    <row r="23" hidden="1"/>
-    <row r="24" hidden="1"/>
-    <row r="25" hidden="1"/>
-    <row r="26" hidden="1"/>
-    <row r="27" hidden="1"/>
-    <row r="28" hidden="1"/>
-    <row r="29" hidden="1"/>
-    <row r="30" hidden="1"/>
-    <row r="31" hidden="1"/>
-    <row r="32" hidden="1"/>
-    <row r="33" hidden="1"/>
-    <row r="34" hidden="1"/>
-    <row r="35" hidden="1"/>
-    <row r="36" hidden="1"/>
-    <row r="37" hidden="1"/>
-    <row r="38" hidden="1"/>
-    <row r="39" hidden="1"/>
-    <row r="40" hidden="1"/>
-    <row r="41" hidden="1"/>
-    <row r="42" hidden="1"/>
-    <row r="43" hidden="1"/>
-    <row r="44" hidden="1"/>
-    <row r="45" hidden="1"/>
-    <row r="46" hidden="1"/>
-    <row r="47" hidden="1"/>
-    <row r="48" hidden="1"/>
-    <row r="49" hidden="1"/>
-    <row r="50" hidden="1"/>
-    <row r="51" hidden="1"/>
-    <row r="52" hidden="1"/>
-    <row r="53" hidden="1"/>
-    <row r="54" hidden="1"/>
-    <row r="55" hidden="1"/>
-    <row r="56" hidden="1"/>
-    <row r="57" hidden="1"/>
-    <row r="58" hidden="1"/>
-    <row r="59" hidden="1"/>
-    <row r="60" hidden="1"/>
-    <row r="61" hidden="1"/>
-    <row r="62" hidden="1"/>
-    <row r="63" hidden="1"/>
-    <row r="64" hidden="1"/>
-    <row r="65" hidden="1"/>
-    <row r="66" hidden="1"/>
-    <row r="67" hidden="1"/>
-    <row r="68" hidden="1"/>
-    <row r="69" hidden="1"/>
-    <row r="70" hidden="1"/>
-    <row r="71" hidden="1"/>
-    <row r="72" hidden="1"/>
-    <row r="73" hidden="1"/>
-    <row r="74" hidden="1"/>
-    <row r="75" hidden="1"/>
-    <row r="76" hidden="1"/>
-    <row r="77" hidden="1"/>
-    <row r="78" hidden="1"/>
-    <row r="79" hidden="1"/>
-    <row r="80" hidden="1"/>
-    <row r="81" hidden="1"/>
-    <row r="82" hidden="1"/>
-    <row r="83" hidden="1"/>
-    <row r="84" hidden="1"/>
-    <row r="85" hidden="1"/>
-    <row r="86" hidden="1"/>
-    <row r="87" hidden="1"/>
-    <row r="88" hidden="1"/>
-    <row r="89" hidden="1"/>
-    <row r="90" hidden="1"/>
-    <row r="91" hidden="1"/>
-    <row r="92" hidden="1"/>
-    <row r="93" hidden="1"/>
-    <row r="94" hidden="1"/>
-    <row r="95" hidden="1"/>
-    <row r="96" hidden="1"/>
-    <row r="97" hidden="1"/>
-    <row r="98" hidden="1"/>
-    <row r="99" hidden="1"/>
-    <row r="100" hidden="1"/>
-    <row r="101" hidden="1"/>
-    <row r="102" hidden="1"/>
-    <row r="103" hidden="1"/>
-    <row r="104" hidden="1"/>
-    <row r="105" hidden="1"/>
-    <row r="106" hidden="1"/>
-    <row r="107" hidden="1"/>
-    <row r="108" hidden="1"/>
-    <row r="109" hidden="1"/>
-    <row r="110" hidden="1"/>
-    <row r="111" hidden="1"/>
-    <row r="112" hidden="1"/>
-    <row r="113" hidden="1"/>
-    <row r="114" hidden="1"/>
-    <row r="115" hidden="1"/>
-    <row r="116" hidden="1"/>
-    <row r="117" hidden="1"/>
-    <row r="118" hidden="1"/>
-    <row r="119" hidden="1"/>
-    <row r="120" hidden="1"/>
-    <row r="121" hidden="1"/>
-    <row r="122" hidden="1"/>
-    <row r="123" hidden="1"/>
-    <row r="124" hidden="1"/>
-    <row r="125" hidden="1"/>
-    <row r="126" hidden="1"/>
-    <row r="127" hidden="1"/>
-    <row r="128" hidden="1"/>
-    <row r="129" hidden="1"/>
-    <row r="130" hidden="1"/>
-    <row r="131" hidden="1"/>
-    <row r="132" hidden="1"/>
-    <row r="133" hidden="1"/>
-    <row r="134" hidden="1"/>
-    <row r="135" hidden="1"/>
-    <row r="136" hidden="1"/>
-    <row r="137" hidden="1"/>
-    <row r="138" hidden="1"/>
-    <row r="139" hidden="1"/>
-    <row r="140" hidden="1"/>
-    <row r="141" hidden="1"/>
-    <row r="142" hidden="1"/>
-    <row r="143" hidden="1"/>
-    <row r="144" hidden="1"/>
-    <row r="145" hidden="1"/>
-    <row r="146" hidden="1"/>
-    <row r="147" hidden="1"/>
-    <row r="148" hidden="1"/>
-    <row r="149" hidden="1"/>
-    <row r="150" hidden="1"/>
-    <row r="151" hidden="1"/>
-    <row r="152" hidden="1"/>
-    <row r="153" hidden="1"/>
-    <row r="154" hidden="1"/>
-    <row r="155" hidden="1"/>
-    <row r="156" hidden="1"/>
-    <row r="157" hidden="1"/>
-    <row r="158" hidden="1"/>
-    <row r="159" hidden="1"/>
-    <row r="160" hidden="1"/>
-    <row r="161" hidden="1"/>
-    <row r="162" hidden="1"/>
-    <row r="163" hidden="1"/>
-    <row r="164" hidden="1"/>
-    <row r="165" hidden="1"/>
-    <row r="166" hidden="1"/>
-    <row r="167" hidden="1"/>
-    <row r="168" hidden="1"/>
-    <row r="169" hidden="1"/>
-    <row r="170" hidden="1"/>
-    <row r="171" hidden="1"/>
-    <row r="172" hidden="1"/>
-    <row r="173" hidden="1"/>
-    <row r="174" hidden="1"/>
-    <row r="175" hidden="1"/>
-    <row r="176" hidden="1"/>
-    <row r="177" hidden="1"/>
-    <row r="178" hidden="1"/>
-    <row r="179" hidden="1"/>
-    <row r="180" hidden="1"/>
-    <row r="181" hidden="1"/>
-    <row r="182" hidden="1"/>
-    <row r="183" hidden="1"/>
-    <row r="184" hidden="1"/>
-    <row r="185" hidden="1"/>
-    <row r="186" hidden="1"/>
-    <row r="187" hidden="1"/>
-    <row r="188" hidden="1"/>
-    <row r="189" hidden="1"/>
-    <row r="190" hidden="1"/>
-    <row r="191" hidden="1"/>
-    <row r="192" hidden="1"/>
-    <row r="193" hidden="1"/>
-    <row r="194" hidden="1"/>
-    <row r="195" hidden="1"/>
-    <row r="196" hidden="1"/>
-    <row r="197" hidden="1"/>
-    <row r="198" hidden="1"/>
-    <row r="199" hidden="1"/>
-    <row r="200" hidden="1"/>
-  </sheetData>
+  <mergeCells count="14">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
+  </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
@@ -14140,51 +14576,51 @@
       <c r="AM29" s="733" t="n"/>
       <c r="AN29" s="734" t="n"/>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="665" t="inlineStr">
+    <row r="30" ht="26" customHeight="1">
+      <c r="A30" s="793" t="inlineStr">
         <is>
           <t>NOTICE  ?  Controlled withdrawal scope log; keep source files external. Maintain traceability to the parent form, superseding package, point-of-use impact and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B30" s="289" t="n"/>
-      <c r="C30" s="289" t="n"/>
-      <c r="D30" s="289" t="n"/>
-      <c r="E30" s="289" t="n"/>
-      <c r="F30" s="289" t="n"/>
-      <c r="G30" s="289" t="n"/>
-      <c r="H30" s="289" t="n"/>
-      <c r="I30" s="716" t="n"/>
-      <c r="J30" s="716" t="n"/>
-      <c r="K30" s="716" t="n"/>
-      <c r="L30" s="716" t="n"/>
-      <c r="M30" s="716" t="n"/>
-      <c r="N30" s="716" t="n"/>
-      <c r="O30" s="716" t="n"/>
-      <c r="P30" s="716" t="n"/>
-      <c r="Q30" s="716" t="n"/>
-      <c r="R30" s="716" t="n"/>
-      <c r="S30" s="716" t="n"/>
-      <c r="T30" s="716" t="n"/>
-      <c r="U30" s="716" t="n"/>
-      <c r="V30" s="716" t="n"/>
-      <c r="W30" s="716" t="n"/>
-      <c r="X30" s="716" t="n"/>
-      <c r="Y30" s="716" t="n"/>
-      <c r="Z30" s="716" t="n"/>
-      <c r="AA30" s="716" t="n"/>
-      <c r="AB30" s="716" t="n"/>
-      <c r="AC30" s="716" t="n"/>
-      <c r="AD30" s="716" t="n"/>
-      <c r="AE30" s="716" t="n"/>
-      <c r="AF30" s="716" t="n"/>
-      <c r="AG30" s="716" t="n"/>
-      <c r="AH30" s="716" t="n"/>
-      <c r="AI30" s="716" t="n"/>
-      <c r="AJ30" s="716" t="n"/>
-      <c r="AK30" s="716" t="n"/>
-      <c r="AL30" s="716" t="n"/>
-      <c r="AM30" s="716" t="n"/>
-      <c r="AN30" s="717" t="n"/>
+      <c r="B30" s="794" t="n"/>
+      <c r="C30" s="794" t="n"/>
+      <c r="D30" s="794" t="n"/>
+      <c r="E30" s="794" t="n"/>
+      <c r="F30" s="794" t="n"/>
+      <c r="G30" s="794" t="n"/>
+      <c r="H30" s="794" t="n"/>
+      <c r="I30" s="794" t="n"/>
+      <c r="J30" s="794" t="n"/>
+      <c r="K30" s="794" t="n"/>
+      <c r="L30" s="794" t="n"/>
+      <c r="M30" s="794" t="n"/>
+      <c r="N30" s="794" t="n"/>
+      <c r="O30" s="794" t="n"/>
+      <c r="P30" s="794" t="n"/>
+      <c r="Q30" s="794" t="n"/>
+      <c r="R30" s="794" t="n"/>
+      <c r="S30" s="794" t="n"/>
+      <c r="T30" s="794" t="n"/>
+      <c r="U30" s="794" t="n"/>
+      <c r="V30" s="794" t="n"/>
+      <c r="W30" s="794" t="n"/>
+      <c r="X30" s="794" t="n"/>
+      <c r="Y30" s="794" t="n"/>
+      <c r="Z30" s="794" t="n"/>
+      <c r="AA30" s="794" t="n"/>
+      <c r="AB30" s="794" t="n"/>
+      <c r="AC30" s="794" t="n"/>
+      <c r="AD30" s="794" t="n"/>
+      <c r="AE30" s="794" t="n"/>
+      <c r="AF30" s="794" t="n"/>
+      <c r="AG30" s="794" t="n"/>
+      <c r="AH30" s="794" t="n"/>
+      <c r="AI30" s="794" t="n"/>
+      <c r="AJ30" s="794" t="n"/>
+      <c r="AK30" s="794" t="n"/>
+      <c r="AL30" s="794" t="n"/>
+      <c r="AM30" s="794" t="n"/>
+      <c r="AN30" s="795" t="n"/>
     </row>
     <row r="31" hidden="1" outlineLevel="1"/>
     <row r="32" hidden="1" outlineLevel="1"/>
@@ -15688,51 +16124,51 @@
       <c r="AM25" s="733" t="n"/>
       <c r="AN25" s="734" t="n"/>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="665" t="inlineStr">
+    <row r="26" ht="26" customHeight="1">
+      <c r="A26" s="793" t="inlineStr">
         <is>
           <t>NOTICE  ?  Point-of-use sweep confirmation log. Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, timestamps and result fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="289" t="n"/>
-      <c r="C26" s="289" t="n"/>
-      <c r="D26" s="289" t="n"/>
-      <c r="E26" s="289" t="n"/>
-      <c r="F26" s="289" t="n"/>
-      <c r="G26" s="289" t="n"/>
-      <c r="H26" s="716" t="n"/>
-      <c r="I26" s="716" t="n"/>
-      <c r="J26" s="716" t="n"/>
-      <c r="K26" s="716" t="n"/>
-      <c r="L26" s="716" t="n"/>
-      <c r="M26" s="716" t="n"/>
-      <c r="N26" s="716" t="n"/>
-      <c r="O26" s="716" t="n"/>
-      <c r="P26" s="716" t="n"/>
-      <c r="Q26" s="716" t="n"/>
-      <c r="R26" s="716" t="n"/>
-      <c r="S26" s="716" t="n"/>
-      <c r="T26" s="716" t="n"/>
-      <c r="U26" s="716" t="n"/>
-      <c r="V26" s="716" t="n"/>
-      <c r="W26" s="716" t="n"/>
-      <c r="X26" s="716" t="n"/>
-      <c r="Y26" s="716" t="n"/>
-      <c r="Z26" s="716" t="n"/>
-      <c r="AA26" s="716" t="n"/>
-      <c r="AB26" s="716" t="n"/>
-      <c r="AC26" s="716" t="n"/>
-      <c r="AD26" s="716" t="n"/>
-      <c r="AE26" s="716" t="n"/>
-      <c r="AF26" s="716" t="n"/>
-      <c r="AG26" s="716" t="n"/>
-      <c r="AH26" s="716" t="n"/>
-      <c r="AI26" s="716" t="n"/>
-      <c r="AJ26" s="716" t="n"/>
-      <c r="AK26" s="716" t="n"/>
-      <c r="AL26" s="716" t="n"/>
-      <c r="AM26" s="716" t="n"/>
-      <c r="AN26" s="717" t="n"/>
+      <c r="B26" s="794" t="n"/>
+      <c r="C26" s="794" t="n"/>
+      <c r="D26" s="794" t="n"/>
+      <c r="E26" s="794" t="n"/>
+      <c r="F26" s="794" t="n"/>
+      <c r="G26" s="794" t="n"/>
+      <c r="H26" s="794" t="n"/>
+      <c r="I26" s="794" t="n"/>
+      <c r="J26" s="794" t="n"/>
+      <c r="K26" s="794" t="n"/>
+      <c r="L26" s="794" t="n"/>
+      <c r="M26" s="794" t="n"/>
+      <c r="N26" s="794" t="n"/>
+      <c r="O26" s="794" t="n"/>
+      <c r="P26" s="794" t="n"/>
+      <c r="Q26" s="794" t="n"/>
+      <c r="R26" s="794" t="n"/>
+      <c r="S26" s="794" t="n"/>
+      <c r="T26" s="794" t="n"/>
+      <c r="U26" s="794" t="n"/>
+      <c r="V26" s="794" t="n"/>
+      <c r="W26" s="794" t="n"/>
+      <c r="X26" s="794" t="n"/>
+      <c r="Y26" s="794" t="n"/>
+      <c r="Z26" s="794" t="n"/>
+      <c r="AA26" s="794" t="n"/>
+      <c r="AB26" s="794" t="n"/>
+      <c r="AC26" s="794" t="n"/>
+      <c r="AD26" s="794" t="n"/>
+      <c r="AE26" s="794" t="n"/>
+      <c r="AF26" s="794" t="n"/>
+      <c r="AG26" s="794" t="n"/>
+      <c r="AH26" s="794" t="n"/>
+      <c r="AI26" s="794" t="n"/>
+      <c r="AJ26" s="794" t="n"/>
+      <c r="AK26" s="794" t="n"/>
+      <c r="AL26" s="794" t="n"/>
+      <c r="AM26" s="794" t="n"/>
+      <c r="AN26" s="795" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -15968,7 +16404,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr autoPageBreaks="0" fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:AN11"/>
+  <dimension ref="A1:AN20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="2.33" customWidth="1" min="1" max="1"/>
@@ -16014,506 +16450,927 @@
   </cols>
   <sheetData>
     <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="632" t="inlineStr">
-        <is>
-          <t>REF LINKS</t>
-        </is>
-      </c>
-      <c r="B1" s="752" t="n"/>
-      <c r="C1" s="752" t="n"/>
-      <c r="D1" s="752" t="n"/>
-      <c r="E1" s="752" t="n"/>
-      <c r="F1" s="752" t="n"/>
-      <c r="G1" s="752" t="n"/>
-      <c r="H1" s="624" t="n"/>
-      <c r="I1" s="503" t="n"/>
-      <c r="J1" s="504" t="n"/>
-      <c r="K1" s="504" t="n"/>
-      <c r="L1" s="504" t="n"/>
-      <c r="M1" s="504" t="n"/>
-      <c r="N1" s="504" t="n"/>
-      <c r="O1" s="504" t="n"/>
-      <c r="P1" s="504" t="n"/>
-      <c r="Q1" s="504" t="n"/>
-      <c r="R1" s="504" t="n"/>
-      <c r="S1" s="504" t="n"/>
-      <c r="T1" s="504" t="n"/>
-      <c r="U1" s="504" t="n"/>
-      <c r="V1" s="504" t="n"/>
-      <c r="W1" s="504" t="n"/>
-      <c r="X1" s="504" t="n"/>
-      <c r="Y1" s="504" t="n"/>
-      <c r="Z1" s="504" t="n"/>
-      <c r="AA1" s="504" t="n"/>
-      <c r="AB1" s="504" t="n"/>
-      <c r="AC1" s="504" t="n"/>
-      <c r="AD1" s="505" t="n"/>
-      <c r="AE1" s="506" t="n"/>
-      <c r="AF1" s="507" t="n"/>
-      <c r="AG1" s="507" t="n"/>
-      <c r="AH1" s="508" t="n"/>
-      <c r="AI1" s="509" t="n"/>
-      <c r="AJ1" s="510" t="n"/>
-      <c r="AK1" s="510" t="n"/>
-      <c r="AL1" s="510" t="n"/>
-      <c r="AM1" s="510" t="n"/>
-      <c r="AN1" s="511" t="n"/>
+      <c r="A1" s="799" t="n"/>
+      <c r="B1" s="800" t="n"/>
+      <c r="C1" s="800" t="n"/>
+      <c r="D1" s="800" t="n"/>
+      <c r="E1" s="800" t="n"/>
+      <c r="F1" s="800" t="n"/>
+      <c r="G1" s="800" t="n"/>
+      <c r="H1" s="801" t="n"/>
+      <c r="I1" s="802" t="inlineStr">
+        <is>
+          <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
+        </is>
+      </c>
+      <c r="J1" s="800" t="n"/>
+      <c r="K1" s="800" t="n"/>
+      <c r="L1" s="800" t="n"/>
+      <c r="M1" s="800" t="n"/>
+      <c r="N1" s="800" t="n"/>
+      <c r="O1" s="800" t="n"/>
+      <c r="P1" s="800" t="n"/>
+      <c r="Q1" s="800" t="n"/>
+      <c r="R1" s="800" t="n"/>
+      <c r="S1" s="800" t="n"/>
+      <c r="T1" s="800" t="n"/>
+      <c r="U1" s="800" t="n"/>
+      <c r="V1" s="800" t="n"/>
+      <c r="W1" s="800" t="n"/>
+      <c r="X1" s="800" t="n"/>
+      <c r="Y1" s="800" t="n"/>
+      <c r="Z1" s="800" t="n"/>
+      <c r="AA1" s="800" t="n"/>
+      <c r="AB1" s="800" t="n"/>
+      <c r="AC1" s="800" t="n"/>
+      <c r="AD1" s="801" t="n"/>
+      <c r="AE1" s="507" t="inlineStr">
+        <is>
+          <t>Form Code</t>
+        </is>
+      </c>
+      <c r="AF1" s="800" t="n"/>
+      <c r="AG1" s="800" t="n"/>
+      <c r="AH1" s="803" t="n"/>
+      <c r="AI1" s="510" t="inlineStr">
+        <is>
+          <t>FRM-306</t>
+        </is>
+      </c>
+      <c r="AJ1" s="800" t="n"/>
+      <c r="AK1" s="800" t="n"/>
+      <c r="AL1" s="800" t="n"/>
+      <c r="AM1" s="800" t="n"/>
+      <c r="AN1" s="801" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="633" t="inlineStr">
-        <is>
-          <t>Reference superseding package, withdrawal evidence and active M365 links only.</t>
-        </is>
-      </c>
-      <c r="H2" s="626" t="n"/>
-      <c r="I2" s="514" t="n"/>
-      <c r="J2" s="515" t="n"/>
-      <c r="K2" s="515" t="n"/>
-      <c r="L2" s="515" t="n"/>
-      <c r="M2" s="515" t="n"/>
-      <c r="N2" s="515" t="n"/>
-      <c r="O2" s="515" t="n"/>
-      <c r="P2" s="515" t="n"/>
-      <c r="Q2" s="515" t="n"/>
-      <c r="R2" s="515" t="n"/>
-      <c r="S2" s="515" t="n"/>
-      <c r="T2" s="515" t="n"/>
-      <c r="U2" s="515" t="n"/>
-      <c r="V2" s="515" t="n"/>
-      <c r="W2" s="515" t="n"/>
-      <c r="X2" s="515" t="n"/>
-      <c r="Y2" s="515" t="n"/>
-      <c r="Z2" s="515" t="n"/>
-      <c r="AA2" s="515" t="n"/>
-      <c r="AB2" s="515" t="n"/>
-      <c r="AC2" s="515" t="n"/>
-      <c r="AD2" s="516" t="n"/>
-      <c r="AE2" s="517" t="n"/>
-      <c r="AF2" s="518" t="n"/>
-      <c r="AG2" s="518" t="n"/>
-      <c r="AH2" s="519" t="n"/>
-      <c r="AI2" s="520" t="n"/>
-      <c r="AJ2" s="521" t="n"/>
-      <c r="AK2" s="521" t="n"/>
-      <c r="AL2" s="521" t="n"/>
-      <c r="AM2" s="521" t="n"/>
-      <c r="AN2" s="522" t="n"/>
+      <c r="A2" s="804" t="n"/>
+      <c r="B2" s="10" t="n"/>
+      <c r="C2" s="10" t="n"/>
+      <c r="D2" s="10" t="n"/>
+      <c r="E2" s="10" t="n"/>
+      <c r="F2" s="10" t="n"/>
+      <c r="G2" s="10" t="n"/>
+      <c r="H2" s="805" t="n"/>
+      <c r="I2" s="10" t="n"/>
+      <c r="J2" s="10" t="n"/>
+      <c r="K2" s="10" t="n"/>
+      <c r="L2" s="10" t="n"/>
+      <c r="M2" s="10" t="n"/>
+      <c r="N2" s="10" t="n"/>
+      <c r="O2" s="10" t="n"/>
+      <c r="P2" s="10" t="n"/>
+      <c r="Q2" s="10" t="n"/>
+      <c r="R2" s="10" t="n"/>
+      <c r="S2" s="10" t="n"/>
+      <c r="T2" s="10" t="n"/>
+      <c r="U2" s="10" t="n"/>
+      <c r="V2" s="10" t="n"/>
+      <c r="W2" s="10" t="n"/>
+      <c r="X2" s="10" t="n"/>
+      <c r="Y2" s="10" t="n"/>
+      <c r="Z2" s="10" t="n"/>
+      <c r="AA2" s="10" t="n"/>
+      <c r="AB2" s="10" t="n"/>
+      <c r="AC2" s="10" t="n"/>
+      <c r="AD2" s="805" t="n"/>
+      <c r="AE2" s="806" t="inlineStr">
+        <is>
+          <t>Revision</t>
+        </is>
+      </c>
+      <c r="AF2" s="10" t="n"/>
+      <c r="AG2" s="10" t="n"/>
+      <c r="AH2" s="807" t="n"/>
+      <c r="AI2" s="808" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="AJ2" s="10" t="n"/>
+      <c r="AK2" s="10" t="n"/>
+      <c r="AL2" s="10" t="n"/>
+      <c r="AM2" s="10" t="n"/>
+      <c r="AN2" s="805" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="634" t="inlineStr">
-        <is>
-          <t>Ref Type</t>
-        </is>
-      </c>
-      <c r="B3" s="635" t="inlineStr">
-        <is>
-          <t>Document / Record</t>
-        </is>
-      </c>
-      <c r="C3" s="635" t="inlineStr">
-        <is>
-          <t>System of Record</t>
-        </is>
-      </c>
-      <c r="D3" s="635" t="inlineStr">
-        <is>
-          <t>Unique Ref</t>
-        </is>
-      </c>
-      <c r="E3" s="635" t="inlineStr">
-        <is>
-          <t>Owner</t>
-        </is>
-      </c>
-      <c r="F3" s="635" t="inlineStr">
-        <is>
-          <t>Status</t>
-        </is>
-      </c>
-      <c r="G3" s="635" t="inlineStr">
-        <is>
-          <t>Note</t>
-        </is>
-      </c>
-      <c r="H3" s="626" t="n"/>
-      <c r="I3" s="514" t="n"/>
-      <c r="J3" s="515" t="n"/>
-      <c r="K3" s="515" t="n"/>
-      <c r="L3" s="515" t="n"/>
-      <c r="M3" s="515" t="n"/>
-      <c r="N3" s="515" t="n"/>
-      <c r="O3" s="515" t="n"/>
-      <c r="P3" s="515" t="n"/>
-      <c r="Q3" s="515" t="n"/>
-      <c r="R3" s="515" t="n"/>
-      <c r="S3" s="515" t="n"/>
-      <c r="T3" s="515" t="n"/>
-      <c r="U3" s="515" t="n"/>
-      <c r="V3" s="515" t="n"/>
-      <c r="W3" s="515" t="n"/>
-      <c r="X3" s="515" t="n"/>
-      <c r="Y3" s="515" t="n"/>
-      <c r="Z3" s="515" t="n"/>
-      <c r="AA3" s="515" t="n"/>
-      <c r="AB3" s="515" t="n"/>
-      <c r="AC3" s="515" t="n"/>
-      <c r="AD3" s="516" t="n"/>
-      <c r="AE3" s="517" t="n"/>
-      <c r="AF3" s="518" t="n"/>
-      <c r="AG3" s="518" t="n"/>
-      <c r="AH3" s="519" t="n"/>
-      <c r="AI3" s="520" t="n"/>
-      <c r="AJ3" s="521" t="n"/>
-      <c r="AK3" s="521" t="n"/>
-      <c r="AL3" s="521" t="n"/>
-      <c r="AM3" s="521" t="n"/>
-      <c r="AN3" s="522" t="n"/>
+      <c r="A3" s="804" t="n"/>
+      <c r="B3" s="10" t="n"/>
+      <c r="C3" s="10" t="n"/>
+      <c r="D3" s="10" t="n"/>
+      <c r="E3" s="10" t="n"/>
+      <c r="F3" s="10" t="n"/>
+      <c r="G3" s="10" t="n"/>
+      <c r="H3" s="805" t="n"/>
+      <c r="I3" s="10" t="n"/>
+      <c r="J3" s="10" t="n"/>
+      <c r="K3" s="10" t="n"/>
+      <c r="L3" s="10" t="n"/>
+      <c r="M3" s="10" t="n"/>
+      <c r="N3" s="10" t="n"/>
+      <c r="O3" s="10" t="n"/>
+      <c r="P3" s="10" t="n"/>
+      <c r="Q3" s="10" t="n"/>
+      <c r="R3" s="10" t="n"/>
+      <c r="S3" s="10" t="n"/>
+      <c r="T3" s="10" t="n"/>
+      <c r="U3" s="10" t="n"/>
+      <c r="V3" s="10" t="n"/>
+      <c r="W3" s="10" t="n"/>
+      <c r="X3" s="10" t="n"/>
+      <c r="Y3" s="10" t="n"/>
+      <c r="Z3" s="10" t="n"/>
+      <c r="AA3" s="10" t="n"/>
+      <c r="AB3" s="10" t="n"/>
+      <c r="AC3" s="10" t="n"/>
+      <c r="AD3" s="805" t="n"/>
+      <c r="AE3" s="806" t="inlineStr">
+        <is>
+          <t>Eff. Date</t>
+        </is>
+      </c>
+      <c r="AF3" s="10" t="n"/>
+      <c r="AG3" s="10" t="n"/>
+      <c r="AH3" s="807" t="n"/>
+      <c r="AI3" s="808" t="inlineStr">
+        <is>
+          <t>YYYY-MM-DD</t>
+        </is>
+      </c>
+      <c r="AJ3" s="10" t="n"/>
+      <c r="AK3" s="10" t="n"/>
+      <c r="AL3" s="10" t="n"/>
+      <c r="AM3" s="10" t="n"/>
+      <c r="AN3" s="805" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="636" t="n"/>
-      <c r="B4" s="637" t="n"/>
-      <c r="C4" s="637" t="n"/>
-      <c r="D4" s="637" t="n"/>
-      <c r="E4" s="637" t="n"/>
-      <c r="F4" s="637" t="n"/>
-      <c r="G4" s="637" t="n"/>
-      <c r="H4" s="626" t="n"/>
-      <c r="I4" s="523" t="n"/>
-      <c r="J4" s="524" t="n"/>
-      <c r="K4" s="524" t="n"/>
-      <c r="L4" s="524" t="n"/>
-      <c r="M4" s="524" t="n"/>
-      <c r="N4" s="524" t="n"/>
-      <c r="O4" s="524" t="n"/>
-      <c r="P4" s="524" t="n"/>
-      <c r="Q4" s="524" t="n"/>
-      <c r="R4" s="524" t="n"/>
-      <c r="S4" s="524" t="n"/>
-      <c r="T4" s="524" t="n"/>
-      <c r="U4" s="524" t="n"/>
-      <c r="V4" s="524" t="n"/>
-      <c r="W4" s="524" t="n"/>
-      <c r="X4" s="524" t="n"/>
-      <c r="Y4" s="524" t="n"/>
-      <c r="Z4" s="524" t="n"/>
-      <c r="AA4" s="524" t="n"/>
-      <c r="AB4" s="524" t="n"/>
-      <c r="AC4" s="524" t="n"/>
-      <c r="AD4" s="525" t="n"/>
-      <c r="AE4" s="517" t="n"/>
-      <c r="AF4" s="518" t="n"/>
-      <c r="AG4" s="518" t="n"/>
-      <c r="AH4" s="519" t="n"/>
-      <c r="AI4" s="520" t="n"/>
-      <c r="AJ4" s="521" t="n"/>
-      <c r="AK4" s="521" t="n"/>
-      <c r="AL4" s="521" t="n"/>
-      <c r="AM4" s="521" t="n"/>
-      <c r="AN4" s="522" t="n"/>
+      <c r="A4" s="804" t="n"/>
+      <c r="B4" s="10" t="n"/>
+      <c r="C4" s="10" t="n"/>
+      <c r="D4" s="10" t="n"/>
+      <c r="E4" s="10" t="n"/>
+      <c r="F4" s="10" t="n"/>
+      <c r="G4" s="10" t="n"/>
+      <c r="H4" s="805" t="n"/>
+      <c r="I4" s="809" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="J4" s="10" t="n"/>
+      <c r="K4" s="10" t="n"/>
+      <c r="L4" s="10" t="n"/>
+      <c r="M4" s="10" t="n"/>
+      <c r="N4" s="10" t="n"/>
+      <c r="O4" s="10" t="n"/>
+      <c r="P4" s="10" t="n"/>
+      <c r="Q4" s="10" t="n"/>
+      <c r="R4" s="10" t="n"/>
+      <c r="S4" s="10" t="n"/>
+      <c r="T4" s="10" t="n"/>
+      <c r="U4" s="10" t="n"/>
+      <c r="V4" s="10" t="n"/>
+      <c r="W4" s="10" t="n"/>
+      <c r="X4" s="10" t="n"/>
+      <c r="Y4" s="10" t="n"/>
+      <c r="Z4" s="10" t="n"/>
+      <c r="AA4" s="10" t="n"/>
+      <c r="AB4" s="10" t="n"/>
+      <c r="AC4" s="10" t="n"/>
+      <c r="AD4" s="805" t="n"/>
+      <c r="AE4" s="806" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="AF4" s="10" t="n"/>
+      <c r="AG4" s="10" t="n"/>
+      <c r="AH4" s="807" t="n"/>
+      <c r="AI4" s="808" t="inlineStr">
+        <is>
+          <t>Engineering / QA / Planning</t>
+        </is>
+      </c>
+      <c r="AJ4" s="10" t="n"/>
+      <c r="AK4" s="10" t="n"/>
+      <c r="AL4" s="10" t="n"/>
+      <c r="AM4" s="10" t="n"/>
+      <c r="AN4" s="805" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="638" t="n"/>
-      <c r="B5" s="639" t="n"/>
-      <c r="C5" s="639" t="n"/>
-      <c r="D5" s="639" t="n"/>
-      <c r="E5" s="639" t="n"/>
-      <c r="F5" s="639" t="n"/>
-      <c r="G5" s="639" t="n"/>
-      <c r="H5" s="628" t="n"/>
-      <c r="I5" s="529" t="n"/>
-      <c r="J5" s="530" t="n"/>
-      <c r="K5" s="530" t="n"/>
-      <c r="L5" s="530" t="n"/>
-      <c r="M5" s="530" t="n"/>
-      <c r="N5" s="530" t="n"/>
-      <c r="O5" s="530" t="n"/>
-      <c r="P5" s="530" t="n"/>
-      <c r="Q5" s="530" t="n"/>
-      <c r="R5" s="530" t="n"/>
-      <c r="S5" s="530" t="n"/>
-      <c r="T5" s="530" t="n"/>
-      <c r="U5" s="530" t="n"/>
-      <c r="V5" s="530" t="n"/>
-      <c r="W5" s="530" t="n"/>
-      <c r="X5" s="530" t="n"/>
-      <c r="Y5" s="530" t="n"/>
-      <c r="Z5" s="530" t="n"/>
-      <c r="AA5" s="530" t="n"/>
-      <c r="AB5" s="530" t="n"/>
-      <c r="AC5" s="530" t="n"/>
-      <c r="AD5" s="531" t="n"/>
-      <c r="AE5" s="532" t="n"/>
-      <c r="AF5" s="533" t="n"/>
-      <c r="AG5" s="533" t="n"/>
-      <c r="AH5" s="534" t="n"/>
-      <c r="AI5" s="535" t="n"/>
-      <c r="AJ5" s="536" t="n"/>
-      <c r="AK5" s="536" t="n"/>
-      <c r="AL5" s="536" t="n"/>
-      <c r="AM5" s="536" t="n"/>
-      <c r="AN5" s="537" t="n"/>
+      <c r="A5" s="810" t="n"/>
+      <c r="B5" s="811" t="n"/>
+      <c r="C5" s="811" t="n"/>
+      <c r="D5" s="811" t="n"/>
+      <c r="E5" s="811" t="n"/>
+      <c r="F5" s="811" t="n"/>
+      <c r="G5" s="811" t="n"/>
+      <c r="H5" s="812" t="n"/>
+      <c r="I5" s="813" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="J5" s="811" t="n"/>
+      <c r="K5" s="811" t="n"/>
+      <c r="L5" s="811" t="n"/>
+      <c r="M5" s="811" t="n"/>
+      <c r="N5" s="811" t="n"/>
+      <c r="O5" s="811" t="n"/>
+      <c r="P5" s="811" t="n"/>
+      <c r="Q5" s="811" t="n"/>
+      <c r="R5" s="811" t="n"/>
+      <c r="S5" s="811" t="n"/>
+      <c r="T5" s="811" t="n"/>
+      <c r="U5" s="811" t="n"/>
+      <c r="V5" s="811" t="n"/>
+      <c r="W5" s="811" t="n"/>
+      <c r="X5" s="811" t="n"/>
+      <c r="Y5" s="811" t="n"/>
+      <c r="Z5" s="811" t="n"/>
+      <c r="AA5" s="811" t="n"/>
+      <c r="AB5" s="811" t="n"/>
+      <c r="AC5" s="811" t="n"/>
+      <c r="AD5" s="812" t="n"/>
+      <c r="AE5" s="814" t="inlineStr">
+        <is>
+          <t>Approved</t>
+        </is>
+      </c>
+      <c r="AF5" s="811" t="n"/>
+      <c r="AG5" s="811" t="n"/>
+      <c r="AH5" s="815" t="n"/>
+      <c r="AI5" s="816" t="inlineStr">
+        <is>
+          <t>Engineering Manager</t>
+        </is>
+      </c>
+      <c r="AJ5" s="811" t="n"/>
+      <c r="AK5" s="811" t="n"/>
+      <c r="AL5" s="811" t="n"/>
+      <c r="AM5" s="811" t="n"/>
+      <c r="AN5" s="812" t="n"/>
     </row>
-    <row r="6">
-      <c r="A6" s="640" t="n"/>
-      <c r="B6" s="641" t="n"/>
-      <c r="C6" s="641" t="n"/>
-      <c r="D6" s="641" t="n"/>
-      <c r="E6" s="641" t="n"/>
-      <c r="F6" s="641" t="n"/>
-      <c r="G6" s="641" t="n"/>
-      <c r="H6" s="543" t="n"/>
-      <c r="I6" s="543" t="n"/>
-      <c r="J6" s="543" t="n"/>
-      <c r="K6" s="543" t="n"/>
-      <c r="L6" s="543" t="n"/>
-      <c r="M6" s="543" t="n"/>
-      <c r="N6" s="543" t="n"/>
-      <c r="O6" s="543" t="n"/>
-      <c r="P6" s="543" t="n"/>
-      <c r="Q6" s="543" t="n"/>
-      <c r="R6" s="543" t="n"/>
-      <c r="S6" s="543" t="n"/>
-      <c r="T6" s="543" t="n"/>
-      <c r="U6" s="543" t="n"/>
-      <c r="V6" s="543" t="n"/>
-      <c r="W6" s="543" t="n"/>
-      <c r="X6" s="543" t="n"/>
-      <c r="Y6" s="543" t="n"/>
-      <c r="Z6" s="543" t="n"/>
-      <c r="AA6" s="543" t="n"/>
-      <c r="AB6" s="543" t="n"/>
-      <c r="AC6" s="543" t="n"/>
-      <c r="AD6" s="543" t="n"/>
-      <c r="AE6" s="543" t="n"/>
-      <c r="AF6" s="543" t="n"/>
-      <c r="AG6" s="543" t="n"/>
-      <c r="AH6" s="543" t="n"/>
-      <c r="AI6" s="543" t="n"/>
-      <c r="AJ6" s="543" t="n"/>
-      <c r="AK6" s="543" t="n"/>
-      <c r="AL6" s="543" t="n"/>
-      <c r="AM6" s="543" t="n"/>
-      <c r="AN6" s="546" t="n"/>
+    <row r="6" ht="1.5" customHeight="1">
+      <c r="A6" s="817" t="n"/>
+      <c r="B6" s="817" t="n"/>
+      <c r="C6" s="817" t="n"/>
+      <c r="D6" s="817" t="n"/>
+      <c r="E6" s="817" t="n"/>
+      <c r="F6" s="817" t="n"/>
+      <c r="G6" s="817" t="n"/>
+      <c r="H6" s="817" t="n"/>
+      <c r="I6" s="817" t="n"/>
+      <c r="J6" s="817" t="n"/>
+      <c r="K6" s="817" t="n"/>
+      <c r="L6" s="817" t="n"/>
+      <c r="M6" s="817" t="n"/>
+      <c r="N6" s="817" t="n"/>
+      <c r="O6" s="817" t="n"/>
+      <c r="P6" s="817" t="n"/>
+      <c r="Q6" s="817" t="n"/>
+      <c r="R6" s="817" t="n"/>
+      <c r="S6" s="817" t="n"/>
+      <c r="T6" s="817" t="n"/>
+      <c r="U6" s="817" t="n"/>
+      <c r="V6" s="817" t="n"/>
+      <c r="W6" s="817" t="n"/>
+      <c r="X6" s="817" t="n"/>
+      <c r="Y6" s="817" t="n"/>
+      <c r="Z6" s="817" t="n"/>
+      <c r="AA6" s="817" t="n"/>
+      <c r="AB6" s="817" t="n"/>
+      <c r="AC6" s="817" t="n"/>
+      <c r="AD6" s="817" t="n"/>
+      <c r="AE6" s="817" t="n"/>
+      <c r="AF6" s="817" t="n"/>
+      <c r="AG6" s="817" t="n"/>
+      <c r="AH6" s="817" t="n"/>
+      <c r="AI6" s="817" t="n"/>
+      <c r="AJ6" s="817" t="n"/>
+      <c r="AK6" s="817" t="n"/>
+      <c r="AL6" s="817" t="n"/>
+      <c r="AM6" s="817" t="n"/>
+      <c r="AN6" s="817" t="n"/>
     </row>
     <row r="7">
-      <c r="A7" s="642" t="n"/>
-      <c r="B7" s="643" t="n"/>
-      <c r="C7" s="643" t="n"/>
-      <c r="D7" s="643" t="n"/>
-      <c r="E7" s="643" t="n"/>
-      <c r="F7" s="643" t="n"/>
-      <c r="G7" s="643" t="n"/>
-      <c r="H7" s="402" t="n"/>
-      <c r="I7" s="402" t="n"/>
-      <c r="J7" s="402" t="n"/>
-      <c r="K7" s="402" t="n"/>
-      <c r="L7" s="402" t="n"/>
-      <c r="M7" s="402" t="n"/>
-      <c r="N7" s="402" t="n"/>
-      <c r="O7" s="402" t="n"/>
-      <c r="P7" s="402" t="n"/>
-      <c r="Q7" s="402" t="n"/>
-      <c r="R7" s="402" t="n"/>
-      <c r="S7" s="402" t="n"/>
-      <c r="T7" s="402" t="n"/>
-      <c r="U7" s="402" t="n"/>
-      <c r="V7" s="402" t="n"/>
-      <c r="W7" s="402" t="n"/>
-      <c r="X7" s="402" t="n"/>
-      <c r="Y7" s="402" t="n"/>
-      <c r="Z7" s="402" t="n"/>
-      <c r="AA7" s="402" t="n"/>
-      <c r="AB7" s="402" t="n"/>
-      <c r="AC7" s="402" t="n"/>
-      <c r="AD7" s="402" t="n"/>
-      <c r="AE7" s="402" t="n"/>
-      <c r="AF7" s="402" t="n"/>
-      <c r="AG7" s="402" t="n"/>
-      <c r="AH7" s="402" t="n"/>
-      <c r="AI7" s="402" t="n"/>
-      <c r="AJ7" s="402" t="n"/>
-      <c r="AK7" s="402" t="n"/>
-      <c r="AL7" s="402" t="n"/>
-      <c r="AM7" s="402" t="n"/>
-      <c r="AN7" s="550" t="n"/>
+      <c r="A7" s="632" t="inlineStr">
+        <is>
+          <t>REF LINKS</t>
+        </is>
+      </c>
+      <c r="B7" s="752" t="n"/>
+      <c r="C7" s="752" t="n"/>
+      <c r="D7" s="752" t="n"/>
+      <c r="E7" s="752" t="n"/>
+      <c r="F7" s="752" t="n"/>
+      <c r="G7" s="752" t="n"/>
+      <c r="H7" s="818" t="n"/>
+      <c r="I7" s="818" t="n"/>
+      <c r="J7" s="818" t="n"/>
+      <c r="K7" s="818" t="n"/>
+      <c r="L7" s="818" t="n"/>
+      <c r="M7" s="818" t="n"/>
+      <c r="N7" s="818" t="n"/>
+      <c r="O7" s="818" t="n"/>
+      <c r="P7" s="818" t="n"/>
+      <c r="Q7" s="818" t="n"/>
+      <c r="R7" s="818" t="n"/>
+      <c r="S7" s="818" t="n"/>
+      <c r="T7" s="818" t="n"/>
+      <c r="U7" s="818" t="n"/>
+      <c r="V7" s="818" t="n"/>
+      <c r="W7" s="818" t="n"/>
+      <c r="X7" s="818" t="n"/>
+      <c r="Y7" s="818" t="n"/>
+      <c r="Z7" s="818" t="n"/>
+      <c r="AA7" s="818" t="n"/>
+      <c r="AB7" s="818" t="n"/>
+      <c r="AC7" s="818" t="n"/>
+      <c r="AD7" s="818" t="n"/>
+      <c r="AE7" s="818" t="n"/>
+      <c r="AF7" s="818" t="n"/>
+      <c r="AG7" s="818" t="n"/>
+      <c r="AH7" s="818" t="n"/>
+      <c r="AI7" s="818" t="n"/>
+      <c r="AJ7" s="818" t="n"/>
+      <c r="AK7" s="818" t="n"/>
+      <c r="AL7" s="818" t="n"/>
+      <c r="AM7" s="818" t="n"/>
+      <c r="AN7" s="818" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="644" t="n"/>
-      <c r="B8" s="645" t="n"/>
-      <c r="C8" s="645" t="n"/>
-      <c r="D8" s="645" t="n"/>
-      <c r="E8" s="645" t="n"/>
-      <c r="F8" s="645" t="n"/>
-      <c r="G8" s="645" t="n"/>
-      <c r="H8" s="417" t="n"/>
-      <c r="I8" s="417" t="n"/>
-      <c r="J8" s="417" t="n"/>
-      <c r="K8" s="417" t="n"/>
-      <c r="L8" s="417" t="n"/>
-      <c r="M8" s="417" t="n"/>
-      <c r="N8" s="417" t="n"/>
-      <c r="O8" s="417" t="n"/>
-      <c r="P8" s="417" t="n"/>
-      <c r="Q8" s="417" t="n"/>
-      <c r="R8" s="417" t="n"/>
-      <c r="S8" s="417" t="n"/>
-      <c r="T8" s="417" t="n"/>
-      <c r="U8" s="417" t="n"/>
-      <c r="V8" s="417" t="n"/>
-      <c r="W8" s="417" t="n"/>
-      <c r="X8" s="417" t="n"/>
-      <c r="Y8" s="417" t="n"/>
-      <c r="Z8" s="417" t="n"/>
-      <c r="AA8" s="417" t="n"/>
-      <c r="AB8" s="417" t="n"/>
-      <c r="AC8" s="417" t="n"/>
-      <c r="AD8" s="417" t="n"/>
-      <c r="AE8" s="417" t="n"/>
-      <c r="AF8" s="417" t="n"/>
-      <c r="AG8" s="417" t="n"/>
-      <c r="AH8" s="417" t="n"/>
-      <c r="AI8" s="417" t="n"/>
-      <c r="AJ8" s="417" t="n"/>
-      <c r="AK8" s="417" t="n"/>
-      <c r="AL8" s="417" t="n"/>
-      <c r="AM8" s="417" t="n"/>
-      <c r="AN8" s="610" t="n"/>
+      <c r="A8" s="633" t="inlineStr">
+        <is>
+          <t>Reference superseding package, withdrawal evidence and active M365 links only.</t>
+        </is>
+      </c>
+      <c r="H8" s="818" t="n"/>
+      <c r="I8" s="818" t="n"/>
+      <c r="J8" s="818" t="n"/>
+      <c r="K8" s="818" t="n"/>
+      <c r="L8" s="818" t="n"/>
+      <c r="M8" s="818" t="n"/>
+      <c r="N8" s="818" t="n"/>
+      <c r="O8" s="818" t="n"/>
+      <c r="P8" s="818" t="n"/>
+      <c r="Q8" s="818" t="n"/>
+      <c r="R8" s="818" t="n"/>
+      <c r="S8" s="818" t="n"/>
+      <c r="T8" s="818" t="n"/>
+      <c r="U8" s="818" t="n"/>
+      <c r="V8" s="818" t="n"/>
+      <c r="W8" s="818" t="n"/>
+      <c r="X8" s="818" t="n"/>
+      <c r="Y8" s="818" t="n"/>
+      <c r="Z8" s="818" t="n"/>
+      <c r="AA8" s="818" t="n"/>
+      <c r="AB8" s="818" t="n"/>
+      <c r="AC8" s="818" t="n"/>
+      <c r="AD8" s="818" t="n"/>
+      <c r="AE8" s="818" t="n"/>
+      <c r="AF8" s="818" t="n"/>
+      <c r="AG8" s="818" t="n"/>
+      <c r="AH8" s="818" t="n"/>
+      <c r="AI8" s="818" t="n"/>
+      <c r="AJ8" s="818" t="n"/>
+      <c r="AK8" s="818" t="n"/>
+      <c r="AL8" s="818" t="n"/>
+      <c r="AM8" s="818" t="n"/>
+      <c r="AN8" s="818" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="642" t="n"/>
-      <c r="B9" s="643" t="n"/>
-      <c r="C9" s="643" t="n"/>
-      <c r="D9" s="643" t="n"/>
-      <c r="E9" s="643" t="n"/>
-      <c r="F9" s="643" t="n"/>
-      <c r="G9" s="643" t="n"/>
-      <c r="H9" s="417" t="n"/>
-      <c r="I9" s="417" t="n"/>
-      <c r="J9" s="417" t="n"/>
-      <c r="K9" s="417" t="n"/>
-      <c r="L9" s="417" t="n"/>
-      <c r="M9" s="417" t="n"/>
-      <c r="N9" s="417" t="n"/>
-      <c r="O9" s="417" t="n"/>
-      <c r="P9" s="417" t="n"/>
-      <c r="Q9" s="417" t="n"/>
-      <c r="R9" s="417" t="n"/>
-      <c r="S9" s="417" t="n"/>
-      <c r="T9" s="417" t="n"/>
-      <c r="U9" s="417" t="n"/>
-      <c r="V9" s="417" t="n"/>
-      <c r="W9" s="417" t="n"/>
-      <c r="X9" s="417" t="n"/>
-      <c r="Y9" s="417" t="n"/>
-      <c r="Z9" s="417" t="n"/>
-      <c r="AA9" s="417" t="n"/>
-      <c r="AB9" s="417" t="n"/>
-      <c r="AC9" s="417" t="n"/>
-      <c r="AD9" s="417" t="n"/>
-      <c r="AE9" s="417" t="n"/>
-      <c r="AF9" s="417" t="n"/>
-      <c r="AG9" s="417" t="n"/>
-      <c r="AH9" s="417" t="n"/>
-      <c r="AI9" s="417" t="n"/>
-      <c r="AJ9" s="417" t="n"/>
-      <c r="AK9" s="417" t="n"/>
-      <c r="AL9" s="417" t="n"/>
-      <c r="AM9" s="417" t="n"/>
-      <c r="AN9" s="610" t="n"/>
+      <c r="A9" s="634" t="inlineStr">
+        <is>
+          <t>Ref Type</t>
+        </is>
+      </c>
+      <c r="B9" s="635" t="inlineStr">
+        <is>
+          <t>Document / Record</t>
+        </is>
+      </c>
+      <c r="C9" s="635" t="inlineStr">
+        <is>
+          <t>System of Record</t>
+        </is>
+      </c>
+      <c r="D9" s="635" t="inlineStr">
+        <is>
+          <t>Unique Ref</t>
+        </is>
+      </c>
+      <c r="E9" s="635" t="inlineStr">
+        <is>
+          <t>Owner</t>
+        </is>
+      </c>
+      <c r="F9" s="635" t="inlineStr">
+        <is>
+          <t>Status</t>
+        </is>
+      </c>
+      <c r="G9" s="635" t="inlineStr">
+        <is>
+          <t>Note</t>
+        </is>
+      </c>
+      <c r="H9" s="818" t="n"/>
+      <c r="I9" s="818" t="n"/>
+      <c r="J9" s="818" t="n"/>
+      <c r="K9" s="818" t="n"/>
+      <c r="L9" s="818" t="n"/>
+      <c r="M9" s="818" t="n"/>
+      <c r="N9" s="818" t="n"/>
+      <c r="O9" s="818" t="n"/>
+      <c r="P9" s="818" t="n"/>
+      <c r="Q9" s="818" t="n"/>
+      <c r="R9" s="818" t="n"/>
+      <c r="S9" s="818" t="n"/>
+      <c r="T9" s="818" t="n"/>
+      <c r="U9" s="818" t="n"/>
+      <c r="V9" s="818" t="n"/>
+      <c r="W9" s="818" t="n"/>
+      <c r="X9" s="818" t="n"/>
+      <c r="Y9" s="818" t="n"/>
+      <c r="Z9" s="818" t="n"/>
+      <c r="AA9" s="818" t="n"/>
+      <c r="AB9" s="818" t="n"/>
+      <c r="AC9" s="818" t="n"/>
+      <c r="AD9" s="818" t="n"/>
+      <c r="AE9" s="818" t="n"/>
+      <c r="AF9" s="818" t="n"/>
+      <c r="AG9" s="818" t="n"/>
+      <c r="AH9" s="818" t="n"/>
+      <c r="AI9" s="818" t="n"/>
+      <c r="AJ9" s="818" t="n"/>
+      <c r="AK9" s="818" t="n"/>
+      <c r="AL9" s="818" t="n"/>
+      <c r="AM9" s="818" t="n"/>
+      <c r="AN9" s="818" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="644" t="n"/>
-      <c r="B10" s="645" t="n"/>
-      <c r="C10" s="645" t="n"/>
-      <c r="D10" s="645" t="n"/>
-      <c r="E10" s="645" t="n"/>
-      <c r="F10" s="645" t="n"/>
-      <c r="G10" s="645" t="n"/>
-      <c r="H10" s="417" t="n"/>
-      <c r="I10" s="417" t="n"/>
-      <c r="J10" s="417" t="n"/>
-      <c r="K10" s="417" t="n"/>
-      <c r="L10" s="417" t="n"/>
-      <c r="M10" s="417" t="n"/>
-      <c r="N10" s="417" t="n"/>
-      <c r="O10" s="417" t="n"/>
-      <c r="P10" s="417" t="n"/>
-      <c r="Q10" s="417" t="n"/>
-      <c r="R10" s="417" t="n"/>
-      <c r="S10" s="417" t="n"/>
-      <c r="T10" s="417" t="n"/>
-      <c r="U10" s="417" t="n"/>
-      <c r="V10" s="417" t="n"/>
-      <c r="W10" s="417" t="n"/>
-      <c r="X10" s="417" t="n"/>
-      <c r="Y10" s="417" t="n"/>
-      <c r="Z10" s="417" t="n"/>
-      <c r="AA10" s="417" t="n"/>
-      <c r="AB10" s="417" t="n"/>
-      <c r="AC10" s="417" t="n"/>
-      <c r="AD10" s="417" t="n"/>
-      <c r="AE10" s="417" t="n"/>
-      <c r="AF10" s="417" t="n"/>
-      <c r="AG10" s="417" t="n"/>
-      <c r="AH10" s="417" t="n"/>
-      <c r="AI10" s="417" t="n"/>
-      <c r="AJ10" s="417" t="n"/>
-      <c r="AK10" s="417" t="n"/>
-      <c r="AL10" s="417" t="n"/>
-      <c r="AM10" s="417" t="n"/>
-      <c r="AN10" s="610" t="n"/>
+      <c r="A10" s="818" t="n"/>
+      <c r="B10" s="818" t="n"/>
+      <c r="C10" s="818" t="n"/>
+      <c r="D10" s="818" t="n"/>
+      <c r="E10" s="818" t="n"/>
+      <c r="F10" s="818" t="n"/>
+      <c r="G10" s="818" t="n"/>
+      <c r="H10" s="818" t="n"/>
+      <c r="I10" s="818" t="n"/>
+      <c r="J10" s="818" t="n"/>
+      <c r="K10" s="818" t="n"/>
+      <c r="L10" s="818" t="n"/>
+      <c r="M10" s="818" t="n"/>
+      <c r="N10" s="818" t="n"/>
+      <c r="O10" s="818" t="n"/>
+      <c r="P10" s="818" t="n"/>
+      <c r="Q10" s="818" t="n"/>
+      <c r="R10" s="818" t="n"/>
+      <c r="S10" s="818" t="n"/>
+      <c r="T10" s="818" t="n"/>
+      <c r="U10" s="818" t="n"/>
+      <c r="V10" s="818" t="n"/>
+      <c r="W10" s="818" t="n"/>
+      <c r="X10" s="818" t="n"/>
+      <c r="Y10" s="818" t="n"/>
+      <c r="Z10" s="818" t="n"/>
+      <c r="AA10" s="818" t="n"/>
+      <c r="AB10" s="818" t="n"/>
+      <c r="AC10" s="818" t="n"/>
+      <c r="AD10" s="818" t="n"/>
+      <c r="AE10" s="818" t="n"/>
+      <c r="AF10" s="818" t="n"/>
+      <c r="AG10" s="818" t="n"/>
+      <c r="AH10" s="818" t="n"/>
+      <c r="AI10" s="818" t="n"/>
+      <c r="AJ10" s="818" t="n"/>
+      <c r="AK10" s="818" t="n"/>
+      <c r="AL10" s="818" t="n"/>
+      <c r="AM10" s="818" t="n"/>
+      <c r="AN10" s="818" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="646" t="n"/>
-      <c r="B11" s="647" t="n"/>
-      <c r="C11" s="647" t="n"/>
-      <c r="D11" s="647" t="n"/>
-      <c r="E11" s="647" t="n"/>
-      <c r="F11" s="647" t="n"/>
-      <c r="G11" s="647" t="n"/>
-      <c r="H11" s="615" t="n"/>
-      <c r="I11" s="615" t="n"/>
-      <c r="J11" s="615" t="n"/>
-      <c r="K11" s="615" t="n"/>
-      <c r="L11" s="615" t="n"/>
-      <c r="M11" s="615" t="n"/>
-      <c r="N11" s="615" t="n"/>
-      <c r="O11" s="615" t="n"/>
-      <c r="P11" s="615" t="n"/>
-      <c r="Q11" s="615" t="n"/>
-      <c r="R11" s="615" t="n"/>
-      <c r="S11" s="615" t="n"/>
-      <c r="T11" s="615" t="n"/>
-      <c r="U11" s="615" t="n"/>
-      <c r="V11" s="615" t="n"/>
-      <c r="W11" s="615" t="n"/>
-      <c r="X11" s="615" t="n"/>
-      <c r="Y11" s="615" t="n"/>
-      <c r="Z11" s="615" t="n"/>
-      <c r="AA11" s="615" t="n"/>
-      <c r="AB11" s="615" t="n"/>
-      <c r="AC11" s="615" t="n"/>
-      <c r="AD11" s="615" t="n"/>
-      <c r="AE11" s="615" t="n"/>
-      <c r="AF11" s="615" t="n"/>
-      <c r="AG11" s="615" t="n"/>
-      <c r="AH11" s="615" t="n"/>
-      <c r="AI11" s="615" t="n"/>
-      <c r="AJ11" s="615" t="n"/>
-      <c r="AK11" s="615" t="n"/>
-      <c r="AL11" s="615" t="n"/>
-      <c r="AM11" s="615" t="n"/>
-      <c r="AN11" s="616" t="n"/>
+      <c r="A11" s="818" t="n"/>
+      <c r="B11" s="818" t="n"/>
+      <c r="C11" s="818" t="n"/>
+      <c r="D11" s="818" t="n"/>
+      <c r="E11" s="818" t="n"/>
+      <c r="F11" s="818" t="n"/>
+      <c r="G11" s="818" t="n"/>
+      <c r="H11" s="818" t="n"/>
+      <c r="I11" s="818" t="n"/>
+      <c r="J11" s="818" t="n"/>
+      <c r="K11" s="818" t="n"/>
+      <c r="L11" s="818" t="n"/>
+      <c r="M11" s="818" t="n"/>
+      <c r="N11" s="818" t="n"/>
+      <c r="O11" s="818" t="n"/>
+      <c r="P11" s="818" t="n"/>
+      <c r="Q11" s="818" t="n"/>
+      <c r="R11" s="818" t="n"/>
+      <c r="S11" s="818" t="n"/>
+      <c r="T11" s="818" t="n"/>
+      <c r="U11" s="818" t="n"/>
+      <c r="V11" s="818" t="n"/>
+      <c r="W11" s="818" t="n"/>
+      <c r="X11" s="818" t="n"/>
+      <c r="Y11" s="818" t="n"/>
+      <c r="Z11" s="818" t="n"/>
+      <c r="AA11" s="818" t="n"/>
+      <c r="AB11" s="818" t="n"/>
+      <c r="AC11" s="818" t="n"/>
+      <c r="AD11" s="818" t="n"/>
+      <c r="AE11" s="818" t="n"/>
+      <c r="AF11" s="818" t="n"/>
+      <c r="AG11" s="818" t="n"/>
+      <c r="AH11" s="818" t="n"/>
+      <c r="AI11" s="818" t="n"/>
+      <c r="AJ11" s="818" t="n"/>
+      <c r="AK11" s="818" t="n"/>
+      <c r="AL11" s="818" t="n"/>
+      <c r="AM11" s="818" t="n"/>
+      <c r="AN11" s="818" t="n"/>
     </row>
-    <row r="12" hidden="1"/>
-    <row r="13" hidden="1"/>
-    <row r="14" hidden="1"/>
-    <row r="15" hidden="1"/>
-    <row r="16" hidden="1"/>
-    <row r="17" hidden="1"/>
-    <row r="18" hidden="1"/>
-    <row r="19" hidden="1"/>
-    <row r="20" hidden="1"/>
+    <row r="12" hidden="1">
+      <c r="A12" s="818" t="n"/>
+      <c r="B12" s="818" t="n"/>
+      <c r="C12" s="818" t="n"/>
+      <c r="D12" s="818" t="n"/>
+      <c r="E12" s="818" t="n"/>
+      <c r="F12" s="818" t="n"/>
+      <c r="G12" s="818" t="n"/>
+      <c r="H12" s="818" t="n"/>
+      <c r="I12" s="818" t="n"/>
+      <c r="J12" s="818" t="n"/>
+      <c r="K12" s="818" t="n"/>
+      <c r="L12" s="818" t="n"/>
+      <c r="M12" s="818" t="n"/>
+      <c r="N12" s="818" t="n"/>
+      <c r="O12" s="818" t="n"/>
+      <c r="P12" s="818" t="n"/>
+      <c r="Q12" s="818" t="n"/>
+      <c r="R12" s="818" t="n"/>
+      <c r="S12" s="818" t="n"/>
+      <c r="T12" s="818" t="n"/>
+      <c r="U12" s="818" t="n"/>
+      <c r="V12" s="818" t="n"/>
+      <c r="W12" s="818" t="n"/>
+      <c r="X12" s="818" t="n"/>
+      <c r="Y12" s="818" t="n"/>
+      <c r="Z12" s="818" t="n"/>
+      <c r="AA12" s="818" t="n"/>
+      <c r="AB12" s="818" t="n"/>
+      <c r="AC12" s="818" t="n"/>
+      <c r="AD12" s="818" t="n"/>
+      <c r="AE12" s="818" t="n"/>
+      <c r="AF12" s="818" t="n"/>
+      <c r="AG12" s="818" t="n"/>
+      <c r="AH12" s="818" t="n"/>
+      <c r="AI12" s="818" t="n"/>
+      <c r="AJ12" s="818" t="n"/>
+      <c r="AK12" s="818" t="n"/>
+      <c r="AL12" s="818" t="n"/>
+      <c r="AM12" s="818" t="n"/>
+      <c r="AN12" s="818" t="n"/>
+    </row>
+    <row r="13" hidden="1">
+      <c r="A13" s="818" t="n"/>
+      <c r="B13" s="818" t="n"/>
+      <c r="C13" s="818" t="n"/>
+      <c r="D13" s="818" t="n"/>
+      <c r="E13" s="818" t="n"/>
+      <c r="F13" s="818" t="n"/>
+      <c r="G13" s="818" t="n"/>
+      <c r="H13" s="818" t="n"/>
+      <c r="I13" s="818" t="n"/>
+      <c r="J13" s="818" t="n"/>
+      <c r="K13" s="818" t="n"/>
+      <c r="L13" s="818" t="n"/>
+      <c r="M13" s="818" t="n"/>
+      <c r="N13" s="818" t="n"/>
+      <c r="O13" s="818" t="n"/>
+      <c r="P13" s="818" t="n"/>
+      <c r="Q13" s="818" t="n"/>
+      <c r="R13" s="818" t="n"/>
+      <c r="S13" s="818" t="n"/>
+      <c r="T13" s="818" t="n"/>
+      <c r="U13" s="818" t="n"/>
+      <c r="V13" s="818" t="n"/>
+      <c r="W13" s="818" t="n"/>
+      <c r="X13" s="818" t="n"/>
+      <c r="Y13" s="818" t="n"/>
+      <c r="Z13" s="818" t="n"/>
+      <c r="AA13" s="818" t="n"/>
+      <c r="AB13" s="818" t="n"/>
+      <c r="AC13" s="818" t="n"/>
+      <c r="AD13" s="818" t="n"/>
+      <c r="AE13" s="818" t="n"/>
+      <c r="AF13" s="818" t="n"/>
+      <c r="AG13" s="818" t="n"/>
+      <c r="AH13" s="818" t="n"/>
+      <c r="AI13" s="818" t="n"/>
+      <c r="AJ13" s="818" t="n"/>
+      <c r="AK13" s="818" t="n"/>
+      <c r="AL13" s="818" t="n"/>
+      <c r="AM13" s="818" t="n"/>
+      <c r="AN13" s="818" t="n"/>
+    </row>
+    <row r="14" hidden="1">
+      <c r="A14" s="818" t="n"/>
+      <c r="B14" s="818" t="n"/>
+      <c r="C14" s="818" t="n"/>
+      <c r="D14" s="818" t="n"/>
+      <c r="E14" s="818" t="n"/>
+      <c r="F14" s="818" t="n"/>
+      <c r="G14" s="818" t="n"/>
+      <c r="H14" s="818" t="n"/>
+      <c r="I14" s="818" t="n"/>
+      <c r="J14" s="818" t="n"/>
+      <c r="K14" s="818" t="n"/>
+      <c r="L14" s="818" t="n"/>
+      <c r="M14" s="818" t="n"/>
+      <c r="N14" s="818" t="n"/>
+      <c r="O14" s="818" t="n"/>
+      <c r="P14" s="818" t="n"/>
+      <c r="Q14" s="818" t="n"/>
+      <c r="R14" s="818" t="n"/>
+      <c r="S14" s="818" t="n"/>
+      <c r="T14" s="818" t="n"/>
+      <c r="U14" s="818" t="n"/>
+      <c r="V14" s="818" t="n"/>
+      <c r="W14" s="818" t="n"/>
+      <c r="X14" s="818" t="n"/>
+      <c r="Y14" s="818" t="n"/>
+      <c r="Z14" s="818" t="n"/>
+      <c r="AA14" s="818" t="n"/>
+      <c r="AB14" s="818" t="n"/>
+      <c r="AC14" s="818" t="n"/>
+      <c r="AD14" s="818" t="n"/>
+      <c r="AE14" s="818" t="n"/>
+      <c r="AF14" s="818" t="n"/>
+      <c r="AG14" s="818" t="n"/>
+      <c r="AH14" s="818" t="n"/>
+      <c r="AI14" s="818" t="n"/>
+      <c r="AJ14" s="818" t="n"/>
+      <c r="AK14" s="818" t="n"/>
+      <c r="AL14" s="818" t="n"/>
+      <c r="AM14" s="818" t="n"/>
+      <c r="AN14" s="818" t="n"/>
+    </row>
+    <row r="15" hidden="1">
+      <c r="A15" s="818" t="n"/>
+      <c r="B15" s="818" t="n"/>
+      <c r="C15" s="818" t="n"/>
+      <c r="D15" s="818" t="n"/>
+      <c r="E15" s="818" t="n"/>
+      <c r="F15" s="818" t="n"/>
+      <c r="G15" s="818" t="n"/>
+      <c r="H15" s="818" t="n"/>
+      <c r="I15" s="818" t="n"/>
+      <c r="J15" s="818" t="n"/>
+      <c r="K15" s="818" t="n"/>
+      <c r="L15" s="818" t="n"/>
+      <c r="M15" s="818" t="n"/>
+      <c r="N15" s="818" t="n"/>
+      <c r="O15" s="818" t="n"/>
+      <c r="P15" s="818" t="n"/>
+      <c r="Q15" s="818" t="n"/>
+      <c r="R15" s="818" t="n"/>
+      <c r="S15" s="818" t="n"/>
+      <c r="T15" s="818" t="n"/>
+      <c r="U15" s="818" t="n"/>
+      <c r="V15" s="818" t="n"/>
+      <c r="W15" s="818" t="n"/>
+      <c r="X15" s="818" t="n"/>
+      <c r="Y15" s="818" t="n"/>
+      <c r="Z15" s="818" t="n"/>
+      <c r="AA15" s="818" t="n"/>
+      <c r="AB15" s="818" t="n"/>
+      <c r="AC15" s="818" t="n"/>
+      <c r="AD15" s="818" t="n"/>
+      <c r="AE15" s="818" t="n"/>
+      <c r="AF15" s="818" t="n"/>
+      <c r="AG15" s="818" t="n"/>
+      <c r="AH15" s="818" t="n"/>
+      <c r="AI15" s="818" t="n"/>
+      <c r="AJ15" s="818" t="n"/>
+      <c r="AK15" s="818" t="n"/>
+      <c r="AL15" s="818" t="n"/>
+      <c r="AM15" s="818" t="n"/>
+      <c r="AN15" s="818" t="n"/>
+    </row>
+    <row r="16" hidden="1">
+      <c r="A16" s="818" t="n"/>
+      <c r="B16" s="818" t="n"/>
+      <c r="C16" s="818" t="n"/>
+      <c r="D16" s="818" t="n"/>
+      <c r="E16" s="818" t="n"/>
+      <c r="F16" s="818" t="n"/>
+      <c r="G16" s="818" t="n"/>
+      <c r="H16" s="818" t="n"/>
+      <c r="I16" s="818" t="n"/>
+      <c r="J16" s="818" t="n"/>
+      <c r="K16" s="818" t="n"/>
+      <c r="L16" s="818" t="n"/>
+      <c r="M16" s="818" t="n"/>
+      <c r="N16" s="818" t="n"/>
+      <c r="O16" s="818" t="n"/>
+      <c r="P16" s="818" t="n"/>
+      <c r="Q16" s="818" t="n"/>
+      <c r="R16" s="818" t="n"/>
+      <c r="S16" s="818" t="n"/>
+      <c r="T16" s="818" t="n"/>
+      <c r="U16" s="818" t="n"/>
+      <c r="V16" s="818" t="n"/>
+      <c r="W16" s="818" t="n"/>
+      <c r="X16" s="818" t="n"/>
+      <c r="Y16" s="818" t="n"/>
+      <c r="Z16" s="818" t="n"/>
+      <c r="AA16" s="818" t="n"/>
+      <c r="AB16" s="818" t="n"/>
+      <c r="AC16" s="818" t="n"/>
+      <c r="AD16" s="818" t="n"/>
+      <c r="AE16" s="818" t="n"/>
+      <c r="AF16" s="818" t="n"/>
+      <c r="AG16" s="818" t="n"/>
+      <c r="AH16" s="818" t="n"/>
+      <c r="AI16" s="818" t="n"/>
+      <c r="AJ16" s="818" t="n"/>
+      <c r="AK16" s="818" t="n"/>
+      <c r="AL16" s="818" t="n"/>
+      <c r="AM16" s="818" t="n"/>
+      <c r="AN16" s="818" t="n"/>
+    </row>
+    <row r="17" hidden="1">
+      <c r="A17" s="818" t="n"/>
+      <c r="B17" s="818" t="n"/>
+      <c r="C17" s="818" t="n"/>
+      <c r="D17" s="818" t="n"/>
+      <c r="E17" s="818" t="n"/>
+      <c r="F17" s="818" t="n"/>
+      <c r="G17" s="818" t="n"/>
+      <c r="H17" s="818" t="n"/>
+      <c r="I17" s="818" t="n"/>
+      <c r="J17" s="818" t="n"/>
+      <c r="K17" s="818" t="n"/>
+      <c r="L17" s="818" t="n"/>
+      <c r="M17" s="818" t="n"/>
+      <c r="N17" s="818" t="n"/>
+      <c r="O17" s="818" t="n"/>
+      <c r="P17" s="818" t="n"/>
+      <c r="Q17" s="818" t="n"/>
+      <c r="R17" s="818" t="n"/>
+      <c r="S17" s="818" t="n"/>
+      <c r="T17" s="818" t="n"/>
+      <c r="U17" s="818" t="n"/>
+      <c r="V17" s="818" t="n"/>
+      <c r="W17" s="818" t="n"/>
+      <c r="X17" s="818" t="n"/>
+      <c r="Y17" s="818" t="n"/>
+      <c r="Z17" s="818" t="n"/>
+      <c r="AA17" s="818" t="n"/>
+      <c r="AB17" s="818" t="n"/>
+      <c r="AC17" s="818" t="n"/>
+      <c r="AD17" s="818" t="n"/>
+      <c r="AE17" s="818" t="n"/>
+      <c r="AF17" s="818" t="n"/>
+      <c r="AG17" s="818" t="n"/>
+      <c r="AH17" s="818" t="n"/>
+      <c r="AI17" s="818" t="n"/>
+      <c r="AJ17" s="818" t="n"/>
+      <c r="AK17" s="818" t="n"/>
+      <c r="AL17" s="818" t="n"/>
+      <c r="AM17" s="818" t="n"/>
+      <c r="AN17" s="818" t="n"/>
+    </row>
+    <row r="18" hidden="1">
+      <c r="A18" s="818" t="n"/>
+      <c r="B18" s="818" t="n"/>
+      <c r="C18" s="818" t="n"/>
+      <c r="D18" s="818" t="n"/>
+      <c r="E18" s="818" t="n"/>
+      <c r="F18" s="818" t="n"/>
+      <c r="G18" s="818" t="n"/>
+      <c r="H18" s="818" t="n"/>
+      <c r="I18" s="818" t="n"/>
+      <c r="J18" s="818" t="n"/>
+      <c r="K18" s="818" t="n"/>
+      <c r="L18" s="818" t="n"/>
+      <c r="M18" s="818" t="n"/>
+      <c r="N18" s="818" t="n"/>
+      <c r="O18" s="818" t="n"/>
+      <c r="P18" s="818" t="n"/>
+      <c r="Q18" s="818" t="n"/>
+      <c r="R18" s="818" t="n"/>
+      <c r="S18" s="818" t="n"/>
+      <c r="T18" s="818" t="n"/>
+      <c r="U18" s="818" t="n"/>
+      <c r="V18" s="818" t="n"/>
+      <c r="W18" s="818" t="n"/>
+      <c r="X18" s="818" t="n"/>
+      <c r="Y18" s="818" t="n"/>
+      <c r="Z18" s="818" t="n"/>
+      <c r="AA18" s="818" t="n"/>
+      <c r="AB18" s="818" t="n"/>
+      <c r="AC18" s="818" t="n"/>
+      <c r="AD18" s="818" t="n"/>
+      <c r="AE18" s="818" t="n"/>
+      <c r="AF18" s="818" t="n"/>
+      <c r="AG18" s="818" t="n"/>
+      <c r="AH18" s="818" t="n"/>
+      <c r="AI18" s="818" t="n"/>
+      <c r="AJ18" s="818" t="n"/>
+      <c r="AK18" s="818" t="n"/>
+      <c r="AL18" s="818" t="n"/>
+      <c r="AM18" s="818" t="n"/>
+      <c r="AN18" s="818" t="n"/>
+    </row>
+    <row r="19" hidden="1">
+      <c r="A19" s="818" t="n"/>
+      <c r="B19" s="818" t="n"/>
+      <c r="C19" s="818" t="n"/>
+      <c r="D19" s="818" t="n"/>
+      <c r="E19" s="818" t="n"/>
+      <c r="F19" s="818" t="n"/>
+      <c r="G19" s="818" t="n"/>
+      <c r="H19" s="818" t="n"/>
+      <c r="I19" s="818" t="n"/>
+      <c r="J19" s="818" t="n"/>
+      <c r="K19" s="818" t="n"/>
+      <c r="L19" s="818" t="n"/>
+      <c r="M19" s="818" t="n"/>
+      <c r="N19" s="818" t="n"/>
+      <c r="O19" s="818" t="n"/>
+      <c r="P19" s="818" t="n"/>
+      <c r="Q19" s="818" t="n"/>
+      <c r="R19" s="818" t="n"/>
+      <c r="S19" s="818" t="n"/>
+      <c r="T19" s="818" t="n"/>
+      <c r="U19" s="818" t="n"/>
+      <c r="V19" s="818" t="n"/>
+      <c r="W19" s="818" t="n"/>
+      <c r="X19" s="818" t="n"/>
+      <c r="Y19" s="818" t="n"/>
+      <c r="Z19" s="818" t="n"/>
+      <c r="AA19" s="818" t="n"/>
+      <c r="AB19" s="818" t="n"/>
+      <c r="AC19" s="818" t="n"/>
+      <c r="AD19" s="818" t="n"/>
+      <c r="AE19" s="818" t="n"/>
+      <c r="AF19" s="818" t="n"/>
+      <c r="AG19" s="818" t="n"/>
+      <c r="AH19" s="818" t="n"/>
+      <c r="AI19" s="818" t="n"/>
+      <c r="AJ19" s="818" t="n"/>
+      <c r="AK19" s="818" t="n"/>
+      <c r="AL19" s="818" t="n"/>
+      <c r="AM19" s="818" t="n"/>
+      <c r="AN19" s="818" t="n"/>
+    </row>
+    <row r="20" hidden="1">
+      <c r="A20" s="818" t="n"/>
+      <c r="B20" s="818" t="n"/>
+      <c r="C20" s="818" t="n"/>
+      <c r="D20" s="818" t="n"/>
+      <c r="E20" s="818" t="n"/>
+      <c r="F20" s="818" t="n"/>
+      <c r="G20" s="818" t="n"/>
+      <c r="H20" s="818" t="n"/>
+      <c r="I20" s="818" t="n"/>
+      <c r="J20" s="818" t="n"/>
+      <c r="K20" s="818" t="n"/>
+      <c r="L20" s="818" t="n"/>
+      <c r="M20" s="818" t="n"/>
+      <c r="N20" s="818" t="n"/>
+      <c r="O20" s="818" t="n"/>
+      <c r="P20" s="818" t="n"/>
+      <c r="Q20" s="818" t="n"/>
+      <c r="R20" s="818" t="n"/>
+      <c r="S20" s="818" t="n"/>
+      <c r="T20" s="818" t="n"/>
+      <c r="U20" s="818" t="n"/>
+      <c r="V20" s="818" t="n"/>
+      <c r="W20" s="818" t="n"/>
+      <c r="X20" s="818" t="n"/>
+      <c r="Y20" s="818" t="n"/>
+      <c r="Z20" s="818" t="n"/>
+      <c r="AA20" s="818" t="n"/>
+      <c r="AB20" s="818" t="n"/>
+      <c r="AC20" s="818" t="n"/>
+      <c r="AD20" s="818" t="n"/>
+      <c r="AE20" s="818" t="n"/>
+      <c r="AF20" s="818" t="n"/>
+      <c r="AG20" s="818" t="n"/>
+      <c r="AH20" s="818" t="n"/>
+      <c r="AI20" s="818" t="n"/>
+      <c r="AJ20" s="818" t="n"/>
+      <c r="AK20" s="818" t="n"/>
+      <c r="AL20" s="818" t="n"/>
+      <c r="AM20" s="818" t="n"/>
+      <c r="AN20" s="818" t="n"/>
+    </row>
     <row r="21" hidden="1"/>
     <row r="22" hidden="1"/>
     <row r="23" hidden="1"/>
@@ -16695,9 +17552,23 @@
     <row r="199" hidden="1"/>
     <row r="200" hidden="1"/>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A2:G2"/>
-    <mergeCell ref="A1:G1"/>
+  <mergeCells count="16">
+    <mergeCell ref="AI2:AN2"/>
+    <mergeCell ref="A8:G8"/>
+    <mergeCell ref="I1:AD3"/>
+    <mergeCell ref="AI1:AN1"/>
+    <mergeCell ref="AE4:AH4"/>
+    <mergeCell ref="I5:AD5"/>
+    <mergeCell ref="AE3:AH3"/>
+    <mergeCell ref="AI5:AN5"/>
+    <mergeCell ref="A1:H5"/>
+    <mergeCell ref="A7:G7"/>
+    <mergeCell ref="AI4:AN4"/>
+    <mergeCell ref="AE2:AH2"/>
+    <mergeCell ref="I4:AD4"/>
+    <mergeCell ref="AI3:AN3"/>
+    <mergeCell ref="AE1:AH1"/>
+    <mergeCell ref="AE5:AH5"/>
   </mergeCells>
   <dataValidations count="2">
     <dataValidation sqref="E4:E11" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from REF_OWNER_PERSON_MASTER." prompt="Select from REF_OWNER_PERSON_MASTER." type="list">

--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -879,7 +879,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="395">
+  <borders count="399">
     <border>
       <left/>
       <right/>
@@ -5162,11 +5162,56 @@
         <color rgb="002C9CD7"/>
       </bottom>
     </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="00C5D9E8"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="002C9CD7"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="00E2E8F0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00E2E8F0"/>
+      </bottom>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="000078D4"/>
+      </left>
+      <right style="thin">
+        <color rgb="000078D4"/>
+      </right>
+      <top style="thin">
+        <color rgb="000078D4"/>
+      </top>
+      <bottom/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="819">
+  <cellXfs count="883">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7184,6 +7229,156 @@
     </xf>
     <xf numFmtId="0" fontId="94" fillId="56" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="94" fillId="0" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="358" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="350" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="87" fillId="0" borderId="316" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="369" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="8" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="10" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="6" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="6" borderId="18" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="9" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="10" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="94" fillId="4" borderId="290" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="396" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="397" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="0" borderId="377" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="13" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="51" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="89" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="85" fillId="4" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="84" fillId="4" borderId="290" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="83" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="92" fillId="4" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7284,11 +7479,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>298782</colOff>
-      <row>0</row>
-      <rowOff>275446</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="1394316" cy="402206"/>
+    <ext cx="1552575" cy="438150"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7302,9 +7497,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7317,11 +7509,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7335,9 +7527,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7350,11 +7539,11 @@
   <oneCellAnchor>
     <from>
       <col>0</col>
-      <colOff>63378</colOff>
-      <row>0</row>
-      <rowOff>442597</rowOff>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
     </from>
-    <ext cx="235404" cy="67905"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7368,9 +7557,6 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7387,7 +7573,7 @@
       <row>1</row>
       <rowOff>0</rowOff>
     </from>
-    <ext cx="1303776" cy="376089"/>
+    <ext cx="1123950" cy="323850"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -7401,9 +7587,66 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:prstDash val="solid"/>
-        </a:ln>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing5.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1123950" cy="323850"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
       </spPr>
     </pic>
     <clientData/>
@@ -7641,66 +7884,66 @@
   <dimension ref="A1:BD47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="2.329999923706055" customWidth="1" min="1" max="1"/>
-    <col width="2.329999923706055" customWidth="1" min="2" max="2"/>
-    <col width="2.329999923706055" customWidth="1" min="3" max="3"/>
-    <col width="2.329999923706055" customWidth="1" min="4" max="4"/>
-    <col width="2.329999923706055" customWidth="1" min="5" max="5"/>
-    <col width="2.329999923706055" customWidth="1" min="6" max="6"/>
-    <col width="2.329999923706055" customWidth="1" min="7" max="7"/>
-    <col width="2.329999923706055" customWidth="1" min="8" max="8"/>
-    <col width="2.329999923706055" customWidth="1" min="9" max="9"/>
-    <col width="2.329999923706055" customWidth="1" min="10" max="10"/>
-    <col width="2.329999923706055" customWidth="1" min="11" max="11"/>
-    <col width="2.329999923706055" customWidth="1" min="12" max="12"/>
-    <col width="2.329999923706055" customWidth="1" min="13" max="13"/>
-    <col width="2.329999923706055" customWidth="1" min="14" max="14"/>
-    <col width="2.329999923706055" customWidth="1" min="15" max="15"/>
-    <col width="2.329999923706055" customWidth="1" min="16" max="16"/>
-    <col width="2.329999923706055" customWidth="1" min="17" max="17"/>
-    <col width="2.329999923706055" customWidth="1" min="18" max="18"/>
-    <col width="2.329999923706055" customWidth="1" min="19" max="19"/>
-    <col width="2.329999923706055" customWidth="1" min="20" max="20"/>
-    <col width="2.329999923706055" customWidth="1" min="21" max="21"/>
-    <col width="2.329999923706055" customWidth="1" min="22" max="22"/>
-    <col width="2.329999923706055" customWidth="1" min="23" max="23"/>
-    <col width="2.329999923706055" customWidth="1" min="24" max="24"/>
-    <col width="2.329999923706055" customWidth="1" min="25" max="25"/>
-    <col width="2.329999923706055" customWidth="1" min="26" max="26"/>
-    <col width="2.329999923706055" customWidth="1" min="27" max="27"/>
-    <col width="2.329999923706055" customWidth="1" min="28" max="28"/>
-    <col width="2.329999923706055" customWidth="1" min="29" max="29"/>
-    <col width="2.329999923706055" customWidth="1" min="30" max="30"/>
-    <col width="2.329999923706055" customWidth="1" min="31" max="31"/>
-    <col width="2.329999923706055" customWidth="1" min="32" max="32"/>
-    <col width="2.329999923706055" customWidth="1" min="33" max="33"/>
-    <col width="2.329999923706055" customWidth="1" min="34" max="34"/>
-    <col width="2.329999923706055" customWidth="1" min="35" max="35"/>
-    <col width="2.329999923706055" customWidth="1" min="36" max="36"/>
-    <col width="2.329999923706055" customWidth="1" min="37" max="37"/>
-    <col width="2.329999923706055" customWidth="1" min="38" max="38"/>
-    <col width="2.329999923706055" customWidth="1" min="39" max="39"/>
-    <col width="2.329999923706055" customWidth="1" min="40" max="40"/>
-    <col width="2.329999923706055" customWidth="1" min="41" max="41"/>
-    <col width="2.329999923706055" customWidth="1" min="42" max="42"/>
-    <col width="2.329999923706055" customWidth="1" min="43" max="43"/>
-    <col width="2.329999923706055" customWidth="1" min="44" max="44"/>
-    <col width="2.329999923706055" customWidth="1" min="45" max="45"/>
-    <col width="2.329999923706055" customWidth="1" min="46" max="46"/>
-    <col width="2.329999923706055" customWidth="1" min="47" max="47"/>
-    <col width="2.329999923706055" customWidth="1" min="48" max="48"/>
-    <col width="2.329999923706055" customWidth="1" min="49" max="49"/>
-    <col width="2.329999923706055" customWidth="1" min="50" max="50"/>
-    <col width="2.329999923706055" customWidth="1" min="51" max="51"/>
-    <col width="2.329999923706055" customWidth="1" min="52" max="52"/>
-    <col width="2.329999923706055" customWidth="1" min="53" max="53"/>
-    <col width="2.329999923706055" customWidth="1" min="54" max="54"/>
-    <col width="2.329999923706055" customWidth="1" min="55" max="55"/>
-    <col width="2.329999923706055" customWidth="1" min="56" max="56"/>
+    <col width="2.33" customWidth="1" min="1" max="1"/>
+    <col width="2.33" customWidth="1" min="2" max="2"/>
+    <col width="2.33" customWidth="1" min="3" max="3"/>
+    <col width="2.33" customWidth="1" min="4" max="4"/>
+    <col width="2.33" customWidth="1" min="5" max="5"/>
+    <col width="2.33" customWidth="1" min="6" max="6"/>
+    <col width="2.33" customWidth="1" min="7" max="7"/>
+    <col width="2.33" customWidth="1" min="8" max="8"/>
+    <col width="2.33" customWidth="1" min="9" max="9"/>
+    <col width="2.33" customWidth="1" min="10" max="10"/>
+    <col width="2.33" customWidth="1" min="11" max="11"/>
+    <col width="2.33" customWidth="1" min="12" max="12"/>
+    <col width="2.33" customWidth="1" min="13" max="13"/>
+    <col width="2.33" customWidth="1" min="14" max="14"/>
+    <col width="2.33" customWidth="1" min="15" max="15"/>
+    <col width="2.33" customWidth="1" min="16" max="16"/>
+    <col width="2.33" customWidth="1" min="17" max="17"/>
+    <col width="2.33" customWidth="1" min="18" max="18"/>
+    <col width="2.33" customWidth="1" min="19" max="19"/>
+    <col width="2.33" customWidth="1" min="20" max="20"/>
+    <col width="2.33" customWidth="1" min="21" max="21"/>
+    <col width="2.33" customWidth="1" min="22" max="22"/>
+    <col width="2.33" customWidth="1" min="23" max="23"/>
+    <col width="2.33" customWidth="1" min="24" max="24"/>
+    <col width="2.33" customWidth="1" min="25" max="25"/>
+    <col width="2.33" customWidth="1" min="26" max="26"/>
+    <col width="2.33" customWidth="1" min="27" max="27"/>
+    <col width="2.33" customWidth="1" min="28" max="28"/>
+    <col width="2.33" customWidth="1" min="29" max="29"/>
+    <col width="2.33" customWidth="1" min="30" max="30"/>
+    <col width="2.33" customWidth="1" min="31" max="31"/>
+    <col width="2.33" customWidth="1" min="32" max="32"/>
+    <col width="2.33" customWidth="1" min="33" max="33"/>
+    <col width="2.33" customWidth="1" min="34" max="34"/>
+    <col width="2.33" customWidth="1" min="35" max="35"/>
+    <col width="2.33" customWidth="1" min="36" max="36"/>
+    <col width="2.33" customWidth="1" min="37" max="37"/>
+    <col width="2.33" customWidth="1" min="38" max="38"/>
+    <col width="2.33" customWidth="1" min="39" max="39"/>
+    <col width="2.33" customWidth="1" min="40" max="40"/>
+    <col width="2.33" customWidth="1" min="41" max="41"/>
+    <col width="2.33" customWidth="1" min="42" max="42"/>
+    <col width="2.33" customWidth="1" min="43" max="43"/>
+    <col width="2.33" customWidth="1" min="44" max="44"/>
+    <col width="2.33" customWidth="1" min="45" max="45"/>
+    <col width="2.33" customWidth="1" min="46" max="46"/>
+    <col width="2.33" customWidth="1" min="47" max="47"/>
+    <col width="2.33" customWidth="1" min="48" max="48"/>
+    <col width="2.33" customWidth="1" min="49" max="49"/>
+    <col width="2.33" customWidth="1" min="50" max="50"/>
+    <col width="2.33" customWidth="1" min="51" max="51"/>
+    <col width="2.33" customWidth="1" min="52" max="52"/>
+    <col width="2.33" customWidth="1" min="53" max="53"/>
+    <col width="2.33" customWidth="1" min="54" max="54"/>
+    <col width="2.33" customWidth="1" min="55" max="55"/>
+    <col width="2.33" customWidth="1" min="56" max="56"/>
     <col hidden="1" outlineLevel="1" width="13" customWidth="1" min="57" max="16384"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="753" t="inlineStr"/>
       <c r="B1" s="268" t="n"/>
       <c r="C1" s="268" t="n"/>
@@ -7712,7 +7955,7 @@
       <c r="I1" s="268" t="n"/>
       <c r="J1" s="268" t="n"/>
       <c r="K1" s="323" t="n"/>
-      <c r="L1" s="649" t="inlineStr">
+      <c r="L1" s="882" t="inlineStr">
         <is>
           <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
         </is>
@@ -7746,7 +7989,7 @@
       <c r="AM1" s="268" t="n"/>
       <c r="AN1" s="268" t="n"/>
       <c r="AO1" s="268" t="n"/>
-      <c r="AP1" s="268" t="n"/>
+      <c r="AP1" s="323" t="n"/>
       <c r="AQ1" s="754" t="inlineStr">
         <is>
           <t>Form Code</t>
@@ -7771,279 +8014,392 @@
       <c r="BD1" s="323" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="K2" s="324" t="n"/>
-      <c r="L2" s="275" t="n"/>
-      <c r="AQ2" s="756" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="819" t="n"/>
+      <c r="G2" s="819" t="n"/>
+      <c r="H2" s="819" t="n"/>
+      <c r="I2" s="819" t="n"/>
+      <c r="J2" s="819" t="n"/>
+      <c r="K2" s="820" t="n"/>
+      <c r="L2" s="819" t="n"/>
+      <c r="M2" s="819" t="n"/>
+      <c r="N2" s="819" t="n"/>
+      <c r="O2" s="819" t="n"/>
+      <c r="P2" s="819" t="n"/>
+      <c r="Q2" s="819" t="n"/>
+      <c r="R2" s="819" t="n"/>
+      <c r="S2" s="819" t="n"/>
+      <c r="T2" s="819" t="n"/>
+      <c r="U2" s="819" t="n"/>
+      <c r="V2" s="819" t="n"/>
+      <c r="W2" s="819" t="n"/>
+      <c r="X2" s="819" t="n"/>
+      <c r="Y2" s="819" t="n"/>
+      <c r="Z2" s="819" t="n"/>
+      <c r="AA2" s="819" t="n"/>
+      <c r="AB2" s="819" t="n"/>
+      <c r="AC2" s="819" t="n"/>
+      <c r="AD2" s="819" t="n"/>
+      <c r="AE2" s="819" t="n"/>
+      <c r="AF2" s="819" t="n"/>
+      <c r="AG2" s="819" t="n"/>
+      <c r="AH2" s="819" t="n"/>
+      <c r="AI2" s="819" t="n"/>
+      <c r="AJ2" s="819" t="n"/>
+      <c r="AK2" s="819" t="n"/>
+      <c r="AL2" s="819" t="n"/>
+      <c r="AM2" s="819" t="n"/>
+      <c r="AN2" s="819" t="n"/>
+      <c r="AO2" s="819" t="n"/>
+      <c r="AP2" s="820" t="n"/>
+      <c r="AQ2" s="821" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="757" t="n"/>
-      <c r="AS2" s="757" t="n"/>
-      <c r="AT2" s="757" t="n"/>
-      <c r="AU2" s="757" t="n"/>
-      <c r="AV2" s="758" t="n"/>
-      <c r="AW2" s="706" t="inlineStr">
+      <c r="AR2" s="822" t="n"/>
+      <c r="AS2" s="822" t="n"/>
+      <c r="AT2" s="822" t="n"/>
+      <c r="AU2" s="822" t="n"/>
+      <c r="AV2" s="823" t="n"/>
+      <c r="AW2" s="824" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="757" t="n"/>
-      <c r="AY2" s="757" t="n"/>
-      <c r="AZ2" s="757" t="n"/>
-      <c r="BA2" s="757" t="n"/>
-      <c r="BB2" s="757" t="n"/>
-      <c r="BC2" s="757" t="n"/>
-      <c r="BD2" s="759" t="n"/>
+      <c r="AX2" s="825" t="n"/>
+      <c r="AY2" s="825" t="n"/>
+      <c r="AZ2" s="825" t="n"/>
+      <c r="BA2" s="825" t="n"/>
+      <c r="BB2" s="825" t="n"/>
+      <c r="BC2" s="825" t="n"/>
+      <c r="BD2" s="826" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="K3" s="324" t="n"/>
-      <c r="L3" s="275" t="n"/>
-      <c r="AQ3" s="756" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="25" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="828" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="25" t="n"/>
+      <c r="AE3" s="25" t="n"/>
+      <c r="AF3" s="25" t="n"/>
+      <c r="AG3" s="25" t="n"/>
+      <c r="AH3" s="25" t="n"/>
+      <c r="AI3" s="25" t="n"/>
+      <c r="AJ3" s="25" t="n"/>
+      <c r="AK3" s="25" t="n"/>
+      <c r="AL3" s="25" t="n"/>
+      <c r="AM3" s="25" t="n"/>
+      <c r="AN3" s="25" t="n"/>
+      <c r="AO3" s="25" t="n"/>
+      <c r="AP3" s="828" t="n"/>
+      <c r="AQ3" s="829" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="757" t="n"/>
-      <c r="AS3" s="757" t="n"/>
-      <c r="AT3" s="757" t="n"/>
-      <c r="AU3" s="757" t="n"/>
-      <c r="AV3" s="758" t="n"/>
-      <c r="AW3" s="706" t="inlineStr">
+      <c r="AR3" s="830" t="n"/>
+      <c r="AS3" s="830" t="n"/>
+      <c r="AT3" s="830" t="n"/>
+      <c r="AU3" s="830" t="n"/>
+      <c r="AV3" s="831" t="n"/>
+      <c r="AW3" s="724" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="757" t="n"/>
-      <c r="AY3" s="757" t="n"/>
-      <c r="AZ3" s="757" t="n"/>
-      <c r="BA3" s="757" t="n"/>
-      <c r="BB3" s="757" t="n"/>
-      <c r="BC3" s="757" t="n"/>
-      <c r="BD3" s="759" t="n"/>
+      <c r="AX3" s="832" t="n"/>
+      <c r="AY3" s="832" t="n"/>
+      <c r="AZ3" s="832" t="n"/>
+      <c r="BA3" s="832" t="n"/>
+      <c r="BB3" s="832" t="n"/>
+      <c r="BC3" s="832" t="n"/>
+      <c r="BD3" s="833" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="K4" s="324" t="n"/>
-      <c r="L4" s="658" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="25" t="n"/>
+      <c r="I4" s="25" t="n"/>
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="828" t="n"/>
+      <c r="L4" s="346" t="inlineStr">
         <is>
           <t>Quality Management System  ?  Controlled Document</t>
         </is>
       </c>
-      <c r="AQ4" s="756" t="inlineStr">
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="25" t="n"/>
+      <c r="AE4" s="25" t="n"/>
+      <c r="AF4" s="25" t="n"/>
+      <c r="AG4" s="25" t="n"/>
+      <c r="AH4" s="25" t="n"/>
+      <c r="AI4" s="25" t="n"/>
+      <c r="AJ4" s="25" t="n"/>
+      <c r="AK4" s="25" t="n"/>
+      <c r="AL4" s="25" t="n"/>
+      <c r="AM4" s="25" t="n"/>
+      <c r="AN4" s="25" t="n"/>
+      <c r="AO4" s="25" t="n"/>
+      <c r="AP4" s="828" t="n"/>
+      <c r="AQ4" s="829" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="757" t="n"/>
-      <c r="AS4" s="757" t="n"/>
-      <c r="AT4" s="757" t="n"/>
-      <c r="AU4" s="757" t="n"/>
-      <c r="AV4" s="758" t="n"/>
-      <c r="AW4" s="706" t="inlineStr">
+      <c r="AR4" s="830" t="n"/>
+      <c r="AS4" s="830" t="n"/>
+      <c r="AT4" s="830" t="n"/>
+      <c r="AU4" s="830" t="n"/>
+      <c r="AV4" s="831" t="n"/>
+      <c r="AW4" s="724" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AX4" s="757" t="n"/>
-      <c r="AY4" s="757" t="n"/>
-      <c r="AZ4" s="757" t="n"/>
-      <c r="BA4" s="757" t="n"/>
-      <c r="BB4" s="757" t="n"/>
-      <c r="BC4" s="757" t="n"/>
-      <c r="BD4" s="759" t="n"/>
+      <c r="AX4" s="832" t="n"/>
+      <c r="AY4" s="832" t="n"/>
+      <c r="AZ4" s="832" t="n"/>
+      <c r="BA4" s="832" t="n"/>
+      <c r="BB4" s="832" t="n"/>
+      <c r="BC4" s="832" t="n"/>
+      <c r="BD4" s="833" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="283" t="n"/>
-      <c r="C5" s="283" t="n"/>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="283" t="n"/>
-      <c r="H5" s="283" t="n"/>
-      <c r="I5" s="283" t="n"/>
-      <c r="J5" s="283" t="n"/>
-      <c r="K5" s="287" t="n"/>
-      <c r="L5" s="20" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="25" t="n"/>
+      <c r="I5" s="25" t="n"/>
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="828" t="n"/>
+      <c r="L5" s="595" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="283" t="n"/>
-      <c r="N5" s="283" t="n"/>
-      <c r="O5" s="283" t="n"/>
-      <c r="P5" s="283" t="n"/>
-      <c r="Q5" s="283" t="n"/>
-      <c r="R5" s="283" t="n"/>
-      <c r="S5" s="283" t="n"/>
-      <c r="T5" s="283" t="n"/>
-      <c r="U5" s="283" t="n"/>
-      <c r="V5" s="283" t="n"/>
-      <c r="W5" s="283" t="n"/>
-      <c r="X5" s="283" t="n"/>
-      <c r="Y5" s="283" t="n"/>
-      <c r="Z5" s="283" t="n"/>
-      <c r="AA5" s="283" t="n"/>
-      <c r="AB5" s="283" t="n"/>
-      <c r="AC5" s="283" t="n"/>
-      <c r="AD5" s="283" t="n"/>
-      <c r="AE5" s="283" t="n"/>
-      <c r="AF5" s="283" t="n"/>
-      <c r="AG5" s="283" t="n"/>
-      <c r="AH5" s="283" t="n"/>
-      <c r="AI5" s="283" t="n"/>
-      <c r="AJ5" s="283" t="n"/>
-      <c r="AK5" s="283" t="n"/>
-      <c r="AL5" s="283" t="n"/>
-      <c r="AM5" s="283" t="n"/>
-      <c r="AN5" s="283" t="n"/>
-      <c r="AO5" s="283" t="n"/>
-      <c r="AP5" s="283" t="n"/>
-      <c r="AQ5" s="760" t="inlineStr">
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="25" t="n"/>
+      <c r="AE5" s="25" t="n"/>
+      <c r="AF5" s="25" t="n"/>
+      <c r="AG5" s="25" t="n"/>
+      <c r="AH5" s="25" t="n"/>
+      <c r="AI5" s="25" t="n"/>
+      <c r="AJ5" s="25" t="n"/>
+      <c r="AK5" s="25" t="n"/>
+      <c r="AL5" s="25" t="n"/>
+      <c r="AM5" s="25" t="n"/>
+      <c r="AN5" s="25" t="n"/>
+      <c r="AO5" s="25" t="n"/>
+      <c r="AP5" s="828" t="n"/>
+      <c r="AQ5" s="829" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="761" t="n"/>
-      <c r="AS5" s="761" t="n"/>
-      <c r="AT5" s="761" t="n"/>
-      <c r="AU5" s="761" t="n"/>
-      <c r="AV5" s="762" t="n"/>
-      <c r="AW5" s="714" t="inlineStr">
+      <c r="AR5" s="830" t="n"/>
+      <c r="AS5" s="830" t="n"/>
+      <c r="AT5" s="830" t="n"/>
+      <c r="AU5" s="830" t="n"/>
+      <c r="AV5" s="831" t="n"/>
+      <c r="AW5" s="724" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AX5" s="761" t="n"/>
-      <c r="AY5" s="761" t="n"/>
-      <c r="AZ5" s="761" t="n"/>
-      <c r="BA5" s="761" t="n"/>
-      <c r="BB5" s="761" t="n"/>
-      <c r="BC5" s="761" t="n"/>
-      <c r="BD5" s="763" t="n"/>
+      <c r="AX5" s="832" t="n"/>
+      <c r="AY5" s="832" t="n"/>
+      <c r="AZ5" s="832" t="n"/>
+      <c r="BA5" s="832" t="n"/>
+      <c r="BB5" s="832" t="n"/>
+      <c r="BC5" s="832" t="n"/>
+      <c r="BD5" s="833" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="664" t="n"/>
-      <c r="B6" s="664" t="n"/>
-      <c r="C6" s="664" t="n"/>
-      <c r="D6" s="664" t="n"/>
-      <c r="E6" s="664" t="n"/>
-      <c r="F6" s="664" t="n"/>
-      <c r="G6" s="664" t="n"/>
-      <c r="H6" s="664" t="n"/>
-      <c r="I6" s="664" t="n"/>
-      <c r="J6" s="664" t="n"/>
-      <c r="K6" s="664" t="n"/>
-      <c r="L6" s="664" t="n"/>
-      <c r="M6" s="664" t="n"/>
-      <c r="N6" s="664" t="n"/>
-      <c r="O6" s="664" t="n"/>
-      <c r="P6" s="664" t="n"/>
-      <c r="Q6" s="664" t="n"/>
-      <c r="R6" s="664" t="n"/>
-      <c r="S6" s="664" t="n"/>
-      <c r="T6" s="664" t="n"/>
-      <c r="U6" s="664" t="n"/>
-      <c r="V6" s="664" t="n"/>
-      <c r="W6" s="664" t="n"/>
-      <c r="X6" s="664" t="n"/>
-      <c r="Y6" s="664" t="n"/>
-      <c r="Z6" s="664" t="n"/>
-      <c r="AA6" s="664" t="n"/>
-      <c r="AB6" s="664" t="n"/>
-      <c r="AC6" s="664" t="n"/>
-      <c r="AD6" s="664" t="n"/>
-      <c r="AE6" s="664" t="n"/>
-      <c r="AF6" s="664" t="n"/>
-      <c r="AG6" s="664" t="n"/>
-      <c r="AH6" s="664" t="n"/>
-      <c r="AI6" s="664" t="n"/>
-      <c r="AJ6" s="664" t="n"/>
-      <c r="AK6" s="664" t="n"/>
-      <c r="AL6" s="664" t="n"/>
-      <c r="AM6" s="664" t="n"/>
-      <c r="AN6" s="664" t="n"/>
-      <c r="AO6" s="664" t="n"/>
-      <c r="AP6" s="664" t="n"/>
-      <c r="AQ6" s="664" t="n"/>
-      <c r="AR6" s="664" t="n"/>
-      <c r="AS6" s="664" t="n"/>
-      <c r="AT6" s="664" t="n"/>
-      <c r="AU6" s="664" t="n"/>
-      <c r="AV6" s="664" t="n"/>
-      <c r="AW6" s="664" t="n"/>
-      <c r="AX6" s="664" t="n"/>
-      <c r="AY6" s="664" t="n"/>
-      <c r="AZ6" s="664" t="n"/>
-      <c r="BA6" s="664" t="n"/>
-      <c r="BB6" s="664" t="n"/>
-      <c r="BC6" s="664" t="n"/>
-      <c r="BD6" s="664" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="834" t="n"/>
+      <c r="B6" s="835" t="n"/>
+      <c r="C6" s="835" t="n"/>
+      <c r="D6" s="835" t="n"/>
+      <c r="E6" s="835" t="n"/>
+      <c r="F6" s="835" t="n"/>
+      <c r="G6" s="835" t="n"/>
+      <c r="H6" s="835" t="n"/>
+      <c r="I6" s="835" t="n"/>
+      <c r="J6" s="835" t="n"/>
+      <c r="K6" s="836" t="n"/>
+      <c r="L6" s="835" t="n"/>
+      <c r="M6" s="835" t="n"/>
+      <c r="N6" s="835" t="n"/>
+      <c r="O6" s="835" t="n"/>
+      <c r="P6" s="835" t="n"/>
+      <c r="Q6" s="835" t="n"/>
+      <c r="R6" s="835" t="n"/>
+      <c r="S6" s="835" t="n"/>
+      <c r="T6" s="835" t="n"/>
+      <c r="U6" s="835" t="n"/>
+      <c r="V6" s="835" t="n"/>
+      <c r="W6" s="835" t="n"/>
+      <c r="X6" s="835" t="n"/>
+      <c r="Y6" s="835" t="n"/>
+      <c r="Z6" s="835" t="n"/>
+      <c r="AA6" s="835" t="n"/>
+      <c r="AB6" s="835" t="n"/>
+      <c r="AC6" s="835" t="n"/>
+      <c r="AD6" s="835" t="n"/>
+      <c r="AE6" s="835" t="n"/>
+      <c r="AF6" s="835" t="n"/>
+      <c r="AG6" s="835" t="n"/>
+      <c r="AH6" s="835" t="n"/>
+      <c r="AI6" s="835" t="n"/>
+      <c r="AJ6" s="835" t="n"/>
+      <c r="AK6" s="835" t="n"/>
+      <c r="AL6" s="835" t="n"/>
+      <c r="AM6" s="835" t="n"/>
+      <c r="AN6" s="835" t="n"/>
+      <c r="AO6" s="835" t="n"/>
+      <c r="AP6" s="836" t="n"/>
+      <c r="AQ6" s="837" t="n"/>
+      <c r="AR6" s="837" t="n"/>
+      <c r="AS6" s="837" t="n"/>
+      <c r="AT6" s="837" t="n"/>
+      <c r="AU6" s="837" t="n"/>
+      <c r="AV6" s="838" t="n"/>
+      <c r="AW6" s="839" t="n"/>
+      <c r="AX6" s="839" t="n"/>
+      <c r="AY6" s="839" t="n"/>
+      <c r="AZ6" s="839" t="n"/>
+      <c r="BA6" s="839" t="n"/>
+      <c r="BB6" s="839" t="n"/>
+      <c r="BC6" s="839" t="n"/>
+      <c r="BD6" s="840" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="764" t="inlineStr">
-        <is>
-          <t>1.  WITHDRAWAL HEADER / CHANGE CONTEXT</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="289" t="n"/>
-      <c r="J7" s="289" t="n"/>
-      <c r="K7" s="289" t="n"/>
-      <c r="L7" s="289" t="n"/>
-      <c r="M7" s="289" t="n"/>
-      <c r="N7" s="289" t="n"/>
-      <c r="O7" s="289" t="n"/>
-      <c r="P7" s="289" t="n"/>
-      <c r="Q7" s="289" t="n"/>
-      <c r="R7" s="289" t="n"/>
-      <c r="S7" s="289" t="n"/>
-      <c r="T7" s="289" t="n"/>
-      <c r="U7" s="289" t="n"/>
-      <c r="V7" s="289" t="n"/>
-      <c r="W7" s="289" t="n"/>
-      <c r="X7" s="289" t="n"/>
-      <c r="Y7" s="289" t="n"/>
-      <c r="Z7" s="289" t="n"/>
-      <c r="AA7" s="289" t="n"/>
-      <c r="AB7" s="289" t="n"/>
-      <c r="AC7" s="289" t="n"/>
-      <c r="AD7" s="289" t="n"/>
-      <c r="AE7" s="289" t="n"/>
-      <c r="AF7" s="289" t="n"/>
-      <c r="AG7" s="289" t="n"/>
-      <c r="AH7" s="289" t="n"/>
-      <c r="AI7" s="289" t="n"/>
-      <c r="AJ7" s="289" t="n"/>
-      <c r="AK7" s="289" t="n"/>
-      <c r="AL7" s="289" t="n"/>
-      <c r="AM7" s="289" t="n"/>
-      <c r="AN7" s="289" t="n"/>
-      <c r="AO7" s="289" t="n"/>
-      <c r="AP7" s="289" t="n"/>
-      <c r="AQ7" s="289" t="n"/>
-      <c r="AR7" s="289" t="n"/>
-      <c r="AS7" s="289" t="n"/>
-      <c r="AT7" s="289" t="n"/>
-      <c r="AU7" s="289" t="n"/>
-      <c r="AV7" s="289" t="n"/>
-      <c r="AW7" s="289" t="n"/>
-      <c r="AX7" s="289" t="n"/>
-      <c r="AY7" s="289" t="n"/>
-      <c r="AZ7" s="289" t="n"/>
-      <c r="BA7" s="289" t="n"/>
-      <c r="BB7" s="289" t="n"/>
-      <c r="BC7" s="289" t="n"/>
-      <c r="BD7" s="290" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="841" t="n"/>
+      <c r="B7" s="842" t="n"/>
+      <c r="C7" s="842" t="n"/>
+      <c r="D7" s="842" t="n"/>
+      <c r="E7" s="842" t="n"/>
+      <c r="F7" s="842" t="n"/>
+      <c r="G7" s="842" t="n"/>
+      <c r="H7" s="842" t="n"/>
+      <c r="I7" s="842" t="n"/>
+      <c r="J7" s="842" t="n"/>
+      <c r="K7" s="842" t="n"/>
+      <c r="L7" s="842" t="n"/>
+      <c r="M7" s="842" t="n"/>
+      <c r="N7" s="842" t="n"/>
+      <c r="O7" s="842" t="n"/>
+      <c r="P7" s="842" t="n"/>
+      <c r="Q7" s="842" t="n"/>
+      <c r="R7" s="842" t="n"/>
+      <c r="S7" s="842" t="n"/>
+      <c r="T7" s="842" t="n"/>
+      <c r="U7" s="842" t="n"/>
+      <c r="V7" s="842" t="n"/>
+      <c r="W7" s="842" t="n"/>
+      <c r="X7" s="842" t="n"/>
+      <c r="Y7" s="842" t="n"/>
+      <c r="Z7" s="842" t="n"/>
+      <c r="AA7" s="842" t="n"/>
+      <c r="AB7" s="842" t="n"/>
+      <c r="AC7" s="842" t="n"/>
+      <c r="AD7" s="842" t="n"/>
+      <c r="AE7" s="842" t="n"/>
+      <c r="AF7" s="842" t="n"/>
+      <c r="AG7" s="842" t="n"/>
+      <c r="AH7" s="842" t="n"/>
+      <c r="AI7" s="842" t="n"/>
+      <c r="AJ7" s="842" t="n"/>
+      <c r="AK7" s="842" t="n"/>
+      <c r="AL7" s="842" t="n"/>
+      <c r="AM7" s="842" t="n"/>
+      <c r="AN7" s="842" t="n"/>
+      <c r="AO7" s="842" t="n"/>
+      <c r="AP7" s="842" t="n"/>
+      <c r="AQ7" s="842" t="n"/>
+      <c r="AR7" s="842" t="n"/>
+      <c r="AS7" s="842" t="n"/>
+      <c r="AT7" s="842" t="n"/>
+      <c r="AU7" s="842" t="n"/>
+      <c r="AV7" s="842" t="n"/>
+      <c r="AW7" s="842" t="n"/>
+      <c r="AX7" s="842" t="n"/>
+      <c r="AY7" s="842" t="n"/>
+      <c r="AZ7" s="842" t="n"/>
+      <c r="BA7" s="842" t="n"/>
+      <c r="BB7" s="842" t="n"/>
+      <c r="BC7" s="842" t="n"/>
+      <c r="BD7" s="842" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="765" t="inlineStr">
@@ -8377,61 +8733,61 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="672" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
-      <c r="I13" s="10" t="n"/>
-      <c r="J13" s="10" t="n"/>
-      <c r="K13" s="10" t="n"/>
-      <c r="L13" s="10" t="n"/>
-      <c r="M13" s="10" t="n"/>
-      <c r="N13" s="10" t="n"/>
-      <c r="O13" s="10" t="n"/>
-      <c r="P13" s="10" t="n"/>
-      <c r="Q13" s="10" t="n"/>
-      <c r="R13" s="10" t="n"/>
-      <c r="S13" s="10" t="n"/>
-      <c r="T13" s="10" t="n"/>
-      <c r="U13" s="10" t="n"/>
-      <c r="V13" s="10" t="n"/>
-      <c r="W13" s="10" t="n"/>
-      <c r="X13" s="10" t="n"/>
-      <c r="Y13" s="10" t="n"/>
-      <c r="Z13" s="10" t="n"/>
-      <c r="AA13" s="10" t="n"/>
-      <c r="AB13" s="10" t="n"/>
-      <c r="AC13" s="10" t="n"/>
-      <c r="AD13" s="10" t="n"/>
-      <c r="AE13" s="10" t="n"/>
-      <c r="AF13" s="10" t="n"/>
-      <c r="AG13" s="10" t="n"/>
-      <c r="AH13" s="10" t="n"/>
-      <c r="AI13" s="10" t="n"/>
-      <c r="AJ13" s="10" t="n"/>
-      <c r="AK13" s="10" t="n"/>
-      <c r="AL13" s="10" t="n"/>
-      <c r="AM13" s="10" t="n"/>
-      <c r="AN13" s="10" t="n"/>
-      <c r="AO13" s="10" t="n"/>
-      <c r="AP13" s="10" t="n"/>
-      <c r="AQ13" s="10" t="n"/>
-      <c r="AR13" s="10" t="n"/>
-      <c r="AS13" s="10" t="n"/>
-      <c r="AT13" s="10" t="n"/>
-      <c r="AU13" s="10" t="n"/>
-      <c r="AV13" s="10" t="n"/>
-      <c r="AW13" s="10" t="n"/>
-      <c r="AX13" s="10" t="n"/>
-      <c r="AY13" s="10" t="n"/>
-      <c r="AZ13" s="10" t="n"/>
-      <c r="BA13" s="10" t="n"/>
-      <c r="BB13" s="10" t="n"/>
-      <c r="BC13" s="10" t="n"/>
-      <c r="BD13" s="10" t="n"/>
+      <c r="B13" s="672" t="n"/>
+      <c r="C13" s="672" t="n"/>
+      <c r="D13" s="672" t="n"/>
+      <c r="E13" s="672" t="n"/>
+      <c r="F13" s="672" t="n"/>
+      <c r="G13" s="672" t="n"/>
+      <c r="H13" s="672" t="n"/>
+      <c r="I13" s="672" t="n"/>
+      <c r="J13" s="672" t="n"/>
+      <c r="K13" s="672" t="n"/>
+      <c r="L13" s="672" t="n"/>
+      <c r="M13" s="672" t="n"/>
+      <c r="N13" s="672" t="n"/>
+      <c r="O13" s="672" t="n"/>
+      <c r="P13" s="672" t="n"/>
+      <c r="Q13" s="672" t="n"/>
+      <c r="R13" s="672" t="n"/>
+      <c r="S13" s="672" t="n"/>
+      <c r="T13" s="672" t="n"/>
+      <c r="U13" s="672" t="n"/>
+      <c r="V13" s="672" t="n"/>
+      <c r="W13" s="672" t="n"/>
+      <c r="X13" s="672" t="n"/>
+      <c r="Y13" s="672" t="n"/>
+      <c r="Z13" s="672" t="n"/>
+      <c r="AA13" s="672" t="n"/>
+      <c r="AB13" s="672" t="n"/>
+      <c r="AC13" s="672" t="n"/>
+      <c r="AD13" s="672" t="n"/>
+      <c r="AE13" s="672" t="n"/>
+      <c r="AF13" s="672" t="n"/>
+      <c r="AG13" s="672" t="n"/>
+      <c r="AH13" s="672" t="n"/>
+      <c r="AI13" s="672" t="n"/>
+      <c r="AJ13" s="672" t="n"/>
+      <c r="AK13" s="672" t="n"/>
+      <c r="AL13" s="672" t="n"/>
+      <c r="AM13" s="672" t="n"/>
+      <c r="AN13" s="672" t="n"/>
+      <c r="AO13" s="672" t="n"/>
+      <c r="AP13" s="672" t="n"/>
+      <c r="AQ13" s="672" t="n"/>
+      <c r="AR13" s="672" t="n"/>
+      <c r="AS13" s="672" t="n"/>
+      <c r="AT13" s="672" t="n"/>
+      <c r="AU13" s="672" t="n"/>
+      <c r="AV13" s="672" t="n"/>
+      <c r="AW13" s="672" t="n"/>
+      <c r="AX13" s="672" t="n"/>
+      <c r="AY13" s="672" t="n"/>
+      <c r="AZ13" s="672" t="n"/>
+      <c r="BA13" s="672" t="n"/>
+      <c r="BB13" s="672" t="n"/>
+      <c r="BC13" s="672" t="n"/>
+      <c r="BD13" s="672" t="n"/>
     </row>
     <row r="14" ht="18" customHeight="1">
       <c r="A14" s="764" t="inlineStr">
@@ -8767,61 +9123,61 @@
     </row>
     <row r="19" ht="3" customHeight="1">
       <c r="A19" s="672" t="n"/>
-      <c r="B19" s="10" t="n"/>
-      <c r="C19" s="10" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="10" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="10" t="n"/>
-      <c r="I19" s="10" t="n"/>
-      <c r="J19" s="10" t="n"/>
-      <c r="K19" s="10" t="n"/>
-      <c r="L19" s="10" t="n"/>
-      <c r="M19" s="10" t="n"/>
-      <c r="N19" s="10" t="n"/>
-      <c r="O19" s="10" t="n"/>
-      <c r="P19" s="10" t="n"/>
-      <c r="Q19" s="10" t="n"/>
-      <c r="R19" s="10" t="n"/>
-      <c r="S19" s="10" t="n"/>
-      <c r="T19" s="10" t="n"/>
-      <c r="U19" s="10" t="n"/>
-      <c r="V19" s="10" t="n"/>
-      <c r="W19" s="10" t="n"/>
-      <c r="X19" s="10" t="n"/>
-      <c r="Y19" s="10" t="n"/>
-      <c r="Z19" s="10" t="n"/>
-      <c r="AA19" s="10" t="n"/>
-      <c r="AB19" s="10" t="n"/>
-      <c r="AC19" s="10" t="n"/>
-      <c r="AD19" s="10" t="n"/>
-      <c r="AE19" s="10" t="n"/>
-      <c r="AF19" s="10" t="n"/>
-      <c r="AG19" s="10" t="n"/>
-      <c r="AH19" s="10" t="n"/>
-      <c r="AI19" s="10" t="n"/>
-      <c r="AJ19" s="10" t="n"/>
-      <c r="AK19" s="10" t="n"/>
-      <c r="AL19" s="10" t="n"/>
-      <c r="AM19" s="10" t="n"/>
-      <c r="AN19" s="10" t="n"/>
-      <c r="AO19" s="10" t="n"/>
-      <c r="AP19" s="10" t="n"/>
-      <c r="AQ19" s="10" t="n"/>
-      <c r="AR19" s="10" t="n"/>
-      <c r="AS19" s="10" t="n"/>
-      <c r="AT19" s="10" t="n"/>
-      <c r="AU19" s="10" t="n"/>
-      <c r="AV19" s="10" t="n"/>
-      <c r="AW19" s="10" t="n"/>
-      <c r="AX19" s="10" t="n"/>
-      <c r="AY19" s="10" t="n"/>
-      <c r="AZ19" s="10" t="n"/>
-      <c r="BA19" s="10" t="n"/>
-      <c r="BB19" s="10" t="n"/>
-      <c r="BC19" s="10" t="n"/>
-      <c r="BD19" s="10" t="n"/>
+      <c r="B19" s="672" t="n"/>
+      <c r="C19" s="672" t="n"/>
+      <c r="D19" s="672" t="n"/>
+      <c r="E19" s="672" t="n"/>
+      <c r="F19" s="672" t="n"/>
+      <c r="G19" s="672" t="n"/>
+      <c r="H19" s="672" t="n"/>
+      <c r="I19" s="672" t="n"/>
+      <c r="J19" s="672" t="n"/>
+      <c r="K19" s="672" t="n"/>
+      <c r="L19" s="672" t="n"/>
+      <c r="M19" s="672" t="n"/>
+      <c r="N19" s="672" t="n"/>
+      <c r="O19" s="672" t="n"/>
+      <c r="P19" s="672" t="n"/>
+      <c r="Q19" s="672" t="n"/>
+      <c r="R19" s="672" t="n"/>
+      <c r="S19" s="672" t="n"/>
+      <c r="T19" s="672" t="n"/>
+      <c r="U19" s="672" t="n"/>
+      <c r="V19" s="672" t="n"/>
+      <c r="W19" s="672" t="n"/>
+      <c r="X19" s="672" t="n"/>
+      <c r="Y19" s="672" t="n"/>
+      <c r="Z19" s="672" t="n"/>
+      <c r="AA19" s="672" t="n"/>
+      <c r="AB19" s="672" t="n"/>
+      <c r="AC19" s="672" t="n"/>
+      <c r="AD19" s="672" t="n"/>
+      <c r="AE19" s="672" t="n"/>
+      <c r="AF19" s="672" t="n"/>
+      <c r="AG19" s="672" t="n"/>
+      <c r="AH19" s="672" t="n"/>
+      <c r="AI19" s="672" t="n"/>
+      <c r="AJ19" s="672" t="n"/>
+      <c r="AK19" s="672" t="n"/>
+      <c r="AL19" s="672" t="n"/>
+      <c r="AM19" s="672" t="n"/>
+      <c r="AN19" s="672" t="n"/>
+      <c r="AO19" s="672" t="n"/>
+      <c r="AP19" s="672" t="n"/>
+      <c r="AQ19" s="672" t="n"/>
+      <c r="AR19" s="672" t="n"/>
+      <c r="AS19" s="672" t="n"/>
+      <c r="AT19" s="672" t="n"/>
+      <c r="AU19" s="672" t="n"/>
+      <c r="AV19" s="672" t="n"/>
+      <c r="AW19" s="672" t="n"/>
+      <c r="AX19" s="672" t="n"/>
+      <c r="AY19" s="672" t="n"/>
+      <c r="AZ19" s="672" t="n"/>
+      <c r="BA19" s="672" t="n"/>
+      <c r="BB19" s="672" t="n"/>
+      <c r="BC19" s="672" t="n"/>
+      <c r="BD19" s="672" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1">
       <c r="A20" s="764" t="inlineStr">
@@ -9693,61 +10049,61 @@
     </row>
     <row r="32" ht="3" customHeight="1">
       <c r="A32" s="672" t="n"/>
-      <c r="B32" s="10" t="n"/>
-      <c r="C32" s="10" t="n"/>
-      <c r="D32" s="10" t="n"/>
-      <c r="E32" s="10" t="n"/>
-      <c r="F32" s="10" t="n"/>
-      <c r="G32" s="10" t="n"/>
-      <c r="H32" s="10" t="n"/>
-      <c r="I32" s="10" t="n"/>
-      <c r="J32" s="10" t="n"/>
-      <c r="K32" s="10" t="n"/>
-      <c r="L32" s="10" t="n"/>
-      <c r="M32" s="10" t="n"/>
-      <c r="N32" s="10" t="n"/>
-      <c r="O32" s="10" t="n"/>
-      <c r="P32" s="10" t="n"/>
-      <c r="Q32" s="10" t="n"/>
-      <c r="R32" s="10" t="n"/>
-      <c r="S32" s="10" t="n"/>
-      <c r="T32" s="10" t="n"/>
-      <c r="U32" s="10" t="n"/>
-      <c r="V32" s="10" t="n"/>
-      <c r="W32" s="10" t="n"/>
-      <c r="X32" s="10" t="n"/>
-      <c r="Y32" s="10" t="n"/>
-      <c r="Z32" s="10" t="n"/>
-      <c r="AA32" s="10" t="n"/>
-      <c r="AB32" s="10" t="n"/>
-      <c r="AC32" s="10" t="n"/>
-      <c r="AD32" s="10" t="n"/>
-      <c r="AE32" s="10" t="n"/>
-      <c r="AF32" s="10" t="n"/>
-      <c r="AG32" s="10" t="n"/>
-      <c r="AH32" s="10" t="n"/>
-      <c r="AI32" s="10" t="n"/>
-      <c r="AJ32" s="10" t="n"/>
-      <c r="AK32" s="10" t="n"/>
-      <c r="AL32" s="10" t="n"/>
-      <c r="AM32" s="10" t="n"/>
-      <c r="AN32" s="10" t="n"/>
-      <c r="AO32" s="10" t="n"/>
-      <c r="AP32" s="10" t="n"/>
-      <c r="AQ32" s="10" t="n"/>
-      <c r="AR32" s="10" t="n"/>
-      <c r="AS32" s="10" t="n"/>
-      <c r="AT32" s="10" t="n"/>
-      <c r="AU32" s="10" t="n"/>
-      <c r="AV32" s="10" t="n"/>
-      <c r="AW32" s="10" t="n"/>
-      <c r="AX32" s="10" t="n"/>
-      <c r="AY32" s="10" t="n"/>
-      <c r="AZ32" s="10" t="n"/>
-      <c r="BA32" s="10" t="n"/>
-      <c r="BB32" s="10" t="n"/>
-      <c r="BC32" s="10" t="n"/>
-      <c r="BD32" s="10" t="n"/>
+      <c r="B32" s="672" t="n"/>
+      <c r="C32" s="672" t="n"/>
+      <c r="D32" s="672" t="n"/>
+      <c r="E32" s="672" t="n"/>
+      <c r="F32" s="672" t="n"/>
+      <c r="G32" s="672" t="n"/>
+      <c r="H32" s="672" t="n"/>
+      <c r="I32" s="672" t="n"/>
+      <c r="J32" s="672" t="n"/>
+      <c r="K32" s="672" t="n"/>
+      <c r="L32" s="672" t="n"/>
+      <c r="M32" s="672" t="n"/>
+      <c r="N32" s="672" t="n"/>
+      <c r="O32" s="672" t="n"/>
+      <c r="P32" s="672" t="n"/>
+      <c r="Q32" s="672" t="n"/>
+      <c r="R32" s="672" t="n"/>
+      <c r="S32" s="672" t="n"/>
+      <c r="T32" s="672" t="n"/>
+      <c r="U32" s="672" t="n"/>
+      <c r="V32" s="672" t="n"/>
+      <c r="W32" s="672" t="n"/>
+      <c r="X32" s="672" t="n"/>
+      <c r="Y32" s="672" t="n"/>
+      <c r="Z32" s="672" t="n"/>
+      <c r="AA32" s="672" t="n"/>
+      <c r="AB32" s="672" t="n"/>
+      <c r="AC32" s="672" t="n"/>
+      <c r="AD32" s="672" t="n"/>
+      <c r="AE32" s="672" t="n"/>
+      <c r="AF32" s="672" t="n"/>
+      <c r="AG32" s="672" t="n"/>
+      <c r="AH32" s="672" t="n"/>
+      <c r="AI32" s="672" t="n"/>
+      <c r="AJ32" s="672" t="n"/>
+      <c r="AK32" s="672" t="n"/>
+      <c r="AL32" s="672" t="n"/>
+      <c r="AM32" s="672" t="n"/>
+      <c r="AN32" s="672" t="n"/>
+      <c r="AO32" s="672" t="n"/>
+      <c r="AP32" s="672" t="n"/>
+      <c r="AQ32" s="672" t="n"/>
+      <c r="AR32" s="672" t="n"/>
+      <c r="AS32" s="672" t="n"/>
+      <c r="AT32" s="672" t="n"/>
+      <c r="AU32" s="672" t="n"/>
+      <c r="AV32" s="672" t="n"/>
+      <c r="AW32" s="672" t="n"/>
+      <c r="AX32" s="672" t="n"/>
+      <c r="AY32" s="672" t="n"/>
+      <c r="AZ32" s="672" t="n"/>
+      <c r="BA32" s="672" t="n"/>
+      <c r="BB32" s="672" t="n"/>
+      <c r="BC32" s="672" t="n"/>
+      <c r="BD32" s="672" t="n"/>
     </row>
     <row r="33" ht="18" customHeight="1">
       <c r="A33" s="764" t="inlineStr">
@@ -10199,61 +10555,61 @@
     </row>
     <row r="40" ht="3" customHeight="1">
       <c r="A40" s="672" t="n"/>
-      <c r="B40" s="10" t="n"/>
-      <c r="C40" s="10" t="n"/>
-      <c r="D40" s="10" t="n"/>
-      <c r="E40" s="10" t="n"/>
-      <c r="F40" s="10" t="n"/>
-      <c r="G40" s="10" t="n"/>
-      <c r="H40" s="10" t="n"/>
-      <c r="I40" s="10" t="n"/>
-      <c r="J40" s="10" t="n"/>
-      <c r="K40" s="10" t="n"/>
-      <c r="L40" s="10" t="n"/>
-      <c r="M40" s="10" t="n"/>
-      <c r="N40" s="10" t="n"/>
-      <c r="O40" s="10" t="n"/>
-      <c r="P40" s="10" t="n"/>
-      <c r="Q40" s="10" t="n"/>
-      <c r="R40" s="10" t="n"/>
-      <c r="S40" s="10" t="n"/>
-      <c r="T40" s="10" t="n"/>
-      <c r="U40" s="10" t="n"/>
-      <c r="V40" s="10" t="n"/>
-      <c r="W40" s="10" t="n"/>
-      <c r="X40" s="10" t="n"/>
-      <c r="Y40" s="10" t="n"/>
-      <c r="Z40" s="10" t="n"/>
-      <c r="AA40" s="10" t="n"/>
-      <c r="AB40" s="10" t="n"/>
-      <c r="AC40" s="10" t="n"/>
-      <c r="AD40" s="10" t="n"/>
-      <c r="AE40" s="10" t="n"/>
-      <c r="AF40" s="10" t="n"/>
-      <c r="AG40" s="10" t="n"/>
-      <c r="AH40" s="10" t="n"/>
-      <c r="AI40" s="10" t="n"/>
-      <c r="AJ40" s="10" t="n"/>
-      <c r="AK40" s="10" t="n"/>
-      <c r="AL40" s="10" t="n"/>
-      <c r="AM40" s="10" t="n"/>
-      <c r="AN40" s="10" t="n"/>
-      <c r="AO40" s="10" t="n"/>
-      <c r="AP40" s="10" t="n"/>
-      <c r="AQ40" s="10" t="n"/>
-      <c r="AR40" s="10" t="n"/>
-      <c r="AS40" s="10" t="n"/>
-      <c r="AT40" s="10" t="n"/>
-      <c r="AU40" s="10" t="n"/>
-      <c r="AV40" s="10" t="n"/>
-      <c r="AW40" s="10" t="n"/>
-      <c r="AX40" s="10" t="n"/>
-      <c r="AY40" s="10" t="n"/>
-      <c r="AZ40" s="10" t="n"/>
-      <c r="BA40" s="10" t="n"/>
-      <c r="BB40" s="10" t="n"/>
-      <c r="BC40" s="10" t="n"/>
-      <c r="BD40" s="10" t="n"/>
+      <c r="B40" s="672" t="n"/>
+      <c r="C40" s="672" t="n"/>
+      <c r="D40" s="672" t="n"/>
+      <c r="E40" s="672" t="n"/>
+      <c r="F40" s="672" t="n"/>
+      <c r="G40" s="672" t="n"/>
+      <c r="H40" s="672" t="n"/>
+      <c r="I40" s="672" t="n"/>
+      <c r="J40" s="672" t="n"/>
+      <c r="K40" s="672" t="n"/>
+      <c r="L40" s="672" t="n"/>
+      <c r="M40" s="672" t="n"/>
+      <c r="N40" s="672" t="n"/>
+      <c r="O40" s="672" t="n"/>
+      <c r="P40" s="672" t="n"/>
+      <c r="Q40" s="672" t="n"/>
+      <c r="R40" s="672" t="n"/>
+      <c r="S40" s="672" t="n"/>
+      <c r="T40" s="672" t="n"/>
+      <c r="U40" s="672" t="n"/>
+      <c r="V40" s="672" t="n"/>
+      <c r="W40" s="672" t="n"/>
+      <c r="X40" s="672" t="n"/>
+      <c r="Y40" s="672" t="n"/>
+      <c r="Z40" s="672" t="n"/>
+      <c r="AA40" s="672" t="n"/>
+      <c r="AB40" s="672" t="n"/>
+      <c r="AC40" s="672" t="n"/>
+      <c r="AD40" s="672" t="n"/>
+      <c r="AE40" s="672" t="n"/>
+      <c r="AF40" s="672" t="n"/>
+      <c r="AG40" s="672" t="n"/>
+      <c r="AH40" s="672" t="n"/>
+      <c r="AI40" s="672" t="n"/>
+      <c r="AJ40" s="672" t="n"/>
+      <c r="AK40" s="672" t="n"/>
+      <c r="AL40" s="672" t="n"/>
+      <c r="AM40" s="672" t="n"/>
+      <c r="AN40" s="672" t="n"/>
+      <c r="AO40" s="672" t="n"/>
+      <c r="AP40" s="672" t="n"/>
+      <c r="AQ40" s="672" t="n"/>
+      <c r="AR40" s="672" t="n"/>
+      <c r="AS40" s="672" t="n"/>
+      <c r="AT40" s="672" t="n"/>
+      <c r="AU40" s="672" t="n"/>
+      <c r="AV40" s="672" t="n"/>
+      <c r="AW40" s="672" t="n"/>
+      <c r="AX40" s="672" t="n"/>
+      <c r="AY40" s="672" t="n"/>
+      <c r="AZ40" s="672" t="n"/>
+      <c r="BA40" s="672" t="n"/>
+      <c r="BB40" s="672" t="n"/>
+      <c r="BC40" s="672" t="n"/>
+      <c r="BD40" s="672" t="n"/>
     </row>
     <row r="41" ht="18" customHeight="1">
       <c r="A41" s="764" t="inlineStr">
@@ -10473,123 +10829,123 @@
     </row>
     <row r="46" ht="3" customHeight="1">
       <c r="A46" s="672" t="n"/>
-      <c r="B46" s="10" t="n"/>
-      <c r="C46" s="10" t="n"/>
-      <c r="D46" s="10" t="n"/>
-      <c r="E46" s="10" t="n"/>
-      <c r="F46" s="10" t="n"/>
-      <c r="G46" s="10" t="n"/>
-      <c r="H46" s="10" t="n"/>
-      <c r="I46" s="10" t="n"/>
-      <c r="J46" s="10" t="n"/>
-      <c r="K46" s="10" t="n"/>
-      <c r="L46" s="10" t="n"/>
-      <c r="M46" s="10" t="n"/>
-      <c r="N46" s="10" t="n"/>
-      <c r="O46" s="10" t="n"/>
-      <c r="P46" s="10" t="n"/>
-      <c r="Q46" s="10" t="n"/>
-      <c r="R46" s="10" t="n"/>
-      <c r="S46" s="10" t="n"/>
-      <c r="T46" s="10" t="n"/>
-      <c r="U46" s="10" t="n"/>
-      <c r="V46" s="10" t="n"/>
-      <c r="W46" s="10" t="n"/>
-      <c r="X46" s="10" t="n"/>
-      <c r="Y46" s="10" t="n"/>
-      <c r="Z46" s="10" t="n"/>
-      <c r="AA46" s="10" t="n"/>
-      <c r="AB46" s="10" t="n"/>
-      <c r="AC46" s="10" t="n"/>
-      <c r="AD46" s="10" t="n"/>
-      <c r="AE46" s="10" t="n"/>
-      <c r="AF46" s="10" t="n"/>
-      <c r="AG46" s="10" t="n"/>
-      <c r="AH46" s="10" t="n"/>
-      <c r="AI46" s="10" t="n"/>
-      <c r="AJ46" s="10" t="n"/>
-      <c r="AK46" s="10" t="n"/>
-      <c r="AL46" s="10" t="n"/>
-      <c r="AM46" s="10" t="n"/>
-      <c r="AN46" s="10" t="n"/>
-      <c r="AO46" s="10" t="n"/>
-      <c r="AP46" s="10" t="n"/>
-      <c r="AQ46" s="10" t="n"/>
-      <c r="AR46" s="10" t="n"/>
-      <c r="AS46" s="10" t="n"/>
-      <c r="AT46" s="10" t="n"/>
-      <c r="AU46" s="10" t="n"/>
-      <c r="AV46" s="10" t="n"/>
-      <c r="AW46" s="10" t="n"/>
-      <c r="AX46" s="10" t="n"/>
-      <c r="AY46" s="10" t="n"/>
-      <c r="AZ46" s="10" t="n"/>
-      <c r="BA46" s="10" t="n"/>
-      <c r="BB46" s="10" t="n"/>
-      <c r="BC46" s="10" t="n"/>
-      <c r="BD46" s="10" t="n"/>
+      <c r="B46" s="672" t="n"/>
+      <c r="C46" s="672" t="n"/>
+      <c r="D46" s="672" t="n"/>
+      <c r="E46" s="672" t="n"/>
+      <c r="F46" s="672" t="n"/>
+      <c r="G46" s="672" t="n"/>
+      <c r="H46" s="672" t="n"/>
+      <c r="I46" s="672" t="n"/>
+      <c r="J46" s="672" t="n"/>
+      <c r="K46" s="672" t="n"/>
+      <c r="L46" s="672" t="n"/>
+      <c r="M46" s="672" t="n"/>
+      <c r="N46" s="672" t="n"/>
+      <c r="O46" s="672" t="n"/>
+      <c r="P46" s="672" t="n"/>
+      <c r="Q46" s="672" t="n"/>
+      <c r="R46" s="672" t="n"/>
+      <c r="S46" s="672" t="n"/>
+      <c r="T46" s="672" t="n"/>
+      <c r="U46" s="672" t="n"/>
+      <c r="V46" s="672" t="n"/>
+      <c r="W46" s="672" t="n"/>
+      <c r="X46" s="672" t="n"/>
+      <c r="Y46" s="672" t="n"/>
+      <c r="Z46" s="672" t="n"/>
+      <c r="AA46" s="672" t="n"/>
+      <c r="AB46" s="672" t="n"/>
+      <c r="AC46" s="672" t="n"/>
+      <c r="AD46" s="672" t="n"/>
+      <c r="AE46" s="672" t="n"/>
+      <c r="AF46" s="672" t="n"/>
+      <c r="AG46" s="672" t="n"/>
+      <c r="AH46" s="672" t="n"/>
+      <c r="AI46" s="672" t="n"/>
+      <c r="AJ46" s="672" t="n"/>
+      <c r="AK46" s="672" t="n"/>
+      <c r="AL46" s="672" t="n"/>
+      <c r="AM46" s="672" t="n"/>
+      <c r="AN46" s="672" t="n"/>
+      <c r="AO46" s="672" t="n"/>
+      <c r="AP46" s="672" t="n"/>
+      <c r="AQ46" s="672" t="n"/>
+      <c r="AR46" s="672" t="n"/>
+      <c r="AS46" s="672" t="n"/>
+      <c r="AT46" s="672" t="n"/>
+      <c r="AU46" s="672" t="n"/>
+      <c r="AV46" s="672" t="n"/>
+      <c r="AW46" s="672" t="n"/>
+      <c r="AX46" s="672" t="n"/>
+      <c r="AY46" s="672" t="n"/>
+      <c r="AZ46" s="672" t="n"/>
+      <c r="BA46" s="672" t="n"/>
+      <c r="BB46" s="672" t="n"/>
+      <c r="BC46" s="672" t="n"/>
+      <c r="BD46" s="672" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="793" t="inlineStr">
+      <c r="A47" s="373" t="inlineStr">
         <is>
           <t>NOTICE  ?  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-307_[EVENTID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="794" t="n"/>
-      <c r="C47" s="794" t="n"/>
-      <c r="D47" s="794" t="n"/>
-      <c r="E47" s="794" t="n"/>
-      <c r="F47" s="794" t="n"/>
-      <c r="G47" s="794" t="n"/>
-      <c r="H47" s="794" t="n"/>
-      <c r="I47" s="794" t="n"/>
-      <c r="J47" s="794" t="n"/>
-      <c r="K47" s="794" t="n"/>
-      <c r="L47" s="794" t="n"/>
-      <c r="M47" s="794" t="n"/>
-      <c r="N47" s="794" t="n"/>
-      <c r="O47" s="794" t="n"/>
-      <c r="P47" s="794" t="n"/>
-      <c r="Q47" s="794" t="n"/>
-      <c r="R47" s="794" t="n"/>
-      <c r="S47" s="794" t="n"/>
-      <c r="T47" s="794" t="n"/>
-      <c r="U47" s="794" t="n"/>
-      <c r="V47" s="794" t="n"/>
-      <c r="W47" s="794" t="n"/>
-      <c r="X47" s="794" t="n"/>
-      <c r="Y47" s="794" t="n"/>
-      <c r="Z47" s="794" t="n"/>
-      <c r="AA47" s="794" t="n"/>
-      <c r="AB47" s="794" t="n"/>
-      <c r="AC47" s="794" t="n"/>
-      <c r="AD47" s="794" t="n"/>
-      <c r="AE47" s="794" t="n"/>
-      <c r="AF47" s="794" t="n"/>
-      <c r="AG47" s="794" t="n"/>
-      <c r="AH47" s="794" t="n"/>
-      <c r="AI47" s="794" t="n"/>
-      <c r="AJ47" s="794" t="n"/>
-      <c r="AK47" s="794" t="n"/>
-      <c r="AL47" s="794" t="n"/>
-      <c r="AM47" s="794" t="n"/>
-      <c r="AN47" s="794" t="n"/>
-      <c r="AO47" s="794" t="n"/>
-      <c r="AP47" s="794" t="n"/>
-      <c r="AQ47" s="794" t="n"/>
-      <c r="AR47" s="794" t="n"/>
-      <c r="AS47" s="794" t="n"/>
-      <c r="AT47" s="794" t="n"/>
-      <c r="AU47" s="794" t="n"/>
-      <c r="AV47" s="794" t="n"/>
-      <c r="AW47" s="794" t="n"/>
-      <c r="AX47" s="794" t="n"/>
-      <c r="AY47" s="794" t="n"/>
-      <c r="AZ47" s="794" t="n"/>
-      <c r="BA47" s="794" t="n"/>
-      <c r="BB47" s="794" t="n"/>
-      <c r="BC47" s="794" t="n"/>
-      <c r="BD47" s="795" t="n"/>
+      <c r="B47" s="374" t="n"/>
+      <c r="C47" s="374" t="n"/>
+      <c r="D47" s="374" t="n"/>
+      <c r="E47" s="374" t="n"/>
+      <c r="F47" s="374" t="n"/>
+      <c r="G47" s="374" t="n"/>
+      <c r="H47" s="374" t="n"/>
+      <c r="I47" s="374" t="n"/>
+      <c r="J47" s="374" t="n"/>
+      <c r="K47" s="374" t="n"/>
+      <c r="L47" s="374" t="n"/>
+      <c r="M47" s="374" t="n"/>
+      <c r="N47" s="374" t="n"/>
+      <c r="O47" s="374" t="n"/>
+      <c r="P47" s="374" t="n"/>
+      <c r="Q47" s="374" t="n"/>
+      <c r="R47" s="374" t="n"/>
+      <c r="S47" s="374" t="n"/>
+      <c r="T47" s="374" t="n"/>
+      <c r="U47" s="374" t="n"/>
+      <c r="V47" s="374" t="n"/>
+      <c r="W47" s="374" t="n"/>
+      <c r="X47" s="374" t="n"/>
+      <c r="Y47" s="374" t="n"/>
+      <c r="Z47" s="374" t="n"/>
+      <c r="AA47" s="374" t="n"/>
+      <c r="AB47" s="374" t="n"/>
+      <c r="AC47" s="374" t="n"/>
+      <c r="AD47" s="374" t="n"/>
+      <c r="AE47" s="374" t="n"/>
+      <c r="AF47" s="374" t="n"/>
+      <c r="AG47" s="374" t="n"/>
+      <c r="AH47" s="374" t="n"/>
+      <c r="AI47" s="374" t="n"/>
+      <c r="AJ47" s="374" t="n"/>
+      <c r="AK47" s="374" t="n"/>
+      <c r="AL47" s="374" t="n"/>
+      <c r="AM47" s="374" t="n"/>
+      <c r="AN47" s="374" t="n"/>
+      <c r="AO47" s="374" t="n"/>
+      <c r="AP47" s="374" t="n"/>
+      <c r="AQ47" s="374" t="n"/>
+      <c r="AR47" s="374" t="n"/>
+      <c r="AS47" s="374" t="n"/>
+      <c r="AT47" s="374" t="n"/>
+      <c r="AU47" s="374" t="n"/>
+      <c r="AV47" s="374" t="n"/>
+      <c r="AW47" s="374" t="n"/>
+      <c r="AX47" s="374" t="n"/>
+      <c r="AY47" s="374" t="n"/>
+      <c r="AZ47" s="374" t="n"/>
+      <c r="BA47" s="374" t="n"/>
+      <c r="BB47" s="374" t="n"/>
+      <c r="BC47" s="374" t="n"/>
+      <c r="BD47" s="375" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -11102,363 +11458,351 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="799" t="n"/>
-      <c r="B1" s="800" t="n"/>
-      <c r="C1" s="800" t="n"/>
-      <c r="D1" s="800" t="n"/>
-      <c r="E1" s="800" t="n"/>
-      <c r="F1" s="800" t="n"/>
-      <c r="G1" s="800" t="n"/>
-      <c r="H1" s="801" t="n"/>
-      <c r="I1" s="802" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="843" t="n"/>
+      <c r="B1" s="752" t="n"/>
+      <c r="C1" s="752" t="n"/>
+      <c r="D1" s="752" t="n"/>
+      <c r="E1" s="752" t="n"/>
+      <c r="F1" s="752" t="n"/>
+      <c r="G1" s="752" t="n"/>
+      <c r="H1" s="844" t="n"/>
+      <c r="I1" s="845" t="inlineStr">
         <is>
           <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
         </is>
       </c>
-      <c r="J1" s="800" t="n"/>
-      <c r="K1" s="800" t="n"/>
-      <c r="L1" s="800" t="n"/>
-      <c r="M1" s="800" t="n"/>
-      <c r="N1" s="800" t="n"/>
-      <c r="O1" s="800" t="n"/>
-      <c r="P1" s="800" t="n"/>
-      <c r="Q1" s="800" t="n"/>
-      <c r="R1" s="800" t="n"/>
-      <c r="S1" s="800" t="n"/>
-      <c r="T1" s="800" t="n"/>
-      <c r="U1" s="800" t="n"/>
-      <c r="V1" s="800" t="n"/>
-      <c r="W1" s="800" t="n"/>
-      <c r="X1" s="800" t="n"/>
-      <c r="Y1" s="800" t="n"/>
-      <c r="Z1" s="800" t="n"/>
-      <c r="AA1" s="800" t="n"/>
-      <c r="AB1" s="800" t="n"/>
-      <c r="AC1" s="800" t="n"/>
-      <c r="AD1" s="801" t="n"/>
-      <c r="AE1" s="507" t="inlineStr">
+      <c r="J1" s="752" t="n"/>
+      <c r="K1" s="752" t="n"/>
+      <c r="L1" s="752" t="n"/>
+      <c r="M1" s="752" t="n"/>
+      <c r="N1" s="752" t="n"/>
+      <c r="O1" s="752" t="n"/>
+      <c r="P1" s="752" t="n"/>
+      <c r="Q1" s="752" t="n"/>
+      <c r="R1" s="752" t="n"/>
+      <c r="S1" s="752" t="n"/>
+      <c r="T1" s="752" t="n"/>
+      <c r="U1" s="752" t="n"/>
+      <c r="V1" s="752" t="n"/>
+      <c r="W1" s="752" t="n"/>
+      <c r="X1" s="752" t="n"/>
+      <c r="Y1" s="752" t="n"/>
+      <c r="Z1" s="752" t="n"/>
+      <c r="AA1" s="752" t="n"/>
+      <c r="AB1" s="752" t="n"/>
+      <c r="AC1" s="752" t="n"/>
+      <c r="AD1" s="844" t="n"/>
+      <c r="AE1" s="508" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="800" t="n"/>
-      <c r="AG1" s="800" t="n"/>
-      <c r="AH1" s="803" t="n"/>
-      <c r="AI1" s="510" t="inlineStr">
+      <c r="AF1" s="752" t="n"/>
+      <c r="AG1" s="752" t="n"/>
+      <c r="AH1" s="846" t="n"/>
+      <c r="AI1" s="511" t="inlineStr">
         <is>
           <t>FRM-306</t>
         </is>
       </c>
-      <c r="AJ1" s="800" t="n"/>
-      <c r="AK1" s="800" t="n"/>
-      <c r="AL1" s="800" t="n"/>
-      <c r="AM1" s="800" t="n"/>
-      <c r="AN1" s="801" t="n"/>
+      <c r="AJ1" s="752" t="n"/>
+      <c r="AK1" s="752" t="n"/>
+      <c r="AL1" s="752" t="n"/>
+      <c r="AM1" s="752" t="n"/>
+      <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="804" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="805" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="805" t="n"/>
-      <c r="AE2" s="806" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="819" t="n"/>
+      <c r="G2" s="819" t="n"/>
+      <c r="H2" s="820" t="n"/>
+      <c r="I2" s="819" t="n"/>
+      <c r="J2" s="819" t="n"/>
+      <c r="K2" s="819" t="n"/>
+      <c r="L2" s="819" t="n"/>
+      <c r="M2" s="819" t="n"/>
+      <c r="N2" s="819" t="n"/>
+      <c r="O2" s="819" t="n"/>
+      <c r="P2" s="819" t="n"/>
+      <c r="Q2" s="819" t="n"/>
+      <c r="R2" s="819" t="n"/>
+      <c r="S2" s="819" t="n"/>
+      <c r="T2" s="819" t="n"/>
+      <c r="U2" s="819" t="n"/>
+      <c r="V2" s="819" t="n"/>
+      <c r="W2" s="819" t="n"/>
+      <c r="X2" s="819" t="n"/>
+      <c r="Y2" s="819" t="n"/>
+      <c r="Z2" s="819" t="n"/>
+      <c r="AA2" s="819" t="n"/>
+      <c r="AB2" s="819" t="n"/>
+      <c r="AC2" s="819" t="n"/>
+      <c r="AD2" s="820" t="n"/>
+      <c r="AE2" s="821" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="807" t="n"/>
-      <c r="AI2" s="808" t="inlineStr">
+      <c r="AF2" s="822" t="n"/>
+      <c r="AG2" s="822" t="n"/>
+      <c r="AH2" s="823" t="n"/>
+      <c r="AI2" s="824" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="805" t="n"/>
+      <c r="AJ2" s="825" t="n"/>
+      <c r="AK2" s="825" t="n"/>
+      <c r="AL2" s="825" t="n"/>
+      <c r="AM2" s="825" t="n"/>
+      <c r="AN2" s="826" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="804" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="805" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="805" t="n"/>
-      <c r="AE3" s="806" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="828" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="828" t="n"/>
+      <c r="AE3" s="829" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="807" t="n"/>
-      <c r="AI3" s="808" t="inlineStr">
+      <c r="AF3" s="830" t="n"/>
+      <c r="AG3" s="830" t="n"/>
+      <c r="AH3" s="831" t="n"/>
+      <c r="AI3" s="724" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="805" t="n"/>
+      <c r="AJ3" s="832" t="n"/>
+      <c r="AK3" s="832" t="n"/>
+      <c r="AL3" s="832" t="n"/>
+      <c r="AM3" s="832" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="804" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="805" t="n"/>
-      <c r="I4" s="809" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="828" t="n"/>
+      <c r="I4" s="346" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="805" t="n"/>
-      <c r="AE4" s="806" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="828" t="n"/>
+      <c r="AE4" s="829" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="807" t="n"/>
-      <c r="AI4" s="808" t="inlineStr">
+      <c r="AF4" s="830" t="n"/>
+      <c r="AG4" s="830" t="n"/>
+      <c r="AH4" s="831" t="n"/>
+      <c r="AI4" s="724" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="805" t="n"/>
+      <c r="AJ4" s="832" t="n"/>
+      <c r="AK4" s="832" t="n"/>
+      <c r="AL4" s="832" t="n"/>
+      <c r="AM4" s="832" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="810" t="n"/>
-      <c r="B5" s="811" t="n"/>
-      <c r="C5" s="811" t="n"/>
-      <c r="D5" s="811" t="n"/>
-      <c r="E5" s="811" t="n"/>
-      <c r="F5" s="811" t="n"/>
-      <c r="G5" s="811" t="n"/>
-      <c r="H5" s="812" t="n"/>
-      <c r="I5" s="813" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="828" t="n"/>
+      <c r="I5" s="595" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="811" t="n"/>
-      <c r="K5" s="811" t="n"/>
-      <c r="L5" s="811" t="n"/>
-      <c r="M5" s="811" t="n"/>
-      <c r="N5" s="811" t="n"/>
-      <c r="O5" s="811" t="n"/>
-      <c r="P5" s="811" t="n"/>
-      <c r="Q5" s="811" t="n"/>
-      <c r="R5" s="811" t="n"/>
-      <c r="S5" s="811" t="n"/>
-      <c r="T5" s="811" t="n"/>
-      <c r="U5" s="811" t="n"/>
-      <c r="V5" s="811" t="n"/>
-      <c r="W5" s="811" t="n"/>
-      <c r="X5" s="811" t="n"/>
-      <c r="Y5" s="811" t="n"/>
-      <c r="Z5" s="811" t="n"/>
-      <c r="AA5" s="811" t="n"/>
-      <c r="AB5" s="811" t="n"/>
-      <c r="AC5" s="811" t="n"/>
-      <c r="AD5" s="812" t="n"/>
-      <c r="AE5" s="814" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="828" t="n"/>
+      <c r="AE5" s="829" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="811" t="n"/>
-      <c r="AG5" s="811" t="n"/>
-      <c r="AH5" s="815" t="n"/>
-      <c r="AI5" s="816" t="inlineStr">
+      <c r="AF5" s="830" t="n"/>
+      <c r="AG5" s="830" t="n"/>
+      <c r="AH5" s="831" t="n"/>
+      <c r="AI5" s="724" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="811" t="n"/>
-      <c r="AK5" s="811" t="n"/>
-      <c r="AL5" s="811" t="n"/>
-      <c r="AM5" s="811" t="n"/>
-      <c r="AN5" s="812" t="n"/>
+      <c r="AJ5" s="832" t="n"/>
+      <c r="AK5" s="832" t="n"/>
+      <c r="AL5" s="832" t="n"/>
+      <c r="AM5" s="832" t="n"/>
+      <c r="AN5" s="833" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="817" t="n"/>
-      <c r="B6" s="817" t="n"/>
-      <c r="C6" s="817" t="n"/>
-      <c r="D6" s="817" t="n"/>
-      <c r="E6" s="817" t="n"/>
-      <c r="F6" s="817" t="n"/>
-      <c r="G6" s="817" t="n"/>
-      <c r="H6" s="817" t="n"/>
-      <c r="I6" s="817" t="n"/>
-      <c r="J6" s="817" t="n"/>
-      <c r="K6" s="817" t="n"/>
-      <c r="L6" s="817" t="n"/>
-      <c r="M6" s="817" t="n"/>
-      <c r="N6" s="817" t="n"/>
-      <c r="O6" s="817" t="n"/>
-      <c r="P6" s="817" t="n"/>
-      <c r="Q6" s="817" t="n"/>
-      <c r="R6" s="817" t="n"/>
-      <c r="S6" s="817" t="n"/>
-      <c r="T6" s="817" t="n"/>
-      <c r="U6" s="817" t="n"/>
-      <c r="V6" s="817" t="n"/>
-      <c r="W6" s="817" t="n"/>
-      <c r="X6" s="817" t="n"/>
-      <c r="Y6" s="817" t="n"/>
-      <c r="Z6" s="817" t="n"/>
-      <c r="AA6" s="817" t="n"/>
-      <c r="AB6" s="817" t="n"/>
-      <c r="AC6" s="817" t="n"/>
-      <c r="AD6" s="817" t="n"/>
-      <c r="AE6" s="817" t="n"/>
-      <c r="AF6" s="817" t="n"/>
-      <c r="AG6" s="817" t="n"/>
-      <c r="AH6" s="817" t="n"/>
-      <c r="AI6" s="817" t="n"/>
-      <c r="AJ6" s="817" t="n"/>
-      <c r="AK6" s="817" t="n"/>
-      <c r="AL6" s="817" t="n"/>
-      <c r="AM6" s="817" t="n"/>
-      <c r="AN6" s="817" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="847" t="n"/>
+      <c r="B6" s="848" t="n"/>
+      <c r="C6" s="848" t="n"/>
+      <c r="D6" s="848" t="n"/>
+      <c r="E6" s="848" t="n"/>
+      <c r="F6" s="848" t="n"/>
+      <c r="G6" s="848" t="n"/>
+      <c r="H6" s="849" t="n"/>
+      <c r="I6" s="848" t="n"/>
+      <c r="J6" s="848" t="n"/>
+      <c r="K6" s="848" t="n"/>
+      <c r="L6" s="848" t="n"/>
+      <c r="M6" s="848" t="n"/>
+      <c r="N6" s="848" t="n"/>
+      <c r="O6" s="848" t="n"/>
+      <c r="P6" s="848" t="n"/>
+      <c r="Q6" s="848" t="n"/>
+      <c r="R6" s="848" t="n"/>
+      <c r="S6" s="848" t="n"/>
+      <c r="T6" s="848" t="n"/>
+      <c r="U6" s="848" t="n"/>
+      <c r="V6" s="848" t="n"/>
+      <c r="W6" s="848" t="n"/>
+      <c r="X6" s="848" t="n"/>
+      <c r="Y6" s="848" t="n"/>
+      <c r="Z6" s="848" t="n"/>
+      <c r="AA6" s="848" t="n"/>
+      <c r="AB6" s="848" t="n"/>
+      <c r="AC6" s="848" t="n"/>
+      <c r="AD6" s="849" t="n"/>
+      <c r="AE6" s="850" t="n"/>
+      <c r="AF6" s="850" t="n"/>
+      <c r="AG6" s="850" t="n"/>
+      <c r="AH6" s="851" t="n"/>
+      <c r="AI6" s="852" t="n"/>
+      <c r="AJ6" s="852" t="n"/>
+      <c r="AK6" s="852" t="n"/>
+      <c r="AL6" s="852" t="n"/>
+      <c r="AM6" s="852" t="n"/>
+      <c r="AN6" s="853" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="406" t="inlineStr">
-        <is>
-          <t>VAL_RESULT_CORE</t>
-        </is>
-      </c>
-      <c r="B7" s="406" t="inlineStr">
-        <is>
-          <t>VAL_DECISION_GATE_CORE</t>
-        </is>
-      </c>
-      <c r="C7" s="406" t="inlineStr">
-        <is>
-          <t>VAL_STATUS_CORE</t>
-        </is>
-      </c>
-      <c r="D7" s="818" t="n"/>
-      <c r="E7" s="818" t="n"/>
-      <c r="F7" s="818" t="n"/>
-      <c r="G7" s="818" t="n"/>
-      <c r="H7" s="818" t="n"/>
-      <c r="I7" s="818" t="n"/>
-      <c r="J7" s="818" t="n"/>
-      <c r="K7" s="818" t="n"/>
-      <c r="L7" s="818" t="n"/>
-      <c r="M7" s="818" t="n"/>
-      <c r="N7" s="818" t="n"/>
-      <c r="O7" s="818" t="n"/>
-      <c r="P7" s="818" t="n"/>
-      <c r="Q7" s="818" t="n"/>
-      <c r="R7" s="818" t="n"/>
-      <c r="S7" s="818" t="n"/>
-      <c r="T7" s="818" t="n"/>
-      <c r="U7" s="818" t="n"/>
-      <c r="V7" s="818" t="n"/>
-      <c r="W7" s="818" t="n"/>
-      <c r="X7" s="818" t="n"/>
-      <c r="Y7" s="818" t="n"/>
-      <c r="Z7" s="818" t="n"/>
-      <c r="AA7" s="818" t="n"/>
-      <c r="AB7" s="818" t="n"/>
-      <c r="AC7" s="818" t="n"/>
-      <c r="AD7" s="818" t="n"/>
-      <c r="AE7" s="818" t="n"/>
-      <c r="AF7" s="818" t="n"/>
-      <c r="AG7" s="818" t="n"/>
-      <c r="AH7" s="818" t="n"/>
-      <c r="AI7" s="818" t="n"/>
-      <c r="AJ7" s="818" t="n"/>
-      <c r="AK7" s="818" t="n"/>
-      <c r="AL7" s="818" t="n"/>
-      <c r="AM7" s="818" t="n"/>
-      <c r="AN7" s="818" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="854" t="n"/>
+      <c r="B7" s="854" t="n"/>
+      <c r="C7" s="854" t="n"/>
+      <c r="D7" s="855" t="n"/>
+      <c r="E7" s="855" t="n"/>
+      <c r="F7" s="855" t="n"/>
+      <c r="G7" s="855" t="n"/>
+      <c r="H7" s="855" t="n"/>
+      <c r="I7" s="855" t="n"/>
+      <c r="J7" s="855" t="n"/>
+      <c r="K7" s="855" t="n"/>
+      <c r="L7" s="855" t="n"/>
+      <c r="M7" s="855" t="n"/>
+      <c r="N7" s="855" t="n"/>
+      <c r="O7" s="855" t="n"/>
+      <c r="P7" s="855" t="n"/>
+      <c r="Q7" s="855" t="n"/>
+      <c r="R7" s="855" t="n"/>
+      <c r="S7" s="855" t="n"/>
+      <c r="T7" s="855" t="n"/>
+      <c r="U7" s="855" t="n"/>
+      <c r="V7" s="855" t="n"/>
+      <c r="W7" s="855" t="n"/>
+      <c r="X7" s="855" t="n"/>
+      <c r="Y7" s="855" t="n"/>
+      <c r="Z7" s="855" t="n"/>
+      <c r="AA7" s="855" t="n"/>
+      <c r="AB7" s="855" t="n"/>
+      <c r="AC7" s="855" t="n"/>
+      <c r="AD7" s="855" t="n"/>
+      <c r="AE7" s="855" t="n"/>
+      <c r="AF7" s="855" t="n"/>
+      <c r="AG7" s="855" t="n"/>
+      <c r="AH7" s="855" t="n"/>
+      <c r="AI7" s="855" t="n"/>
+      <c r="AJ7" s="855" t="n"/>
+      <c r="AK7" s="855" t="n"/>
+      <c r="AL7" s="855" t="n"/>
+      <c r="AM7" s="855" t="n"/>
+      <c r="AN7" s="855" t="n"/>
     </row>
     <row r="8" hidden="1">
       <c r="A8" s="406" t="inlineStr">
@@ -12097,6 +12441,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -12151,385 +12496,369 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="799" t="n"/>
-      <c r="B1" s="800" t="n"/>
-      <c r="C1" s="800" t="n"/>
-      <c r="D1" s="800" t="n"/>
-      <c r="E1" s="800" t="n"/>
-      <c r="F1" s="800" t="n"/>
-      <c r="G1" s="800" t="n"/>
-      <c r="H1" s="801" t="n"/>
-      <c r="I1" s="802" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="843" t="n"/>
+      <c r="B1" s="752" t="n"/>
+      <c r="C1" s="752" t="n"/>
+      <c r="D1" s="752" t="n"/>
+      <c r="E1" s="752" t="n"/>
+      <c r="F1" s="752" t="n"/>
+      <c r="G1" s="752" t="n"/>
+      <c r="H1" s="844" t="n"/>
+      <c r="I1" s="845" t="inlineStr">
         <is>
           <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
         </is>
       </c>
-      <c r="J1" s="800" t="n"/>
-      <c r="K1" s="800" t="n"/>
-      <c r="L1" s="800" t="n"/>
-      <c r="M1" s="800" t="n"/>
-      <c r="N1" s="800" t="n"/>
-      <c r="O1" s="800" t="n"/>
-      <c r="P1" s="800" t="n"/>
-      <c r="Q1" s="800" t="n"/>
-      <c r="R1" s="800" t="n"/>
-      <c r="S1" s="800" t="n"/>
-      <c r="T1" s="800" t="n"/>
-      <c r="U1" s="800" t="n"/>
-      <c r="V1" s="800" t="n"/>
-      <c r="W1" s="800" t="n"/>
-      <c r="X1" s="800" t="n"/>
-      <c r="Y1" s="800" t="n"/>
-      <c r="Z1" s="800" t="n"/>
-      <c r="AA1" s="800" t="n"/>
-      <c r="AB1" s="800" t="n"/>
-      <c r="AC1" s="800" t="n"/>
-      <c r="AD1" s="801" t="n"/>
-      <c r="AE1" s="507" t="inlineStr">
+      <c r="J1" s="752" t="n"/>
+      <c r="K1" s="752" t="n"/>
+      <c r="L1" s="752" t="n"/>
+      <c r="M1" s="752" t="n"/>
+      <c r="N1" s="752" t="n"/>
+      <c r="O1" s="752" t="n"/>
+      <c r="P1" s="752" t="n"/>
+      <c r="Q1" s="752" t="n"/>
+      <c r="R1" s="752" t="n"/>
+      <c r="S1" s="752" t="n"/>
+      <c r="T1" s="752" t="n"/>
+      <c r="U1" s="752" t="n"/>
+      <c r="V1" s="752" t="n"/>
+      <c r="W1" s="752" t="n"/>
+      <c r="X1" s="752" t="n"/>
+      <c r="Y1" s="752" t="n"/>
+      <c r="Z1" s="752" t="n"/>
+      <c r="AA1" s="752" t="n"/>
+      <c r="AB1" s="752" t="n"/>
+      <c r="AC1" s="752" t="n"/>
+      <c r="AD1" s="844" t="n"/>
+      <c r="AE1" s="508" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="800" t="n"/>
-      <c r="AG1" s="800" t="n"/>
-      <c r="AH1" s="803" t="n"/>
-      <c r="AI1" s="510" t="inlineStr">
+      <c r="AF1" s="752" t="n"/>
+      <c r="AG1" s="752" t="n"/>
+      <c r="AH1" s="846" t="n"/>
+      <c r="AI1" s="511" t="inlineStr">
         <is>
           <t>FRM-306</t>
         </is>
       </c>
-      <c r="AJ1" s="800" t="n"/>
-      <c r="AK1" s="800" t="n"/>
-      <c r="AL1" s="800" t="n"/>
-      <c r="AM1" s="800" t="n"/>
-      <c r="AN1" s="801" t="n"/>
+      <c r="AJ1" s="752" t="n"/>
+      <c r="AK1" s="752" t="n"/>
+      <c r="AL1" s="752" t="n"/>
+      <c r="AM1" s="752" t="n"/>
+      <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="804" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="805" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="805" t="n"/>
-      <c r="AE2" s="806" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="819" t="n"/>
+      <c r="G2" s="819" t="n"/>
+      <c r="H2" s="820" t="n"/>
+      <c r="I2" s="819" t="n"/>
+      <c r="J2" s="819" t="n"/>
+      <c r="K2" s="819" t="n"/>
+      <c r="L2" s="819" t="n"/>
+      <c r="M2" s="819" t="n"/>
+      <c r="N2" s="819" t="n"/>
+      <c r="O2" s="819" t="n"/>
+      <c r="P2" s="819" t="n"/>
+      <c r="Q2" s="819" t="n"/>
+      <c r="R2" s="819" t="n"/>
+      <c r="S2" s="819" t="n"/>
+      <c r="T2" s="819" t="n"/>
+      <c r="U2" s="819" t="n"/>
+      <c r="V2" s="819" t="n"/>
+      <c r="W2" s="819" t="n"/>
+      <c r="X2" s="819" t="n"/>
+      <c r="Y2" s="819" t="n"/>
+      <c r="Z2" s="819" t="n"/>
+      <c r="AA2" s="819" t="n"/>
+      <c r="AB2" s="819" t="n"/>
+      <c r="AC2" s="819" t="n"/>
+      <c r="AD2" s="820" t="n"/>
+      <c r="AE2" s="821" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="807" t="n"/>
-      <c r="AI2" s="808" t="inlineStr">
+      <c r="AF2" s="822" t="n"/>
+      <c r="AG2" s="822" t="n"/>
+      <c r="AH2" s="823" t="n"/>
+      <c r="AI2" s="824" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="805" t="n"/>
+      <c r="AJ2" s="825" t="n"/>
+      <c r="AK2" s="825" t="n"/>
+      <c r="AL2" s="825" t="n"/>
+      <c r="AM2" s="825" t="n"/>
+      <c r="AN2" s="826" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="804" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="805" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="805" t="n"/>
-      <c r="AE3" s="806" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="828" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="828" t="n"/>
+      <c r="AE3" s="829" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="807" t="n"/>
-      <c r="AI3" s="808" t="inlineStr">
+      <c r="AF3" s="830" t="n"/>
+      <c r="AG3" s="830" t="n"/>
+      <c r="AH3" s="831" t="n"/>
+      <c r="AI3" s="724" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="805" t="n"/>
+      <c r="AJ3" s="832" t="n"/>
+      <c r="AK3" s="832" t="n"/>
+      <c r="AL3" s="832" t="n"/>
+      <c r="AM3" s="832" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="804" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="805" t="n"/>
-      <c r="I4" s="809" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="828" t="n"/>
+      <c r="I4" s="346" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="805" t="n"/>
-      <c r="AE4" s="806" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="828" t="n"/>
+      <c r="AE4" s="829" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="807" t="n"/>
-      <c r="AI4" s="808" t="inlineStr">
+      <c r="AF4" s="830" t="n"/>
+      <c r="AG4" s="830" t="n"/>
+      <c r="AH4" s="831" t="n"/>
+      <c r="AI4" s="724" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="805" t="n"/>
+      <c r="AJ4" s="832" t="n"/>
+      <c r="AK4" s="832" t="n"/>
+      <c r="AL4" s="832" t="n"/>
+      <c r="AM4" s="832" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="810" t="n"/>
-      <c r="B5" s="811" t="n"/>
-      <c r="C5" s="811" t="n"/>
-      <c r="D5" s="811" t="n"/>
-      <c r="E5" s="811" t="n"/>
-      <c r="F5" s="811" t="n"/>
-      <c r="G5" s="811" t="n"/>
-      <c r="H5" s="812" t="n"/>
-      <c r="I5" s="813" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="828" t="n"/>
+      <c r="I5" s="595" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="811" t="n"/>
-      <c r="K5" s="811" t="n"/>
-      <c r="L5" s="811" t="n"/>
-      <c r="M5" s="811" t="n"/>
-      <c r="N5" s="811" t="n"/>
-      <c r="O5" s="811" t="n"/>
-      <c r="P5" s="811" t="n"/>
-      <c r="Q5" s="811" t="n"/>
-      <c r="R5" s="811" t="n"/>
-      <c r="S5" s="811" t="n"/>
-      <c r="T5" s="811" t="n"/>
-      <c r="U5" s="811" t="n"/>
-      <c r="V5" s="811" t="n"/>
-      <c r="W5" s="811" t="n"/>
-      <c r="X5" s="811" t="n"/>
-      <c r="Y5" s="811" t="n"/>
-      <c r="Z5" s="811" t="n"/>
-      <c r="AA5" s="811" t="n"/>
-      <c r="AB5" s="811" t="n"/>
-      <c r="AC5" s="811" t="n"/>
-      <c r="AD5" s="812" t="n"/>
-      <c r="AE5" s="814" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="828" t="n"/>
+      <c r="AE5" s="829" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="811" t="n"/>
-      <c r="AG5" s="811" t="n"/>
-      <c r="AH5" s="815" t="n"/>
-      <c r="AI5" s="816" t="inlineStr">
+      <c r="AF5" s="830" t="n"/>
+      <c r="AG5" s="830" t="n"/>
+      <c r="AH5" s="831" t="n"/>
+      <c r="AI5" s="724" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="811" t="n"/>
-      <c r="AK5" s="811" t="n"/>
-      <c r="AL5" s="811" t="n"/>
-      <c r="AM5" s="811" t="n"/>
-      <c r="AN5" s="812" t="n"/>
+      <c r="AJ5" s="832" t="n"/>
+      <c r="AK5" s="832" t="n"/>
+      <c r="AL5" s="832" t="n"/>
+      <c r="AM5" s="832" t="n"/>
+      <c r="AN5" s="833" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="817" t="n"/>
-      <c r="B6" s="817" t="n"/>
-      <c r="C6" s="817" t="n"/>
-      <c r="D6" s="817" t="n"/>
-      <c r="E6" s="817" t="n"/>
-      <c r="F6" s="817" t="n"/>
-      <c r="G6" s="817" t="n"/>
-      <c r="H6" s="817" t="n"/>
-      <c r="I6" s="817" t="n"/>
-      <c r="J6" s="817" t="n"/>
-      <c r="K6" s="817" t="n"/>
-      <c r="L6" s="817" t="n"/>
-      <c r="M6" s="817" t="n"/>
-      <c r="N6" s="817" t="n"/>
-      <c r="O6" s="817" t="n"/>
-      <c r="P6" s="817" t="n"/>
-      <c r="Q6" s="817" t="n"/>
-      <c r="R6" s="817" t="n"/>
-      <c r="S6" s="817" t="n"/>
-      <c r="T6" s="817" t="n"/>
-      <c r="U6" s="817" t="n"/>
-      <c r="V6" s="817" t="n"/>
-      <c r="W6" s="817" t="n"/>
-      <c r="X6" s="817" t="n"/>
-      <c r="Y6" s="817" t="n"/>
-      <c r="Z6" s="817" t="n"/>
-      <c r="AA6" s="817" t="n"/>
-      <c r="AB6" s="817" t="n"/>
-      <c r="AC6" s="817" t="n"/>
-      <c r="AD6" s="817" t="n"/>
-      <c r="AE6" s="817" t="n"/>
-      <c r="AF6" s="817" t="n"/>
-      <c r="AG6" s="817" t="n"/>
-      <c r="AH6" s="817" t="n"/>
-      <c r="AI6" s="817" t="n"/>
-      <c r="AJ6" s="817" t="n"/>
-      <c r="AK6" s="817" t="n"/>
-      <c r="AL6" s="817" t="n"/>
-      <c r="AM6" s="817" t="n"/>
-      <c r="AN6" s="817" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="847" t="n"/>
+      <c r="B6" s="848" t="n"/>
+      <c r="C6" s="848" t="n"/>
+      <c r="D6" s="848" t="n"/>
+      <c r="E6" s="848" t="n"/>
+      <c r="F6" s="848" t="n"/>
+      <c r="G6" s="848" t="n"/>
+      <c r="H6" s="849" t="n"/>
+      <c r="I6" s="848" t="n"/>
+      <c r="J6" s="848" t="n"/>
+      <c r="K6" s="848" t="n"/>
+      <c r="L6" s="848" t="n"/>
+      <c r="M6" s="848" t="n"/>
+      <c r="N6" s="848" t="n"/>
+      <c r="O6" s="848" t="n"/>
+      <c r="P6" s="848" t="n"/>
+      <c r="Q6" s="848" t="n"/>
+      <c r="R6" s="848" t="n"/>
+      <c r="S6" s="848" t="n"/>
+      <c r="T6" s="848" t="n"/>
+      <c r="U6" s="848" t="n"/>
+      <c r="V6" s="848" t="n"/>
+      <c r="W6" s="848" t="n"/>
+      <c r="X6" s="848" t="n"/>
+      <c r="Y6" s="848" t="n"/>
+      <c r="Z6" s="848" t="n"/>
+      <c r="AA6" s="848" t="n"/>
+      <c r="AB6" s="848" t="n"/>
+      <c r="AC6" s="848" t="n"/>
+      <c r="AD6" s="849" t="n"/>
+      <c r="AE6" s="850" t="n"/>
+      <c r="AF6" s="850" t="n"/>
+      <c r="AG6" s="850" t="n"/>
+      <c r="AH6" s="851" t="n"/>
+      <c r="AI6" s="852" t="n"/>
+      <c r="AJ6" s="852" t="n"/>
+      <c r="AK6" s="852" t="n"/>
+      <c r="AL6" s="852" t="n"/>
+      <c r="AM6" s="852" t="n"/>
+      <c r="AN6" s="853" t="n"/>
     </row>
-    <row r="7" hidden="1">
-      <c r="A7" s="588" t="inlineStr">
-        <is>
-          <t>REF_PART_REV_MASTER</t>
-        </is>
-      </c>
-      <c r="B7" s="543" t="inlineStr">
-        <is>
-          <t>REF_JOB_WO_MASTER</t>
-        </is>
-      </c>
-      <c r="C7" s="543" t="inlineStr">
-        <is>
-          <t>REF_OWNER_PERSON_MASTER</t>
-        </is>
-      </c>
-      <c r="D7" s="543" t="inlineStr">
-        <is>
-          <t>REF_DOCUMENT_CODE_MASTER</t>
-        </is>
-      </c>
-      <c r="E7" s="818" t="n"/>
-      <c r="F7" s="818" t="n"/>
-      <c r="G7" s="818" t="n"/>
-      <c r="H7" s="818" t="n"/>
-      <c r="I7" s="818" t="n"/>
-      <c r="J7" s="818" t="n"/>
-      <c r="K7" s="818" t="n"/>
-      <c r="L7" s="818" t="n"/>
-      <c r="M7" s="818" t="n"/>
-      <c r="N7" s="818" t="n"/>
-      <c r="O7" s="818" t="n"/>
-      <c r="P7" s="818" t="n"/>
-      <c r="Q7" s="818" t="n"/>
-      <c r="R7" s="818" t="n"/>
-      <c r="S7" s="818" t="n"/>
-      <c r="T7" s="818" t="n"/>
-      <c r="U7" s="818" t="n"/>
-      <c r="V7" s="818" t="n"/>
-      <c r="W7" s="818" t="n"/>
-      <c r="X7" s="818" t="n"/>
-      <c r="Y7" s="818" t="n"/>
-      <c r="Z7" s="818" t="n"/>
-      <c r="AA7" s="818" t="n"/>
-      <c r="AB7" s="818" t="n"/>
-      <c r="AC7" s="818" t="n"/>
-      <c r="AD7" s="818" t="n"/>
-      <c r="AE7" s="818" t="n"/>
-      <c r="AF7" s="818" t="n"/>
-      <c r="AG7" s="818" t="n"/>
-      <c r="AH7" s="818" t="n"/>
-      <c r="AI7" s="818" t="n"/>
-      <c r="AJ7" s="818" t="n"/>
-      <c r="AK7" s="818" t="n"/>
-      <c r="AL7" s="818" t="n"/>
-      <c r="AM7" s="818" t="n"/>
-      <c r="AN7" s="818" t="n"/>
+    <row r="7" hidden="1" ht="4" customHeight="1">
+      <c r="A7" s="854" t="n"/>
+      <c r="B7" s="854" t="n"/>
+      <c r="C7" s="854" t="n"/>
+      <c r="D7" s="854" t="n"/>
+      <c r="E7" s="855" t="n"/>
+      <c r="F7" s="855" t="n"/>
+      <c r="G7" s="855" t="n"/>
+      <c r="H7" s="855" t="n"/>
+      <c r="I7" s="855" t="n"/>
+      <c r="J7" s="855" t="n"/>
+      <c r="K7" s="855" t="n"/>
+      <c r="L7" s="855" t="n"/>
+      <c r="M7" s="855" t="n"/>
+      <c r="N7" s="855" t="n"/>
+      <c r="O7" s="855" t="n"/>
+      <c r="P7" s="855" t="n"/>
+      <c r="Q7" s="855" t="n"/>
+      <c r="R7" s="855" t="n"/>
+      <c r="S7" s="855" t="n"/>
+      <c r="T7" s="855" t="n"/>
+      <c r="U7" s="855" t="n"/>
+      <c r="V7" s="855" t="n"/>
+      <c r="W7" s="855" t="n"/>
+      <c r="X7" s="855" t="n"/>
+      <c r="Y7" s="855" t="n"/>
+      <c r="Z7" s="855" t="n"/>
+      <c r="AA7" s="855" t="n"/>
+      <c r="AB7" s="855" t="n"/>
+      <c r="AC7" s="855" t="n"/>
+      <c r="AD7" s="855" t="n"/>
+      <c r="AE7" s="855" t="n"/>
+      <c r="AF7" s="855" t="n"/>
+      <c r="AG7" s="855" t="n"/>
+      <c r="AH7" s="855" t="n"/>
+      <c r="AI7" s="855" t="n"/>
+      <c r="AJ7" s="855" t="n"/>
+      <c r="AK7" s="855" t="n"/>
+      <c r="AL7" s="855" t="n"/>
+      <c r="AM7" s="855" t="n"/>
+      <c r="AN7" s="855" t="n"/>
     </row>
     <row r="8" hidden="1">
-      <c r="A8" s="584" t="inlineStr">
+      <c r="A8" s="856" t="inlineStr">
         <is>
           <t>PN-1001 / Rev.A</t>
         </is>
       </c>
-      <c r="B8" s="402" t="inlineStr">
+      <c r="B8" s="857" t="inlineStr">
         <is>
           <t>JOB-240001</t>
         </is>
       </c>
-      <c r="C8" s="402" t="inlineStr">
+      <c r="C8" s="857" t="inlineStr">
         <is>
           <t>Planning Lead</t>
         </is>
       </c>
-      <c r="D8" s="402" t="inlineStr">
+      <c r="D8" s="857" t="inlineStr">
         <is>
           <t>FRM-202</t>
         </is>
@@ -12572,22 +12901,22 @@
       <c r="AN8" s="818" t="n"/>
     </row>
     <row r="9" hidden="1">
-      <c r="A9" s="584" t="inlineStr">
+      <c r="A9" s="856" t="inlineStr">
         <is>
           <t>PN-1002 / Rev.B</t>
         </is>
       </c>
-      <c r="B9" s="402" t="inlineStr">
+      <c r="B9" s="857" t="inlineStr">
         <is>
           <t>JOB-240002</t>
         </is>
       </c>
-      <c r="C9" s="402" t="inlineStr">
+      <c r="C9" s="857" t="inlineStr">
         <is>
           <t>Production Supervisor</t>
         </is>
       </c>
-      <c r="D9" s="402" t="inlineStr">
+      <c r="D9" s="857" t="inlineStr">
         <is>
           <t>FRM-302</t>
         </is>
@@ -12630,22 +12959,22 @@
       <c r="AN9" s="818" t="n"/>
     </row>
     <row r="10" hidden="1">
-      <c r="A10" s="584" t="inlineStr">
+      <c r="A10" s="856" t="inlineStr">
         <is>
           <t>PN-1003 / Rev.C</t>
         </is>
       </c>
-      <c r="B10" s="402" t="inlineStr">
+      <c r="B10" s="857" t="inlineStr">
         <is>
           <t>JOB-240003</t>
         </is>
       </c>
-      <c r="C10" s="402" t="inlineStr">
+      <c r="C10" s="857" t="inlineStr">
         <is>
           <t>QA Engineer</t>
         </is>
       </c>
-      <c r="D10" s="402" t="inlineStr">
+      <c r="D10" s="857" t="inlineStr">
         <is>
           <t>FRM-306</t>
         </is>
@@ -12690,12 +13019,12 @@
     <row r="11" hidden="1">
       <c r="A11" s="818" t="n"/>
       <c r="B11" s="818" t="n"/>
-      <c r="C11" s="402" t="inlineStr">
+      <c r="C11" s="857" t="inlineStr">
         <is>
           <t>Engineering Lead</t>
         </is>
       </c>
-      <c r="D11" s="402" t="inlineStr">
+      <c r="D11" s="857" t="inlineStr">
         <is>
           <t>FRM-511</t>
         </is>
@@ -12740,12 +13069,12 @@
     <row r="12" hidden="1">
       <c r="A12" s="818" t="n"/>
       <c r="B12" s="818" t="n"/>
-      <c r="C12" s="552" t="inlineStr">
+      <c r="C12" s="858" t="inlineStr">
         <is>
           <t>Setup Technician</t>
         </is>
       </c>
-      <c r="D12" s="552" t="inlineStr">
+      <c r="D12" s="858" t="inlineStr">
         <is>
           <t>FRM-519</t>
         </is>
@@ -13117,6 +13446,7 @@
   </mergeCells>
   <pageMargins left="0.197" right="0.197" top="0.197" bottom="0.197" header="0.1" footer="0.1"/>
   <pageSetup paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -13171,7 +13501,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="391" t="n"/>
       <c r="B1" s="323" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -13226,283 +13556,288 @@
       <c r="AN1" s="701" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="324" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="G2" s="702" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="819" t="n"/>
+      <c r="G2" s="859" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="H2" s="703" t="inlineStr">
+      <c r="H2" s="860" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="I2" s="704" t="n"/>
-      <c r="J2" s="704" t="n"/>
-      <c r="K2" s="704" t="n"/>
-      <c r="L2" s="704" t="n"/>
-      <c r="M2" s="704" t="n"/>
-      <c r="N2" s="704" t="n"/>
-      <c r="O2" s="704" t="n"/>
-      <c r="P2" s="704" t="n"/>
-      <c r="Q2" s="704" t="n"/>
-      <c r="R2" s="704" t="n"/>
-      <c r="S2" s="704" t="n"/>
-      <c r="T2" s="704" t="n"/>
-      <c r="U2" s="704" t="n"/>
-      <c r="V2" s="704" t="n"/>
-      <c r="W2" s="704" t="n"/>
-      <c r="X2" s="704" t="n"/>
-      <c r="Y2" s="704" t="n"/>
-      <c r="Z2" s="704" t="n"/>
-      <c r="AA2" s="704" t="n"/>
-      <c r="AB2" s="704" t="n"/>
-      <c r="AC2" s="704" t="n"/>
-      <c r="AD2" s="704" t="n"/>
-      <c r="AE2" s="705" t="n"/>
-      <c r="AF2" s="705" t="n"/>
-      <c r="AG2" s="705" t="n"/>
-      <c r="AH2" s="705" t="n"/>
-      <c r="AI2" s="656" t="n"/>
-      <c r="AJ2" s="656" t="n"/>
-      <c r="AK2" s="656" t="n"/>
-      <c r="AL2" s="656" t="n"/>
-      <c r="AM2" s="656" t="n"/>
-      <c r="AN2" s="706" t="n"/>
+      <c r="I2" s="699" t="n"/>
+      <c r="J2" s="699" t="n"/>
+      <c r="K2" s="699" t="n"/>
+      <c r="L2" s="699" t="n"/>
+      <c r="M2" s="699" t="n"/>
+      <c r="N2" s="699" t="n"/>
+      <c r="O2" s="699" t="n"/>
+      <c r="P2" s="699" t="n"/>
+      <c r="Q2" s="699" t="n"/>
+      <c r="R2" s="699" t="n"/>
+      <c r="S2" s="699" t="n"/>
+      <c r="T2" s="699" t="n"/>
+      <c r="U2" s="699" t="n"/>
+      <c r="V2" s="699" t="n"/>
+      <c r="W2" s="699" t="n"/>
+      <c r="X2" s="699" t="n"/>
+      <c r="Y2" s="699" t="n"/>
+      <c r="Z2" s="699" t="n"/>
+      <c r="AA2" s="699" t="n"/>
+      <c r="AB2" s="699" t="n"/>
+      <c r="AC2" s="699" t="n"/>
+      <c r="AD2" s="861" t="n"/>
+      <c r="AE2" s="862" t="n"/>
+      <c r="AF2" s="862" t="n"/>
+      <c r="AG2" s="862" t="n"/>
+      <c r="AH2" s="863" t="n"/>
+      <c r="AI2" s="864" t="n"/>
+      <c r="AJ2" s="864" t="n"/>
+      <c r="AK2" s="864" t="n"/>
+      <c r="AL2" s="864" t="n"/>
+      <c r="AM2" s="864" t="n"/>
+      <c r="AN2" s="865" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="324" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="G3" s="702" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="593" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="H3" s="703" t="inlineStr">
+      <c r="H3" s="866" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="I3" s="704" t="n"/>
-      <c r="J3" s="704" t="n"/>
-      <c r="K3" s="704" t="n"/>
-      <c r="L3" s="704" t="n"/>
-      <c r="M3" s="704" t="n"/>
-      <c r="N3" s="704" t="n"/>
-      <c r="O3" s="704" t="n"/>
-      <c r="P3" s="704" t="n"/>
-      <c r="Q3" s="704" t="n"/>
-      <c r="R3" s="704" t="n"/>
-      <c r="S3" s="704" t="n"/>
-      <c r="T3" s="704" t="n"/>
-      <c r="U3" s="704" t="n"/>
-      <c r="V3" s="704" t="n"/>
-      <c r="W3" s="704" t="n"/>
-      <c r="X3" s="704" t="n"/>
-      <c r="Y3" s="704" t="n"/>
-      <c r="Z3" s="704" t="n"/>
-      <c r="AA3" s="704" t="n"/>
-      <c r="AB3" s="704" t="n"/>
-      <c r="AC3" s="704" t="n"/>
-      <c r="AD3" s="704" t="n"/>
-      <c r="AE3" s="705" t="n"/>
-      <c r="AF3" s="705" t="n"/>
-      <c r="AG3" s="705" t="n"/>
-      <c r="AH3" s="705" t="n"/>
-      <c r="AI3" s="656" t="n"/>
-      <c r="AJ3" s="656" t="n"/>
-      <c r="AK3" s="656" t="n"/>
-      <c r="AL3" s="656" t="n"/>
-      <c r="AM3" s="656" t="n"/>
-      <c r="AN3" s="706" t="n"/>
+      <c r="I3" s="867" t="n"/>
+      <c r="J3" s="867" t="n"/>
+      <c r="K3" s="867" t="n"/>
+      <c r="L3" s="867" t="n"/>
+      <c r="M3" s="867" t="n"/>
+      <c r="N3" s="867" t="n"/>
+      <c r="O3" s="867" t="n"/>
+      <c r="P3" s="867" t="n"/>
+      <c r="Q3" s="867" t="n"/>
+      <c r="R3" s="867" t="n"/>
+      <c r="S3" s="867" t="n"/>
+      <c r="T3" s="867" t="n"/>
+      <c r="U3" s="867" t="n"/>
+      <c r="V3" s="867" t="n"/>
+      <c r="W3" s="867" t="n"/>
+      <c r="X3" s="867" t="n"/>
+      <c r="Y3" s="867" t="n"/>
+      <c r="Z3" s="867" t="n"/>
+      <c r="AA3" s="867" t="n"/>
+      <c r="AB3" s="867" t="n"/>
+      <c r="AC3" s="867" t="n"/>
+      <c r="AD3" s="868" t="n"/>
+      <c r="AE3" s="869" t="n"/>
+      <c r="AF3" s="869" t="n"/>
+      <c r="AG3" s="869" t="n"/>
+      <c r="AH3" s="870" t="n"/>
+      <c r="AI3" s="871" t="n"/>
+      <c r="AJ3" s="871" t="n"/>
+      <c r="AK3" s="871" t="n"/>
+      <c r="AL3" s="871" t="n"/>
+      <c r="AM3" s="871" t="n"/>
+      <c r="AN3" s="872" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="324" t="n"/>
-      <c r="C4" s="707" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="595" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="G4" s="702" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="593" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="H4" s="703" t="inlineStr"/>
-      <c r="I4" s="708" t="n"/>
-      <c r="J4" s="708" t="n"/>
-      <c r="K4" s="708" t="n"/>
-      <c r="L4" s="708" t="n"/>
-      <c r="M4" s="708" t="n"/>
-      <c r="N4" s="708" t="n"/>
-      <c r="O4" s="708" t="n"/>
-      <c r="P4" s="708" t="n"/>
-      <c r="Q4" s="708" t="n"/>
-      <c r="R4" s="708" t="n"/>
-      <c r="S4" s="708" t="n"/>
-      <c r="T4" s="708" t="n"/>
-      <c r="U4" s="708" t="n"/>
-      <c r="V4" s="708" t="n"/>
-      <c r="W4" s="708" t="n"/>
-      <c r="X4" s="708" t="n"/>
-      <c r="Y4" s="708" t="n"/>
-      <c r="Z4" s="708" t="n"/>
-      <c r="AA4" s="708" t="n"/>
-      <c r="AB4" s="708" t="n"/>
-      <c r="AC4" s="708" t="n"/>
-      <c r="AD4" s="708" t="n"/>
-      <c r="AE4" s="705" t="n"/>
-      <c r="AF4" s="705" t="n"/>
-      <c r="AG4" s="705" t="n"/>
-      <c r="AH4" s="705" t="n"/>
-      <c r="AI4" s="656" t="n"/>
-      <c r="AJ4" s="656" t="n"/>
-      <c r="AK4" s="656" t="n"/>
-      <c r="AL4" s="656" t="n"/>
-      <c r="AM4" s="656" t="n"/>
-      <c r="AN4" s="706" t="n"/>
+      <c r="H4" s="866" t="inlineStr"/>
+      <c r="I4" s="524" t="n"/>
+      <c r="J4" s="524" t="n"/>
+      <c r="K4" s="524" t="n"/>
+      <c r="L4" s="524" t="n"/>
+      <c r="M4" s="524" t="n"/>
+      <c r="N4" s="524" t="n"/>
+      <c r="O4" s="524" t="n"/>
+      <c r="P4" s="524" t="n"/>
+      <c r="Q4" s="524" t="n"/>
+      <c r="R4" s="524" t="n"/>
+      <c r="S4" s="524" t="n"/>
+      <c r="T4" s="524" t="n"/>
+      <c r="U4" s="524" t="n"/>
+      <c r="V4" s="524" t="n"/>
+      <c r="W4" s="524" t="n"/>
+      <c r="X4" s="524" t="n"/>
+      <c r="Y4" s="524" t="n"/>
+      <c r="Z4" s="524" t="n"/>
+      <c r="AA4" s="524" t="n"/>
+      <c r="AB4" s="524" t="n"/>
+      <c r="AC4" s="524" t="n"/>
+      <c r="AD4" s="873" t="n"/>
+      <c r="AE4" s="869" t="n"/>
+      <c r="AF4" s="869" t="n"/>
+      <c r="AG4" s="869" t="n"/>
+      <c r="AH4" s="870" t="n"/>
+      <c r="AI4" s="871" t="n"/>
+      <c r="AJ4" s="871" t="n"/>
+      <c r="AK4" s="871" t="n"/>
+      <c r="AL4" s="871" t="n"/>
+      <c r="AM4" s="871" t="n"/>
+      <c r="AN4" s="872" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="709" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="874" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="283" t="n"/>
-      <c r="G5" s="710" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="593" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="H5" s="711" t="inlineStr"/>
-      <c r="I5" s="712" t="n"/>
-      <c r="J5" s="712" t="n"/>
-      <c r="K5" s="712" t="n"/>
-      <c r="L5" s="712" t="n"/>
-      <c r="M5" s="712" t="n"/>
-      <c r="N5" s="712" t="n"/>
-      <c r="O5" s="712" t="n"/>
-      <c r="P5" s="712" t="n"/>
-      <c r="Q5" s="712" t="n"/>
-      <c r="R5" s="712" t="n"/>
-      <c r="S5" s="712" t="n"/>
-      <c r="T5" s="712" t="n"/>
-      <c r="U5" s="712" t="n"/>
-      <c r="V5" s="712" t="n"/>
-      <c r="W5" s="712" t="n"/>
-      <c r="X5" s="712" t="n"/>
-      <c r="Y5" s="712" t="n"/>
-      <c r="Z5" s="712" t="n"/>
-      <c r="AA5" s="712" t="n"/>
-      <c r="AB5" s="712" t="n"/>
-      <c r="AC5" s="712" t="n"/>
-      <c r="AD5" s="712" t="n"/>
-      <c r="AE5" s="713" t="n"/>
-      <c r="AF5" s="713" t="n"/>
-      <c r="AG5" s="713" t="n"/>
-      <c r="AH5" s="713" t="n"/>
-      <c r="AI5" s="662" t="n"/>
-      <c r="AJ5" s="662" t="n"/>
-      <c r="AK5" s="662" t="n"/>
-      <c r="AL5" s="662" t="n"/>
-      <c r="AM5" s="662" t="n"/>
-      <c r="AN5" s="714" t="n"/>
+      <c r="H5" s="866" t="inlineStr"/>
+      <c r="I5" s="875" t="n"/>
+      <c r="J5" s="875" t="n"/>
+      <c r="K5" s="875" t="n"/>
+      <c r="L5" s="875" t="n"/>
+      <c r="M5" s="875" t="n"/>
+      <c r="N5" s="875" t="n"/>
+      <c r="O5" s="875" t="n"/>
+      <c r="P5" s="875" t="n"/>
+      <c r="Q5" s="875" t="n"/>
+      <c r="R5" s="875" t="n"/>
+      <c r="S5" s="875" t="n"/>
+      <c r="T5" s="875" t="n"/>
+      <c r="U5" s="875" t="n"/>
+      <c r="V5" s="875" t="n"/>
+      <c r="W5" s="875" t="n"/>
+      <c r="X5" s="875" t="n"/>
+      <c r="Y5" s="875" t="n"/>
+      <c r="Z5" s="875" t="n"/>
+      <c r="AA5" s="875" t="n"/>
+      <c r="AB5" s="875" t="n"/>
+      <c r="AC5" s="875" t="n"/>
+      <c r="AD5" s="876" t="n"/>
+      <c r="AE5" s="869" t="n"/>
+      <c r="AF5" s="869" t="n"/>
+      <c r="AG5" s="869" t="n"/>
+      <c r="AH5" s="870" t="n"/>
+      <c r="AI5" s="871" t="n"/>
+      <c r="AJ5" s="871" t="n"/>
+      <c r="AK5" s="871" t="n"/>
+      <c r="AL5" s="871" t="n"/>
+      <c r="AM5" s="871" t="n"/>
+      <c r="AN5" s="872" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="715" t="n"/>
-      <c r="B6" s="664" t="n"/>
-      <c r="C6" s="664" t="n"/>
-      <c r="D6" s="664" t="n"/>
-      <c r="E6" s="664" t="n"/>
-      <c r="F6" s="664" t="n"/>
-      <c r="G6" s="664" t="n"/>
-      <c r="H6" s="664" t="n"/>
-      <c r="I6" s="664" t="n"/>
-      <c r="J6" s="664" t="n"/>
-      <c r="K6" s="664" t="n"/>
-      <c r="L6" s="664" t="n"/>
-      <c r="M6" s="664" t="n"/>
-      <c r="N6" s="664" t="n"/>
-      <c r="O6" s="664" t="n"/>
-      <c r="P6" s="664" t="n"/>
-      <c r="Q6" s="664" t="n"/>
-      <c r="R6" s="664" t="n"/>
-      <c r="S6" s="664" t="n"/>
-      <c r="T6" s="664" t="n"/>
-      <c r="U6" s="664" t="n"/>
-      <c r="V6" s="664" t="n"/>
-      <c r="W6" s="664" t="n"/>
-      <c r="X6" s="664" t="n"/>
-      <c r="Y6" s="664" t="n"/>
-      <c r="Z6" s="664" t="n"/>
-      <c r="AA6" s="664" t="n"/>
-      <c r="AB6" s="664" t="n"/>
-      <c r="AC6" s="664" t="n"/>
-      <c r="AD6" s="664" t="n"/>
-      <c r="AE6" s="664" t="n"/>
-      <c r="AF6" s="664" t="n"/>
-      <c r="AG6" s="664" t="n"/>
-      <c r="AH6" s="664" t="n"/>
-      <c r="AI6" s="664" t="n"/>
-      <c r="AJ6" s="664" t="n"/>
-      <c r="AK6" s="664" t="n"/>
-      <c r="AL6" s="664" t="n"/>
-      <c r="AM6" s="664" t="n"/>
-      <c r="AN6" s="664" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="356" t="n"/>
+      <c r="B6" s="835" t="n"/>
+      <c r="C6" s="835" t="n"/>
+      <c r="D6" s="835" t="n"/>
+      <c r="E6" s="835" t="n"/>
+      <c r="F6" s="835" t="n"/>
+      <c r="G6" s="835" t="n"/>
+      <c r="H6" s="836" t="n"/>
+      <c r="I6" s="835" t="n"/>
+      <c r="J6" s="835" t="n"/>
+      <c r="K6" s="835" t="n"/>
+      <c r="L6" s="835" t="n"/>
+      <c r="M6" s="835" t="n"/>
+      <c r="N6" s="835" t="n"/>
+      <c r="O6" s="835" t="n"/>
+      <c r="P6" s="835" t="n"/>
+      <c r="Q6" s="835" t="n"/>
+      <c r="R6" s="835" t="n"/>
+      <c r="S6" s="835" t="n"/>
+      <c r="T6" s="835" t="n"/>
+      <c r="U6" s="835" t="n"/>
+      <c r="V6" s="835" t="n"/>
+      <c r="W6" s="835" t="n"/>
+      <c r="X6" s="835" t="n"/>
+      <c r="Y6" s="835" t="n"/>
+      <c r="Z6" s="835" t="n"/>
+      <c r="AA6" s="835" t="n"/>
+      <c r="AB6" s="835" t="n"/>
+      <c r="AC6" s="835" t="n"/>
+      <c r="AD6" s="836" t="n"/>
+      <c r="AE6" s="837" t="n"/>
+      <c r="AF6" s="837" t="n"/>
+      <c r="AG6" s="837" t="n"/>
+      <c r="AH6" s="838" t="n"/>
+      <c r="AI6" s="839" t="n"/>
+      <c r="AJ6" s="839" t="n"/>
+      <c r="AK6" s="839" t="n"/>
+      <c r="AL6" s="839" t="n"/>
+      <c r="AM6" s="839" t="n"/>
+      <c r="AN6" s="840" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="665" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="289" t="n"/>
-      <c r="I7" s="716" t="n"/>
-      <c r="J7" s="716" t="n"/>
-      <c r="K7" s="716" t="n"/>
-      <c r="L7" s="716" t="n"/>
-      <c r="M7" s="716" t="n"/>
-      <c r="N7" s="716" t="n"/>
-      <c r="O7" s="716" t="n"/>
-      <c r="P7" s="716" t="n"/>
-      <c r="Q7" s="716" t="n"/>
-      <c r="R7" s="716" t="n"/>
-      <c r="S7" s="716" t="n"/>
-      <c r="T7" s="716" t="n"/>
-      <c r="U7" s="716" t="n"/>
-      <c r="V7" s="716" t="n"/>
-      <c r="W7" s="716" t="n"/>
-      <c r="X7" s="716" t="n"/>
-      <c r="Y7" s="716" t="n"/>
-      <c r="Z7" s="716" t="n"/>
-      <c r="AA7" s="716" t="n"/>
-      <c r="AB7" s="716" t="n"/>
-      <c r="AC7" s="716" t="n"/>
-      <c r="AD7" s="716" t="n"/>
-      <c r="AE7" s="716" t="n"/>
-      <c r="AF7" s="716" t="n"/>
-      <c r="AG7" s="716" t="n"/>
-      <c r="AH7" s="716" t="n"/>
-      <c r="AI7" s="716" t="n"/>
-      <c r="AJ7" s="716" t="n"/>
-      <c r="AK7" s="716" t="n"/>
-      <c r="AL7" s="716" t="n"/>
-      <c r="AM7" s="716" t="n"/>
-      <c r="AN7" s="717" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="841" t="n"/>
+      <c r="B7" s="842" t="n"/>
+      <c r="C7" s="842" t="n"/>
+      <c r="D7" s="842" t="n"/>
+      <c r="E7" s="842" t="n"/>
+      <c r="F7" s="842" t="n"/>
+      <c r="G7" s="842" t="n"/>
+      <c r="H7" s="842" t="n"/>
+      <c r="I7" s="841" t="n"/>
+      <c r="J7" s="841" t="n"/>
+      <c r="K7" s="841" t="n"/>
+      <c r="L7" s="841" t="n"/>
+      <c r="M7" s="841" t="n"/>
+      <c r="N7" s="841" t="n"/>
+      <c r="O7" s="841" t="n"/>
+      <c r="P7" s="841" t="n"/>
+      <c r="Q7" s="841" t="n"/>
+      <c r="R7" s="841" t="n"/>
+      <c r="S7" s="841" t="n"/>
+      <c r="T7" s="841" t="n"/>
+      <c r="U7" s="841" t="n"/>
+      <c r="V7" s="841" t="n"/>
+      <c r="W7" s="841" t="n"/>
+      <c r="X7" s="841" t="n"/>
+      <c r="Y7" s="841" t="n"/>
+      <c r="Z7" s="841" t="n"/>
+      <c r="AA7" s="841" t="n"/>
+      <c r="AB7" s="841" t="n"/>
+      <c r="AC7" s="841" t="n"/>
+      <c r="AD7" s="841" t="n"/>
+      <c r="AE7" s="841" t="n"/>
+      <c r="AF7" s="841" t="n"/>
+      <c r="AG7" s="841" t="n"/>
+      <c r="AH7" s="841" t="n"/>
+      <c r="AI7" s="841" t="n"/>
+      <c r="AJ7" s="841" t="n"/>
+      <c r="AK7" s="841" t="n"/>
+      <c r="AL7" s="841" t="n"/>
+      <c r="AM7" s="841" t="n"/>
+      <c r="AN7" s="841" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="743" t="inlineStr">
@@ -13788,13 +14123,13 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="735" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
-      <c r="H13" s="10" t="n"/>
+      <c r="B13" s="672" t="n"/>
+      <c r="C13" s="672" t="n"/>
+      <c r="D13" s="672" t="n"/>
+      <c r="E13" s="672" t="n"/>
+      <c r="F13" s="672" t="n"/>
+      <c r="G13" s="672" t="n"/>
+      <c r="H13" s="672" t="n"/>
       <c r="I13" s="672" t="n"/>
       <c r="J13" s="672" t="n"/>
       <c r="K13" s="672" t="n"/>
@@ -14577,50 +14912,50 @@
       <c r="AN29" s="734" t="n"/>
     </row>
     <row r="30" ht="26" customHeight="1">
-      <c r="A30" s="793" t="inlineStr">
+      <c r="A30" s="373" t="inlineStr">
         <is>
           <t>NOTICE  ?  Controlled withdrawal scope log; keep source files external. Maintain traceability to the parent form, superseding package, point-of-use impact and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B30" s="794" t="n"/>
-      <c r="C30" s="794" t="n"/>
-      <c r="D30" s="794" t="n"/>
-      <c r="E30" s="794" t="n"/>
-      <c r="F30" s="794" t="n"/>
-      <c r="G30" s="794" t="n"/>
-      <c r="H30" s="794" t="n"/>
-      <c r="I30" s="794" t="n"/>
-      <c r="J30" s="794" t="n"/>
-      <c r="K30" s="794" t="n"/>
-      <c r="L30" s="794" t="n"/>
-      <c r="M30" s="794" t="n"/>
-      <c r="N30" s="794" t="n"/>
-      <c r="O30" s="794" t="n"/>
-      <c r="P30" s="794" t="n"/>
-      <c r="Q30" s="794" t="n"/>
-      <c r="R30" s="794" t="n"/>
-      <c r="S30" s="794" t="n"/>
-      <c r="T30" s="794" t="n"/>
-      <c r="U30" s="794" t="n"/>
-      <c r="V30" s="794" t="n"/>
-      <c r="W30" s="794" t="n"/>
-      <c r="X30" s="794" t="n"/>
-      <c r="Y30" s="794" t="n"/>
-      <c r="Z30" s="794" t="n"/>
-      <c r="AA30" s="794" t="n"/>
-      <c r="AB30" s="794" t="n"/>
-      <c r="AC30" s="794" t="n"/>
-      <c r="AD30" s="794" t="n"/>
-      <c r="AE30" s="794" t="n"/>
-      <c r="AF30" s="794" t="n"/>
-      <c r="AG30" s="794" t="n"/>
-      <c r="AH30" s="794" t="n"/>
-      <c r="AI30" s="794" t="n"/>
-      <c r="AJ30" s="794" t="n"/>
-      <c r="AK30" s="794" t="n"/>
-      <c r="AL30" s="794" t="n"/>
-      <c r="AM30" s="794" t="n"/>
-      <c r="AN30" s="795" t="n"/>
+      <c r="B30" s="374" t="n"/>
+      <c r="C30" s="374" t="n"/>
+      <c r="D30" s="374" t="n"/>
+      <c r="E30" s="374" t="n"/>
+      <c r="F30" s="374" t="n"/>
+      <c r="G30" s="374" t="n"/>
+      <c r="H30" s="374" t="n"/>
+      <c r="I30" s="374" t="n"/>
+      <c r="J30" s="374" t="n"/>
+      <c r="K30" s="374" t="n"/>
+      <c r="L30" s="374" t="n"/>
+      <c r="M30" s="374" t="n"/>
+      <c r="N30" s="374" t="n"/>
+      <c r="O30" s="374" t="n"/>
+      <c r="P30" s="374" t="n"/>
+      <c r="Q30" s="374" t="n"/>
+      <c r="R30" s="374" t="n"/>
+      <c r="S30" s="374" t="n"/>
+      <c r="T30" s="374" t="n"/>
+      <c r="U30" s="374" t="n"/>
+      <c r="V30" s="374" t="n"/>
+      <c r="W30" s="374" t="n"/>
+      <c r="X30" s="374" t="n"/>
+      <c r="Y30" s="374" t="n"/>
+      <c r="Z30" s="374" t="n"/>
+      <c r="AA30" s="374" t="n"/>
+      <c r="AB30" s="374" t="n"/>
+      <c r="AC30" s="374" t="n"/>
+      <c r="AD30" s="374" t="n"/>
+      <c r="AE30" s="374" t="n"/>
+      <c r="AF30" s="374" t="n"/>
+      <c r="AG30" s="374" t="n"/>
+      <c r="AH30" s="374" t="n"/>
+      <c r="AI30" s="374" t="n"/>
+      <c r="AJ30" s="374" t="n"/>
+      <c r="AK30" s="374" t="n"/>
+      <c r="AL30" s="374" t="n"/>
+      <c r="AM30" s="374" t="n"/>
+      <c r="AN30" s="375" t="n"/>
     </row>
     <row r="31" hidden="1" outlineLevel="1"/>
     <row r="32" hidden="1" outlineLevel="1"/>
@@ -14900,7 +15235,7 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
+    <row r="1" hidden="1">
       <c r="A1" s="391" t="n"/>
       <c r="B1" s="323" t="n"/>
       <c r="C1" s="3" t="inlineStr">
@@ -14955,286 +15290,288 @@
       <c r="AN1" s="701" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="275" t="n"/>
-      <c r="B2" s="324" t="n"/>
-      <c r="C2" s="275" t="n"/>
-      <c r="F2" s="702" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="859" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="G2" s="703" t="inlineStr">
+      <c r="G2" s="698" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="H2" s="741" t="n"/>
-      <c r="I2" s="704" t="n"/>
-      <c r="J2" s="704" t="n"/>
-      <c r="K2" s="704" t="n"/>
-      <c r="L2" s="704" t="n"/>
-      <c r="M2" s="704" t="n"/>
-      <c r="N2" s="704" t="n"/>
-      <c r="O2" s="704" t="n"/>
-      <c r="P2" s="704" t="n"/>
-      <c r="Q2" s="704" t="n"/>
-      <c r="R2" s="704" t="n"/>
-      <c r="S2" s="704" t="n"/>
-      <c r="T2" s="704" t="n"/>
-      <c r="U2" s="704" t="n"/>
-      <c r="V2" s="704" t="n"/>
-      <c r="W2" s="704" t="n"/>
-      <c r="X2" s="704" t="n"/>
-      <c r="Y2" s="704" t="n"/>
-      <c r="Z2" s="704" t="n"/>
-      <c r="AA2" s="704" t="n"/>
-      <c r="AB2" s="704" t="n"/>
-      <c r="AC2" s="704" t="n"/>
-      <c r="AD2" s="704" t="n"/>
-      <c r="AE2" s="705" t="n"/>
-      <c r="AF2" s="705" t="n"/>
-      <c r="AG2" s="705" t="n"/>
-      <c r="AH2" s="705" t="n"/>
-      <c r="AI2" s="656" t="n"/>
-      <c r="AJ2" s="656" t="n"/>
-      <c r="AK2" s="656" t="n"/>
-      <c r="AL2" s="656" t="n"/>
-      <c r="AM2" s="656" t="n"/>
-      <c r="AN2" s="706" t="n"/>
+      <c r="H2" s="877" t="n"/>
+      <c r="I2" s="699" t="n"/>
+      <c r="J2" s="699" t="n"/>
+      <c r="K2" s="699" t="n"/>
+      <c r="L2" s="699" t="n"/>
+      <c r="M2" s="699" t="n"/>
+      <c r="N2" s="699" t="n"/>
+      <c r="O2" s="699" t="n"/>
+      <c r="P2" s="699" t="n"/>
+      <c r="Q2" s="699" t="n"/>
+      <c r="R2" s="699" t="n"/>
+      <c r="S2" s="699" t="n"/>
+      <c r="T2" s="699" t="n"/>
+      <c r="U2" s="699" t="n"/>
+      <c r="V2" s="699" t="n"/>
+      <c r="W2" s="699" t="n"/>
+      <c r="X2" s="699" t="n"/>
+      <c r="Y2" s="699" t="n"/>
+      <c r="Z2" s="699" t="n"/>
+      <c r="AA2" s="699" t="n"/>
+      <c r="AB2" s="699" t="n"/>
+      <c r="AC2" s="699" t="n"/>
+      <c r="AD2" s="861" t="n"/>
+      <c r="AE2" s="862" t="n"/>
+      <c r="AF2" s="862" t="n"/>
+      <c r="AG2" s="862" t="n"/>
+      <c r="AH2" s="863" t="n"/>
+      <c r="AI2" s="864" t="n"/>
+      <c r="AJ2" s="864" t="n"/>
+      <c r="AK2" s="864" t="n"/>
+      <c r="AL2" s="864" t="n"/>
+      <c r="AM2" s="864" t="n"/>
+      <c r="AN2" s="865" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="275" t="n"/>
-      <c r="B3" s="324" t="n"/>
-      <c r="C3" s="275" t="n"/>
-      <c r="F3" s="702" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="593" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="G3" s="703" t="inlineStr">
+      <c r="G3" s="625" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="H3" s="741" t="n"/>
-      <c r="I3" s="704" t="n"/>
-      <c r="J3" s="704" t="n"/>
-      <c r="K3" s="704" t="n"/>
-      <c r="L3" s="704" t="n"/>
-      <c r="M3" s="704" t="n"/>
-      <c r="N3" s="704" t="n"/>
-      <c r="O3" s="704" t="n"/>
-      <c r="P3" s="704" t="n"/>
-      <c r="Q3" s="704" t="n"/>
-      <c r="R3" s="704" t="n"/>
-      <c r="S3" s="704" t="n"/>
-      <c r="T3" s="704" t="n"/>
-      <c r="U3" s="704" t="n"/>
-      <c r="V3" s="704" t="n"/>
-      <c r="W3" s="704" t="n"/>
-      <c r="X3" s="704" t="n"/>
-      <c r="Y3" s="704" t="n"/>
-      <c r="Z3" s="704" t="n"/>
-      <c r="AA3" s="704" t="n"/>
-      <c r="AB3" s="704" t="n"/>
-      <c r="AC3" s="704" t="n"/>
-      <c r="AD3" s="704" t="n"/>
-      <c r="AE3" s="705" t="n"/>
-      <c r="AF3" s="705" t="n"/>
-      <c r="AG3" s="705" t="n"/>
-      <c r="AH3" s="705" t="n"/>
-      <c r="AI3" s="656" t="n"/>
-      <c r="AJ3" s="656" t="n"/>
-      <c r="AK3" s="656" t="n"/>
-      <c r="AL3" s="656" t="n"/>
-      <c r="AM3" s="656" t="n"/>
-      <c r="AN3" s="706" t="n"/>
+      <c r="H3" s="878" t="n"/>
+      <c r="I3" s="867" t="n"/>
+      <c r="J3" s="867" t="n"/>
+      <c r="K3" s="867" t="n"/>
+      <c r="L3" s="867" t="n"/>
+      <c r="M3" s="867" t="n"/>
+      <c r="N3" s="867" t="n"/>
+      <c r="O3" s="867" t="n"/>
+      <c r="P3" s="867" t="n"/>
+      <c r="Q3" s="867" t="n"/>
+      <c r="R3" s="867" t="n"/>
+      <c r="S3" s="867" t="n"/>
+      <c r="T3" s="867" t="n"/>
+      <c r="U3" s="867" t="n"/>
+      <c r="V3" s="867" t="n"/>
+      <c r="W3" s="867" t="n"/>
+      <c r="X3" s="867" t="n"/>
+      <c r="Y3" s="867" t="n"/>
+      <c r="Z3" s="867" t="n"/>
+      <c r="AA3" s="867" t="n"/>
+      <c r="AB3" s="867" t="n"/>
+      <c r="AC3" s="867" t="n"/>
+      <c r="AD3" s="868" t="n"/>
+      <c r="AE3" s="869" t="n"/>
+      <c r="AF3" s="869" t="n"/>
+      <c r="AG3" s="869" t="n"/>
+      <c r="AH3" s="870" t="n"/>
+      <c r="AI3" s="871" t="n"/>
+      <c r="AJ3" s="871" t="n"/>
+      <c r="AK3" s="871" t="n"/>
+      <c r="AL3" s="871" t="n"/>
+      <c r="AM3" s="871" t="n"/>
+      <c r="AN3" s="872" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="275" t="n"/>
-      <c r="B4" s="324" t="n"/>
-      <c r="C4" s="707" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="595" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="F4" s="702" t="inlineStr">
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="593" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="G4" s="703" t="inlineStr"/>
-      <c r="H4" s="741" t="n"/>
-      <c r="I4" s="708" t="n"/>
-      <c r="J4" s="708" t="n"/>
-      <c r="K4" s="708" t="n"/>
-      <c r="L4" s="708" t="n"/>
-      <c r="M4" s="708" t="n"/>
-      <c r="N4" s="708" t="n"/>
-      <c r="O4" s="708" t="n"/>
-      <c r="P4" s="708" t="n"/>
-      <c r="Q4" s="708" t="n"/>
-      <c r="R4" s="708" t="n"/>
-      <c r="S4" s="708" t="n"/>
-      <c r="T4" s="708" t="n"/>
-      <c r="U4" s="708" t="n"/>
-      <c r="V4" s="708" t="n"/>
-      <c r="W4" s="708" t="n"/>
-      <c r="X4" s="708" t="n"/>
-      <c r="Y4" s="708" t="n"/>
-      <c r="Z4" s="708" t="n"/>
-      <c r="AA4" s="708" t="n"/>
-      <c r="AB4" s="708" t="n"/>
-      <c r="AC4" s="708" t="n"/>
-      <c r="AD4" s="708" t="n"/>
-      <c r="AE4" s="705" t="n"/>
-      <c r="AF4" s="705" t="n"/>
-      <c r="AG4" s="705" t="n"/>
-      <c r="AH4" s="705" t="n"/>
-      <c r="AI4" s="656" t="n"/>
-      <c r="AJ4" s="656" t="n"/>
-      <c r="AK4" s="656" t="n"/>
-      <c r="AL4" s="656" t="n"/>
-      <c r="AM4" s="656" t="n"/>
-      <c r="AN4" s="706" t="n"/>
+      <c r="G4" s="625" t="inlineStr"/>
+      <c r="H4" s="878" t="n"/>
+      <c r="I4" s="524" t="n"/>
+      <c r="J4" s="524" t="n"/>
+      <c r="K4" s="524" t="n"/>
+      <c r="L4" s="524" t="n"/>
+      <c r="M4" s="524" t="n"/>
+      <c r="N4" s="524" t="n"/>
+      <c r="O4" s="524" t="n"/>
+      <c r="P4" s="524" t="n"/>
+      <c r="Q4" s="524" t="n"/>
+      <c r="R4" s="524" t="n"/>
+      <c r="S4" s="524" t="n"/>
+      <c r="T4" s="524" t="n"/>
+      <c r="U4" s="524" t="n"/>
+      <c r="V4" s="524" t="n"/>
+      <c r="W4" s="524" t="n"/>
+      <c r="X4" s="524" t="n"/>
+      <c r="Y4" s="524" t="n"/>
+      <c r="Z4" s="524" t="n"/>
+      <c r="AA4" s="524" t="n"/>
+      <c r="AB4" s="524" t="n"/>
+      <c r="AC4" s="524" t="n"/>
+      <c r="AD4" s="873" t="n"/>
+      <c r="AE4" s="869" t="n"/>
+      <c r="AF4" s="869" t="n"/>
+      <c r="AG4" s="869" t="n"/>
+      <c r="AH4" s="870" t="n"/>
+      <c r="AI4" s="871" t="n"/>
+      <c r="AJ4" s="871" t="n"/>
+      <c r="AK4" s="871" t="n"/>
+      <c r="AL4" s="871" t="n"/>
+      <c r="AM4" s="871" t="n"/>
+      <c r="AN4" s="872" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="282" t="n"/>
-      <c r="B5" s="287" t="n"/>
-      <c r="C5" s="709" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="874" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="283" t="n"/>
-      <c r="E5" s="283" t="n"/>
-      <c r="F5" s="710" t="inlineStr">
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="593" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="G5" s="711" t="inlineStr"/>
-      <c r="H5" s="742" t="n"/>
-      <c r="I5" s="712" t="n"/>
-      <c r="J5" s="712" t="n"/>
-      <c r="K5" s="712" t="n"/>
-      <c r="L5" s="712" t="n"/>
-      <c r="M5" s="712" t="n"/>
-      <c r="N5" s="712" t="n"/>
-      <c r="O5" s="712" t="n"/>
-      <c r="P5" s="712" t="n"/>
-      <c r="Q5" s="712" t="n"/>
-      <c r="R5" s="712" t="n"/>
-      <c r="S5" s="712" t="n"/>
-      <c r="T5" s="712" t="n"/>
-      <c r="U5" s="712" t="n"/>
-      <c r="V5" s="712" t="n"/>
-      <c r="W5" s="712" t="n"/>
-      <c r="X5" s="712" t="n"/>
-      <c r="Y5" s="712" t="n"/>
-      <c r="Z5" s="712" t="n"/>
-      <c r="AA5" s="712" t="n"/>
-      <c r="AB5" s="712" t="n"/>
-      <c r="AC5" s="712" t="n"/>
-      <c r="AD5" s="712" t="n"/>
-      <c r="AE5" s="713" t="n"/>
-      <c r="AF5" s="713" t="n"/>
-      <c r="AG5" s="713" t="n"/>
-      <c r="AH5" s="713" t="n"/>
-      <c r="AI5" s="662" t="n"/>
-      <c r="AJ5" s="662" t="n"/>
-      <c r="AK5" s="662" t="n"/>
-      <c r="AL5" s="662" t="n"/>
-      <c r="AM5" s="662" t="n"/>
-      <c r="AN5" s="714" t="n"/>
+      <c r="G5" s="625" t="inlineStr"/>
+      <c r="H5" s="878" t="n"/>
+      <c r="I5" s="875" t="n"/>
+      <c r="J5" s="875" t="n"/>
+      <c r="K5" s="875" t="n"/>
+      <c r="L5" s="875" t="n"/>
+      <c r="M5" s="875" t="n"/>
+      <c r="N5" s="875" t="n"/>
+      <c r="O5" s="875" t="n"/>
+      <c r="P5" s="875" t="n"/>
+      <c r="Q5" s="875" t="n"/>
+      <c r="R5" s="875" t="n"/>
+      <c r="S5" s="875" t="n"/>
+      <c r="T5" s="875" t="n"/>
+      <c r="U5" s="875" t="n"/>
+      <c r="V5" s="875" t="n"/>
+      <c r="W5" s="875" t="n"/>
+      <c r="X5" s="875" t="n"/>
+      <c r="Y5" s="875" t="n"/>
+      <c r="Z5" s="875" t="n"/>
+      <c r="AA5" s="875" t="n"/>
+      <c r="AB5" s="875" t="n"/>
+      <c r="AC5" s="875" t="n"/>
+      <c r="AD5" s="876" t="n"/>
+      <c r="AE5" s="869" t="n"/>
+      <c r="AF5" s="869" t="n"/>
+      <c r="AG5" s="869" t="n"/>
+      <c r="AH5" s="870" t="n"/>
+      <c r="AI5" s="871" t="n"/>
+      <c r="AJ5" s="871" t="n"/>
+      <c r="AK5" s="871" t="n"/>
+      <c r="AL5" s="871" t="n"/>
+      <c r="AM5" s="871" t="n"/>
+      <c r="AN5" s="872" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="715" t="n"/>
-      <c r="B6" s="664" t="n"/>
-      <c r="C6" s="664" t="n"/>
-      <c r="D6" s="664" t="n"/>
-      <c r="E6" s="664" t="n"/>
-      <c r="F6" s="664" t="n"/>
-      <c r="G6" s="664" t="n"/>
-      <c r="H6" s="664" t="n"/>
-      <c r="I6" s="664" t="n"/>
-      <c r="J6" s="664" t="n"/>
-      <c r="K6" s="664" t="n"/>
-      <c r="L6" s="664" t="n"/>
-      <c r="M6" s="664" t="n"/>
-      <c r="N6" s="664" t="n"/>
-      <c r="O6" s="664" t="n"/>
-      <c r="P6" s="664" t="n"/>
-      <c r="Q6" s="664" t="n"/>
-      <c r="R6" s="664" t="n"/>
-      <c r="S6" s="664" t="n"/>
-      <c r="T6" s="664" t="n"/>
-      <c r="U6" s="664" t="n"/>
-      <c r="V6" s="664" t="n"/>
-      <c r="W6" s="664" t="n"/>
-      <c r="X6" s="664" t="n"/>
-      <c r="Y6" s="664" t="n"/>
-      <c r="Z6" s="664" t="n"/>
-      <c r="AA6" s="664" t="n"/>
-      <c r="AB6" s="664" t="n"/>
-      <c r="AC6" s="664" t="n"/>
-      <c r="AD6" s="664" t="n"/>
-      <c r="AE6" s="664" t="n"/>
-      <c r="AF6" s="664" t="n"/>
-      <c r="AG6" s="664" t="n"/>
-      <c r="AH6" s="664" t="n"/>
-      <c r="AI6" s="664" t="n"/>
-      <c r="AJ6" s="664" t="n"/>
-      <c r="AK6" s="664" t="n"/>
-      <c r="AL6" s="664" t="n"/>
-      <c r="AM6" s="664" t="n"/>
-      <c r="AN6" s="664" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="356" t="n"/>
+      <c r="B6" s="835" t="n"/>
+      <c r="C6" s="835" t="n"/>
+      <c r="D6" s="835" t="n"/>
+      <c r="E6" s="835" t="n"/>
+      <c r="F6" s="835" t="n"/>
+      <c r="G6" s="835" t="n"/>
+      <c r="H6" s="836" t="n"/>
+      <c r="I6" s="835" t="n"/>
+      <c r="J6" s="835" t="n"/>
+      <c r="K6" s="835" t="n"/>
+      <c r="L6" s="835" t="n"/>
+      <c r="M6" s="835" t="n"/>
+      <c r="N6" s="835" t="n"/>
+      <c r="O6" s="835" t="n"/>
+      <c r="P6" s="835" t="n"/>
+      <c r="Q6" s="835" t="n"/>
+      <c r="R6" s="835" t="n"/>
+      <c r="S6" s="835" t="n"/>
+      <c r="T6" s="835" t="n"/>
+      <c r="U6" s="835" t="n"/>
+      <c r="V6" s="835" t="n"/>
+      <c r="W6" s="835" t="n"/>
+      <c r="X6" s="835" t="n"/>
+      <c r="Y6" s="835" t="n"/>
+      <c r="Z6" s="835" t="n"/>
+      <c r="AA6" s="835" t="n"/>
+      <c r="AB6" s="835" t="n"/>
+      <c r="AC6" s="835" t="n"/>
+      <c r="AD6" s="836" t="n"/>
+      <c r="AE6" s="837" t="n"/>
+      <c r="AF6" s="837" t="n"/>
+      <c r="AG6" s="837" t="n"/>
+      <c r="AH6" s="838" t="n"/>
+      <c r="AI6" s="839" t="n"/>
+      <c r="AJ6" s="839" t="n"/>
+      <c r="AK6" s="839" t="n"/>
+      <c r="AL6" s="839" t="n"/>
+      <c r="AM6" s="839" t="n"/>
+      <c r="AN6" s="840" t="n"/>
     </row>
-    <row r="7" ht="18" customHeight="1">
-      <c r="A7" s="665" t="inlineStr">
-        <is>
-          <t>1.  CONTROL CONTEXT / SUPPORT TAB PURPOSE</t>
-        </is>
-      </c>
-      <c r="B7" s="289" t="n"/>
-      <c r="C7" s="289" t="n"/>
-      <c r="D7" s="289" t="n"/>
-      <c r="E7" s="289" t="n"/>
-      <c r="F7" s="289" t="n"/>
-      <c r="G7" s="289" t="n"/>
-      <c r="H7" s="716" t="n"/>
-      <c r="I7" s="716" t="n"/>
-      <c r="J7" s="716" t="n"/>
-      <c r="K7" s="716" t="n"/>
-      <c r="L7" s="716" t="n"/>
-      <c r="M7" s="716" t="n"/>
-      <c r="N7" s="716" t="n"/>
-      <c r="O7" s="716" t="n"/>
-      <c r="P7" s="716" t="n"/>
-      <c r="Q7" s="716" t="n"/>
-      <c r="R7" s="716" t="n"/>
-      <c r="S7" s="716" t="n"/>
-      <c r="T7" s="716" t="n"/>
-      <c r="U7" s="716" t="n"/>
-      <c r="V7" s="716" t="n"/>
-      <c r="W7" s="716" t="n"/>
-      <c r="X7" s="716" t="n"/>
-      <c r="Y7" s="716" t="n"/>
-      <c r="Z7" s="716" t="n"/>
-      <c r="AA7" s="716" t="n"/>
-      <c r="AB7" s="716" t="n"/>
-      <c r="AC7" s="716" t="n"/>
-      <c r="AD7" s="716" t="n"/>
-      <c r="AE7" s="716" t="n"/>
-      <c r="AF7" s="716" t="n"/>
-      <c r="AG7" s="716" t="n"/>
-      <c r="AH7" s="716" t="n"/>
-      <c r="AI7" s="716" t="n"/>
-      <c r="AJ7" s="716" t="n"/>
-      <c r="AK7" s="716" t="n"/>
-      <c r="AL7" s="716" t="n"/>
-      <c r="AM7" s="716" t="n"/>
-      <c r="AN7" s="717" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="841" t="n"/>
+      <c r="B7" s="842" t="n"/>
+      <c r="C7" s="842" t="n"/>
+      <c r="D7" s="842" t="n"/>
+      <c r="E7" s="842" t="n"/>
+      <c r="F7" s="842" t="n"/>
+      <c r="G7" s="842" t="n"/>
+      <c r="H7" s="841" t="n"/>
+      <c r="I7" s="841" t="n"/>
+      <c r="J7" s="841" t="n"/>
+      <c r="K7" s="841" t="n"/>
+      <c r="L7" s="841" t="n"/>
+      <c r="M7" s="841" t="n"/>
+      <c r="N7" s="841" t="n"/>
+      <c r="O7" s="841" t="n"/>
+      <c r="P7" s="841" t="n"/>
+      <c r="Q7" s="841" t="n"/>
+      <c r="R7" s="841" t="n"/>
+      <c r="S7" s="841" t="n"/>
+      <c r="T7" s="841" t="n"/>
+      <c r="U7" s="841" t="n"/>
+      <c r="V7" s="841" t="n"/>
+      <c r="W7" s="841" t="n"/>
+      <c r="X7" s="841" t="n"/>
+      <c r="Y7" s="841" t="n"/>
+      <c r="Z7" s="841" t="n"/>
+      <c r="AA7" s="841" t="n"/>
+      <c r="AB7" s="841" t="n"/>
+      <c r="AC7" s="841" t="n"/>
+      <c r="AD7" s="841" t="n"/>
+      <c r="AE7" s="841" t="n"/>
+      <c r="AF7" s="841" t="n"/>
+      <c r="AG7" s="841" t="n"/>
+      <c r="AH7" s="841" t="n"/>
+      <c r="AI7" s="841" t="n"/>
+      <c r="AJ7" s="841" t="n"/>
+      <c r="AK7" s="841" t="n"/>
+      <c r="AL7" s="841" t="n"/>
+      <c r="AM7" s="841" t="n"/>
+      <c r="AN7" s="841" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="743" t="inlineStr">
@@ -15520,12 +15857,12 @@
     </row>
     <row r="13" ht="3" customHeight="1">
       <c r="A13" s="735" t="n"/>
-      <c r="B13" s="10" t="n"/>
-      <c r="C13" s="10" t="n"/>
-      <c r="D13" s="10" t="n"/>
-      <c r="E13" s="10" t="n"/>
-      <c r="F13" s="10" t="n"/>
-      <c r="G13" s="10" t="n"/>
+      <c r="B13" s="672" t="n"/>
+      <c r="C13" s="672" t="n"/>
+      <c r="D13" s="672" t="n"/>
+      <c r="E13" s="672" t="n"/>
+      <c r="F13" s="672" t="n"/>
+      <c r="G13" s="672" t="n"/>
       <c r="H13" s="672" t="n"/>
       <c r="I13" s="672" t="n"/>
       <c r="J13" s="672" t="n"/>
@@ -16125,50 +16462,50 @@
       <c r="AN25" s="734" t="n"/>
     </row>
     <row r="26" ht="26" customHeight="1">
-      <c r="A26" s="793" t="inlineStr">
+      <c r="A26" s="373" t="inlineStr">
         <is>
           <t>NOTICE  ?  Point-of-use sweep confirmation log. Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, timestamps and result fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="794" t="n"/>
-      <c r="C26" s="794" t="n"/>
-      <c r="D26" s="794" t="n"/>
-      <c r="E26" s="794" t="n"/>
-      <c r="F26" s="794" t="n"/>
-      <c r="G26" s="794" t="n"/>
-      <c r="H26" s="794" t="n"/>
-      <c r="I26" s="794" t="n"/>
-      <c r="J26" s="794" t="n"/>
-      <c r="K26" s="794" t="n"/>
-      <c r="L26" s="794" t="n"/>
-      <c r="M26" s="794" t="n"/>
-      <c r="N26" s="794" t="n"/>
-      <c r="O26" s="794" t="n"/>
-      <c r="P26" s="794" t="n"/>
-      <c r="Q26" s="794" t="n"/>
-      <c r="R26" s="794" t="n"/>
-      <c r="S26" s="794" t="n"/>
-      <c r="T26" s="794" t="n"/>
-      <c r="U26" s="794" t="n"/>
-      <c r="V26" s="794" t="n"/>
-      <c r="W26" s="794" t="n"/>
-      <c r="X26" s="794" t="n"/>
-      <c r="Y26" s="794" t="n"/>
-      <c r="Z26" s="794" t="n"/>
-      <c r="AA26" s="794" t="n"/>
-      <c r="AB26" s="794" t="n"/>
-      <c r="AC26" s="794" t="n"/>
-      <c r="AD26" s="794" t="n"/>
-      <c r="AE26" s="794" t="n"/>
-      <c r="AF26" s="794" t="n"/>
-      <c r="AG26" s="794" t="n"/>
-      <c r="AH26" s="794" t="n"/>
-      <c r="AI26" s="794" t="n"/>
-      <c r="AJ26" s="794" t="n"/>
-      <c r="AK26" s="794" t="n"/>
-      <c r="AL26" s="794" t="n"/>
-      <c r="AM26" s="794" t="n"/>
-      <c r="AN26" s="795" t="n"/>
+      <c r="B26" s="374" t="n"/>
+      <c r="C26" s="374" t="n"/>
+      <c r="D26" s="374" t="n"/>
+      <c r="E26" s="374" t="n"/>
+      <c r="F26" s="374" t="n"/>
+      <c r="G26" s="374" t="n"/>
+      <c r="H26" s="374" t="n"/>
+      <c r="I26" s="374" t="n"/>
+      <c r="J26" s="374" t="n"/>
+      <c r="K26" s="374" t="n"/>
+      <c r="L26" s="374" t="n"/>
+      <c r="M26" s="374" t="n"/>
+      <c r="N26" s="374" t="n"/>
+      <c r="O26" s="374" t="n"/>
+      <c r="P26" s="374" t="n"/>
+      <c r="Q26" s="374" t="n"/>
+      <c r="R26" s="374" t="n"/>
+      <c r="S26" s="374" t="n"/>
+      <c r="T26" s="374" t="n"/>
+      <c r="U26" s="374" t="n"/>
+      <c r="V26" s="374" t="n"/>
+      <c r="W26" s="374" t="n"/>
+      <c r="X26" s="374" t="n"/>
+      <c r="Y26" s="374" t="n"/>
+      <c r="Z26" s="374" t="n"/>
+      <c r="AA26" s="374" t="n"/>
+      <c r="AB26" s="374" t="n"/>
+      <c r="AC26" s="374" t="n"/>
+      <c r="AD26" s="374" t="n"/>
+      <c r="AE26" s="374" t="n"/>
+      <c r="AF26" s="374" t="n"/>
+      <c r="AG26" s="374" t="n"/>
+      <c r="AH26" s="374" t="n"/>
+      <c r="AI26" s="374" t="n"/>
+      <c r="AJ26" s="374" t="n"/>
+      <c r="AK26" s="374" t="n"/>
+      <c r="AL26" s="374" t="n"/>
+      <c r="AM26" s="374" t="n"/>
+      <c r="AN26" s="375" t="n"/>
     </row>
     <row r="27" hidden="1" outlineLevel="1"/>
     <row r="28" hidden="1" outlineLevel="1"/>
@@ -16449,358 +16786,354 @@
     <col width="2.33" customWidth="1" min="40" max="40"/>
   </cols>
   <sheetData>
-    <row r="1" ht="15" customHeight="1">
-      <c r="A1" s="799" t="n"/>
-      <c r="B1" s="800" t="n"/>
-      <c r="C1" s="800" t="n"/>
-      <c r="D1" s="800" t="n"/>
-      <c r="E1" s="800" t="n"/>
-      <c r="F1" s="800" t="n"/>
-      <c r="G1" s="800" t="n"/>
-      <c r="H1" s="801" t="n"/>
-      <c r="I1" s="802" t="inlineStr">
+    <row r="1" hidden="1">
+      <c r="A1" s="843" t="n"/>
+      <c r="B1" s="752" t="n"/>
+      <c r="C1" s="752" t="n"/>
+      <c r="D1" s="752" t="n"/>
+      <c r="E1" s="752" t="n"/>
+      <c r="F1" s="752" t="n"/>
+      <c r="G1" s="752" t="n"/>
+      <c r="H1" s="844" t="n"/>
+      <c r="I1" s="845" t="inlineStr">
         <is>
           <t>PACKAGE SUPERSEDURE AND WITHDRAWAL NOTICE</t>
         </is>
       </c>
-      <c r="J1" s="800" t="n"/>
-      <c r="K1" s="800" t="n"/>
-      <c r="L1" s="800" t="n"/>
-      <c r="M1" s="800" t="n"/>
-      <c r="N1" s="800" t="n"/>
-      <c r="O1" s="800" t="n"/>
-      <c r="P1" s="800" t="n"/>
-      <c r="Q1" s="800" t="n"/>
-      <c r="R1" s="800" t="n"/>
-      <c r="S1" s="800" t="n"/>
-      <c r="T1" s="800" t="n"/>
-      <c r="U1" s="800" t="n"/>
-      <c r="V1" s="800" t="n"/>
-      <c r="W1" s="800" t="n"/>
-      <c r="X1" s="800" t="n"/>
-      <c r="Y1" s="800" t="n"/>
-      <c r="Z1" s="800" t="n"/>
-      <c r="AA1" s="800" t="n"/>
-      <c r="AB1" s="800" t="n"/>
-      <c r="AC1" s="800" t="n"/>
-      <c r="AD1" s="801" t="n"/>
-      <c r="AE1" s="507" t="inlineStr">
+      <c r="J1" s="752" t="n"/>
+      <c r="K1" s="752" t="n"/>
+      <c r="L1" s="752" t="n"/>
+      <c r="M1" s="752" t="n"/>
+      <c r="N1" s="752" t="n"/>
+      <c r="O1" s="752" t="n"/>
+      <c r="P1" s="752" t="n"/>
+      <c r="Q1" s="752" t="n"/>
+      <c r="R1" s="752" t="n"/>
+      <c r="S1" s="752" t="n"/>
+      <c r="T1" s="752" t="n"/>
+      <c r="U1" s="752" t="n"/>
+      <c r="V1" s="752" t="n"/>
+      <c r="W1" s="752" t="n"/>
+      <c r="X1" s="752" t="n"/>
+      <c r="Y1" s="752" t="n"/>
+      <c r="Z1" s="752" t="n"/>
+      <c r="AA1" s="752" t="n"/>
+      <c r="AB1" s="752" t="n"/>
+      <c r="AC1" s="752" t="n"/>
+      <c r="AD1" s="844" t="n"/>
+      <c r="AE1" s="508" t="inlineStr">
         <is>
           <t>Form Code</t>
         </is>
       </c>
-      <c r="AF1" s="800" t="n"/>
-      <c r="AG1" s="800" t="n"/>
-      <c r="AH1" s="803" t="n"/>
-      <c r="AI1" s="510" t="inlineStr">
+      <c r="AF1" s="752" t="n"/>
+      <c r="AG1" s="752" t="n"/>
+      <c r="AH1" s="846" t="n"/>
+      <c r="AI1" s="511" t="inlineStr">
         <is>
           <t>FRM-306</t>
         </is>
       </c>
-      <c r="AJ1" s="800" t="n"/>
-      <c r="AK1" s="800" t="n"/>
-      <c r="AL1" s="800" t="n"/>
-      <c r="AM1" s="800" t="n"/>
-      <c r="AN1" s="801" t="n"/>
+      <c r="AJ1" s="752" t="n"/>
+      <c r="AK1" s="752" t="n"/>
+      <c r="AL1" s="752" t="n"/>
+      <c r="AM1" s="752" t="n"/>
+      <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="804" t="n"/>
-      <c r="B2" s="10" t="n"/>
-      <c r="C2" s="10" t="n"/>
-      <c r="D2" s="10" t="n"/>
-      <c r="E2" s="10" t="n"/>
-      <c r="F2" s="10" t="n"/>
-      <c r="G2" s="10" t="n"/>
-      <c r="H2" s="805" t="n"/>
-      <c r="I2" s="10" t="n"/>
-      <c r="J2" s="10" t="n"/>
-      <c r="K2" s="10" t="n"/>
-      <c r="L2" s="10" t="n"/>
-      <c r="M2" s="10" t="n"/>
-      <c r="N2" s="10" t="n"/>
-      <c r="O2" s="10" t="n"/>
-      <c r="P2" s="10" t="n"/>
-      <c r="Q2" s="10" t="n"/>
-      <c r="R2" s="10" t="n"/>
-      <c r="S2" s="10" t="n"/>
-      <c r="T2" s="10" t="n"/>
-      <c r="U2" s="10" t="n"/>
-      <c r="V2" s="10" t="n"/>
-      <c r="W2" s="10" t="n"/>
-      <c r="X2" s="10" t="n"/>
-      <c r="Y2" s="10" t="n"/>
-      <c r="Z2" s="10" t="n"/>
-      <c r="AA2" s="10" t="n"/>
-      <c r="AB2" s="10" t="n"/>
-      <c r="AC2" s="10" t="n"/>
-      <c r="AD2" s="805" t="n"/>
-      <c r="AE2" s="806" t="inlineStr">
+      <c r="A2" s="1" t="n"/>
+      <c r="B2" s="819" t="n"/>
+      <c r="C2" s="819" t="n"/>
+      <c r="D2" s="819" t="n"/>
+      <c r="E2" s="819" t="n"/>
+      <c r="F2" s="819" t="n"/>
+      <c r="G2" s="819" t="n"/>
+      <c r="H2" s="820" t="n"/>
+      <c r="I2" s="819" t="n"/>
+      <c r="J2" s="819" t="n"/>
+      <c r="K2" s="819" t="n"/>
+      <c r="L2" s="819" t="n"/>
+      <c r="M2" s="819" t="n"/>
+      <c r="N2" s="819" t="n"/>
+      <c r="O2" s="819" t="n"/>
+      <c r="P2" s="819" t="n"/>
+      <c r="Q2" s="819" t="n"/>
+      <c r="R2" s="819" t="n"/>
+      <c r="S2" s="819" t="n"/>
+      <c r="T2" s="819" t="n"/>
+      <c r="U2" s="819" t="n"/>
+      <c r="V2" s="819" t="n"/>
+      <c r="W2" s="819" t="n"/>
+      <c r="X2" s="819" t="n"/>
+      <c r="Y2" s="819" t="n"/>
+      <c r="Z2" s="819" t="n"/>
+      <c r="AA2" s="819" t="n"/>
+      <c r="AB2" s="819" t="n"/>
+      <c r="AC2" s="819" t="n"/>
+      <c r="AD2" s="820" t="n"/>
+      <c r="AE2" s="821" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="10" t="n"/>
-      <c r="AG2" s="10" t="n"/>
-      <c r="AH2" s="807" t="n"/>
-      <c r="AI2" s="808" t="inlineStr">
+      <c r="AF2" s="822" t="n"/>
+      <c r="AG2" s="822" t="n"/>
+      <c r="AH2" s="823" t="n"/>
+      <c r="AI2" s="824" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="10" t="n"/>
-      <c r="AK2" s="10" t="n"/>
-      <c r="AL2" s="10" t="n"/>
-      <c r="AM2" s="10" t="n"/>
-      <c r="AN2" s="805" t="n"/>
+      <c r="AJ2" s="825" t="n"/>
+      <c r="AK2" s="825" t="n"/>
+      <c r="AL2" s="825" t="n"/>
+      <c r="AM2" s="825" t="n"/>
+      <c r="AN2" s="826" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="804" t="n"/>
-      <c r="B3" s="10" t="n"/>
-      <c r="C3" s="10" t="n"/>
-      <c r="D3" s="10" t="n"/>
-      <c r="E3" s="10" t="n"/>
-      <c r="F3" s="10" t="n"/>
-      <c r="G3" s="10" t="n"/>
-      <c r="H3" s="805" t="n"/>
-      <c r="I3" s="10" t="n"/>
-      <c r="J3" s="10" t="n"/>
-      <c r="K3" s="10" t="n"/>
-      <c r="L3" s="10" t="n"/>
-      <c r="M3" s="10" t="n"/>
-      <c r="N3" s="10" t="n"/>
-      <c r="O3" s="10" t="n"/>
-      <c r="P3" s="10" t="n"/>
-      <c r="Q3" s="10" t="n"/>
-      <c r="R3" s="10" t="n"/>
-      <c r="S3" s="10" t="n"/>
-      <c r="T3" s="10" t="n"/>
-      <c r="U3" s="10" t="n"/>
-      <c r="V3" s="10" t="n"/>
-      <c r="W3" s="10" t="n"/>
-      <c r="X3" s="10" t="n"/>
-      <c r="Y3" s="10" t="n"/>
-      <c r="Z3" s="10" t="n"/>
-      <c r="AA3" s="10" t="n"/>
-      <c r="AB3" s="10" t="n"/>
-      <c r="AC3" s="10" t="n"/>
-      <c r="AD3" s="805" t="n"/>
-      <c r="AE3" s="806" t="inlineStr">
+      <c r="A3" s="827" t="n"/>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+      <c r="E3" s="25" t="n"/>
+      <c r="F3" s="25" t="n"/>
+      <c r="G3" s="25" t="n"/>
+      <c r="H3" s="828" t="n"/>
+      <c r="I3" s="25" t="n"/>
+      <c r="J3" s="25" t="n"/>
+      <c r="K3" s="25" t="n"/>
+      <c r="L3" s="25" t="n"/>
+      <c r="M3" s="25" t="n"/>
+      <c r="N3" s="25" t="n"/>
+      <c r="O3" s="25" t="n"/>
+      <c r="P3" s="25" t="n"/>
+      <c r="Q3" s="25" t="n"/>
+      <c r="R3" s="25" t="n"/>
+      <c r="S3" s="25" t="n"/>
+      <c r="T3" s="25" t="n"/>
+      <c r="U3" s="25" t="n"/>
+      <c r="V3" s="25" t="n"/>
+      <c r="W3" s="25" t="n"/>
+      <c r="X3" s="25" t="n"/>
+      <c r="Y3" s="25" t="n"/>
+      <c r="Z3" s="25" t="n"/>
+      <c r="AA3" s="25" t="n"/>
+      <c r="AB3" s="25" t="n"/>
+      <c r="AC3" s="25" t="n"/>
+      <c r="AD3" s="828" t="n"/>
+      <c r="AE3" s="829" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="10" t="n"/>
-      <c r="AG3" s="10" t="n"/>
-      <c r="AH3" s="807" t="n"/>
-      <c r="AI3" s="808" t="inlineStr">
+      <c r="AF3" s="830" t="n"/>
+      <c r="AG3" s="830" t="n"/>
+      <c r="AH3" s="831" t="n"/>
+      <c r="AI3" s="724" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="10" t="n"/>
-      <c r="AK3" s="10" t="n"/>
-      <c r="AL3" s="10" t="n"/>
-      <c r="AM3" s="10" t="n"/>
-      <c r="AN3" s="805" t="n"/>
+      <c r="AJ3" s="832" t="n"/>
+      <c r="AK3" s="832" t="n"/>
+      <c r="AL3" s="832" t="n"/>
+      <c r="AM3" s="832" t="n"/>
+      <c r="AN3" s="833" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="804" t="n"/>
-      <c r="B4" s="10" t="n"/>
-      <c r="C4" s="10" t="n"/>
-      <c r="D4" s="10" t="n"/>
-      <c r="E4" s="10" t="n"/>
-      <c r="F4" s="10" t="n"/>
-      <c r="G4" s="10" t="n"/>
-      <c r="H4" s="805" t="n"/>
-      <c r="I4" s="809" t="inlineStr">
+      <c r="A4" s="827" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
+      <c r="E4" s="25" t="n"/>
+      <c r="F4" s="25" t="n"/>
+      <c r="G4" s="25" t="n"/>
+      <c r="H4" s="828" t="n"/>
+      <c r="I4" s="346" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="10" t="n"/>
-      <c r="K4" s="10" t="n"/>
-      <c r="L4" s="10" t="n"/>
-      <c r="M4" s="10" t="n"/>
-      <c r="N4" s="10" t="n"/>
-      <c r="O4" s="10" t="n"/>
-      <c r="P4" s="10" t="n"/>
-      <c r="Q4" s="10" t="n"/>
-      <c r="R4" s="10" t="n"/>
-      <c r="S4" s="10" t="n"/>
-      <c r="T4" s="10" t="n"/>
-      <c r="U4" s="10" t="n"/>
-      <c r="V4" s="10" t="n"/>
-      <c r="W4" s="10" t="n"/>
-      <c r="X4" s="10" t="n"/>
-      <c r="Y4" s="10" t="n"/>
-      <c r="Z4" s="10" t="n"/>
-      <c r="AA4" s="10" t="n"/>
-      <c r="AB4" s="10" t="n"/>
-      <c r="AC4" s="10" t="n"/>
-      <c r="AD4" s="805" t="n"/>
-      <c r="AE4" s="806" t="inlineStr">
+      <c r="J4" s="25" t="n"/>
+      <c r="K4" s="25" t="n"/>
+      <c r="L4" s="25" t="n"/>
+      <c r="M4" s="25" t="n"/>
+      <c r="N4" s="25" t="n"/>
+      <c r="O4" s="25" t="n"/>
+      <c r="P4" s="25" t="n"/>
+      <c r="Q4" s="25" t="n"/>
+      <c r="R4" s="25" t="n"/>
+      <c r="S4" s="25" t="n"/>
+      <c r="T4" s="25" t="n"/>
+      <c r="U4" s="25" t="n"/>
+      <c r="V4" s="25" t="n"/>
+      <c r="W4" s="25" t="n"/>
+      <c r="X4" s="25" t="n"/>
+      <c r="Y4" s="25" t="n"/>
+      <c r="Z4" s="25" t="n"/>
+      <c r="AA4" s="25" t="n"/>
+      <c r="AB4" s="25" t="n"/>
+      <c r="AC4" s="25" t="n"/>
+      <c r="AD4" s="828" t="n"/>
+      <c r="AE4" s="829" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="10" t="n"/>
-      <c r="AG4" s="10" t="n"/>
-      <c r="AH4" s="807" t="n"/>
-      <c r="AI4" s="808" t="inlineStr">
+      <c r="AF4" s="830" t="n"/>
+      <c r="AG4" s="830" t="n"/>
+      <c r="AH4" s="831" t="n"/>
+      <c r="AI4" s="724" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="10" t="n"/>
-      <c r="AK4" s="10" t="n"/>
-      <c r="AL4" s="10" t="n"/>
-      <c r="AM4" s="10" t="n"/>
-      <c r="AN4" s="805" t="n"/>
+      <c r="AJ4" s="832" t="n"/>
+      <c r="AK4" s="832" t="n"/>
+      <c r="AL4" s="832" t="n"/>
+      <c r="AM4" s="832" t="n"/>
+      <c r="AN4" s="833" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="810" t="n"/>
-      <c r="B5" s="811" t="n"/>
-      <c r="C5" s="811" t="n"/>
-      <c r="D5" s="811" t="n"/>
-      <c r="E5" s="811" t="n"/>
-      <c r="F5" s="811" t="n"/>
-      <c r="G5" s="811" t="n"/>
-      <c r="H5" s="812" t="n"/>
-      <c r="I5" s="813" t="inlineStr">
+      <c r="A5" s="827" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+      <c r="E5" s="25" t="n"/>
+      <c r="F5" s="25" t="n"/>
+      <c r="G5" s="25" t="n"/>
+      <c r="H5" s="828" t="n"/>
+      <c r="I5" s="595" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="811" t="n"/>
-      <c r="K5" s="811" t="n"/>
-      <c r="L5" s="811" t="n"/>
-      <c r="M5" s="811" t="n"/>
-      <c r="N5" s="811" t="n"/>
-      <c r="O5" s="811" t="n"/>
-      <c r="P5" s="811" t="n"/>
-      <c r="Q5" s="811" t="n"/>
-      <c r="R5" s="811" t="n"/>
-      <c r="S5" s="811" t="n"/>
-      <c r="T5" s="811" t="n"/>
-      <c r="U5" s="811" t="n"/>
-      <c r="V5" s="811" t="n"/>
-      <c r="W5" s="811" t="n"/>
-      <c r="X5" s="811" t="n"/>
-      <c r="Y5" s="811" t="n"/>
-      <c r="Z5" s="811" t="n"/>
-      <c r="AA5" s="811" t="n"/>
-      <c r="AB5" s="811" t="n"/>
-      <c r="AC5" s="811" t="n"/>
-      <c r="AD5" s="812" t="n"/>
-      <c r="AE5" s="814" t="inlineStr">
+      <c r="J5" s="25" t="n"/>
+      <c r="K5" s="25" t="n"/>
+      <c r="L5" s="25" t="n"/>
+      <c r="M5" s="25" t="n"/>
+      <c r="N5" s="25" t="n"/>
+      <c r="O5" s="25" t="n"/>
+      <c r="P5" s="25" t="n"/>
+      <c r="Q5" s="25" t="n"/>
+      <c r="R5" s="25" t="n"/>
+      <c r="S5" s="25" t="n"/>
+      <c r="T5" s="25" t="n"/>
+      <c r="U5" s="25" t="n"/>
+      <c r="V5" s="25" t="n"/>
+      <c r="W5" s="25" t="n"/>
+      <c r="X5" s="25" t="n"/>
+      <c r="Y5" s="25" t="n"/>
+      <c r="Z5" s="25" t="n"/>
+      <c r="AA5" s="25" t="n"/>
+      <c r="AB5" s="25" t="n"/>
+      <c r="AC5" s="25" t="n"/>
+      <c r="AD5" s="828" t="n"/>
+      <c r="AE5" s="829" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="811" t="n"/>
-      <c r="AG5" s="811" t="n"/>
-      <c r="AH5" s="815" t="n"/>
-      <c r="AI5" s="816" t="inlineStr">
+      <c r="AF5" s="830" t="n"/>
+      <c r="AG5" s="830" t="n"/>
+      <c r="AH5" s="831" t="n"/>
+      <c r="AI5" s="724" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="811" t="n"/>
-      <c r="AK5" s="811" t="n"/>
-      <c r="AL5" s="811" t="n"/>
-      <c r="AM5" s="811" t="n"/>
-      <c r="AN5" s="812" t="n"/>
+      <c r="AJ5" s="832" t="n"/>
+      <c r="AK5" s="832" t="n"/>
+      <c r="AL5" s="832" t="n"/>
+      <c r="AM5" s="832" t="n"/>
+      <c r="AN5" s="833" t="n"/>
     </row>
-    <row r="6" ht="1.5" customHeight="1">
-      <c r="A6" s="817" t="n"/>
-      <c r="B6" s="817" t="n"/>
-      <c r="C6" s="817" t="n"/>
-      <c r="D6" s="817" t="n"/>
-      <c r="E6" s="817" t="n"/>
-      <c r="F6" s="817" t="n"/>
-      <c r="G6" s="817" t="n"/>
-      <c r="H6" s="817" t="n"/>
-      <c r="I6" s="817" t="n"/>
-      <c r="J6" s="817" t="n"/>
-      <c r="K6" s="817" t="n"/>
-      <c r="L6" s="817" t="n"/>
-      <c r="M6" s="817" t="n"/>
-      <c r="N6" s="817" t="n"/>
-      <c r="O6" s="817" t="n"/>
-      <c r="P6" s="817" t="n"/>
-      <c r="Q6" s="817" t="n"/>
-      <c r="R6" s="817" t="n"/>
-      <c r="S6" s="817" t="n"/>
-      <c r="T6" s="817" t="n"/>
-      <c r="U6" s="817" t="n"/>
-      <c r="V6" s="817" t="n"/>
-      <c r="W6" s="817" t="n"/>
-      <c r="X6" s="817" t="n"/>
-      <c r="Y6" s="817" t="n"/>
-      <c r="Z6" s="817" t="n"/>
-      <c r="AA6" s="817" t="n"/>
-      <c r="AB6" s="817" t="n"/>
-      <c r="AC6" s="817" t="n"/>
-      <c r="AD6" s="817" t="n"/>
-      <c r="AE6" s="817" t="n"/>
-      <c r="AF6" s="817" t="n"/>
-      <c r="AG6" s="817" t="n"/>
-      <c r="AH6" s="817" t="n"/>
-      <c r="AI6" s="817" t="n"/>
-      <c r="AJ6" s="817" t="n"/>
-      <c r="AK6" s="817" t="n"/>
-      <c r="AL6" s="817" t="n"/>
-      <c r="AM6" s="817" t="n"/>
-      <c r="AN6" s="817" t="n"/>
+    <row r="6" ht="15" customHeight="1">
+      <c r="A6" s="847" t="n"/>
+      <c r="B6" s="848" t="n"/>
+      <c r="C6" s="848" t="n"/>
+      <c r="D6" s="848" t="n"/>
+      <c r="E6" s="848" t="n"/>
+      <c r="F6" s="848" t="n"/>
+      <c r="G6" s="848" t="n"/>
+      <c r="H6" s="849" t="n"/>
+      <c r="I6" s="848" t="n"/>
+      <c r="J6" s="848" t="n"/>
+      <c r="K6" s="848" t="n"/>
+      <c r="L6" s="848" t="n"/>
+      <c r="M6" s="848" t="n"/>
+      <c r="N6" s="848" t="n"/>
+      <c r="O6" s="848" t="n"/>
+      <c r="P6" s="848" t="n"/>
+      <c r="Q6" s="848" t="n"/>
+      <c r="R6" s="848" t="n"/>
+      <c r="S6" s="848" t="n"/>
+      <c r="T6" s="848" t="n"/>
+      <c r="U6" s="848" t="n"/>
+      <c r="V6" s="848" t="n"/>
+      <c r="W6" s="848" t="n"/>
+      <c r="X6" s="848" t="n"/>
+      <c r="Y6" s="848" t="n"/>
+      <c r="Z6" s="848" t="n"/>
+      <c r="AA6" s="848" t="n"/>
+      <c r="AB6" s="848" t="n"/>
+      <c r="AC6" s="848" t="n"/>
+      <c r="AD6" s="849" t="n"/>
+      <c r="AE6" s="850" t="n"/>
+      <c r="AF6" s="850" t="n"/>
+      <c r="AG6" s="850" t="n"/>
+      <c r="AH6" s="851" t="n"/>
+      <c r="AI6" s="852" t="n"/>
+      <c r="AJ6" s="852" t="n"/>
+      <c r="AK6" s="852" t="n"/>
+      <c r="AL6" s="852" t="n"/>
+      <c r="AM6" s="852" t="n"/>
+      <c r="AN6" s="853" t="n"/>
     </row>
-    <row r="7">
-      <c r="A7" s="632" t="inlineStr">
-        <is>
-          <t>REF LINKS</t>
-        </is>
-      </c>
-      <c r="B7" s="752" t="n"/>
-      <c r="C7" s="752" t="n"/>
-      <c r="D7" s="752" t="n"/>
-      <c r="E7" s="752" t="n"/>
-      <c r="F7" s="752" t="n"/>
-      <c r="G7" s="752" t="n"/>
-      <c r="H7" s="818" t="n"/>
-      <c r="I7" s="818" t="n"/>
-      <c r="J7" s="818" t="n"/>
-      <c r="K7" s="818" t="n"/>
-      <c r="L7" s="818" t="n"/>
-      <c r="M7" s="818" t="n"/>
-      <c r="N7" s="818" t="n"/>
-      <c r="O7" s="818" t="n"/>
-      <c r="P7" s="818" t="n"/>
-      <c r="Q7" s="818" t="n"/>
-      <c r="R7" s="818" t="n"/>
-      <c r="S7" s="818" t="n"/>
-      <c r="T7" s="818" t="n"/>
-      <c r="U7" s="818" t="n"/>
-      <c r="V7" s="818" t="n"/>
-      <c r="W7" s="818" t="n"/>
-      <c r="X7" s="818" t="n"/>
-      <c r="Y7" s="818" t="n"/>
-      <c r="Z7" s="818" t="n"/>
-      <c r="AA7" s="818" t="n"/>
-      <c r="AB7" s="818" t="n"/>
-      <c r="AC7" s="818" t="n"/>
-      <c r="AD7" s="818" t="n"/>
-      <c r="AE7" s="818" t="n"/>
-      <c r="AF7" s="818" t="n"/>
-      <c r="AG7" s="818" t="n"/>
-      <c r="AH7" s="818" t="n"/>
-      <c r="AI7" s="818" t="n"/>
-      <c r="AJ7" s="818" t="n"/>
-      <c r="AK7" s="818" t="n"/>
-      <c r="AL7" s="818" t="n"/>
-      <c r="AM7" s="818" t="n"/>
-      <c r="AN7" s="818" t="n"/>
+    <row r="7" ht="4" customHeight="1">
+      <c r="A7" s="879" t="n"/>
+      <c r="B7" s="842" t="n"/>
+      <c r="C7" s="842" t="n"/>
+      <c r="D7" s="842" t="n"/>
+      <c r="E7" s="842" t="n"/>
+      <c r="F7" s="842" t="n"/>
+      <c r="G7" s="842" t="n"/>
+      <c r="H7" s="855" t="n"/>
+      <c r="I7" s="855" t="n"/>
+      <c r="J7" s="855" t="n"/>
+      <c r="K7" s="855" t="n"/>
+      <c r="L7" s="855" t="n"/>
+      <c r="M7" s="855" t="n"/>
+      <c r="N7" s="855" t="n"/>
+      <c r="O7" s="855" t="n"/>
+      <c r="P7" s="855" t="n"/>
+      <c r="Q7" s="855" t="n"/>
+      <c r="R7" s="855" t="n"/>
+      <c r="S7" s="855" t="n"/>
+      <c r="T7" s="855" t="n"/>
+      <c r="U7" s="855" t="n"/>
+      <c r="V7" s="855" t="n"/>
+      <c r="W7" s="855" t="n"/>
+      <c r="X7" s="855" t="n"/>
+      <c r="Y7" s="855" t="n"/>
+      <c r="Z7" s="855" t="n"/>
+      <c r="AA7" s="855" t="n"/>
+      <c r="AB7" s="855" t="n"/>
+      <c r="AC7" s="855" t="n"/>
+      <c r="AD7" s="855" t="n"/>
+      <c r="AE7" s="855" t="n"/>
+      <c r="AF7" s="855" t="n"/>
+      <c r="AG7" s="855" t="n"/>
+      <c r="AH7" s="855" t="n"/>
+      <c r="AI7" s="855" t="n"/>
+      <c r="AJ7" s="855" t="n"/>
+      <c r="AK7" s="855" t="n"/>
+      <c r="AL7" s="855" t="n"/>
+      <c r="AM7" s="855" t="n"/>
+      <c r="AN7" s="855" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="633" t="inlineStr">
+      <c r="A8" s="880" t="inlineStr">
         <is>
           <t>Reference superseding package, withdrawal evidence and active M365 links only.</t>
         </is>
@@ -16840,7 +17173,7 @@
       <c r="AN8" s="818" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="634" t="inlineStr">
+      <c r="A9" s="881" t="inlineStr">
         <is>
           <t>Ref Type</t>
         </is>

--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -5211,7 +5211,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="85" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="883">
+  <cellXfs count="893">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="3" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -7379,6 +7379,26 @@
     <xf numFmtId="0" fontId="92" fillId="4" borderId="398" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="16" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="14" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="17" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="15" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1" indent="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="4" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="362" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="353" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="364" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="365" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="366" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
@@ -7497,6 +7517,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7527,6 +7550,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7557,6 +7583,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7587,6 +7616,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7617,6 +7649,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -7647,6 +7682,9 @@
       </blipFill>
       <spPr>
         <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+        <a:ln xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:prstDash val="solid"/>
+        </a:ln>
       </spPr>
     </pic>
     <clientData/>
@@ -8014,276 +8052,133 @@
       <c r="BD1" s="323" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
-      <c r="F2" s="819" t="n"/>
-      <c r="G2" s="819" t="n"/>
-      <c r="H2" s="819" t="n"/>
-      <c r="I2" s="819" t="n"/>
-      <c r="J2" s="819" t="n"/>
-      <c r="K2" s="820" t="n"/>
-      <c r="L2" s="819" t="n"/>
-      <c r="M2" s="819" t="n"/>
-      <c r="N2" s="819" t="n"/>
-      <c r="O2" s="819" t="n"/>
-      <c r="P2" s="819" t="n"/>
-      <c r="Q2" s="819" t="n"/>
-      <c r="R2" s="819" t="n"/>
-      <c r="S2" s="819" t="n"/>
-      <c r="T2" s="819" t="n"/>
-      <c r="U2" s="819" t="n"/>
-      <c r="V2" s="819" t="n"/>
-      <c r="W2" s="819" t="n"/>
-      <c r="X2" s="819" t="n"/>
-      <c r="Y2" s="819" t="n"/>
-      <c r="Z2" s="819" t="n"/>
-      <c r="AA2" s="819" t="n"/>
-      <c r="AB2" s="819" t="n"/>
-      <c r="AC2" s="819" t="n"/>
-      <c r="AD2" s="819" t="n"/>
-      <c r="AE2" s="819" t="n"/>
-      <c r="AF2" s="819" t="n"/>
-      <c r="AG2" s="819" t="n"/>
-      <c r="AH2" s="819" t="n"/>
-      <c r="AI2" s="819" t="n"/>
-      <c r="AJ2" s="819" t="n"/>
-      <c r="AK2" s="819" t="n"/>
-      <c r="AL2" s="819" t="n"/>
-      <c r="AM2" s="819" t="n"/>
-      <c r="AN2" s="819" t="n"/>
-      <c r="AO2" s="819" t="n"/>
-      <c r="AP2" s="820" t="n"/>
-      <c r="AQ2" s="821" t="inlineStr">
+      <c r="A2" s="275" t="n"/>
+      <c r="K2" s="324" t="n"/>
+      <c r="L2" s="275" t="n"/>
+      <c r="AP2" s="324" t="n"/>
+      <c r="AQ2" s="883" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AR2" s="822" t="n"/>
-      <c r="AS2" s="822" t="n"/>
-      <c r="AT2" s="822" t="n"/>
-      <c r="AU2" s="822" t="n"/>
-      <c r="AV2" s="823" t="n"/>
-      <c r="AW2" s="824" t="inlineStr">
+      <c r="AR2" s="271" t="n"/>
+      <c r="AS2" s="271" t="n"/>
+      <c r="AT2" s="271" t="n"/>
+      <c r="AU2" s="271" t="n"/>
+      <c r="AV2" s="272" t="n"/>
+      <c r="AW2" s="884" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AX2" s="825" t="n"/>
-      <c r="AY2" s="825" t="n"/>
-      <c r="AZ2" s="825" t="n"/>
-      <c r="BA2" s="825" t="n"/>
-      <c r="BB2" s="825" t="n"/>
-      <c r="BC2" s="825" t="n"/>
-      <c r="BD2" s="826" t="n"/>
+      <c r="AX2" s="271" t="n"/>
+      <c r="AY2" s="271" t="n"/>
+      <c r="AZ2" s="271" t="n"/>
+      <c r="BA2" s="271" t="n"/>
+      <c r="BB2" s="271" t="n"/>
+      <c r="BC2" s="271" t="n"/>
+      <c r="BD2" s="274" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="25" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="828" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="25" t="n"/>
-      <c r="AE3" s="25" t="n"/>
-      <c r="AF3" s="25" t="n"/>
-      <c r="AG3" s="25" t="n"/>
-      <c r="AH3" s="25" t="n"/>
-      <c r="AI3" s="25" t="n"/>
-      <c r="AJ3" s="25" t="n"/>
-      <c r="AK3" s="25" t="n"/>
-      <c r="AL3" s="25" t="n"/>
-      <c r="AM3" s="25" t="n"/>
-      <c r="AN3" s="25" t="n"/>
-      <c r="AO3" s="25" t="n"/>
-      <c r="AP3" s="828" t="n"/>
-      <c r="AQ3" s="829" t="inlineStr">
+      <c r="A3" s="275" t="n"/>
+      <c r="K3" s="324" t="n"/>
+      <c r="L3" s="275" t="n"/>
+      <c r="AP3" s="324" t="n"/>
+      <c r="AQ3" s="885" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AR3" s="830" t="n"/>
-      <c r="AS3" s="830" t="n"/>
-      <c r="AT3" s="830" t="n"/>
-      <c r="AU3" s="830" t="n"/>
-      <c r="AV3" s="831" t="n"/>
-      <c r="AW3" s="724" t="inlineStr">
+      <c r="AR3" s="277" t="n"/>
+      <c r="AS3" s="277" t="n"/>
+      <c r="AT3" s="277" t="n"/>
+      <c r="AU3" s="277" t="n"/>
+      <c r="AV3" s="278" t="n"/>
+      <c r="AW3" s="886" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AX3" s="832" t="n"/>
-      <c r="AY3" s="832" t="n"/>
-      <c r="AZ3" s="832" t="n"/>
-      <c r="BA3" s="832" t="n"/>
-      <c r="BB3" s="832" t="n"/>
-      <c r="BC3" s="832" t="n"/>
-      <c r="BD3" s="833" t="n"/>
+      <c r="AX3" s="277" t="n"/>
+      <c r="AY3" s="277" t="n"/>
+      <c r="AZ3" s="277" t="n"/>
+      <c r="BA3" s="277" t="n"/>
+      <c r="BB3" s="277" t="n"/>
+      <c r="BC3" s="277" t="n"/>
+      <c r="BD3" s="280" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="25" t="n"/>
-      <c r="I4" s="25" t="n"/>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="828" t="n"/>
-      <c r="L4" s="346" t="inlineStr">
+      <c r="A4" s="275" t="n"/>
+      <c r="K4" s="324" t="n"/>
+      <c r="L4" s="347" t="inlineStr">
         <is>
           <t>Quality Management System  ?  Controlled Document</t>
         </is>
       </c>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="25" t="n"/>
-      <c r="AE4" s="25" t="n"/>
-      <c r="AF4" s="25" t="n"/>
-      <c r="AG4" s="25" t="n"/>
-      <c r="AH4" s="25" t="n"/>
-      <c r="AI4" s="25" t="n"/>
-      <c r="AJ4" s="25" t="n"/>
-      <c r="AK4" s="25" t="n"/>
-      <c r="AL4" s="25" t="n"/>
-      <c r="AM4" s="25" t="n"/>
-      <c r="AN4" s="25" t="n"/>
-      <c r="AO4" s="25" t="n"/>
-      <c r="AP4" s="828" t="n"/>
-      <c r="AQ4" s="829" t="inlineStr">
+      <c r="AP4" s="324" t="n"/>
+      <c r="AQ4" s="885" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AR4" s="830" t="n"/>
-      <c r="AS4" s="830" t="n"/>
-      <c r="AT4" s="830" t="n"/>
-      <c r="AU4" s="830" t="n"/>
-      <c r="AV4" s="831" t="n"/>
-      <c r="AW4" s="724" t="inlineStr">
+      <c r="AR4" s="277" t="n"/>
+      <c r="AS4" s="277" t="n"/>
+      <c r="AT4" s="277" t="n"/>
+      <c r="AU4" s="277" t="n"/>
+      <c r="AV4" s="278" t="n"/>
+      <c r="AW4" s="886" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AX4" s="832" t="n"/>
-      <c r="AY4" s="832" t="n"/>
-      <c r="AZ4" s="832" t="n"/>
-      <c r="BA4" s="832" t="n"/>
-      <c r="BB4" s="832" t="n"/>
-      <c r="BC4" s="832" t="n"/>
-      <c r="BD4" s="833" t="n"/>
+      <c r="AX4" s="277" t="n"/>
+      <c r="AY4" s="277" t="n"/>
+      <c r="AZ4" s="277" t="n"/>
+      <c r="BA4" s="277" t="n"/>
+      <c r="BB4" s="277" t="n"/>
+      <c r="BC4" s="277" t="n"/>
+      <c r="BD4" s="280" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="25" t="n"/>
-      <c r="I5" s="25" t="n"/>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="828" t="n"/>
-      <c r="L5" s="595" t="inlineStr">
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="283" t="n"/>
+      <c r="C5" s="283" t="n"/>
+      <c r="D5" s="283" t="n"/>
+      <c r="E5" s="283" t="n"/>
+      <c r="F5" s="283" t="n"/>
+      <c r="G5" s="283" t="n"/>
+      <c r="H5" s="283" t="n"/>
+      <c r="I5" s="283" t="n"/>
+      <c r="J5" s="283" t="n"/>
+      <c r="K5" s="287" t="n"/>
+      <c r="L5" s="887" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="25" t="n"/>
-      <c r="AE5" s="25" t="n"/>
-      <c r="AF5" s="25" t="n"/>
-      <c r="AG5" s="25" t="n"/>
-      <c r="AH5" s="25" t="n"/>
-      <c r="AI5" s="25" t="n"/>
-      <c r="AJ5" s="25" t="n"/>
-      <c r="AK5" s="25" t="n"/>
-      <c r="AL5" s="25" t="n"/>
-      <c r="AM5" s="25" t="n"/>
-      <c r="AN5" s="25" t="n"/>
-      <c r="AO5" s="25" t="n"/>
-      <c r="AP5" s="828" t="n"/>
-      <c r="AQ5" s="829" t="inlineStr">
+      <c r="AP5" s="324" t="n"/>
+      <c r="AQ5" s="885" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AR5" s="830" t="n"/>
-      <c r="AS5" s="830" t="n"/>
-      <c r="AT5" s="830" t="n"/>
-      <c r="AU5" s="830" t="n"/>
-      <c r="AV5" s="831" t="n"/>
-      <c r="AW5" s="724" t="inlineStr">
+      <c r="AR5" s="277" t="n"/>
+      <c r="AS5" s="277" t="n"/>
+      <c r="AT5" s="277" t="n"/>
+      <c r="AU5" s="277" t="n"/>
+      <c r="AV5" s="278" t="n"/>
+      <c r="AW5" s="886" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AX5" s="832" t="n"/>
-      <c r="AY5" s="832" t="n"/>
-      <c r="AZ5" s="832" t="n"/>
-      <c r="BA5" s="832" t="n"/>
-      <c r="BB5" s="832" t="n"/>
-      <c r="BC5" s="832" t="n"/>
-      <c r="BD5" s="833" t="n"/>
+      <c r="AX5" s="277" t="n"/>
+      <c r="AY5" s="277" t="n"/>
+      <c r="AZ5" s="277" t="n"/>
+      <c r="BA5" s="277" t="n"/>
+      <c r="BB5" s="277" t="n"/>
+      <c r="BC5" s="277" t="n"/>
+      <c r="BD5" s="280" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="834" t="n"/>
@@ -8345,61 +8240,6 @@
     </row>
     <row r="7" ht="4" customHeight="1">
       <c r="A7" s="841" t="n"/>
-      <c r="B7" s="842" t="n"/>
-      <c r="C7" s="842" t="n"/>
-      <c r="D7" s="842" t="n"/>
-      <c r="E7" s="842" t="n"/>
-      <c r="F7" s="842" t="n"/>
-      <c r="G7" s="842" t="n"/>
-      <c r="H7" s="842" t="n"/>
-      <c r="I7" s="842" t="n"/>
-      <c r="J7" s="842" t="n"/>
-      <c r="K7" s="842" t="n"/>
-      <c r="L7" s="842" t="n"/>
-      <c r="M7" s="842" t="n"/>
-      <c r="N7" s="842" t="n"/>
-      <c r="O7" s="842" t="n"/>
-      <c r="P7" s="842" t="n"/>
-      <c r="Q7" s="842" t="n"/>
-      <c r="R7" s="842" t="n"/>
-      <c r="S7" s="842" t="n"/>
-      <c r="T7" s="842" t="n"/>
-      <c r="U7" s="842" t="n"/>
-      <c r="V7" s="842" t="n"/>
-      <c r="W7" s="842" t="n"/>
-      <c r="X7" s="842" t="n"/>
-      <c r="Y7" s="842" t="n"/>
-      <c r="Z7" s="842" t="n"/>
-      <c r="AA7" s="842" t="n"/>
-      <c r="AB7" s="842" t="n"/>
-      <c r="AC7" s="842" t="n"/>
-      <c r="AD7" s="842" t="n"/>
-      <c r="AE7" s="842" t="n"/>
-      <c r="AF7" s="842" t="n"/>
-      <c r="AG7" s="842" t="n"/>
-      <c r="AH7" s="842" t="n"/>
-      <c r="AI7" s="842" t="n"/>
-      <c r="AJ7" s="842" t="n"/>
-      <c r="AK7" s="842" t="n"/>
-      <c r="AL7" s="842" t="n"/>
-      <c r="AM7" s="842" t="n"/>
-      <c r="AN7" s="842" t="n"/>
-      <c r="AO7" s="842" t="n"/>
-      <c r="AP7" s="842" t="n"/>
-      <c r="AQ7" s="842" t="n"/>
-      <c r="AR7" s="842" t="n"/>
-      <c r="AS7" s="842" t="n"/>
-      <c r="AT7" s="842" t="n"/>
-      <c r="AU7" s="842" t="n"/>
-      <c r="AV7" s="842" t="n"/>
-      <c r="AW7" s="842" t="n"/>
-      <c r="AX7" s="842" t="n"/>
-      <c r="AY7" s="842" t="n"/>
-      <c r="AZ7" s="842" t="n"/>
-      <c r="BA7" s="842" t="n"/>
-      <c r="BB7" s="842" t="n"/>
-      <c r="BC7" s="842" t="n"/>
-      <c r="BD7" s="842" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="765" t="inlineStr">
@@ -10886,66 +10726,66 @@
       <c r="BD46" s="672" t="n"/>
     </row>
     <row r="47" ht="26" customHeight="1">
-      <c r="A47" s="373" t="inlineStr">
+      <c r="A47" s="397" t="inlineStr">
         <is>
           <t>NOTICE  ?  Enter data only in designated white input cells. Do not add, delete or resize columns/rows. File naming: FRM-307_[EVENTID]_[YYYYMMDD].xlsx | Controlled source sets: Epicor / M365 / approved ANNEX references only.</t>
         </is>
       </c>
-      <c r="B47" s="374" t="n"/>
-      <c r="C47" s="374" t="n"/>
-      <c r="D47" s="374" t="n"/>
-      <c r="E47" s="374" t="n"/>
-      <c r="F47" s="374" t="n"/>
-      <c r="G47" s="374" t="n"/>
-      <c r="H47" s="374" t="n"/>
-      <c r="I47" s="374" t="n"/>
-      <c r="J47" s="374" t="n"/>
-      <c r="K47" s="374" t="n"/>
-      <c r="L47" s="374" t="n"/>
-      <c r="M47" s="374" t="n"/>
-      <c r="N47" s="374" t="n"/>
-      <c r="O47" s="374" t="n"/>
-      <c r="P47" s="374" t="n"/>
-      <c r="Q47" s="374" t="n"/>
-      <c r="R47" s="374" t="n"/>
-      <c r="S47" s="374" t="n"/>
-      <c r="T47" s="374" t="n"/>
-      <c r="U47" s="374" t="n"/>
-      <c r="V47" s="374" t="n"/>
-      <c r="W47" s="374" t="n"/>
-      <c r="X47" s="374" t="n"/>
-      <c r="Y47" s="374" t="n"/>
-      <c r="Z47" s="374" t="n"/>
-      <c r="AA47" s="374" t="n"/>
-      <c r="AB47" s="374" t="n"/>
-      <c r="AC47" s="374" t="n"/>
-      <c r="AD47" s="374" t="n"/>
-      <c r="AE47" s="374" t="n"/>
-      <c r="AF47" s="374" t="n"/>
-      <c r="AG47" s="374" t="n"/>
-      <c r="AH47" s="374" t="n"/>
-      <c r="AI47" s="374" t="n"/>
-      <c r="AJ47" s="374" t="n"/>
-      <c r="AK47" s="374" t="n"/>
-      <c r="AL47" s="374" t="n"/>
-      <c r="AM47" s="374" t="n"/>
-      <c r="AN47" s="374" t="n"/>
-      <c r="AO47" s="374" t="n"/>
-      <c r="AP47" s="374" t="n"/>
-      <c r="AQ47" s="374" t="n"/>
-      <c r="AR47" s="374" t="n"/>
-      <c r="AS47" s="374" t="n"/>
-      <c r="AT47" s="374" t="n"/>
-      <c r="AU47" s="374" t="n"/>
-      <c r="AV47" s="374" t="n"/>
-      <c r="AW47" s="374" t="n"/>
-      <c r="AX47" s="374" t="n"/>
-      <c r="AY47" s="374" t="n"/>
-      <c r="AZ47" s="374" t="n"/>
-      <c r="BA47" s="374" t="n"/>
-      <c r="BB47" s="374" t="n"/>
-      <c r="BC47" s="374" t="n"/>
-      <c r="BD47" s="375" t="n"/>
+      <c r="B47" s="289" t="n"/>
+      <c r="C47" s="289" t="n"/>
+      <c r="D47" s="289" t="n"/>
+      <c r="E47" s="289" t="n"/>
+      <c r="F47" s="289" t="n"/>
+      <c r="G47" s="289" t="n"/>
+      <c r="H47" s="289" t="n"/>
+      <c r="I47" s="289" t="n"/>
+      <c r="J47" s="289" t="n"/>
+      <c r="K47" s="289" t="n"/>
+      <c r="L47" s="289" t="n"/>
+      <c r="M47" s="289" t="n"/>
+      <c r="N47" s="289" t="n"/>
+      <c r="O47" s="289" t="n"/>
+      <c r="P47" s="289" t="n"/>
+      <c r="Q47" s="289" t="n"/>
+      <c r="R47" s="289" t="n"/>
+      <c r="S47" s="289" t="n"/>
+      <c r="T47" s="289" t="n"/>
+      <c r="U47" s="289" t="n"/>
+      <c r="V47" s="289" t="n"/>
+      <c r="W47" s="289" t="n"/>
+      <c r="X47" s="289" t="n"/>
+      <c r="Y47" s="289" t="n"/>
+      <c r="Z47" s="289" t="n"/>
+      <c r="AA47" s="289" t="n"/>
+      <c r="AB47" s="289" t="n"/>
+      <c r="AC47" s="289" t="n"/>
+      <c r="AD47" s="289" t="n"/>
+      <c r="AE47" s="289" t="n"/>
+      <c r="AF47" s="289" t="n"/>
+      <c r="AG47" s="289" t="n"/>
+      <c r="AH47" s="289" t="n"/>
+      <c r="AI47" s="289" t="n"/>
+      <c r="AJ47" s="289" t="n"/>
+      <c r="AK47" s="289" t="n"/>
+      <c r="AL47" s="289" t="n"/>
+      <c r="AM47" s="289" t="n"/>
+      <c r="AN47" s="289" t="n"/>
+      <c r="AO47" s="289" t="n"/>
+      <c r="AP47" s="289" t="n"/>
+      <c r="AQ47" s="289" t="n"/>
+      <c r="AR47" s="289" t="n"/>
+      <c r="AS47" s="289" t="n"/>
+      <c r="AT47" s="289" t="n"/>
+      <c r="AU47" s="289" t="n"/>
+      <c r="AV47" s="289" t="n"/>
+      <c r="AW47" s="289" t="n"/>
+      <c r="AX47" s="289" t="n"/>
+      <c r="AY47" s="289" t="n"/>
+      <c r="AZ47" s="289" t="n"/>
+      <c r="BA47" s="289" t="n"/>
+      <c r="BB47" s="289" t="n"/>
+      <c r="BC47" s="289" t="n"/>
+      <c r="BD47" s="290" t="n"/>
     </row>
     <row r="48" hidden="1" outlineLevel="1"/>
     <row r="49" hidden="1" outlineLevel="1"/>
@@ -11513,212 +11353,112 @@
       <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
-      <c r="F2" s="819" t="n"/>
-      <c r="G2" s="819" t="n"/>
-      <c r="H2" s="820" t="n"/>
-      <c r="I2" s="819" t="n"/>
-      <c r="J2" s="819" t="n"/>
-      <c r="K2" s="819" t="n"/>
-      <c r="L2" s="819" t="n"/>
-      <c r="M2" s="819" t="n"/>
-      <c r="N2" s="819" t="n"/>
-      <c r="O2" s="819" t="n"/>
-      <c r="P2" s="819" t="n"/>
-      <c r="Q2" s="819" t="n"/>
-      <c r="R2" s="819" t="n"/>
-      <c r="S2" s="819" t="n"/>
-      <c r="T2" s="819" t="n"/>
-      <c r="U2" s="819" t="n"/>
-      <c r="V2" s="819" t="n"/>
-      <c r="W2" s="819" t="n"/>
-      <c r="X2" s="819" t="n"/>
-      <c r="Y2" s="819" t="n"/>
-      <c r="Z2" s="819" t="n"/>
-      <c r="AA2" s="819" t="n"/>
-      <c r="AB2" s="819" t="n"/>
-      <c r="AC2" s="819" t="n"/>
-      <c r="AD2" s="820" t="n"/>
-      <c r="AE2" s="821" t="inlineStr">
+      <c r="A2" s="888" t="n"/>
+      <c r="H2" s="889" t="n"/>
+      <c r="AD2" s="889" t="n"/>
+      <c r="AE2" s="883" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="822" t="n"/>
-      <c r="AG2" s="822" t="n"/>
-      <c r="AH2" s="823" t="n"/>
-      <c r="AI2" s="824" t="inlineStr">
+      <c r="AF2" s="271" t="n"/>
+      <c r="AG2" s="271" t="n"/>
+      <c r="AH2" s="272" t="n"/>
+      <c r="AI2" s="884" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="825" t="n"/>
-      <c r="AK2" s="825" t="n"/>
-      <c r="AL2" s="825" t="n"/>
-      <c r="AM2" s="825" t="n"/>
-      <c r="AN2" s="826" t="n"/>
+      <c r="AJ2" s="271" t="n"/>
+      <c r="AK2" s="271" t="n"/>
+      <c r="AL2" s="271" t="n"/>
+      <c r="AM2" s="271" t="n"/>
+      <c r="AN2" s="274" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="828" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="828" t="n"/>
-      <c r="AE3" s="829" t="inlineStr">
+      <c r="A3" s="888" t="n"/>
+      <c r="H3" s="889" t="n"/>
+      <c r="AD3" s="889" t="n"/>
+      <c r="AE3" s="885" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="830" t="n"/>
-      <c r="AG3" s="830" t="n"/>
-      <c r="AH3" s="831" t="n"/>
-      <c r="AI3" s="724" t="inlineStr">
+      <c r="AF3" s="277" t="n"/>
+      <c r="AG3" s="277" t="n"/>
+      <c r="AH3" s="278" t="n"/>
+      <c r="AI3" s="886" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="832" t="n"/>
-      <c r="AK3" s="832" t="n"/>
-      <c r="AL3" s="832" t="n"/>
-      <c r="AM3" s="832" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="277" t="n"/>
+      <c r="AK3" s="277" t="n"/>
+      <c r="AL3" s="277" t="n"/>
+      <c r="AM3" s="277" t="n"/>
+      <c r="AN3" s="280" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="828" t="n"/>
-      <c r="I4" s="346" t="inlineStr">
+      <c r="A4" s="888" t="n"/>
+      <c r="H4" s="889" t="n"/>
+      <c r="I4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="828" t="n"/>
-      <c r="AE4" s="829" t="inlineStr">
+      <c r="AD4" s="324" t="n"/>
+      <c r="AE4" s="885" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="830" t="n"/>
-      <c r="AG4" s="830" t="n"/>
-      <c r="AH4" s="831" t="n"/>
-      <c r="AI4" s="724" t="inlineStr">
+      <c r="AF4" s="277" t="n"/>
+      <c r="AG4" s="277" t="n"/>
+      <c r="AH4" s="278" t="n"/>
+      <c r="AI4" s="886" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="832" t="n"/>
-      <c r="AK4" s="832" t="n"/>
-      <c r="AL4" s="832" t="n"/>
-      <c r="AM4" s="832" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="277" t="n"/>
+      <c r="AK4" s="277" t="n"/>
+      <c r="AL4" s="277" t="n"/>
+      <c r="AM4" s="277" t="n"/>
+      <c r="AN4" s="280" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="828" t="n"/>
-      <c r="I5" s="595" t="inlineStr">
+      <c r="A5" s="890" t="n"/>
+      <c r="B5" s="891" t="n"/>
+      <c r="C5" s="891" t="n"/>
+      <c r="D5" s="891" t="n"/>
+      <c r="E5" s="891" t="n"/>
+      <c r="F5" s="891" t="n"/>
+      <c r="G5" s="891" t="n"/>
+      <c r="H5" s="892" t="n"/>
+      <c r="I5" s="887" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="828" t="n"/>
-      <c r="AE5" s="829" t="inlineStr">
+      <c r="AD5" s="324" t="n"/>
+      <c r="AE5" s="885" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="830" t="n"/>
-      <c r="AG5" s="830" t="n"/>
-      <c r="AH5" s="831" t="n"/>
-      <c r="AI5" s="724" t="inlineStr">
+      <c r="AF5" s="277" t="n"/>
+      <c r="AG5" s="277" t="n"/>
+      <c r="AH5" s="278" t="n"/>
+      <c r="AI5" s="886" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="832" t="n"/>
-      <c r="AK5" s="832" t="n"/>
-      <c r="AL5" s="832" t="n"/>
-      <c r="AM5" s="832" t="n"/>
-      <c r="AN5" s="833" t="n"/>
+      <c r="AJ5" s="277" t="n"/>
+      <c r="AK5" s="277" t="n"/>
+      <c r="AL5" s="277" t="n"/>
+      <c r="AM5" s="277" t="n"/>
+      <c r="AN5" s="280" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="847" t="n"/>
@@ -12551,212 +12291,112 @@
       <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
-      <c r="F2" s="819" t="n"/>
-      <c r="G2" s="819" t="n"/>
-      <c r="H2" s="820" t="n"/>
-      <c r="I2" s="819" t="n"/>
-      <c r="J2" s="819" t="n"/>
-      <c r="K2" s="819" t="n"/>
-      <c r="L2" s="819" t="n"/>
-      <c r="M2" s="819" t="n"/>
-      <c r="N2" s="819" t="n"/>
-      <c r="O2" s="819" t="n"/>
-      <c r="P2" s="819" t="n"/>
-      <c r="Q2" s="819" t="n"/>
-      <c r="R2" s="819" t="n"/>
-      <c r="S2" s="819" t="n"/>
-      <c r="T2" s="819" t="n"/>
-      <c r="U2" s="819" t="n"/>
-      <c r="V2" s="819" t="n"/>
-      <c r="W2" s="819" t="n"/>
-      <c r="X2" s="819" t="n"/>
-      <c r="Y2" s="819" t="n"/>
-      <c r="Z2" s="819" t="n"/>
-      <c r="AA2" s="819" t="n"/>
-      <c r="AB2" s="819" t="n"/>
-      <c r="AC2" s="819" t="n"/>
-      <c r="AD2" s="820" t="n"/>
-      <c r="AE2" s="821" t="inlineStr">
+      <c r="A2" s="888" t="n"/>
+      <c r="H2" s="889" t="n"/>
+      <c r="AD2" s="889" t="n"/>
+      <c r="AE2" s="883" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="822" t="n"/>
-      <c r="AG2" s="822" t="n"/>
-      <c r="AH2" s="823" t="n"/>
-      <c r="AI2" s="824" t="inlineStr">
+      <c r="AF2" s="271" t="n"/>
+      <c r="AG2" s="271" t="n"/>
+      <c r="AH2" s="272" t="n"/>
+      <c r="AI2" s="884" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="825" t="n"/>
-      <c r="AK2" s="825" t="n"/>
-      <c r="AL2" s="825" t="n"/>
-      <c r="AM2" s="825" t="n"/>
-      <c r="AN2" s="826" t="n"/>
+      <c r="AJ2" s="271" t="n"/>
+      <c r="AK2" s="271" t="n"/>
+      <c r="AL2" s="271" t="n"/>
+      <c r="AM2" s="271" t="n"/>
+      <c r="AN2" s="274" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="828" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="828" t="n"/>
-      <c r="AE3" s="829" t="inlineStr">
+      <c r="A3" s="888" t="n"/>
+      <c r="H3" s="889" t="n"/>
+      <c r="AD3" s="889" t="n"/>
+      <c r="AE3" s="885" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="830" t="n"/>
-      <c r="AG3" s="830" t="n"/>
-      <c r="AH3" s="831" t="n"/>
-      <c r="AI3" s="724" t="inlineStr">
+      <c r="AF3" s="277" t="n"/>
+      <c r="AG3" s="277" t="n"/>
+      <c r="AH3" s="278" t="n"/>
+      <c r="AI3" s="886" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="832" t="n"/>
-      <c r="AK3" s="832" t="n"/>
-      <c r="AL3" s="832" t="n"/>
-      <c r="AM3" s="832" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="277" t="n"/>
+      <c r="AK3" s="277" t="n"/>
+      <c r="AL3" s="277" t="n"/>
+      <c r="AM3" s="277" t="n"/>
+      <c r="AN3" s="280" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="828" t="n"/>
-      <c r="I4" s="346" t="inlineStr">
+      <c r="A4" s="888" t="n"/>
+      <c r="H4" s="889" t="n"/>
+      <c r="I4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="828" t="n"/>
-      <c r="AE4" s="829" t="inlineStr">
+      <c r="AD4" s="324" t="n"/>
+      <c r="AE4" s="885" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="830" t="n"/>
-      <c r="AG4" s="830" t="n"/>
-      <c r="AH4" s="831" t="n"/>
-      <c r="AI4" s="724" t="inlineStr">
+      <c r="AF4" s="277" t="n"/>
+      <c r="AG4" s="277" t="n"/>
+      <c r="AH4" s="278" t="n"/>
+      <c r="AI4" s="886" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="832" t="n"/>
-      <c r="AK4" s="832" t="n"/>
-      <c r="AL4" s="832" t="n"/>
-      <c r="AM4" s="832" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="277" t="n"/>
+      <c r="AK4" s="277" t="n"/>
+      <c r="AL4" s="277" t="n"/>
+      <c r="AM4" s="277" t="n"/>
+      <c r="AN4" s="280" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="828" t="n"/>
-      <c r="I5" s="595" t="inlineStr">
+      <c r="A5" s="890" t="n"/>
+      <c r="B5" s="891" t="n"/>
+      <c r="C5" s="891" t="n"/>
+      <c r="D5" s="891" t="n"/>
+      <c r="E5" s="891" t="n"/>
+      <c r="F5" s="891" t="n"/>
+      <c r="G5" s="891" t="n"/>
+      <c r="H5" s="892" t="n"/>
+      <c r="I5" s="887" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="828" t="n"/>
-      <c r="AE5" s="829" t="inlineStr">
+      <c r="AD5" s="324" t="n"/>
+      <c r="AE5" s="885" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="830" t="n"/>
-      <c r="AG5" s="830" t="n"/>
-      <c r="AH5" s="831" t="n"/>
-      <c r="AI5" s="724" t="inlineStr">
+      <c r="AF5" s="277" t="n"/>
+      <c r="AG5" s="277" t="n"/>
+      <c r="AH5" s="278" t="n"/>
+      <c r="AI5" s="886" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="832" t="n"/>
-      <c r="AK5" s="832" t="n"/>
-      <c r="AL5" s="832" t="n"/>
-      <c r="AM5" s="832" t="n"/>
-      <c r="AN5" s="833" t="n"/>
+      <c r="AJ5" s="277" t="n"/>
+      <c r="AK5" s="277" t="n"/>
+      <c r="AL5" s="277" t="n"/>
+      <c r="AM5" s="277" t="n"/>
+      <c r="AN5" s="280" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="847" t="n"/>
@@ -13556,12 +13196,9 @@
       <c r="AN1" s="701" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
-      <c r="F2" s="819" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="324" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="G2" s="859" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -13606,12 +13243,9 @@
       <c r="AN2" s="865" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="324" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="G3" s="593" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -13656,16 +13290,13 @@
       <c r="AN3" s="872" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="324" t="n"/>
       <c r="C4" s="595" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
       <c r="G4" s="593" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -13706,16 +13337,13 @@
       <c r="AN4" s="872" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="874" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
       <c r="G5" s="593" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -13799,13 +13427,6 @@
     </row>
     <row r="7" ht="4" customHeight="1">
       <c r="A7" s="841" t="n"/>
-      <c r="B7" s="842" t="n"/>
-      <c r="C7" s="842" t="n"/>
-      <c r="D7" s="842" t="n"/>
-      <c r="E7" s="842" t="n"/>
-      <c r="F7" s="842" t="n"/>
-      <c r="G7" s="842" t="n"/>
-      <c r="H7" s="842" t="n"/>
       <c r="I7" s="841" t="n"/>
       <c r="J7" s="841" t="n"/>
       <c r="K7" s="841" t="n"/>
@@ -14917,13 +14538,13 @@
           <t>NOTICE  ?  Controlled withdrawal scope log; keep source files external. Maintain traceability to the parent form, superseding package, point-of-use impact and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, review dates and status fields controlled.</t>
         </is>
       </c>
-      <c r="B30" s="374" t="n"/>
-      <c r="C30" s="374" t="n"/>
-      <c r="D30" s="374" t="n"/>
-      <c r="E30" s="374" t="n"/>
-      <c r="F30" s="374" t="n"/>
-      <c r="G30" s="374" t="n"/>
-      <c r="H30" s="374" t="n"/>
+      <c r="B30" s="289" t="n"/>
+      <c r="C30" s="289" t="n"/>
+      <c r="D30" s="289" t="n"/>
+      <c r="E30" s="289" t="n"/>
+      <c r="F30" s="289" t="n"/>
+      <c r="G30" s="289" t="n"/>
+      <c r="H30" s="289" t="n"/>
       <c r="I30" s="374" t="n"/>
       <c r="J30" s="374" t="n"/>
       <c r="K30" s="374" t="n"/>
@@ -15290,11 +14911,9 @@
       <c r="AN1" s="701" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
+      <c r="A2" s="275" t="n"/>
+      <c r="B2" s="324" t="n"/>
+      <c r="C2" s="275" t="n"/>
       <c r="F2" s="859" t="inlineStr">
         <is>
           <t>Revision</t>
@@ -15340,11 +14959,9 @@
       <c r="AN2" s="865" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
+      <c r="A3" s="275" t="n"/>
+      <c r="B3" s="324" t="n"/>
+      <c r="C3" s="275" t="n"/>
       <c r="F3" s="593" t="inlineStr">
         <is>
           <t>Eff. Date</t>
@@ -15390,15 +15007,13 @@
       <c r="AN3" s="872" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
+      <c r="A4" s="275" t="n"/>
+      <c r="B4" s="324" t="n"/>
       <c r="C4" s="595" t="inlineStr">
         <is>
           <t>Quality Management System  ·  Controlled Document</t>
         </is>
       </c>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
       <c r="F4" s="593" t="inlineStr">
         <is>
           <t>Owner</t>
@@ -15440,15 +15055,13 @@
       <c r="AN4" s="872" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
+      <c r="A5" s="282" t="n"/>
+      <c r="B5" s="287" t="n"/>
       <c r="C5" s="874" t="inlineStr">
         <is>
           <t>HESEM Engineering  ·  ISO 9001 / AS9100  ·  Semiconductor Equipment Parts</t>
         </is>
       </c>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
       <c r="F5" s="593" t="inlineStr">
         <is>
           <t>Approved</t>
@@ -15533,12 +15146,6 @@
     </row>
     <row r="7" ht="4" customHeight="1">
       <c r="A7" s="841" t="n"/>
-      <c r="B7" s="842" t="n"/>
-      <c r="C7" s="842" t="n"/>
-      <c r="D7" s="842" t="n"/>
-      <c r="E7" s="842" t="n"/>
-      <c r="F7" s="842" t="n"/>
-      <c r="G7" s="842" t="n"/>
       <c r="H7" s="841" t="n"/>
       <c r="I7" s="841" t="n"/>
       <c r="J7" s="841" t="n"/>
@@ -16467,12 +16074,12 @@
           <t>NOTICE  ?  Point-of-use sweep confirmation log. Maintain traceability to the parent form and approved evidence references. Do not add, delete or resize structured columns. Keep dropdown values, timestamps and result fields controlled.</t>
         </is>
       </c>
-      <c r="B26" s="374" t="n"/>
-      <c r="C26" s="374" t="n"/>
-      <c r="D26" s="374" t="n"/>
-      <c r="E26" s="374" t="n"/>
-      <c r="F26" s="374" t="n"/>
-      <c r="G26" s="374" t="n"/>
+      <c r="B26" s="289" t="n"/>
+      <c r="C26" s="289" t="n"/>
+      <c r="D26" s="289" t="n"/>
+      <c r="E26" s="289" t="n"/>
+      <c r="F26" s="289" t="n"/>
+      <c r="G26" s="289" t="n"/>
       <c r="H26" s="374" t="n"/>
       <c r="I26" s="374" t="n"/>
       <c r="J26" s="374" t="n"/>
@@ -16841,212 +16448,112 @@
       <c r="AN1" s="844" t="n"/>
     </row>
     <row r="2" ht="15" customHeight="1">
-      <c r="A2" s="1" t="n"/>
-      <c r="B2" s="819" t="n"/>
-      <c r="C2" s="819" t="n"/>
-      <c r="D2" s="819" t="n"/>
-      <c r="E2" s="819" t="n"/>
-      <c r="F2" s="819" t="n"/>
-      <c r="G2" s="819" t="n"/>
-      <c r="H2" s="820" t="n"/>
-      <c r="I2" s="819" t="n"/>
-      <c r="J2" s="819" t="n"/>
-      <c r="K2" s="819" t="n"/>
-      <c r="L2" s="819" t="n"/>
-      <c r="M2" s="819" t="n"/>
-      <c r="N2" s="819" t="n"/>
-      <c r="O2" s="819" t="n"/>
-      <c r="P2" s="819" t="n"/>
-      <c r="Q2" s="819" t="n"/>
-      <c r="R2" s="819" t="n"/>
-      <c r="S2" s="819" t="n"/>
-      <c r="T2" s="819" t="n"/>
-      <c r="U2" s="819" t="n"/>
-      <c r="V2" s="819" t="n"/>
-      <c r="W2" s="819" t="n"/>
-      <c r="X2" s="819" t="n"/>
-      <c r="Y2" s="819" t="n"/>
-      <c r="Z2" s="819" t="n"/>
-      <c r="AA2" s="819" t="n"/>
-      <c r="AB2" s="819" t="n"/>
-      <c r="AC2" s="819" t="n"/>
-      <c r="AD2" s="820" t="n"/>
-      <c r="AE2" s="821" t="inlineStr">
+      <c r="A2" s="888" t="n"/>
+      <c r="H2" s="889" t="n"/>
+      <c r="AD2" s="889" t="n"/>
+      <c r="AE2" s="883" t="inlineStr">
         <is>
           <t>Revision</t>
         </is>
       </c>
-      <c r="AF2" s="822" t="n"/>
-      <c r="AG2" s="822" t="n"/>
-      <c r="AH2" s="823" t="n"/>
-      <c r="AI2" s="824" t="inlineStr">
+      <c r="AF2" s="271" t="n"/>
+      <c r="AG2" s="271" t="n"/>
+      <c r="AH2" s="272" t="n"/>
+      <c r="AI2" s="884" t="inlineStr">
         <is>
           <t>V0</t>
         </is>
       </c>
-      <c r="AJ2" s="825" t="n"/>
-      <c r="AK2" s="825" t="n"/>
-      <c r="AL2" s="825" t="n"/>
-      <c r="AM2" s="825" t="n"/>
-      <c r="AN2" s="826" t="n"/>
+      <c r="AJ2" s="271" t="n"/>
+      <c r="AK2" s="271" t="n"/>
+      <c r="AL2" s="271" t="n"/>
+      <c r="AM2" s="271" t="n"/>
+      <c r="AN2" s="274" t="n"/>
     </row>
     <row r="3" ht="15" customHeight="1">
-      <c r="A3" s="827" t="n"/>
-      <c r="B3" s="25" t="n"/>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
-      <c r="E3" s="25" t="n"/>
-      <c r="F3" s="25" t="n"/>
-      <c r="G3" s="25" t="n"/>
-      <c r="H3" s="828" t="n"/>
-      <c r="I3" s="25" t="n"/>
-      <c r="J3" s="25" t="n"/>
-      <c r="K3" s="25" t="n"/>
-      <c r="L3" s="25" t="n"/>
-      <c r="M3" s="25" t="n"/>
-      <c r="N3" s="25" t="n"/>
-      <c r="O3" s="25" t="n"/>
-      <c r="P3" s="25" t="n"/>
-      <c r="Q3" s="25" t="n"/>
-      <c r="R3" s="25" t="n"/>
-      <c r="S3" s="25" t="n"/>
-      <c r="T3" s="25" t="n"/>
-      <c r="U3" s="25" t="n"/>
-      <c r="V3" s="25" t="n"/>
-      <c r="W3" s="25" t="n"/>
-      <c r="X3" s="25" t="n"/>
-      <c r="Y3" s="25" t="n"/>
-      <c r="Z3" s="25" t="n"/>
-      <c r="AA3" s="25" t="n"/>
-      <c r="AB3" s="25" t="n"/>
-      <c r="AC3" s="25" t="n"/>
-      <c r="AD3" s="828" t="n"/>
-      <c r="AE3" s="829" t="inlineStr">
+      <c r="A3" s="888" t="n"/>
+      <c r="H3" s="889" t="n"/>
+      <c r="AD3" s="889" t="n"/>
+      <c r="AE3" s="885" t="inlineStr">
         <is>
           <t>Eff. Date</t>
         </is>
       </c>
-      <c r="AF3" s="830" t="n"/>
-      <c r="AG3" s="830" t="n"/>
-      <c r="AH3" s="831" t="n"/>
-      <c r="AI3" s="724" t="inlineStr">
+      <c r="AF3" s="277" t="n"/>
+      <c r="AG3" s="277" t="n"/>
+      <c r="AH3" s="278" t="n"/>
+      <c r="AI3" s="886" t="inlineStr">
         <is>
           <t>YYYY-MM-DD</t>
         </is>
       </c>
-      <c r="AJ3" s="832" t="n"/>
-      <c r="AK3" s="832" t="n"/>
-      <c r="AL3" s="832" t="n"/>
-      <c r="AM3" s="832" t="n"/>
-      <c r="AN3" s="833" t="n"/>
+      <c r="AJ3" s="277" t="n"/>
+      <c r="AK3" s="277" t="n"/>
+      <c r="AL3" s="277" t="n"/>
+      <c r="AM3" s="277" t="n"/>
+      <c r="AN3" s="280" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1">
-      <c r="A4" s="827" t="n"/>
-      <c r="B4" s="25" t="n"/>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
-      <c r="E4" s="25" t="n"/>
-      <c r="F4" s="25" t="n"/>
-      <c r="G4" s="25" t="n"/>
-      <c r="H4" s="828" t="n"/>
-      <c r="I4" s="346" t="inlineStr">
+      <c r="A4" s="888" t="n"/>
+      <c r="H4" s="889" t="n"/>
+      <c r="I4" s="347" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="J4" s="25" t="n"/>
-      <c r="K4" s="25" t="n"/>
-      <c r="L4" s="25" t="n"/>
-      <c r="M4" s="25" t="n"/>
-      <c r="N4" s="25" t="n"/>
-      <c r="O4" s="25" t="n"/>
-      <c r="P4" s="25" t="n"/>
-      <c r="Q4" s="25" t="n"/>
-      <c r="R4" s="25" t="n"/>
-      <c r="S4" s="25" t="n"/>
-      <c r="T4" s="25" t="n"/>
-      <c r="U4" s="25" t="n"/>
-      <c r="V4" s="25" t="n"/>
-      <c r="W4" s="25" t="n"/>
-      <c r="X4" s="25" t="n"/>
-      <c r="Y4" s="25" t="n"/>
-      <c r="Z4" s="25" t="n"/>
-      <c r="AA4" s="25" t="n"/>
-      <c r="AB4" s="25" t="n"/>
-      <c r="AC4" s="25" t="n"/>
-      <c r="AD4" s="828" t="n"/>
-      <c r="AE4" s="829" t="inlineStr">
+      <c r="AD4" s="324" t="n"/>
+      <c r="AE4" s="885" t="inlineStr">
         <is>
           <t>Owner</t>
         </is>
       </c>
-      <c r="AF4" s="830" t="n"/>
-      <c r="AG4" s="830" t="n"/>
-      <c r="AH4" s="831" t="n"/>
-      <c r="AI4" s="724" t="inlineStr">
+      <c r="AF4" s="277" t="n"/>
+      <c r="AG4" s="277" t="n"/>
+      <c r="AH4" s="278" t="n"/>
+      <c r="AI4" s="886" t="inlineStr">
         <is>
           <t>Engineering / QA / Planning</t>
         </is>
       </c>
-      <c r="AJ4" s="832" t="n"/>
-      <c r="AK4" s="832" t="n"/>
-      <c r="AL4" s="832" t="n"/>
-      <c r="AM4" s="832" t="n"/>
-      <c r="AN4" s="833" t="n"/>
+      <c r="AJ4" s="277" t="n"/>
+      <c r="AK4" s="277" t="n"/>
+      <c r="AL4" s="277" t="n"/>
+      <c r="AM4" s="277" t="n"/>
+      <c r="AN4" s="280" t="n"/>
     </row>
     <row r="5" ht="15" customHeight="1">
-      <c r="A5" s="827" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
-      <c r="E5" s="25" t="n"/>
-      <c r="F5" s="25" t="n"/>
-      <c r="G5" s="25" t="n"/>
-      <c r="H5" s="828" t="n"/>
-      <c r="I5" s="595" t="inlineStr">
+      <c r="A5" s="890" t="n"/>
+      <c r="B5" s="891" t="n"/>
+      <c r="C5" s="891" t="n"/>
+      <c r="D5" s="891" t="n"/>
+      <c r="E5" s="891" t="n"/>
+      <c r="F5" s="891" t="n"/>
+      <c r="G5" s="891" t="n"/>
+      <c r="H5" s="892" t="n"/>
+      <c r="I5" s="887" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="J5" s="25" t="n"/>
-      <c r="K5" s="25" t="n"/>
-      <c r="L5" s="25" t="n"/>
-      <c r="M5" s="25" t="n"/>
-      <c r="N5" s="25" t="n"/>
-      <c r="O5" s="25" t="n"/>
-      <c r="P5" s="25" t="n"/>
-      <c r="Q5" s="25" t="n"/>
-      <c r="R5" s="25" t="n"/>
-      <c r="S5" s="25" t="n"/>
-      <c r="T5" s="25" t="n"/>
-      <c r="U5" s="25" t="n"/>
-      <c r="V5" s="25" t="n"/>
-      <c r="W5" s="25" t="n"/>
-      <c r="X5" s="25" t="n"/>
-      <c r="Y5" s="25" t="n"/>
-      <c r="Z5" s="25" t="n"/>
-      <c r="AA5" s="25" t="n"/>
-      <c r="AB5" s="25" t="n"/>
-      <c r="AC5" s="25" t="n"/>
-      <c r="AD5" s="828" t="n"/>
-      <c r="AE5" s="829" t="inlineStr">
+      <c r="AD5" s="324" t="n"/>
+      <c r="AE5" s="885" t="inlineStr">
         <is>
           <t>Approved</t>
         </is>
       </c>
-      <c r="AF5" s="830" t="n"/>
-      <c r="AG5" s="830" t="n"/>
-      <c r="AH5" s="831" t="n"/>
-      <c r="AI5" s="724" t="inlineStr">
+      <c r="AF5" s="277" t="n"/>
+      <c r="AG5" s="277" t="n"/>
+      <c r="AH5" s="278" t="n"/>
+      <c r="AI5" s="886" t="inlineStr">
         <is>
           <t>Engineering Manager</t>
         </is>
       </c>
-      <c r="AJ5" s="832" t="n"/>
-      <c r="AK5" s="832" t="n"/>
-      <c r="AL5" s="832" t="n"/>
-      <c r="AM5" s="832" t="n"/>
-      <c r="AN5" s="833" t="n"/>
+      <c r="AJ5" s="277" t="n"/>
+      <c r="AK5" s="277" t="n"/>
+      <c r="AL5" s="277" t="n"/>
+      <c r="AM5" s="277" t="n"/>
+      <c r="AN5" s="280" t="n"/>
     </row>
     <row r="6" ht="15" customHeight="1">
       <c r="A6" s="847" t="n"/>
@@ -17092,12 +16599,6 @@
     </row>
     <row r="7" ht="4" customHeight="1">
       <c r="A7" s="879" t="n"/>
-      <c r="B7" s="842" t="n"/>
-      <c r="C7" s="842" t="n"/>
-      <c r="D7" s="842" t="n"/>
-      <c r="E7" s="842" t="n"/>
-      <c r="F7" s="842" t="n"/>
-      <c r="G7" s="842" t="n"/>
       <c r="H7" s="855" t="n"/>
       <c r="I7" s="855" t="n"/>
       <c r="J7" s="855" t="n"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -8128,7 +8128,7 @@
       <c r="AV4" s="278" t="n"/>
       <c r="AW4" s="886" t="inlineStr">
         <is>
-          <t>Engineering / QA / Planning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="AX4" s="277" t="n"/>
@@ -8169,7 +8169,7 @@
       <c r="AV5" s="278" t="n"/>
       <c r="AW5" s="886" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AX5" s="277" t="n"/>
@@ -11417,7 +11417,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="886" t="inlineStr">
         <is>
-          <t>Engineering / QA / Planning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>
@@ -11451,7 +11451,7 @@
       <c r="AH5" s="278" t="n"/>
       <c r="AI5" s="886" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AJ5" s="277" t="n"/>
@@ -12355,7 +12355,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="886" t="inlineStr">
         <is>
-          <t>Engineering / QA / Planning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>
@@ -12389,7 +12389,7 @@
       <c r="AH5" s="278" t="n"/>
       <c r="AI5" s="886" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AJ5" s="277" t="n"/>
@@ -16512,7 +16512,7 @@
       <c r="AH4" s="278" t="n"/>
       <c r="AI4" s="886" t="inlineStr">
         <is>
-          <t>Engineering / QA / Planning</t>
+          <t>Engineering</t>
         </is>
       </c>
       <c r="AJ4" s="277" t="n"/>
@@ -16546,7 +16546,7 @@
       <c r="AH5" s="278" t="n"/>
       <c r="AI5" s="886" t="inlineStr">
         <is>
-          <t>Engineering Manager</t>
+          <t>General Manager</t>
         </is>
       </c>
       <c r="AJ5" s="277" t="n"/>

--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -9,6 +9,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="WITHDRAWAL_SCOPE" sheetId="4" state="veryHidden" r:id="rId4"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="POU_SWEEP_LOG" sheetId="5" state="veryHidden" r:id="rId5"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REF_LINKS" sheetId="6" state="veryHidden" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="REV_HISTORY" sheetId="7" state="hidden" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="VAL_RESULT_CORE">'_LISTS'!$A$2:$A$5</definedName>
@@ -7403,6 +7404,41 @@
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0"/>
   </cellStyles>
+  <dxfs count="3">
+    <dxf>
+      <font>
+        <color rgb="009C0006"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFC7CE"/>
+          <bgColor rgb="00FFC7CE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="009C6500"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00FFEB9C"/>
+          <bgColor rgb="00FFEB9C"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <color rgb="00006100"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="00C6EFCE"/>
+          <bgColor rgb="00C6EFCE"/>
+        </patternFill>
+      </fill>
+    </dxf>
+  </dxfs>
   <colors>
     <indexedColors>
       <rgbColor rgb="00000000"/>
@@ -8068,7 +8104,7 @@
       <c r="AV2" s="272" t="n"/>
       <c r="AW2" s="884" t="inlineStr">
         <is>
-          <t>V0</t>
+          <t>V1</t>
         </is>
       </c>
       <c r="AX2" s="271" t="n"/>
@@ -8096,7 +8132,7 @@
       <c r="AV3" s="278" t="n"/>
       <c r="AW3" s="886" t="inlineStr">
         <is>
-          <t>YYYY-MM-DD</t>
+          <t>2026-03-23</t>
         </is>
       </c>
       <c r="AX3" s="277" t="n"/>
@@ -11124,6 +11160,28 @@
     <mergeCell ref="BA39:BD39"/>
     <mergeCell ref="AR23:AW23"/>
   </mergeCells>
+  <conditionalFormatting sqref="AR22:AR31">
+    <cfRule type="cellIs" priority="1" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="2" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="3" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="AP35:AP39">
+    <cfRule type="cellIs" priority="4" operator="equal" dxfId="0">
+      <formula>"FAIL"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="5" operator="equal" dxfId="1">
+      <formula>"HOLD"</formula>
+    </cfRule>
+    <cfRule type="cellIs" priority="6" operator="equal" dxfId="2">
+      <formula>"PASS"</formula>
+    </cfRule>
+  </conditionalFormatting>
   <dataValidations count="35">
     <dataValidation sqref="AR22" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="Use controlled value from VAL_RESULT_CORE." prompt="Select from VAL_RESULT_CORE." type="list">
       <formula1>=VAL_RESULT_CORE</formula1>
@@ -17420,4 +17478,84 @@
     <tablePart xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId2"/>
   </tableParts>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D3"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Rev</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Date</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Author</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>V0</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2026-03-21</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Initial release</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>QMS Team</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>V1</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-03-23</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>CF: checklist Result; CF: action Status</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>QMS Upgrade</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
+++ b/04-Bieu-Mau/03-FRM-300/FRM-307_Package_Supersedure_and_Withdrawal_Notice.xlsx
@@ -4812,6 +4812,85 @@
     </indexedColors>
   </colors>
 </styleSheet>
+</file>
+
+<file path=xl/comments/comment1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>QMS</author>
+  </authors>
+  <commentList>
+    <comment ref="A9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã gói baseline
+Mã gói kỹ thuật bị thay thế hoặc thu hồi.</t>
+      </text>
+    </comment>
+    <comment ref="U9" authorId="0" shapeId="0">
+      <text>
+        <t>Mã chi tiết / Phiên bản
+Part bị ảnh hưởng.</t>
+      </text>
+    </comment>
+    <comment ref="A10" authorId="0" shapeId="0">
+      <text>
+        <t>Ngày thông báo
+Ngày ban hành thông báo.</t>
+      </text>
+    </comment>
+    <comment ref="U10" authorId="0" shapeId="0">
+      <text>
+        <t>Người ban hành
+Engineer chịu trách nhiệm.</t>
+      </text>
+    </comment>
+    <comment ref="A12" authorId="0" shapeId="0">
+      <text>
+        <t>Chi tiết thay thế / thu hồi
+Ghi rõ package cũ, package mới (nếu thay thế), lý do và hành động cần thiết.</t>
+      </text>
+    </comment>
+    <comment ref="A13" authorId="0" shapeId="0">
+      <text>
+        <t>Package cũ
+Mã và revision package bị thay thế.</t>
+      </text>
+    </comment>
+    <comment ref="U13" authorId="0" shapeId="0">
+      <text>
+        <t>Package mới
+Mã và revision package thay thế.
+Để trống nếu là withdrawal (thu hồi, không thay thế).</t>
+      </text>
+    </comment>
+    <comment ref="A14" authorId="0" shapeId="0">
+      <text>
+        <t>Lý do
+Tại sao thay thế hoặc thu hồi.
+Ví dụ: Drawing updated, Process change, Error correction.</t>
+      </text>
+    </comment>
+    <comment ref="U14" authorId="0" shapeId="0">
+      <text>
+        <t>Job bị ảnh hưởng
+Liệt kê Job/WO đang sử dụng package cũ.
+Cần kiểm tra và cập nhật từng job.</t>
+      </text>
+    </comment>
+    <comment ref="A15" authorId="0" shapeId="0">
+      <text>
+        <t>Hành động cần thực hiện
+Ví dụ: Recall old package, update job packets, notify operators.</t>
+      </text>
+    </comment>
+    <comment ref="U15" authorId="0" shapeId="0">
+      <text>
+        <t>Hạn hoàn thành
+Ngày hoàn tất tất cả hành động.</t>
+      </text>
+    </comment>
+  </commentList>
+</comments>
 </file>
 
 <file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5519,7 +5598,7 @@
     <row r="10" ht="20" customHeight="1" s="264">
       <c r="A10" s="480" t="inlineStr">
         <is>
-          <t>Supersedure Date</t>
+          <t>Notice Date</t>
         </is>
       </c>
       <c r="B10" s="481" t="n"/>
@@ -5707,7 +5786,7 @@
     <row r="14" ht="20" customHeight="1" s="264">
       <c r="A14" s="487" t="inlineStr">
         <is>
-          <t>Reason for Supersedure</t>
+          <t>Reason for Supersedure / Withdrawal</t>
         </is>
       </c>
       <c r="B14" s="488" t="n"/>
@@ -5757,7 +5836,7 @@
     <row r="15" ht="20" customHeight="1" s="264">
       <c r="A15" s="480" t="inlineStr">
         <is>
-          <t>Action Required (recall / update / notify)</t>
+          <t>Action Required</t>
         </is>
       </c>
       <c r="B15" s="481" t="n"/>
@@ -6085,7 +6164,7 @@
     <row r="23" ht="24" customHeight="1" s="264">
       <c r="A23" s="501" t="inlineStr">
         <is>
-          <t>NOTICE — Issue when a baseline package is superseded or withdrawn. Ref: SOP-301. Retain: 10 years.</t>
+          <t>NOTICE — Issue when a baseline package is superseded or withdrawn. Complete within 24h. Ref: SOP-301. Retain: 10 years.</t>
         </is>
       </c>
       <c r="B23" s="471" t="n"/>
@@ -6180,6 +6259,7 @@
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  <legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="anysvml"/>
 </worksheet>
 </file>
 
